--- a/bloomberg/Bootstrap_Check.xlsx
+++ b/bloomberg/Bootstrap_Check.xlsx
@@ -153,11 +153,11 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,35 +555,35 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
-    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
-    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
-    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
-    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
-    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
-    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
-    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
-    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
-    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
-    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
-    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
-    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
-    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,11 +592,16 @@
           <t>CURVE TEST CASE 1 — paste and read</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>WORKING — the bootstrap itself, left visible so every step can be audited: dates, taus, annuity, then the 16 solver passes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Paste the yellow columns. Everything green is computed on this sheet — nothing here points at another sheet.</t>
+          <t>Paste YELLOW: tenor into A, then swap mid / BBG zero / BBG discount into C:E. Green is computed here — this sheet points at nothing outside itself.</t>
         </is>
       </c>
     </row>
@@ -632,32 +637,32 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
           <t>Swap rate (mid) %</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>BBG zero %</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>BBG discount</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>our DF</t>
+          <t>Our zero %</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>our zero %</t>
+          <t>Our discount</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -738,27 +743,27 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
+      <c r="B8" s="10">
+        <f>IF($A8="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A8,$K$8:$K$72,0),MATCH(IF($A8="1Y","12M",IF($A8="12M","1Y",$A8)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="11" t="n"/>
       <c r="D8" s="11" t="n"/>
-      <c r="E8" s="12">
-        <f>IF($A8="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A8,$K$8:$K$72,0),MATCH(IF($A8="1Y","12M",IF($A8="12M","1Y",$A8)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E8" s="12" t="n"/>
       <c r="F8" s="13">
+        <f>IF(OR($A8="",G8=""),"",-LN(G8)/((B8-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
         <f>IF($A8="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A8,$K$8:$K$72,0),MATCH(IF($A8="1Y","12M",IF($A8="12M","1Y",$A8)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G8" s="14">
-        <f>IF(OR($A8="",F8=""),"",-LN(F8)/((E8-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H8" s="15">
-        <f>IF(OR(G8="",NOT(ISNUMBER(C8))),"",(G8-C8)*100)</f>
+        <f>IF(OR(F8="",NOT(ISNUMBER(D8))),"",(F8-D8)*100)</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>IF(OR(F8="",NOT(ISNUMBER(D8))),"",F8-D8)</f>
+        <f>IF(OR(G8="",NOT(ISNUMBER(E8))),"",G8-E8)</f>
         <v/>
       </c>
       <c r="K8" s="17" t="inlineStr">
@@ -793,7 +798,7 @@
         <v/>
       </c>
       <c r="S8" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("1W",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("1W",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("1W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U8" s="20">
@@ -807,27 +812,27 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
+      <c r="B9" s="10">
+        <f>IF($A9="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A9,$K$8:$K$72,0),MATCH(IF($A9="1Y","12M",IF($A9="12M","1Y",$A9)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C9" s="11" t="n"/>
       <c r="D9" s="11" t="n"/>
-      <c r="E9" s="12">
-        <f>IF($A9="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A9,$K$8:$K$72,0),MATCH(IF($A9="1Y","12M",IF($A9="12M","1Y",$A9)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E9" s="12" t="n"/>
       <c r="F9" s="13">
+        <f>IF(OR($A9="",G9=""),"",-LN(G9)/((B9-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
         <f>IF($A9="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A9,$K$8:$K$72,0),MATCH(IF($A9="1Y","12M",IF($A9="12M","1Y",$A9)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G9" s="14">
-        <f>IF(OR($A9="",F9=""),"",-LN(F9)/((E9-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H9" s="15">
-        <f>IF(OR(G9="",NOT(ISNUMBER(C9))),"",(G9-C9)*100)</f>
+        <f>IF(OR(F9="",NOT(ISNUMBER(D9))),"",(F9-D9)*100)</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>IF(OR(F9="",NOT(ISNUMBER(D9))),"",F9-D9)</f>
+        <f>IF(OR(G9="",NOT(ISNUMBER(E9))),"",G9-E9)</f>
         <v/>
       </c>
       <c r="K9" s="17" t="inlineStr">
@@ -862,7 +867,7 @@
         <v/>
       </c>
       <c r="S9" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("2W",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("2W",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U9" s="20">
@@ -876,27 +881,27 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
+      <c r="B10" s="10">
+        <f>IF($A10="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A10,$K$8:$K$72,0),MATCH(IF($A10="1Y","12M",IF($A10="12M","1Y",$A10)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12">
-        <f>IF($A10="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A10,$K$8:$K$72,0),MATCH(IF($A10="1Y","12M",IF($A10="12M","1Y",$A10)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E10" s="12" t="n"/>
       <c r="F10" s="13">
+        <f>IF(OR($A10="",G10=""),"",-LN(G10)/((B10-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
         <f>IF($A10="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A10,$K$8:$K$72,0),MATCH(IF($A10="1Y","12M",IF($A10="12M","1Y",$A10)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G10" s="14">
-        <f>IF(OR($A10="",F10=""),"",-LN(F10)/((E10-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H10" s="15">
-        <f>IF(OR(G10="",NOT(ISNUMBER(C10))),"",(G10-C10)*100)</f>
+        <f>IF(OR(F10="",NOT(ISNUMBER(D10))),"",(F10-D10)*100)</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>IF(OR(F10="",NOT(ISNUMBER(D10))),"",F10-D10)</f>
+        <f>IF(OR(G10="",NOT(ISNUMBER(E10))),"",G10-E10)</f>
         <v/>
       </c>
       <c r="K10" s="17" t="inlineStr">
@@ -931,7 +936,7 @@
         <v/>
       </c>
       <c r="S10" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("3W",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("3W",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U10" s="20">
@@ -945,27 +950,27 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
+      <c r="B11" s="10">
+        <f>IF($A11="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A11,$K$8:$K$72,0),MATCH(IF($A11="1Y","12M",IF($A11="12M","1Y",$A11)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="11" t="n"/>
       <c r="D11" s="11" t="n"/>
-      <c r="E11" s="12">
-        <f>IF($A11="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A11,$K$8:$K$72,0),MATCH(IF($A11="1Y","12M",IF($A11="12M","1Y",$A11)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E11" s="12" t="n"/>
       <c r="F11" s="13">
+        <f>IF(OR($A11="",G11=""),"",-LN(G11)/((B11-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
         <f>IF($A11="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A11,$K$8:$K$72,0),MATCH(IF($A11="1Y","12M",IF($A11="12M","1Y",$A11)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G11" s="14">
-        <f>IF(OR($A11="",F11=""),"",-LN(F11)/((E11-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H11" s="15">
-        <f>IF(OR(G11="",NOT(ISNUMBER(C11))),"",(G11-C11)*100)</f>
+        <f>IF(OR(F11="",NOT(ISNUMBER(D11))),"",(F11-D11)*100)</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>IF(OR(F11="",NOT(ISNUMBER(D11))),"",F11-D11)</f>
+        <f>IF(OR(G11="",NOT(ISNUMBER(E11))),"",G11-E11)</f>
         <v/>
       </c>
       <c r="K11" s="17" t="inlineStr">
@@ -1000,7 +1005,7 @@
         <v/>
       </c>
       <c r="S11" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("1M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("1M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("1M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U11" s="20">
@@ -1014,27 +1019,27 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
+      <c r="B12" s="10">
+        <f>IF($A12="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A12,$K$8:$K$72,0),MATCH(IF($A12="1Y","12M",IF($A12="12M","1Y",$A12)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C12" s="11" t="n"/>
       <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12">
-        <f>IF($A12="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A12,$K$8:$K$72,0),MATCH(IF($A12="1Y","12M",IF($A12="12M","1Y",$A12)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E12" s="12" t="n"/>
       <c r="F12" s="13">
+        <f>IF(OR($A12="",G12=""),"",-LN(G12)/((B12-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
         <f>IF($A12="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A12,$K$8:$K$72,0),MATCH(IF($A12="1Y","12M",IF($A12="12M","1Y",$A12)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G12" s="14">
-        <f>IF(OR($A12="",F12=""),"",-LN(F12)/((E12-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H12" s="15">
-        <f>IF(OR(G12="",NOT(ISNUMBER(C12))),"",(G12-C12)*100)</f>
+        <f>IF(OR(F12="",NOT(ISNUMBER(D12))),"",(F12-D12)*100)</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>IF(OR(F12="",NOT(ISNUMBER(D12))),"",F12-D12)</f>
+        <f>IF(OR(G12="",NOT(ISNUMBER(E12))),"",G12-E12)</f>
         <v/>
       </c>
       <c r="K12" s="17" t="inlineStr">
@@ -1069,7 +1074,7 @@
         <v/>
       </c>
       <c r="S12" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("2M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("2M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U12" s="20">
@@ -1083,27 +1088,27 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
+      <c r="B13" s="10">
+        <f>IF($A13="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A13,$K$8:$K$72,0),MATCH(IF($A13="1Y","12M",IF($A13="12M","1Y",$A13)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="12">
-        <f>IF($A13="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A13,$K$8:$K$72,0),MATCH(IF($A13="1Y","12M",IF($A13="12M","1Y",$A13)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E13" s="12" t="n"/>
       <c r="F13" s="13">
+        <f>IF(OR($A13="",G13=""),"",-LN(G13)/((B13-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
         <f>IF($A13="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A13,$K$8:$K$72,0),MATCH(IF($A13="1Y","12M",IF($A13="12M","1Y",$A13)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G13" s="14">
-        <f>IF(OR($A13="",F13=""),"",-LN(F13)/((E13-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H13" s="15">
-        <f>IF(OR(G13="",NOT(ISNUMBER(C13))),"",(G13-C13)*100)</f>
+        <f>IF(OR(F13="",NOT(ISNUMBER(D13))),"",(F13-D13)*100)</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>IF(OR(F13="",NOT(ISNUMBER(D13))),"",F13-D13)</f>
+        <f>IF(OR(G13="",NOT(ISNUMBER(E13))),"",G13-E13)</f>
         <v/>
       </c>
       <c r="K13" s="17" t="inlineStr">
@@ -1138,7 +1143,7 @@
         <v/>
       </c>
       <c r="S13" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("3M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("3M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U13" s="20">
@@ -1152,27 +1157,27 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
+      <c r="B14" s="10">
+        <f>IF($A14="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A14,$K$8:$K$72,0),MATCH(IF($A14="1Y","12M",IF($A14="12M","1Y",$A14)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12">
-        <f>IF($A14="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A14,$K$8:$K$72,0),MATCH(IF($A14="1Y","12M",IF($A14="12M","1Y",$A14)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E14" s="12" t="n"/>
       <c r="F14" s="13">
+        <f>IF(OR($A14="",G14=""),"",-LN(G14)/((B14-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
         <f>IF($A14="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A14,$K$8:$K$72,0),MATCH(IF($A14="1Y","12M",IF($A14="12M","1Y",$A14)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G14" s="14">
-        <f>IF(OR($A14="",F14=""),"",-LN(F14)/((E14-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H14" s="15">
-        <f>IF(OR(G14="",NOT(ISNUMBER(C14))),"",(G14-C14)*100)</f>
+        <f>IF(OR(F14="",NOT(ISNUMBER(D14))),"",(F14-D14)*100)</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>IF(OR(F14="",NOT(ISNUMBER(D14))),"",F14-D14)</f>
+        <f>IF(OR(G14="",NOT(ISNUMBER(E14))),"",G14-E14)</f>
         <v/>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -1207,7 +1212,7 @@
         <v/>
       </c>
       <c r="S14" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("4M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("4M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("4M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("4M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U14" s="20">
@@ -1221,27 +1226,27 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
+      <c r="B15" s="10">
+        <f>IF($A15="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A15,$K$8:$K$72,0),MATCH(IF($A15="1Y","12M",IF($A15="12M","1Y",$A15)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="11" t="n"/>
       <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12">
-        <f>IF($A15="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A15,$K$8:$K$72,0),MATCH(IF($A15="1Y","12M",IF($A15="12M","1Y",$A15)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="13">
+        <f>IF(OR($A15="",G15=""),"",-LN(G15)/((B15-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
         <f>IF($A15="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A15,$K$8:$K$72,0),MATCH(IF($A15="1Y","12M",IF($A15="12M","1Y",$A15)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G15" s="14">
-        <f>IF(OR($A15="",F15=""),"",-LN(F15)/((E15-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H15" s="15">
-        <f>IF(OR(G15="",NOT(ISNUMBER(C15))),"",(G15-C15)*100)</f>
+        <f>IF(OR(F15="",NOT(ISNUMBER(D15))),"",(F15-D15)*100)</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>IF(OR(F15="",NOT(ISNUMBER(D15))),"",F15-D15)</f>
+        <f>IF(OR(G15="",NOT(ISNUMBER(E15))),"",G15-E15)</f>
         <v/>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1276,7 +1281,7 @@
         <v/>
       </c>
       <c r="S15" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("5M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("5M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("5M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("5M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U15" s="20">
@@ -1290,27 +1295,27 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
+      <c r="B16" s="10">
+        <f>IF($A16="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A16,$K$8:$K$72,0),MATCH(IF($A16="1Y","12M",IF($A16="12M","1Y",$A16)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C16" s="11" t="n"/>
       <c r="D16" s="11" t="n"/>
-      <c r="E16" s="12">
-        <f>IF($A16="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A16,$K$8:$K$72,0),MATCH(IF($A16="1Y","12M",IF($A16="12M","1Y",$A16)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E16" s="12" t="n"/>
       <c r="F16" s="13">
+        <f>IF(OR($A16="",G16=""),"",-LN(G16)/((B16-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
         <f>IF($A16="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A16,$K$8:$K$72,0),MATCH(IF($A16="1Y","12M",IF($A16="12M","1Y",$A16)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G16" s="14">
-        <f>IF(OR($A16="",F16=""),"",-LN(F16)/((E16-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H16" s="15">
-        <f>IF(OR(G16="",NOT(ISNUMBER(C16))),"",(G16-C16)*100)</f>
+        <f>IF(OR(F16="",NOT(ISNUMBER(D16))),"",(F16-D16)*100)</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>IF(OR(F16="",NOT(ISNUMBER(D16))),"",F16-D16)</f>
+        <f>IF(OR(G16="",NOT(ISNUMBER(E16))),"",G16-E16)</f>
         <v/>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1345,7 +1350,7 @@
         <v/>
       </c>
       <c r="S16" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("6M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("6M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("6M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("6M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U16" s="20">
@@ -1359,27 +1364,27 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
+      <c r="B17" s="10">
+        <f>IF($A17="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A17,$K$8:$K$72,0),MATCH(IF($A17="1Y","12M",IF($A17="12M","1Y",$A17)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="11" t="n"/>
       <c r="D17" s="11" t="n"/>
-      <c r="E17" s="12">
-        <f>IF($A17="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A17,$K$8:$K$72,0),MATCH(IF($A17="1Y","12M",IF($A17="12M","1Y",$A17)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E17" s="12" t="n"/>
       <c r="F17" s="13">
+        <f>IF(OR($A17="",G17=""),"",-LN(G17)/((B17-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
         <f>IF($A17="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A17,$K$8:$K$72,0),MATCH(IF($A17="1Y","12M",IF($A17="12M","1Y",$A17)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G17" s="14">
-        <f>IF(OR($A17="",F17=""),"",-LN(F17)/((E17-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H17" s="15">
-        <f>IF(OR(G17="",NOT(ISNUMBER(C17))),"",(G17-C17)*100)</f>
+        <f>IF(OR(F17="",NOT(ISNUMBER(D17))),"",(F17-D17)*100)</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>IF(OR(F17="",NOT(ISNUMBER(D17))),"",F17-D17)</f>
+        <f>IF(OR(G17="",NOT(ISNUMBER(E17))),"",G17-E17)</f>
         <v/>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1414,7 +1419,7 @@
         <v/>
       </c>
       <c r="S17" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("7M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("7M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("7M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("7M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U17" s="20">
@@ -1428,27 +1433,27 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
+      <c r="B18" s="10">
+        <f>IF($A18="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A18,$K$8:$K$72,0),MATCH(IF($A18="1Y","12M",IF($A18="12M","1Y",$A18)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="11" t="n"/>
       <c r="D18" s="11" t="n"/>
-      <c r="E18" s="12">
-        <f>IF($A18="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A18,$K$8:$K$72,0),MATCH(IF($A18="1Y","12M",IF($A18="12M","1Y",$A18)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E18" s="12" t="n"/>
       <c r="F18" s="13">
+        <f>IF(OR($A18="",G18=""),"",-LN(G18)/((B18-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
         <f>IF($A18="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A18,$K$8:$K$72,0),MATCH(IF($A18="1Y","12M",IF($A18="12M","1Y",$A18)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G18" s="14">
-        <f>IF(OR($A18="",F18=""),"",-LN(F18)/((E18-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H18" s="15">
-        <f>IF(OR(G18="",NOT(ISNUMBER(C18))),"",(G18-C18)*100)</f>
+        <f>IF(OR(F18="",NOT(ISNUMBER(D18))),"",(F18-D18)*100)</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>IF(OR(F18="",NOT(ISNUMBER(D18))),"",F18-D18)</f>
+        <f>IF(OR(G18="",NOT(ISNUMBER(E18))),"",G18-E18)</f>
         <v/>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1483,7 +1488,7 @@
         <v/>
       </c>
       <c r="S18" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("8M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("8M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("8M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("8M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U18" s="20">
@@ -1497,27 +1502,27 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
+      <c r="B19" s="10">
+        <f>IF($A19="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A19,$K$8:$K$72,0),MATCH(IF($A19="1Y","12M",IF($A19="12M","1Y",$A19)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12">
-        <f>IF($A19="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A19,$K$8:$K$72,0),MATCH(IF($A19="1Y","12M",IF($A19="12M","1Y",$A19)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E19" s="12" t="n"/>
       <c r="F19" s="13">
+        <f>IF(OR($A19="",G19=""),"",-LN(G19)/((B19-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G19" s="14">
         <f>IF($A19="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A19,$K$8:$K$72,0),MATCH(IF($A19="1Y","12M",IF($A19="12M","1Y",$A19)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G19" s="14">
-        <f>IF(OR($A19="",F19=""),"",-LN(F19)/((E19-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H19" s="15">
-        <f>IF(OR(G19="",NOT(ISNUMBER(C19))),"",(G19-C19)*100)</f>
+        <f>IF(OR(F19="",NOT(ISNUMBER(D19))),"",(F19-D19)*100)</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>IF(OR(F19="",NOT(ISNUMBER(D19))),"",F19-D19)</f>
+        <f>IF(OR(G19="",NOT(ISNUMBER(E19))),"",G19-E19)</f>
         <v/>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1552,7 +1557,7 @@
         <v/>
       </c>
       <c r="S19" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("9M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("9M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("9M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("9M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U19" s="20">
@@ -1566,27 +1571,27 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
+      <c r="B20" s="10">
+        <f>IF($A20="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A20,$K$8:$K$72,0),MATCH(IF($A20="1Y","12M",IF($A20="12M","1Y",$A20)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C20" s="11" t="n"/>
       <c r="D20" s="11" t="n"/>
-      <c r="E20" s="12">
-        <f>IF($A20="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A20,$K$8:$K$72,0),MATCH(IF($A20="1Y","12M",IF($A20="12M","1Y",$A20)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E20" s="12" t="n"/>
       <c r="F20" s="13">
+        <f>IF(OR($A20="",G20=""),"",-LN(G20)/((B20-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
         <f>IF($A20="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A20,$K$8:$K$72,0),MATCH(IF($A20="1Y","12M",IF($A20="12M","1Y",$A20)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G20" s="14">
-        <f>IF(OR($A20="",F20=""),"",-LN(F20)/((E20-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H20" s="15">
-        <f>IF(OR(G20="",NOT(ISNUMBER(C20))),"",(G20-C20)*100)</f>
+        <f>IF(OR(F20="",NOT(ISNUMBER(D20))),"",(F20-D20)*100)</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>IF(OR(F20="",NOT(ISNUMBER(D20))),"",F20-D20)</f>
+        <f>IF(OR(G20="",NOT(ISNUMBER(E20))),"",G20-E20)</f>
         <v/>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1621,7 +1626,7 @@
         <v/>
       </c>
       <c r="S20" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("10M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("10M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("10M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("10M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U20" s="20">
@@ -1635,27 +1640,27 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
+      <c r="B21" s="10">
+        <f>IF($A21="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A21,$K$8:$K$72,0),MATCH(IF($A21="1Y","12M",IF($A21="12M","1Y",$A21)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="11" t="n"/>
       <c r="D21" s="11" t="n"/>
-      <c r="E21" s="12">
-        <f>IF($A21="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A21,$K$8:$K$72,0),MATCH(IF($A21="1Y","12M",IF($A21="12M","1Y",$A21)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E21" s="12" t="n"/>
       <c r="F21" s="13">
+        <f>IF(OR($A21="",G21=""),"",-LN(G21)/((B21-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
         <f>IF($A21="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A21,$K$8:$K$72,0),MATCH(IF($A21="1Y","12M",IF($A21="12M","1Y",$A21)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G21" s="14">
-        <f>IF(OR($A21="",F21=""),"",-LN(F21)/((E21-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H21" s="15">
-        <f>IF(OR(G21="",NOT(ISNUMBER(C21))),"",(G21-C21)*100)</f>
+        <f>IF(OR(F21="",NOT(ISNUMBER(D21))),"",(F21-D21)*100)</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>IF(OR(F21="",NOT(ISNUMBER(D21))),"",F21-D21)</f>
+        <f>IF(OR(G21="",NOT(ISNUMBER(E21))),"",G21-E21)</f>
         <v/>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1690,7 +1695,7 @@
         <v/>
       </c>
       <c r="S21" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("11M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("11M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("11M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("11M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U21" s="20">
@@ -1704,27 +1709,27 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
+      <c r="B22" s="10">
+        <f>IF($A22="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A22,$K$8:$K$72,0),MATCH(IF($A22="1Y","12M",IF($A22="12M","1Y",$A22)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12">
-        <f>IF($A22="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A22,$K$8:$K$72,0),MATCH(IF($A22="1Y","12M",IF($A22="12M","1Y",$A22)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="13">
+        <f>IF(OR($A22="",G22=""),"",-LN(G22)/((B22-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
         <f>IF($A22="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A22,$K$8:$K$72,0),MATCH(IF($A22="1Y","12M",IF($A22="12M","1Y",$A22)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G22" s="14">
-        <f>IF(OR($A22="",F22=""),"",-LN(F22)/((E22-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H22" s="15">
-        <f>IF(OR(G22="",NOT(ISNUMBER(C22))),"",(G22-C22)*100)</f>
+        <f>IF(OR(F22="",NOT(ISNUMBER(D22))),"",(F22-D22)*100)</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>IF(OR(F22="",NOT(ISNUMBER(D22))),"",F22-D22)</f>
+        <f>IF(OR(G22="",NOT(ISNUMBER(E22))),"",G22-E22)</f>
         <v/>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1759,7 +1764,7 @@
         <v/>
       </c>
       <c r="S22" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("12M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("1Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("12M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U22" s="20">
@@ -1773,27 +1778,27 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
+      <c r="B23" s="10">
+        <f>IF($A23="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A23,$K$8:$K$72,0),MATCH(IF($A23="1Y","12M",IF($A23="12M","1Y",$A23)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="11" t="n"/>
       <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12">
-        <f>IF($A23="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A23,$K$8:$K$72,0),MATCH(IF($A23="1Y","12M",IF($A23="12M","1Y",$A23)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E23" s="12" t="n"/>
       <c r="F23" s="13">
+        <f>IF(OR($A23="",G23=""),"",-LN(G23)/((B23-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
         <f>IF($A23="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A23,$K$8:$K$72,0),MATCH(IF($A23="1Y","12M",IF($A23="12M","1Y",$A23)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G23" s="14">
-        <f>IF(OR($A23="",F23=""),"",-LN(F23)/((E23-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H23" s="15">
-        <f>IF(OR(G23="",NOT(ISNUMBER(C23))),"",(G23-C23)*100)</f>
+        <f>IF(OR(F23="",NOT(ISNUMBER(D23))),"",(F23-D23)*100)</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>IF(OR(F23="",NOT(ISNUMBER(D23))),"",F23-D23)</f>
+        <f>IF(OR(G23="",NOT(ISNUMBER(E23))),"",G23-E23)</f>
         <v/>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1828,7 +1833,7 @@
         <v/>
       </c>
       <c r="S23" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("18M",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("18M",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("18M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("18M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U23" s="20">
@@ -1842,27 +1847,27 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
+      <c r="B24" s="10">
+        <f>IF($A24="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A24,$K$8:$K$72,0),MATCH(IF($A24="1Y","12M",IF($A24="12M","1Y",$A24)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C24" s="11" t="n"/>
       <c r="D24" s="11" t="n"/>
-      <c r="E24" s="12">
-        <f>IF($A24="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A24,$K$8:$K$72,0),MATCH(IF($A24="1Y","12M",IF($A24="12M","1Y",$A24)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="13">
+        <f>IF(OR($A24="",G24=""),"",-LN(G24)/((B24-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
         <f>IF($A24="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A24,$K$8:$K$72,0),MATCH(IF($A24="1Y","12M",IF($A24="12M","1Y",$A24)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G24" s="14">
-        <f>IF(OR($A24="",F24=""),"",-LN(F24)/((E24-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H24" s="15">
-        <f>IF(OR(G24="",NOT(ISNUMBER(C24))),"",(G24-C24)*100)</f>
+        <f>IF(OR(F24="",NOT(ISNUMBER(D24))),"",(F24-D24)*100)</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>IF(OR(F24="",NOT(ISNUMBER(D24))),"",F24-D24)</f>
+        <f>IF(OR(G24="",NOT(ISNUMBER(E24))),"",G24-E24)</f>
         <v/>
       </c>
       <c r="K24" s="17" t="inlineStr">
@@ -1897,7 +1902,7 @@
         <v/>
       </c>
       <c r="S24" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("2Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("2Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U24" s="20">
@@ -1911,27 +1916,27 @@
     </row>
     <row r="25">
       <c r="A25" s="9" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
+      <c r="B25" s="10">
+        <f>IF($A25="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A25,$K$8:$K$72,0),MATCH(IF($A25="1Y","12M",IF($A25="12M","1Y",$A25)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
-      <c r="E25" s="12">
-        <f>IF($A25="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A25,$K$8:$K$72,0),MATCH(IF($A25="1Y","12M",IF($A25="12M","1Y",$A25)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E25" s="12" t="n"/>
       <c r="F25" s="13">
+        <f>IF(OR($A25="",G25=""),"",-LN(G25)/((B25-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
         <f>IF($A25="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A25,$K$8:$K$72,0),MATCH(IF($A25="1Y","12M",IF($A25="12M","1Y",$A25)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G25" s="14">
-        <f>IF(OR($A25="",F25=""),"",-LN(F25)/((E25-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H25" s="15">
-        <f>IF(OR(G25="",NOT(ISNUMBER(C25))),"",(G25-C25)*100)</f>
+        <f>IF(OR(F25="",NOT(ISNUMBER(D25))),"",(F25-D25)*100)</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>IF(OR(F25="",NOT(ISNUMBER(D25))),"",F25-D25)</f>
+        <f>IF(OR(G25="",NOT(ISNUMBER(E25))),"",G25-E25)</f>
         <v/>
       </c>
       <c r="K25" s="17" t="inlineStr">
@@ -1966,7 +1971,7 @@
         <v/>
       </c>
       <c r="S25" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("3Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("3Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U25" s="20">
@@ -1980,27 +1985,27 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
+      <c r="B26" s="10">
+        <f>IF($A26="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A26,$K$8:$K$72,0),MATCH(IF($A26="1Y","12M",IF($A26="12M","1Y",$A26)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12">
-        <f>IF($A26="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A26,$K$8:$K$72,0),MATCH(IF($A26="1Y","12M",IF($A26="12M","1Y",$A26)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E26" s="12" t="n"/>
       <c r="F26" s="13">
+        <f>IF(OR($A26="",G26=""),"",-LN(G26)/((B26-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
         <f>IF($A26="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A26,$K$8:$K$72,0),MATCH(IF($A26="1Y","12M",IF($A26="12M","1Y",$A26)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G26" s="14">
-        <f>IF(OR($A26="",F26=""),"",-LN(F26)/((E26-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H26" s="15">
-        <f>IF(OR(G26="",NOT(ISNUMBER(C26))),"",(G26-C26)*100)</f>
+        <f>IF(OR(F26="",NOT(ISNUMBER(D26))),"",(F26-D26)*100)</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>IF(OR(F26="",NOT(ISNUMBER(D26))),"",F26-D26)</f>
+        <f>IF(OR(G26="",NOT(ISNUMBER(E26))),"",G26-E26)</f>
         <v/>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -2035,7 +2040,7 @@
         <v/>
       </c>
       <c r="S26" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("4Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("4Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("4Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("4Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U26" s="20">
@@ -2049,27 +2054,27 @@
     </row>
     <row r="27">
       <c r="A27" s="9" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="B27" s="10">
+        <f>IF($A27="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A27,$K$8:$K$72,0),MATCH(IF($A27="1Y","12M",IF($A27="12M","1Y",$A27)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
-      <c r="E27" s="12">
-        <f>IF($A27="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A27,$K$8:$K$72,0),MATCH(IF($A27="1Y","12M",IF($A27="12M","1Y",$A27)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E27" s="12" t="n"/>
       <c r="F27" s="13">
+        <f>IF(OR($A27="",G27=""),"",-LN(G27)/((B27-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
         <f>IF($A27="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A27,$K$8:$K$72,0),MATCH(IF($A27="1Y","12M",IF($A27="12M","1Y",$A27)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G27" s="14">
-        <f>IF(OR($A27="",F27=""),"",-LN(F27)/((E27-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H27" s="15">
-        <f>IF(OR(G27="",NOT(ISNUMBER(C27))),"",(G27-C27)*100)</f>
+        <f>IF(OR(F27="",NOT(ISNUMBER(D27))),"",(F27-D27)*100)</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>IF(OR(F27="",NOT(ISNUMBER(D27))),"",F27-D27)</f>
+        <f>IF(OR(G27="",NOT(ISNUMBER(E27))),"",G27-E27)</f>
         <v/>
       </c>
       <c r="K27" s="17" t="inlineStr">
@@ -2104,7 +2109,7 @@
         <v/>
       </c>
       <c r="S27" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("5Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("5Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("5Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("5Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U27" s="20">
@@ -2118,27 +2123,27 @@
     </row>
     <row r="28">
       <c r="A28" s="9" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
+      <c r="B28" s="10">
+        <f>IF($A28="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A28,$K$8:$K$72,0),MATCH(IF($A28="1Y","12M",IF($A28="12M","1Y",$A28)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12">
-        <f>IF($A28="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A28,$K$8:$K$72,0),MATCH(IF($A28="1Y","12M",IF($A28="12M","1Y",$A28)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="13">
+        <f>IF(OR($A28="",G28=""),"",-LN(G28)/((B28-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
         <f>IF($A28="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A28,$K$8:$K$72,0),MATCH(IF($A28="1Y","12M",IF($A28="12M","1Y",$A28)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G28" s="14">
-        <f>IF(OR($A28="",F28=""),"",-LN(F28)/((E28-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H28" s="15">
-        <f>IF(OR(G28="",NOT(ISNUMBER(C28))),"",(G28-C28)*100)</f>
+        <f>IF(OR(F28="",NOT(ISNUMBER(D28))),"",(F28-D28)*100)</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>IF(OR(F28="",NOT(ISNUMBER(D28))),"",F28-D28)</f>
+        <f>IF(OR(G28="",NOT(ISNUMBER(E28))),"",G28-E28)</f>
         <v/>
       </c>
       <c r="K28" s="17" t="inlineStr">
@@ -2173,7 +2178,7 @@
         <v/>
       </c>
       <c r="S28" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("6Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("6Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("6Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("6Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U28" s="20">
@@ -2187,27 +2192,27 @@
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="B29" s="10">
+        <f>IF($A29="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A29,$K$8:$K$72,0),MATCH(IF($A29="1Y","12M",IF($A29="12M","1Y",$A29)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C29" s="11" t="n"/>
       <c r="D29" s="11" t="n"/>
-      <c r="E29" s="12">
-        <f>IF($A29="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A29,$K$8:$K$72,0),MATCH(IF($A29="1Y","12M",IF($A29="12M","1Y",$A29)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E29" s="12" t="n"/>
       <c r="F29" s="13">
+        <f>IF(OR($A29="",G29=""),"",-LN(G29)/((B29-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
         <f>IF($A29="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A29,$K$8:$K$72,0),MATCH(IF($A29="1Y","12M",IF($A29="12M","1Y",$A29)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G29" s="14">
-        <f>IF(OR($A29="",F29=""),"",-LN(F29)/((E29-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H29" s="15">
-        <f>IF(OR(G29="",NOT(ISNUMBER(C29))),"",(G29-C29)*100)</f>
+        <f>IF(OR(F29="",NOT(ISNUMBER(D29))),"",(F29-D29)*100)</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>IF(OR(F29="",NOT(ISNUMBER(D29))),"",F29-D29)</f>
+        <f>IF(OR(G29="",NOT(ISNUMBER(E29))),"",G29-E29)</f>
         <v/>
       </c>
       <c r="K29" s="17" t="inlineStr">
@@ -2242,7 +2247,7 @@
         <v/>
       </c>
       <c r="S29" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("7Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("7Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("7Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("7Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U29" s="20">
@@ -2256,27 +2261,27 @@
     </row>
     <row r="30">
       <c r="A30" s="9" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+      <c r="B30" s="10">
+        <f>IF($A30="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A30,$K$8:$K$72,0),MATCH(IF($A30="1Y","12M",IF($A30="12M","1Y",$A30)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12">
-        <f>IF($A30="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A30,$K$8:$K$72,0),MATCH(IF($A30="1Y","12M",IF($A30="12M","1Y",$A30)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="13">
+        <f>IF(OR($A30="",G30=""),"",-LN(G30)/((B30-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
         <f>IF($A30="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A30,$K$8:$K$72,0),MATCH(IF($A30="1Y","12M",IF($A30="12M","1Y",$A30)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G30" s="14">
-        <f>IF(OR($A30="",F30=""),"",-LN(F30)/((E30-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H30" s="15">
-        <f>IF(OR(G30="",NOT(ISNUMBER(C30))),"",(G30-C30)*100)</f>
+        <f>IF(OR(F30="",NOT(ISNUMBER(D30))),"",(F30-D30)*100)</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>IF(OR(F30="",NOT(ISNUMBER(D30))),"",F30-D30)</f>
+        <f>IF(OR(G30="",NOT(ISNUMBER(E30))),"",G30-E30)</f>
         <v/>
       </c>
       <c r="K30" s="17" t="inlineStr">
@@ -2311,7 +2316,7 @@
         <v/>
       </c>
       <c r="S30" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("8Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("8Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("8Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("8Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U30" s="20">
@@ -2325,27 +2330,27 @@
     </row>
     <row r="31">
       <c r="A31" s="9" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+      <c r="B31" s="10">
+        <f>IF($A31="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A31,$K$8:$K$72,0),MATCH(IF($A31="1Y","12M",IF($A31="12M","1Y",$A31)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C31" s="11" t="n"/>
       <c r="D31" s="11" t="n"/>
-      <c r="E31" s="12">
-        <f>IF($A31="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A31,$K$8:$K$72,0),MATCH(IF($A31="1Y","12M",IF($A31="12M","1Y",$A31)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E31" s="12" t="n"/>
       <c r="F31" s="13">
+        <f>IF(OR($A31="",G31=""),"",-LN(G31)/((B31-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
         <f>IF($A31="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A31,$K$8:$K$72,0),MATCH(IF($A31="1Y","12M",IF($A31="12M","1Y",$A31)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G31" s="14">
-        <f>IF(OR($A31="",F31=""),"",-LN(F31)/((E31-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H31" s="15">
-        <f>IF(OR(G31="",NOT(ISNUMBER(C31))),"",(G31-C31)*100)</f>
+        <f>IF(OR(F31="",NOT(ISNUMBER(D31))),"",(F31-D31)*100)</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>IF(OR(F31="",NOT(ISNUMBER(D31))),"",F31-D31)</f>
+        <f>IF(OR(G31="",NOT(ISNUMBER(E31))),"",G31-E31)</f>
         <v/>
       </c>
       <c r="K31" s="17" t="inlineStr">
@@ -2380,7 +2385,7 @@
         <v/>
       </c>
       <c r="S31" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("9Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("9Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("9Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("9Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U31" s="20">
@@ -2394,27 +2399,27 @@
     </row>
     <row r="32">
       <c r="A32" s="9" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="B32" s="10">
+        <f>IF($A32="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A32,$K$8:$K$72,0),MATCH(IF($A32="1Y","12M",IF($A32="12M","1Y",$A32)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
-      <c r="E32" s="12">
-        <f>IF($A32="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A32,$K$8:$K$72,0),MATCH(IF($A32="1Y","12M",IF($A32="12M","1Y",$A32)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E32" s="12" t="n"/>
       <c r="F32" s="13">
+        <f>IF(OR($A32="",G32=""),"",-LN(G32)/((B32-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
         <f>IF($A32="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A32,$K$8:$K$72,0),MATCH(IF($A32="1Y","12M",IF($A32="12M","1Y",$A32)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G32" s="14">
-        <f>IF(OR($A32="",F32=""),"",-LN(F32)/((E32-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H32" s="15">
-        <f>IF(OR(G32="",NOT(ISNUMBER(C32))),"",(G32-C32)*100)</f>
+        <f>IF(OR(F32="",NOT(ISNUMBER(D32))),"",(F32-D32)*100)</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>IF(OR(F32="",NOT(ISNUMBER(D32))),"",F32-D32)</f>
+        <f>IF(OR(G32="",NOT(ISNUMBER(E32))),"",G32-E32)</f>
         <v/>
       </c>
       <c r="K32" s="17" t="inlineStr">
@@ -2449,7 +2454,7 @@
         <v/>
       </c>
       <c r="S32" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("10Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("10Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("10Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("10Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U32" s="20">
@@ -2463,27 +2468,27 @@
     </row>
     <row r="33">
       <c r="A33" s="9" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
+      <c r="B33" s="10">
+        <f>IF($A33="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A33,$K$8:$K$72,0),MATCH(IF($A33="1Y","12M",IF($A33="12M","1Y",$A33)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
-      <c r="E33" s="12">
-        <f>IF($A33="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A33,$K$8:$K$72,0),MATCH(IF($A33="1Y","12M",IF($A33="12M","1Y",$A33)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E33" s="12" t="n"/>
       <c r="F33" s="13">
+        <f>IF(OR($A33="",G33=""),"",-LN(G33)/((B33-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
         <f>IF($A33="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A33,$K$8:$K$72,0),MATCH(IF($A33="1Y","12M",IF($A33="12M","1Y",$A33)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G33" s="14">
-        <f>IF(OR($A33="",F33=""),"",-LN(F33)/((E33-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H33" s="15">
-        <f>IF(OR(G33="",NOT(ISNUMBER(C33))),"",(G33-C33)*100)</f>
+        <f>IF(OR(F33="",NOT(ISNUMBER(D33))),"",(F33-D33)*100)</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>IF(OR(F33="",NOT(ISNUMBER(D33))),"",F33-D33)</f>
+        <f>IF(OR(G33="",NOT(ISNUMBER(E33))),"",G33-E33)</f>
         <v/>
       </c>
       <c r="K33" s="17" t="inlineStr">
@@ -2518,7 +2523,7 @@
         <v/>
       </c>
       <c r="S33" s="19">
-        <f>IFERROR(IF(R33=1,IFERROR(INDEX($B$8:$B$59,MATCH("11Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("11Y",$A$8:$A$59,0))),S32+(S34-S32)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R33=1,IFERROR(INDEX($C$8:$C$59,MATCH("11Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("11Y",$A$8:$A$59,0))),S32+(S34-S32)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T33">
@@ -2536,27 +2541,27 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
+      <c r="B34" s="10">
+        <f>IF($A34="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A34,$K$8:$K$72,0),MATCH(IF($A34="1Y","12M",IF($A34="12M","1Y",$A34)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
-      <c r="E34" s="12">
-        <f>IF($A34="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A34,$K$8:$K$72,0),MATCH(IF($A34="1Y","12M",IF($A34="12M","1Y",$A34)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E34" s="12" t="n"/>
       <c r="F34" s="13">
+        <f>IF(OR($A34="",G34=""),"",-LN(G34)/((B34-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
         <f>IF($A34="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A34,$K$8:$K$72,0),MATCH(IF($A34="1Y","12M",IF($A34="12M","1Y",$A34)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G34" s="14">
-        <f>IF(OR($A34="",F34=""),"",-LN(F34)/((E34-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H34" s="15">
-        <f>IF(OR(G34="",NOT(ISNUMBER(C34))),"",(G34-C34)*100)</f>
+        <f>IF(OR(F34="",NOT(ISNUMBER(D34))),"",(F34-D34)*100)</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>IF(OR(F34="",NOT(ISNUMBER(D34))),"",F34-D34)</f>
+        <f>IF(OR(G34="",NOT(ISNUMBER(E34))),"",G34-E34)</f>
         <v/>
       </c>
       <c r="K34" s="17" t="inlineStr">
@@ -2591,7 +2596,7 @@
         <v/>
       </c>
       <c r="S34" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("12Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("12Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("12Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("12Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U34" s="20">
@@ -2669,27 +2674,27 @@
     </row>
     <row r="35">
       <c r="A35" s="9" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
+      <c r="B35" s="10">
+        <f>IF($A35="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A35,$K$8:$K$72,0),MATCH(IF($A35="1Y","12M",IF($A35="12M","1Y",$A35)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
-      <c r="E35" s="12">
-        <f>IF($A35="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A35,$K$8:$K$72,0),MATCH(IF($A35="1Y","12M",IF($A35="12M","1Y",$A35)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E35" s="12" t="n"/>
       <c r="F35" s="13">
+        <f>IF(OR($A35="",G35=""),"",-LN(G35)/((B35-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
         <f>IF($A35="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A35,$K$8:$K$72,0),MATCH(IF($A35="1Y","12M",IF($A35="12M","1Y",$A35)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G35" s="14">
-        <f>IF(OR($A35="",F35=""),"",-LN(F35)/((E35-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H35" s="15">
-        <f>IF(OR(G35="",NOT(ISNUMBER(C35))),"",(G35-C35)*100)</f>
+        <f>IF(OR(F35="",NOT(ISNUMBER(D35))),"",(F35-D35)*100)</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>IF(OR(F35="",NOT(ISNUMBER(D35))),"",F35-D35)</f>
+        <f>IF(OR(G35="",NOT(ISNUMBER(E35))),"",G35-E35)</f>
         <v/>
       </c>
       <c r="K35" s="17" t="inlineStr">
@@ -2724,7 +2729,7 @@
         <v/>
       </c>
       <c r="S35" s="19">
-        <f>IFERROR(IF(R35=1,IFERROR(INDEX($B$8:$B$59,MATCH("13Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("13Y",$A$8:$A$59,0))),S34+(S37-S34)*0.3333333333),"")</f>
+        <f>IFERROR(IF(R35=1,IFERROR(INDEX($C$8:$C$59,MATCH("13Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("13Y",$A$8:$A$59,0))),S34+(S37-S34)*0.3333333333),"")</f>
         <v/>
       </c>
       <c r="T35">
@@ -2742,27 +2747,27 @@
     </row>
     <row r="36">
       <c r="A36" s="9" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
+      <c r="B36" s="10">
+        <f>IF($A36="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A36,$K$8:$K$72,0),MATCH(IF($A36="1Y","12M",IF($A36="12M","1Y",$A36)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
-      <c r="E36" s="12">
-        <f>IF($A36="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A36,$K$8:$K$72,0),MATCH(IF($A36="1Y","12M",IF($A36="12M","1Y",$A36)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E36" s="12" t="n"/>
       <c r="F36" s="13">
+        <f>IF(OR($A36="",G36=""),"",-LN(G36)/((B36-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
         <f>IF($A36="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A36,$K$8:$K$72,0),MATCH(IF($A36="1Y","12M",IF($A36="12M","1Y",$A36)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G36" s="14">
-        <f>IF(OR($A36="",F36=""),"",-LN(F36)/((E36-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H36" s="15">
-        <f>IF(OR(G36="",NOT(ISNUMBER(C36))),"",(G36-C36)*100)</f>
+        <f>IF(OR(F36="",NOT(ISNUMBER(D36))),"",(F36-D36)*100)</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>IF(OR(F36="",NOT(ISNUMBER(D36))),"",F36-D36)</f>
+        <f>IF(OR(G36="",NOT(ISNUMBER(E36))),"",G36-E36)</f>
         <v/>
       </c>
       <c r="K36" s="17" t="inlineStr">
@@ -2797,7 +2802,7 @@
         <v/>
       </c>
       <c r="S36" s="19">
-        <f>IFERROR(IF(R36=1,IFERROR(INDEX($B$8:$B$59,MATCH("14Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("14Y",$A$8:$A$59,0))),S34+(S37-S34)*0.6666666667),"")</f>
+        <f>IFERROR(IF(R36=1,IFERROR(INDEX($C$8:$C$59,MATCH("14Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("14Y",$A$8:$A$59,0))),S34+(S37-S34)*0.6666666667),"")</f>
         <v/>
       </c>
       <c r="T36">
@@ -2815,27 +2820,27 @@
     </row>
     <row r="37">
       <c r="A37" s="9" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
+      <c r="B37" s="10">
+        <f>IF($A37="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A37,$K$8:$K$72,0),MATCH(IF($A37="1Y","12M",IF($A37="12M","1Y",$A37)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
-      <c r="E37" s="12">
-        <f>IF($A37="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A37,$K$8:$K$72,0),MATCH(IF($A37="1Y","12M",IF($A37="12M","1Y",$A37)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="13">
+        <f>IF(OR($A37="",G37=""),"",-LN(G37)/((B37-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
         <f>IF($A37="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A37,$K$8:$K$72,0),MATCH(IF($A37="1Y","12M",IF($A37="12M","1Y",$A37)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G37" s="14">
-        <f>IF(OR($A37="",F37=""),"",-LN(F37)/((E37-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H37" s="15">
-        <f>IF(OR(G37="",NOT(ISNUMBER(C37))),"",(G37-C37)*100)</f>
+        <f>IF(OR(F37="",NOT(ISNUMBER(D37))),"",(F37-D37)*100)</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>IF(OR(F37="",NOT(ISNUMBER(D37))),"",F37-D37)</f>
+        <f>IF(OR(G37="",NOT(ISNUMBER(E37))),"",G37-E37)</f>
         <v/>
       </c>
       <c r="K37" s="17" t="inlineStr">
@@ -2870,7 +2875,7 @@
         <v/>
       </c>
       <c r="S37" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("15Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("15Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("15Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("15Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U37" s="20">
@@ -2948,27 +2953,27 @@
     </row>
     <row r="38">
       <c r="A38" s="9" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
+      <c r="B38" s="10">
+        <f>IF($A38="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A38,$K$8:$K$72,0),MATCH(IF($A38="1Y","12M",IF($A38="12M","1Y",$A38)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12">
-        <f>IF($A38="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A38,$K$8:$K$72,0),MATCH(IF($A38="1Y","12M",IF($A38="12M","1Y",$A38)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E38" s="12" t="n"/>
       <c r="F38" s="13">
+        <f>IF(OR($A38="",G38=""),"",-LN(G38)/((B38-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G38" s="14">
         <f>IF($A38="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A38,$K$8:$K$72,0),MATCH(IF($A38="1Y","12M",IF($A38="12M","1Y",$A38)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G38" s="14">
-        <f>IF(OR($A38="",F38=""),"",-LN(F38)/((E38-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H38" s="15">
-        <f>IF(OR(G38="",NOT(ISNUMBER(C38))),"",(G38-C38)*100)</f>
+        <f>IF(OR(F38="",NOT(ISNUMBER(D38))),"",(F38-D38)*100)</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>IF(OR(F38="",NOT(ISNUMBER(D38))),"",F38-D38)</f>
+        <f>IF(OR(G38="",NOT(ISNUMBER(E38))),"",G38-E38)</f>
         <v/>
       </c>
       <c r="K38" s="17" t="inlineStr">
@@ -3003,7 +3008,7 @@
         <v/>
       </c>
       <c r="S38" s="19">
-        <f>IFERROR(IF(R38=1,IFERROR(INDEX($B$8:$B$59,MATCH("16Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("16Y",$A$8:$A$59,0))),S37+(S42-S37)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R38=1,IFERROR(INDEX($C$8:$C$59,MATCH("16Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("16Y",$A$8:$A$59,0))),S37+(S42-S37)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T38">
@@ -3021,27 +3026,27 @@
     </row>
     <row r="39">
       <c r="A39" s="9" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
+      <c r="B39" s="10">
+        <f>IF($A39="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A39,$K$8:$K$72,0),MATCH(IF($A39="1Y","12M",IF($A39="12M","1Y",$A39)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
-      <c r="E39" s="12">
-        <f>IF($A39="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A39,$K$8:$K$72,0),MATCH(IF($A39="1Y","12M",IF($A39="12M","1Y",$A39)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E39" s="12" t="n"/>
       <c r="F39" s="13">
+        <f>IF(OR($A39="",G39=""),"",-LN(G39)/((B39-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G39" s="14">
         <f>IF($A39="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A39,$K$8:$K$72,0),MATCH(IF($A39="1Y","12M",IF($A39="12M","1Y",$A39)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G39" s="14">
-        <f>IF(OR($A39="",F39=""),"",-LN(F39)/((E39-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H39" s="15">
-        <f>IF(OR(G39="",NOT(ISNUMBER(C39))),"",(G39-C39)*100)</f>
+        <f>IF(OR(F39="",NOT(ISNUMBER(D39))),"",(F39-D39)*100)</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>IF(OR(F39="",NOT(ISNUMBER(D39))),"",F39-D39)</f>
+        <f>IF(OR(G39="",NOT(ISNUMBER(E39))),"",G39-E39)</f>
         <v/>
       </c>
       <c r="K39" s="17" t="inlineStr">
@@ -3076,7 +3081,7 @@
         <v/>
       </c>
       <c r="S39" s="19">
-        <f>IFERROR(IF(R39=1,IFERROR(INDEX($B$8:$B$59,MATCH("17Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("17Y",$A$8:$A$59,0))),S37+(S42-S37)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R39=1,IFERROR(INDEX($C$8:$C$59,MATCH("17Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("17Y",$A$8:$A$59,0))),S37+(S42-S37)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T39">
@@ -3094,27 +3099,27 @@
     </row>
     <row r="40">
       <c r="A40" s="9" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
+      <c r="B40" s="10">
+        <f>IF($A40="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A40,$K$8:$K$72,0),MATCH(IF($A40="1Y","12M",IF($A40="12M","1Y",$A40)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
-      <c r="E40" s="12">
-        <f>IF($A40="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A40,$K$8:$K$72,0),MATCH(IF($A40="1Y","12M",IF($A40="12M","1Y",$A40)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E40" s="12" t="n"/>
       <c r="F40" s="13">
+        <f>IF(OR($A40="",G40=""),"",-LN(G40)/((B40-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G40" s="14">
         <f>IF($A40="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A40,$K$8:$K$72,0),MATCH(IF($A40="1Y","12M",IF($A40="12M","1Y",$A40)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G40" s="14">
-        <f>IF(OR($A40="",F40=""),"",-LN(F40)/((E40-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H40" s="15">
-        <f>IF(OR(G40="",NOT(ISNUMBER(C40))),"",(G40-C40)*100)</f>
+        <f>IF(OR(F40="",NOT(ISNUMBER(D40))),"",(F40-D40)*100)</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>IF(OR(F40="",NOT(ISNUMBER(D40))),"",F40-D40)</f>
+        <f>IF(OR(G40="",NOT(ISNUMBER(E40))),"",G40-E40)</f>
         <v/>
       </c>
       <c r="K40" s="17" t="inlineStr">
@@ -3149,7 +3154,7 @@
         <v/>
       </c>
       <c r="S40" s="19">
-        <f>IFERROR(IF(R40=1,IFERROR(INDEX($B$8:$B$59,MATCH("18Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("18Y",$A$8:$A$59,0))),S37+(S42-S37)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R40=1,IFERROR(INDEX($C$8:$C$59,MATCH("18Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("18Y",$A$8:$A$59,0))),S37+(S42-S37)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T40">
@@ -3167,27 +3172,27 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
+      <c r="B41" s="10">
+        <f>IF($A41="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A41,$K$8:$K$72,0),MATCH(IF($A41="1Y","12M",IF($A41="12M","1Y",$A41)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
-      <c r="E41" s="12">
-        <f>IF($A41="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A41,$K$8:$K$72,0),MATCH(IF($A41="1Y","12M",IF($A41="12M","1Y",$A41)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E41" s="12" t="n"/>
       <c r="F41" s="13">
+        <f>IF(OR($A41="",G41=""),"",-LN(G41)/((B41-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G41" s="14">
         <f>IF($A41="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A41,$K$8:$K$72,0),MATCH(IF($A41="1Y","12M",IF($A41="12M","1Y",$A41)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G41" s="14">
-        <f>IF(OR($A41="",F41=""),"",-LN(F41)/((E41-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H41" s="15">
-        <f>IF(OR(G41="",NOT(ISNUMBER(C41))),"",(G41-C41)*100)</f>
+        <f>IF(OR(F41="",NOT(ISNUMBER(D41))),"",(F41-D41)*100)</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>IF(OR(F41="",NOT(ISNUMBER(D41))),"",F41-D41)</f>
+        <f>IF(OR(G41="",NOT(ISNUMBER(E41))),"",G41-E41)</f>
         <v/>
       </c>
       <c r="K41" s="17" t="inlineStr">
@@ -3222,7 +3227,7 @@
         <v/>
       </c>
       <c r="S41" s="19">
-        <f>IFERROR(IF(R41=1,IFERROR(INDEX($B$8:$B$59,MATCH("19Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("19Y",$A$8:$A$59,0))),S37+(S42-S37)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R41=1,IFERROR(INDEX($C$8:$C$59,MATCH("19Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("19Y",$A$8:$A$59,0))),S37+(S42-S37)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T41">
@@ -3240,27 +3245,27 @@
     </row>
     <row r="42">
       <c r="A42" s="9" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
+      <c r="B42" s="10">
+        <f>IF($A42="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A42,$K$8:$K$72,0),MATCH(IF($A42="1Y","12M",IF($A42="12M","1Y",$A42)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
-      <c r="E42" s="12">
-        <f>IF($A42="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A42,$K$8:$K$72,0),MATCH(IF($A42="1Y","12M",IF($A42="12M","1Y",$A42)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E42" s="12" t="n"/>
       <c r="F42" s="13">
+        <f>IF(OR($A42="",G42=""),"",-LN(G42)/((B42-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
         <f>IF($A42="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A42,$K$8:$K$72,0),MATCH(IF($A42="1Y","12M",IF($A42="12M","1Y",$A42)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G42" s="14">
-        <f>IF(OR($A42="",F42=""),"",-LN(F42)/((E42-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H42" s="15">
-        <f>IF(OR(G42="",NOT(ISNUMBER(C42))),"",(G42-C42)*100)</f>
+        <f>IF(OR(F42="",NOT(ISNUMBER(D42))),"",(F42-D42)*100)</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>IF(OR(F42="",NOT(ISNUMBER(D42))),"",F42-D42)</f>
+        <f>IF(OR(G42="",NOT(ISNUMBER(E42))),"",G42-E42)</f>
         <v/>
       </c>
       <c r="K42" s="17" t="inlineStr">
@@ -3295,7 +3300,7 @@
         <v/>
       </c>
       <c r="S42" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("20Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("20Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("20Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("20Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U42" s="20">
@@ -3373,27 +3378,27 @@
     </row>
     <row r="43">
       <c r="A43" s="9" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
+      <c r="B43" s="10">
+        <f>IF($A43="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A43,$K$8:$K$72,0),MATCH(IF($A43="1Y","12M",IF($A43="12M","1Y",$A43)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C43" s="11" t="n"/>
       <c r="D43" s="11" t="n"/>
-      <c r="E43" s="12">
-        <f>IF($A43="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A43,$K$8:$K$72,0),MATCH(IF($A43="1Y","12M",IF($A43="12M","1Y",$A43)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E43" s="12" t="n"/>
       <c r="F43" s="13">
+        <f>IF(OR($A43="",G43=""),"",-LN(G43)/((B43-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G43" s="14">
         <f>IF($A43="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A43,$K$8:$K$72,0),MATCH(IF($A43="1Y","12M",IF($A43="12M","1Y",$A43)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G43" s="14">
-        <f>IF(OR($A43="",F43=""),"",-LN(F43)/((E43-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H43" s="15">
-        <f>IF(OR(G43="",NOT(ISNUMBER(C43))),"",(G43-C43)*100)</f>
+        <f>IF(OR(F43="",NOT(ISNUMBER(D43))),"",(F43-D43)*100)</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>IF(OR(F43="",NOT(ISNUMBER(D43))),"",F43-D43)</f>
+        <f>IF(OR(G43="",NOT(ISNUMBER(E43))),"",G43-E43)</f>
         <v/>
       </c>
       <c r="K43" s="17" t="inlineStr">
@@ -3428,7 +3433,7 @@
         <v/>
       </c>
       <c r="S43" s="19">
-        <f>IFERROR(IF(R43=1,IFERROR(INDEX($B$8:$B$59,MATCH("21Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("21Y",$A$8:$A$59,0))),S42+(S47-S42)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R43=1,IFERROR(INDEX($C$8:$C$59,MATCH("21Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("21Y",$A$8:$A$59,0))),S42+(S47-S42)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T43">
@@ -3446,27 +3451,27 @@
     </row>
     <row r="44">
       <c r="A44" s="9" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
+      <c r="B44" s="10">
+        <f>IF($A44="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A44,$K$8:$K$72,0),MATCH(IF($A44="1Y","12M",IF($A44="12M","1Y",$A44)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
-      <c r="E44" s="12">
-        <f>IF($A44="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A44,$K$8:$K$72,0),MATCH(IF($A44="1Y","12M",IF($A44="12M","1Y",$A44)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E44" s="12" t="n"/>
       <c r="F44" s="13">
+        <f>IF(OR($A44="",G44=""),"",-LN(G44)/((B44-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G44" s="14">
         <f>IF($A44="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A44,$K$8:$K$72,0),MATCH(IF($A44="1Y","12M",IF($A44="12M","1Y",$A44)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G44" s="14">
-        <f>IF(OR($A44="",F44=""),"",-LN(F44)/((E44-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H44" s="15">
-        <f>IF(OR(G44="",NOT(ISNUMBER(C44))),"",(G44-C44)*100)</f>
+        <f>IF(OR(F44="",NOT(ISNUMBER(D44))),"",(F44-D44)*100)</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>IF(OR(F44="",NOT(ISNUMBER(D44))),"",F44-D44)</f>
+        <f>IF(OR(G44="",NOT(ISNUMBER(E44))),"",G44-E44)</f>
         <v/>
       </c>
       <c r="K44" s="17" t="inlineStr">
@@ -3501,7 +3506,7 @@
         <v/>
       </c>
       <c r="S44" s="19">
-        <f>IFERROR(IF(R44=1,IFERROR(INDEX($B$8:$B$59,MATCH("22Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("22Y",$A$8:$A$59,0))),S42+(S47-S42)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R44=1,IFERROR(INDEX($C$8:$C$59,MATCH("22Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("22Y",$A$8:$A$59,0))),S42+(S47-S42)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T44">
@@ -3519,27 +3524,27 @@
     </row>
     <row r="45">
       <c r="A45" s="9" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
+      <c r="B45" s="10">
+        <f>IF($A45="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A45,$K$8:$K$72,0),MATCH(IF($A45="1Y","12M",IF($A45="12M","1Y",$A45)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C45" s="11" t="n"/>
       <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12">
-        <f>IF($A45="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A45,$K$8:$K$72,0),MATCH(IF($A45="1Y","12M",IF($A45="12M","1Y",$A45)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E45" s="12" t="n"/>
       <c r="F45" s="13">
+        <f>IF(OR($A45="",G45=""),"",-LN(G45)/((B45-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G45" s="14">
         <f>IF($A45="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A45,$K$8:$K$72,0),MATCH(IF($A45="1Y","12M",IF($A45="12M","1Y",$A45)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G45" s="14">
-        <f>IF(OR($A45="",F45=""),"",-LN(F45)/((E45-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H45" s="15">
-        <f>IF(OR(G45="",NOT(ISNUMBER(C45))),"",(G45-C45)*100)</f>
+        <f>IF(OR(F45="",NOT(ISNUMBER(D45))),"",(F45-D45)*100)</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>IF(OR(F45="",NOT(ISNUMBER(D45))),"",F45-D45)</f>
+        <f>IF(OR(G45="",NOT(ISNUMBER(E45))),"",G45-E45)</f>
         <v/>
       </c>
       <c r="K45" s="17" t="inlineStr">
@@ -3574,7 +3579,7 @@
         <v/>
       </c>
       <c r="S45" s="19">
-        <f>IFERROR(IF(R45=1,IFERROR(INDEX($B$8:$B$59,MATCH("23Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("23Y",$A$8:$A$59,0))),S42+(S47-S42)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R45=1,IFERROR(INDEX($C$8:$C$59,MATCH("23Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("23Y",$A$8:$A$59,0))),S42+(S47-S42)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T45">
@@ -3592,27 +3597,27 @@
     </row>
     <row r="46">
       <c r="A46" s="9" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
+      <c r="B46" s="10">
+        <f>IF($A46="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A46,$K$8:$K$72,0),MATCH(IF($A46="1Y","12M",IF($A46="12M","1Y",$A46)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C46" s="11" t="n"/>
       <c r="D46" s="11" t="n"/>
-      <c r="E46" s="12">
-        <f>IF($A46="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A46,$K$8:$K$72,0),MATCH(IF($A46="1Y","12M",IF($A46="12M","1Y",$A46)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="13">
+        <f>IF(OR($A46="",G46=""),"",-LN(G46)/((B46-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
         <f>IF($A46="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A46,$K$8:$K$72,0),MATCH(IF($A46="1Y","12M",IF($A46="12M","1Y",$A46)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G46" s="14">
-        <f>IF(OR($A46="",F46=""),"",-LN(F46)/((E46-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H46" s="15">
-        <f>IF(OR(G46="",NOT(ISNUMBER(C46))),"",(G46-C46)*100)</f>
+        <f>IF(OR(F46="",NOT(ISNUMBER(D46))),"",(F46-D46)*100)</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>IF(OR(F46="",NOT(ISNUMBER(D46))),"",F46-D46)</f>
+        <f>IF(OR(G46="",NOT(ISNUMBER(E46))),"",G46-E46)</f>
         <v/>
       </c>
       <c r="K46" s="17" t="inlineStr">
@@ -3647,7 +3652,7 @@
         <v/>
       </c>
       <c r="S46" s="19">
-        <f>IFERROR(IF(R46=1,IFERROR(INDEX($B$8:$B$59,MATCH("24Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("24Y",$A$8:$A$59,0))),S42+(S47-S42)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R46=1,IFERROR(INDEX($C$8:$C$59,MATCH("24Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("24Y",$A$8:$A$59,0))),S42+(S47-S42)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T46">
@@ -3665,27 +3670,27 @@
     </row>
     <row r="47">
       <c r="A47" s="9" t="n"/>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
+      <c r="B47" s="10">
+        <f>IF($A47="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A47,$K$8:$K$72,0),MATCH(IF($A47="1Y","12M",IF($A47="12M","1Y",$A47)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C47" s="11" t="n"/>
       <c r="D47" s="11" t="n"/>
-      <c r="E47" s="12">
-        <f>IF($A47="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A47,$K$8:$K$72,0),MATCH(IF($A47="1Y","12M",IF($A47="12M","1Y",$A47)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E47" s="12" t="n"/>
       <c r="F47" s="13">
+        <f>IF(OR($A47="",G47=""),"",-LN(G47)/((B47-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G47" s="14">
         <f>IF($A47="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A47,$K$8:$K$72,0),MATCH(IF($A47="1Y","12M",IF($A47="12M","1Y",$A47)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G47" s="14">
-        <f>IF(OR($A47="",F47=""),"",-LN(F47)/((E47-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H47" s="15">
-        <f>IF(OR(G47="",NOT(ISNUMBER(C47))),"",(G47-C47)*100)</f>
+        <f>IF(OR(F47="",NOT(ISNUMBER(D47))),"",(F47-D47)*100)</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>IF(OR(F47="",NOT(ISNUMBER(D47))),"",F47-D47)</f>
+        <f>IF(OR(G47="",NOT(ISNUMBER(E47))),"",G47-E47)</f>
         <v/>
       </c>
       <c r="K47" s="17" t="inlineStr">
@@ -3720,7 +3725,7 @@
         <v/>
       </c>
       <c r="S47" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("25Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("25Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("25Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("25Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U47" s="20">
@@ -3798,27 +3803,27 @@
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
+      <c r="B48" s="10">
+        <f>IF($A48="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A48,$K$8:$K$72,0),MATCH(IF($A48="1Y","12M",IF($A48="12M","1Y",$A48)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C48" s="11" t="n"/>
       <c r="D48" s="11" t="n"/>
-      <c r="E48" s="12">
-        <f>IF($A48="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A48,$K$8:$K$72,0),MATCH(IF($A48="1Y","12M",IF($A48="12M","1Y",$A48)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="13">
+        <f>IF(OR($A48="",G48=""),"",-LN(G48)/((B48-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
         <f>IF($A48="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A48,$K$8:$K$72,0),MATCH(IF($A48="1Y","12M",IF($A48="12M","1Y",$A48)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G48" s="14">
-        <f>IF(OR($A48="",F48=""),"",-LN(F48)/((E48-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H48" s="15">
-        <f>IF(OR(G48="",NOT(ISNUMBER(C48))),"",(G48-C48)*100)</f>
+        <f>IF(OR(F48="",NOT(ISNUMBER(D48))),"",(F48-D48)*100)</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>IF(OR(F48="",NOT(ISNUMBER(D48))),"",F48-D48)</f>
+        <f>IF(OR(G48="",NOT(ISNUMBER(E48))),"",G48-E48)</f>
         <v/>
       </c>
       <c r="K48" s="17" t="inlineStr">
@@ -3853,7 +3858,7 @@
         <v/>
       </c>
       <c r="S48" s="19">
-        <f>IFERROR(IF(R48=1,IFERROR(INDEX($B$8:$B$59,MATCH("26Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("26Y",$A$8:$A$59,0))),S47+(S52-S47)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R48=1,IFERROR(INDEX($C$8:$C$59,MATCH("26Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("26Y",$A$8:$A$59,0))),S47+(S52-S47)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T48">
@@ -3871,27 +3876,27 @@
     </row>
     <row r="49">
       <c r="A49" s="9" t="n"/>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
+      <c r="B49" s="10">
+        <f>IF($A49="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A49,$K$8:$K$72,0),MATCH(IF($A49="1Y","12M",IF($A49="12M","1Y",$A49)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C49" s="11" t="n"/>
       <c r="D49" s="11" t="n"/>
-      <c r="E49" s="12">
-        <f>IF($A49="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A49,$K$8:$K$72,0),MATCH(IF($A49="1Y","12M",IF($A49="12M","1Y",$A49)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E49" s="12" t="n"/>
       <c r="F49" s="13">
+        <f>IF(OR($A49="",G49=""),"",-LN(G49)/((B49-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G49" s="14">
         <f>IF($A49="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A49,$K$8:$K$72,0),MATCH(IF($A49="1Y","12M",IF($A49="12M","1Y",$A49)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G49" s="14">
-        <f>IF(OR($A49="",F49=""),"",-LN(F49)/((E49-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H49" s="15">
-        <f>IF(OR(G49="",NOT(ISNUMBER(C49))),"",(G49-C49)*100)</f>
+        <f>IF(OR(F49="",NOT(ISNUMBER(D49))),"",(F49-D49)*100)</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>IF(OR(F49="",NOT(ISNUMBER(D49))),"",F49-D49)</f>
+        <f>IF(OR(G49="",NOT(ISNUMBER(E49))),"",G49-E49)</f>
         <v/>
       </c>
       <c r="K49" s="17" t="inlineStr">
@@ -3926,7 +3931,7 @@
         <v/>
       </c>
       <c r="S49" s="19">
-        <f>IFERROR(IF(R49=1,IFERROR(INDEX($B$8:$B$59,MATCH("27Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("27Y",$A$8:$A$59,0))),S47+(S52-S47)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R49=1,IFERROR(INDEX($C$8:$C$59,MATCH("27Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("27Y",$A$8:$A$59,0))),S47+(S52-S47)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T49">
@@ -3944,27 +3949,27 @@
     </row>
     <row r="50">
       <c r="A50" s="9" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
+      <c r="B50" s="10">
+        <f>IF($A50="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A50,$K$8:$K$72,0),MATCH(IF($A50="1Y","12M",IF($A50="12M","1Y",$A50)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C50" s="11" t="n"/>
       <c r="D50" s="11" t="n"/>
-      <c r="E50" s="12">
-        <f>IF($A50="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A50,$K$8:$K$72,0),MATCH(IF($A50="1Y","12M",IF($A50="12M","1Y",$A50)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E50" s="12" t="n"/>
       <c r="F50" s="13">
+        <f>IF(OR($A50="",G50=""),"",-LN(G50)/((B50-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G50" s="14">
         <f>IF($A50="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A50,$K$8:$K$72,0),MATCH(IF($A50="1Y","12M",IF($A50="12M","1Y",$A50)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G50" s="14">
-        <f>IF(OR($A50="",F50=""),"",-LN(F50)/((E50-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H50" s="15">
-        <f>IF(OR(G50="",NOT(ISNUMBER(C50))),"",(G50-C50)*100)</f>
+        <f>IF(OR(F50="",NOT(ISNUMBER(D50))),"",(F50-D50)*100)</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>IF(OR(F50="",NOT(ISNUMBER(D50))),"",F50-D50)</f>
+        <f>IF(OR(G50="",NOT(ISNUMBER(E50))),"",G50-E50)</f>
         <v/>
       </c>
       <c r="K50" s="17" t="inlineStr">
@@ -3999,7 +4004,7 @@
         <v/>
       </c>
       <c r="S50" s="19">
-        <f>IFERROR(IF(R50=1,IFERROR(INDEX($B$8:$B$59,MATCH("28Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("28Y",$A$8:$A$59,0))),S47+(S52-S47)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R50=1,IFERROR(INDEX($C$8:$C$59,MATCH("28Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("28Y",$A$8:$A$59,0))),S47+(S52-S47)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T50">
@@ -4017,27 +4022,27 @@
     </row>
     <row r="51">
       <c r="A51" s="9" t="n"/>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
+      <c r="B51" s="10">
+        <f>IF($A51="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A51,$K$8:$K$72,0),MATCH(IF($A51="1Y","12M",IF($A51="12M","1Y",$A51)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C51" s="11" t="n"/>
       <c r="D51" s="11" t="n"/>
-      <c r="E51" s="12">
-        <f>IF($A51="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A51,$K$8:$K$72,0),MATCH(IF($A51="1Y","12M",IF($A51="12M","1Y",$A51)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E51" s="12" t="n"/>
       <c r="F51" s="13">
+        <f>IF(OR($A51="",G51=""),"",-LN(G51)/((B51-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G51" s="14">
         <f>IF($A51="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A51,$K$8:$K$72,0),MATCH(IF($A51="1Y","12M",IF($A51="12M","1Y",$A51)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G51" s="14">
-        <f>IF(OR($A51="",F51=""),"",-LN(F51)/((E51-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H51" s="15">
-        <f>IF(OR(G51="",NOT(ISNUMBER(C51))),"",(G51-C51)*100)</f>
+        <f>IF(OR(F51="",NOT(ISNUMBER(D51))),"",(F51-D51)*100)</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>IF(OR(F51="",NOT(ISNUMBER(D51))),"",F51-D51)</f>
+        <f>IF(OR(G51="",NOT(ISNUMBER(E51))),"",G51-E51)</f>
         <v/>
       </c>
       <c r="K51" s="17" t="inlineStr">
@@ -4072,7 +4077,7 @@
         <v/>
       </c>
       <c r="S51" s="19">
-        <f>IFERROR(IF(R51=1,IFERROR(INDEX($B$8:$B$59,MATCH("29Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("29Y",$A$8:$A$59,0))),S47+(S52-S47)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R51=1,IFERROR(INDEX($C$8:$C$59,MATCH("29Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("29Y",$A$8:$A$59,0))),S47+(S52-S47)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T51">
@@ -4090,27 +4095,27 @@
     </row>
     <row r="52">
       <c r="A52" s="9" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
+      <c r="B52" s="10">
+        <f>IF($A52="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A52,$K$8:$K$72,0),MATCH(IF($A52="1Y","12M",IF($A52="12M","1Y",$A52)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C52" s="11" t="n"/>
       <c r="D52" s="11" t="n"/>
-      <c r="E52" s="12">
-        <f>IF($A52="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A52,$K$8:$K$72,0),MATCH(IF($A52="1Y","12M",IF($A52="12M","1Y",$A52)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E52" s="12" t="n"/>
       <c r="F52" s="13">
+        <f>IF(OR($A52="",G52=""),"",-LN(G52)/((B52-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G52" s="14">
         <f>IF($A52="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A52,$K$8:$K$72,0),MATCH(IF($A52="1Y","12M",IF($A52="12M","1Y",$A52)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G52" s="14">
-        <f>IF(OR($A52="",F52=""),"",-LN(F52)/((E52-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H52" s="15">
-        <f>IF(OR(G52="",NOT(ISNUMBER(C52))),"",(G52-C52)*100)</f>
+        <f>IF(OR(F52="",NOT(ISNUMBER(D52))),"",(F52-D52)*100)</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>IF(OR(F52="",NOT(ISNUMBER(D52))),"",F52-D52)</f>
+        <f>IF(OR(G52="",NOT(ISNUMBER(E52))),"",G52-E52)</f>
         <v/>
       </c>
       <c r="K52" s="17" t="inlineStr">
@@ -4145,7 +4150,7 @@
         <v/>
       </c>
       <c r="S52" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("30Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("30Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("30Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("30Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U52" s="20">
@@ -4223,27 +4228,27 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
+      <c r="B53" s="10">
+        <f>IF($A53="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A53,$K$8:$K$72,0),MATCH(IF($A53="1Y","12M",IF($A53="12M","1Y",$A53)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C53" s="11" t="n"/>
       <c r="D53" s="11" t="n"/>
-      <c r="E53" s="12">
-        <f>IF($A53="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A53,$K$8:$K$72,0),MATCH(IF($A53="1Y","12M",IF($A53="12M","1Y",$A53)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E53" s="12" t="n"/>
       <c r="F53" s="13">
+        <f>IF(OR($A53="",G53=""),"",-LN(G53)/((B53-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G53" s="14">
         <f>IF($A53="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A53,$K$8:$K$72,0),MATCH(IF($A53="1Y","12M",IF($A53="12M","1Y",$A53)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G53" s="14">
-        <f>IF(OR($A53="",F53=""),"",-LN(F53)/((E53-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H53" s="15">
-        <f>IF(OR(G53="",NOT(ISNUMBER(C53))),"",(G53-C53)*100)</f>
+        <f>IF(OR(F53="",NOT(ISNUMBER(D53))),"",(F53-D53)*100)</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>IF(OR(F53="",NOT(ISNUMBER(D53))),"",F53-D53)</f>
+        <f>IF(OR(G53="",NOT(ISNUMBER(E53))),"",G53-E53)</f>
         <v/>
       </c>
       <c r="K53" s="17" t="inlineStr">
@@ -4278,7 +4283,7 @@
         <v/>
       </c>
       <c r="S53" s="19">
-        <f>IFERROR(IF(R53=1,IFERROR(INDEX($B$8:$B$59,MATCH("31Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("31Y",$A$8:$A$59,0))),S52+(S62-S52)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R53=1,IFERROR(INDEX($C$8:$C$59,MATCH("31Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("31Y",$A$8:$A$59,0))),S52+(S62-S52)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T53">
@@ -4296,27 +4301,27 @@
     </row>
     <row r="54">
       <c r="A54" s="9" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
+      <c r="B54" s="10">
+        <f>IF($A54="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A54,$K$8:$K$72,0),MATCH(IF($A54="1Y","12M",IF($A54="12M","1Y",$A54)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C54" s="11" t="n"/>
       <c r="D54" s="11" t="n"/>
-      <c r="E54" s="12">
-        <f>IF($A54="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A54,$K$8:$K$72,0),MATCH(IF($A54="1Y","12M",IF($A54="12M","1Y",$A54)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E54" s="12" t="n"/>
       <c r="F54" s="13">
+        <f>IF(OR($A54="",G54=""),"",-LN(G54)/((B54-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G54" s="14">
         <f>IF($A54="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A54,$K$8:$K$72,0),MATCH(IF($A54="1Y","12M",IF($A54="12M","1Y",$A54)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G54" s="14">
-        <f>IF(OR($A54="",F54=""),"",-LN(F54)/((E54-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H54" s="15">
-        <f>IF(OR(G54="",NOT(ISNUMBER(C54))),"",(G54-C54)*100)</f>
+        <f>IF(OR(F54="",NOT(ISNUMBER(D54))),"",(F54-D54)*100)</f>
         <v/>
       </c>
       <c r="I54" s="16">
-        <f>IF(OR(F54="",NOT(ISNUMBER(D54))),"",F54-D54)</f>
+        <f>IF(OR(G54="",NOT(ISNUMBER(E54))),"",G54-E54)</f>
         <v/>
       </c>
       <c r="K54" s="17" t="inlineStr">
@@ -4351,7 +4356,7 @@
         <v/>
       </c>
       <c r="S54" s="19">
-        <f>IFERROR(IF(R54=1,IFERROR(INDEX($B$8:$B$59,MATCH("32Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("32Y",$A$8:$A$59,0))),S52+(S62-S52)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R54=1,IFERROR(INDEX($C$8:$C$59,MATCH("32Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("32Y",$A$8:$A$59,0))),S52+(S62-S52)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T54">
@@ -4369,27 +4374,27 @@
     </row>
     <row r="55">
       <c r="A55" s="9" t="n"/>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
+      <c r="B55" s="10">
+        <f>IF($A55="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A55,$K$8:$K$72,0),MATCH(IF($A55="1Y","12M",IF($A55="12M","1Y",$A55)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C55" s="11" t="n"/>
       <c r="D55" s="11" t="n"/>
-      <c r="E55" s="12">
-        <f>IF($A55="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A55,$K$8:$K$72,0),MATCH(IF($A55="1Y","12M",IF($A55="12M","1Y",$A55)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E55" s="12" t="n"/>
       <c r="F55" s="13">
+        <f>IF(OR($A55="",G55=""),"",-LN(G55)/((B55-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G55" s="14">
         <f>IF($A55="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A55,$K$8:$K$72,0),MATCH(IF($A55="1Y","12M",IF($A55="12M","1Y",$A55)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G55" s="14">
-        <f>IF(OR($A55="",F55=""),"",-LN(F55)/((E55-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H55" s="15">
-        <f>IF(OR(G55="",NOT(ISNUMBER(C55))),"",(G55-C55)*100)</f>
+        <f>IF(OR(F55="",NOT(ISNUMBER(D55))),"",(F55-D55)*100)</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>IF(OR(F55="",NOT(ISNUMBER(D55))),"",F55-D55)</f>
+        <f>IF(OR(G55="",NOT(ISNUMBER(E55))),"",G55-E55)</f>
         <v/>
       </c>
       <c r="K55" s="17" t="inlineStr">
@@ -4424,7 +4429,7 @@
         <v/>
       </c>
       <c r="S55" s="19">
-        <f>IFERROR(IF(R55=1,IFERROR(INDEX($B$8:$B$59,MATCH("33Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("33Y",$A$8:$A$59,0))),S52+(S62-S52)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R55=1,IFERROR(INDEX($C$8:$C$59,MATCH("33Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("33Y",$A$8:$A$59,0))),S52+(S62-S52)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T55">
@@ -4442,27 +4447,27 @@
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="10" t="n"/>
+      <c r="B56" s="10">
+        <f>IF($A56="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A56,$K$8:$K$72,0),MATCH(IF($A56="1Y","12M",IF($A56="12M","1Y",$A56)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C56" s="11" t="n"/>
       <c r="D56" s="11" t="n"/>
-      <c r="E56" s="12">
-        <f>IF($A56="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A56,$K$8:$K$72,0),MATCH(IF($A56="1Y","12M",IF($A56="12M","1Y",$A56)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E56" s="12" t="n"/>
       <c r="F56" s="13">
+        <f>IF(OR($A56="",G56=""),"",-LN(G56)/((B56-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G56" s="14">
         <f>IF($A56="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A56,$K$8:$K$72,0),MATCH(IF($A56="1Y","12M",IF($A56="12M","1Y",$A56)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G56" s="14">
-        <f>IF(OR($A56="",F56=""),"",-LN(F56)/((E56-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H56" s="15">
-        <f>IF(OR(G56="",NOT(ISNUMBER(C56))),"",(G56-C56)*100)</f>
+        <f>IF(OR(F56="",NOT(ISNUMBER(D56))),"",(F56-D56)*100)</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>IF(OR(F56="",NOT(ISNUMBER(D56))),"",F56-D56)</f>
+        <f>IF(OR(G56="",NOT(ISNUMBER(E56))),"",G56-E56)</f>
         <v/>
       </c>
       <c r="K56" s="17" t="inlineStr">
@@ -4497,7 +4502,7 @@
         <v/>
       </c>
       <c r="S56" s="19">
-        <f>IFERROR(IF(R56=1,IFERROR(INDEX($B$8:$B$59,MATCH("34Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("34Y",$A$8:$A$59,0))),S52+(S62-S52)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R56=1,IFERROR(INDEX($C$8:$C$59,MATCH("34Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("34Y",$A$8:$A$59,0))),S52+(S62-S52)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T56">
@@ -4515,27 +4520,27 @@
     </row>
     <row r="57">
       <c r="A57" s="9" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
+      <c r="B57" s="10">
+        <f>IF($A57="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A57,$K$8:$K$72,0),MATCH(IF($A57="1Y","12M",IF($A57="12M","1Y",$A57)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C57" s="11" t="n"/>
       <c r="D57" s="11" t="n"/>
-      <c r="E57" s="12">
-        <f>IF($A57="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A57,$K$8:$K$72,0),MATCH(IF($A57="1Y","12M",IF($A57="12M","1Y",$A57)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E57" s="12" t="n"/>
       <c r="F57" s="13">
+        <f>IF(OR($A57="",G57=""),"",-LN(G57)/((B57-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G57" s="14">
         <f>IF($A57="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A57,$K$8:$K$72,0),MATCH(IF($A57="1Y","12M",IF($A57="12M","1Y",$A57)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G57" s="14">
-        <f>IF(OR($A57="",F57=""),"",-LN(F57)/((E57-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H57" s="15">
-        <f>IF(OR(G57="",NOT(ISNUMBER(C57))),"",(G57-C57)*100)</f>
+        <f>IF(OR(F57="",NOT(ISNUMBER(D57))),"",(F57-D57)*100)</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>IF(OR(F57="",NOT(ISNUMBER(D57))),"",F57-D57)</f>
+        <f>IF(OR(G57="",NOT(ISNUMBER(E57))),"",G57-E57)</f>
         <v/>
       </c>
       <c r="K57" s="17" t="inlineStr">
@@ -4570,7 +4575,7 @@
         <v/>
       </c>
       <c r="S57" s="19">
-        <f>IFERROR(IF(R57=1,IFERROR(INDEX($B$8:$B$59,MATCH("35Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("35Y",$A$8:$A$59,0))),S52+(S62-S52)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R57=1,IFERROR(INDEX($C$8:$C$59,MATCH("35Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("35Y",$A$8:$A$59,0))),S52+(S62-S52)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T57">
@@ -4588,27 +4593,27 @@
     </row>
     <row r="58">
       <c r="A58" s="9" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
+      <c r="B58" s="10">
+        <f>IF($A58="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A58,$K$8:$K$72,0),MATCH(IF($A58="1Y","12M",IF($A58="12M","1Y",$A58)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C58" s="11" t="n"/>
       <c r="D58" s="11" t="n"/>
-      <c r="E58" s="12">
-        <f>IF($A58="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A58,$K$8:$K$72,0),MATCH(IF($A58="1Y","12M",IF($A58="12M","1Y",$A58)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E58" s="12" t="n"/>
       <c r="F58" s="13">
+        <f>IF(OR($A58="",G58=""),"",-LN(G58)/((B58-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G58" s="14">
         <f>IF($A58="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A58,$K$8:$K$72,0),MATCH(IF($A58="1Y","12M",IF($A58="12M","1Y",$A58)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G58" s="14">
-        <f>IF(OR($A58="",F58=""),"",-LN(F58)/((E58-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H58" s="15">
-        <f>IF(OR(G58="",NOT(ISNUMBER(C58))),"",(G58-C58)*100)</f>
+        <f>IF(OR(F58="",NOT(ISNUMBER(D58))),"",(F58-D58)*100)</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>IF(OR(F58="",NOT(ISNUMBER(D58))),"",F58-D58)</f>
+        <f>IF(OR(G58="",NOT(ISNUMBER(E58))),"",G58-E58)</f>
         <v/>
       </c>
       <c r="K58" s="17" t="inlineStr">
@@ -4643,7 +4648,7 @@
         <v/>
       </c>
       <c r="S58" s="19">
-        <f>IFERROR(IF(R58=1,IFERROR(INDEX($B$8:$B$59,MATCH("36Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("36Y",$A$8:$A$59,0))),S52+(S62-S52)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R58=1,IFERROR(INDEX($C$8:$C$59,MATCH("36Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("36Y",$A$8:$A$59,0))),S52+(S62-S52)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T58">
@@ -4661,27 +4666,27 @@
     </row>
     <row r="59">
       <c r="A59" s="9" t="n"/>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
+      <c r="B59" s="10">
+        <f>IF($A59="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A59,$K$8:$K$72,0),MATCH(IF($A59="1Y","12M",IF($A59="12M","1Y",$A59)),$K$8:$K$72,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C59" s="11" t="n"/>
       <c r="D59" s="11" t="n"/>
-      <c r="E59" s="12">
-        <f>IF($A59="","",IFERROR(INDEX($M$8:$M$72,IFERROR(MATCH($A59,$K$8:$K$72,0),MATCH(IF($A59="1Y","12M",IF($A59="12M","1Y",$A59)),$K$8:$K$72,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E59" s="12" t="n"/>
       <c r="F59" s="13">
+        <f>IF(OR($A59="",G59=""),"",-LN(G59)/((B59-$C$3)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G59" s="14">
         <f>IF($A59="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A59,$K$8:$K$72,0),MATCH(IF($A59="1Y","12M",IF($A59="12M","1Y",$A59)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="G59" s="14">
-        <f>IF(OR($A59="",F59=""),"",-LN(F59)/((E59-$C$3)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H59" s="15">
-        <f>IF(OR(G59="",NOT(ISNUMBER(C59))),"",(G59-C59)*100)</f>
+        <f>IF(OR(F59="",NOT(ISNUMBER(D59))),"",(F59-D59)*100)</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>IF(OR(F59="",NOT(ISNUMBER(D59))),"",F59-D59)</f>
+        <f>IF(OR(G59="",NOT(ISNUMBER(E59))),"",G59-E59)</f>
         <v/>
       </c>
       <c r="K59" s="17" t="inlineStr">
@@ -4716,7 +4721,7 @@
         <v/>
       </c>
       <c r="S59" s="19">
-        <f>IFERROR(IF(R59=1,IFERROR(INDEX($B$8:$B$59,MATCH("37Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("37Y",$A$8:$A$59,0))),S52+(S62-S52)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R59=1,IFERROR(INDEX($C$8:$C$59,MATCH("37Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("37Y",$A$8:$A$59,0))),S52+(S62-S52)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T59">
@@ -4765,7 +4770,7 @@
         <v/>
       </c>
       <c r="S60" s="19">
-        <f>IFERROR(IF(R60=1,IFERROR(INDEX($B$8:$B$59,MATCH("38Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("38Y",$A$8:$A$59,0))),S52+(S62-S52)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R60=1,IFERROR(INDEX($C$8:$C$59,MATCH("38Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("38Y",$A$8:$A$59,0))),S52+(S62-S52)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T60">
@@ -4797,7 +4802,7 @@
         </is>
       </c>
       <c r="F61" s="22">
-        <f>COUNT($G$8:$G$59)</f>
+        <f>COUNT($F$8:$F$59)</f>
         <v/>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4841,7 +4846,7 @@
         <v/>
       </c>
       <c r="S61" s="19">
-        <f>IFERROR(IF(R61=1,IFERROR(INDEX($B$8:$B$59,MATCH("39Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("39Y",$A$8:$A$59,0))),S52+(S62-S52)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R61=1,IFERROR(INDEX($C$8:$C$59,MATCH("39Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("39Y",$A$8:$A$59,0))),S52+(S62-S52)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T61">
@@ -4899,7 +4904,7 @@
         <v/>
       </c>
       <c r="S62" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("40Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("40Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("40Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("40Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U62" s="20">
@@ -5013,7 +5018,7 @@
         <v/>
       </c>
       <c r="S63" s="19">
-        <f>IFERROR(IF(R63=1,IFERROR(INDEX($B$8:$B$59,MATCH("41Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("41Y",$A$8:$A$59,0))),S62+(S72-S62)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R63=1,IFERROR(INDEX($C$8:$C$59,MATCH("41Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("41Y",$A$8:$A$59,0))),S62+(S72-S62)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T63">
@@ -5062,7 +5067,7 @@
         <v/>
       </c>
       <c r="S64" s="19">
-        <f>IFERROR(IF(R64=1,IFERROR(INDEX($B$8:$B$59,MATCH("42Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("42Y",$A$8:$A$59,0))),S62+(S72-S62)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R64=1,IFERROR(INDEX($C$8:$C$59,MATCH("42Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("42Y",$A$8:$A$59,0))),S62+(S72-S62)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T64">
@@ -5111,7 +5116,7 @@
         <v/>
       </c>
       <c r="S65" s="19">
-        <f>IFERROR(IF(R65=1,IFERROR(INDEX($B$8:$B$59,MATCH("43Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("43Y",$A$8:$A$59,0))),S62+(S72-S62)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R65=1,IFERROR(INDEX($C$8:$C$59,MATCH("43Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("43Y",$A$8:$A$59,0))),S62+(S72-S62)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T65">
@@ -5160,7 +5165,7 @@
         <v/>
       </c>
       <c r="S66" s="19">
-        <f>IFERROR(IF(R66=1,IFERROR(INDEX($B$8:$B$59,MATCH("44Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("44Y",$A$8:$A$59,0))),S62+(S72-S62)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R66=1,IFERROR(INDEX($C$8:$C$59,MATCH("44Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("44Y",$A$8:$A$59,0))),S62+(S72-S62)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T66">
@@ -5209,7 +5214,7 @@
         <v/>
       </c>
       <c r="S67" s="19">
-        <f>IFERROR(IF(R67=1,IFERROR(INDEX($B$8:$B$59,MATCH("45Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("45Y",$A$8:$A$59,0))),S62+(S72-S62)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R67=1,IFERROR(INDEX($C$8:$C$59,MATCH("45Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("45Y",$A$8:$A$59,0))),S62+(S72-S62)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T67">
@@ -5258,7 +5263,7 @@
         <v/>
       </c>
       <c r="S68" s="19">
-        <f>IFERROR(IF(R68=1,IFERROR(INDEX($B$8:$B$59,MATCH("46Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("46Y",$A$8:$A$59,0))),S62+(S72-S62)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R68=1,IFERROR(INDEX($C$8:$C$59,MATCH("46Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("46Y",$A$8:$A$59,0))),S62+(S72-S62)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T68">
@@ -5307,7 +5312,7 @@
         <v/>
       </c>
       <c r="S69" s="19">
-        <f>IFERROR(IF(R69=1,IFERROR(INDEX($B$8:$B$59,MATCH("47Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("47Y",$A$8:$A$59,0))),S62+(S72-S62)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R69=1,IFERROR(INDEX($C$8:$C$59,MATCH("47Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("47Y",$A$8:$A$59,0))),S62+(S72-S62)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T69">
@@ -5356,7 +5361,7 @@
         <v/>
       </c>
       <c r="S70" s="19">
-        <f>IFERROR(IF(R70=1,IFERROR(INDEX($B$8:$B$59,MATCH("48Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("48Y",$A$8:$A$59,0))),S62+(S72-S62)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R70=1,IFERROR(INDEX($C$8:$C$59,MATCH("48Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("48Y",$A$8:$A$59,0))),S62+(S72-S62)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T70">
@@ -5405,7 +5410,7 @@
         <v/>
       </c>
       <c r="S71" s="19">
-        <f>IFERROR(IF(R71=1,IFERROR(INDEX($B$8:$B$59,MATCH("49Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("49Y",$A$8:$A$59,0))),S62+(S72-S62)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R71=1,IFERROR(INDEX($C$8:$C$59,MATCH("49Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("49Y",$A$8:$A$59,0))),S62+(S72-S62)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T71">
@@ -5454,7 +5459,7 @@
         <v/>
       </c>
       <c r="S72" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$8:$B$59,MATCH("50Y",$A$8:$A$59,0)),INDEX($B$8:$B$59,MATCH("50Y",$A$8:$A$59,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("50Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("50Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
       <c r="U72" s="20">
@@ -5540,7 +5545,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Paste the yellow columns. Everything green is computed on this sheet — nothing here points at another sheet.</t>
+          <t>Paste YELLOW: tenor into A, then swap mid / BBG zero / BBG discount into C:E. Green is computed here — this sheet points at nothing outside itself.</t>
         </is>
       </c>
     </row>
@@ -5576,32 +5581,32 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
           <t>Swap rate (mid) %</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>BBG zero %</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>BBG discount</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>our DF</t>
+          <t>Our zero %</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>our zero %</t>
+          <t>Our discount</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -5682,27 +5687,27 @@
     </row>
     <row r="82">
       <c r="A82" s="9" t="n"/>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="10" t="n"/>
+      <c r="B82" s="10">
+        <f>IF($A82="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A82,$K$82:$K$146,0),MATCH(IF($A82="1Y","12M",IF($A82="12M","1Y",$A82)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C82" s="11" t="n"/>
       <c r="D82" s="11" t="n"/>
-      <c r="E82" s="12">
-        <f>IF($A82="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A82,$K$82:$K$146,0),MATCH(IF($A82="1Y","12M",IF($A82="12M","1Y",$A82)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E82" s="12" t="n"/>
       <c r="F82" s="13">
+        <f>IF(OR($A82="",G82=""),"",-LN(G82)/((B82-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G82" s="14">
         <f>IF($A82="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A82,$K$82:$K$146,0),MATCH(IF($A82="1Y","12M",IF($A82="12M","1Y",$A82)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G82" s="14">
-        <f>IF(OR($A82="",F82=""),"",-LN(F82)/((E82-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H82" s="15">
-        <f>IF(OR(G82="",NOT(ISNUMBER(C82))),"",(G82-C82)*100)</f>
+        <f>IF(OR(F82="",NOT(ISNUMBER(D82))),"",(F82-D82)*100)</f>
         <v/>
       </c>
       <c r="I82" s="16">
-        <f>IF(OR(F82="",NOT(ISNUMBER(D82))),"",F82-D82)</f>
+        <f>IF(OR(G82="",NOT(ISNUMBER(E82))),"",G82-E82)</f>
         <v/>
       </c>
       <c r="K82" s="17" t="inlineStr">
@@ -5737,7 +5742,7 @@
         <v/>
       </c>
       <c r="S82" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("1W",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("1W",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("1W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U82" s="20">
@@ -5751,27 +5756,27 @@
     </row>
     <row r="83">
       <c r="A83" s="9" t="n"/>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="10" t="n"/>
+      <c r="B83" s="10">
+        <f>IF($A83="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A83,$K$82:$K$146,0),MATCH(IF($A83="1Y","12M",IF($A83="12M","1Y",$A83)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C83" s="11" t="n"/>
       <c r="D83" s="11" t="n"/>
-      <c r="E83" s="12">
-        <f>IF($A83="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A83,$K$82:$K$146,0),MATCH(IF($A83="1Y","12M",IF($A83="12M","1Y",$A83)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E83" s="12" t="n"/>
       <c r="F83" s="13">
+        <f>IF(OR($A83="",G83=""),"",-LN(G83)/((B83-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G83" s="14">
         <f>IF($A83="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A83,$K$82:$K$146,0),MATCH(IF($A83="1Y","12M",IF($A83="12M","1Y",$A83)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G83" s="14">
-        <f>IF(OR($A83="",F83=""),"",-LN(F83)/((E83-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H83" s="15">
-        <f>IF(OR(G83="",NOT(ISNUMBER(C83))),"",(G83-C83)*100)</f>
+        <f>IF(OR(F83="",NOT(ISNUMBER(D83))),"",(F83-D83)*100)</f>
         <v/>
       </c>
       <c r="I83" s="16">
-        <f>IF(OR(F83="",NOT(ISNUMBER(D83))),"",F83-D83)</f>
+        <f>IF(OR(G83="",NOT(ISNUMBER(E83))),"",G83-E83)</f>
         <v/>
       </c>
       <c r="K83" s="17" t="inlineStr">
@@ -5806,7 +5811,7 @@
         <v/>
       </c>
       <c r="S83" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("2W",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("2W",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U83" s="20">
@@ -5820,27 +5825,27 @@
     </row>
     <row r="84">
       <c r="A84" s="9" t="n"/>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="10" t="n"/>
+      <c r="B84" s="10">
+        <f>IF($A84="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A84,$K$82:$K$146,0),MATCH(IF($A84="1Y","12M",IF($A84="12M","1Y",$A84)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C84" s="11" t="n"/>
       <c r="D84" s="11" t="n"/>
-      <c r="E84" s="12">
-        <f>IF($A84="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A84,$K$82:$K$146,0),MATCH(IF($A84="1Y","12M",IF($A84="12M","1Y",$A84)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E84" s="12" t="n"/>
       <c r="F84" s="13">
+        <f>IF(OR($A84="",G84=""),"",-LN(G84)/((B84-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G84" s="14">
         <f>IF($A84="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A84,$K$82:$K$146,0),MATCH(IF($A84="1Y","12M",IF($A84="12M","1Y",$A84)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G84" s="14">
-        <f>IF(OR($A84="",F84=""),"",-LN(F84)/((E84-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H84" s="15">
-        <f>IF(OR(G84="",NOT(ISNUMBER(C84))),"",(G84-C84)*100)</f>
+        <f>IF(OR(F84="",NOT(ISNUMBER(D84))),"",(F84-D84)*100)</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>IF(OR(F84="",NOT(ISNUMBER(D84))),"",F84-D84)</f>
+        <f>IF(OR(G84="",NOT(ISNUMBER(E84))),"",G84-E84)</f>
         <v/>
       </c>
       <c r="K84" s="17" t="inlineStr">
@@ -5875,7 +5880,7 @@
         <v/>
       </c>
       <c r="S84" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("3W",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("3W",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U84" s="20">
@@ -5889,27 +5894,27 @@
     </row>
     <row r="85">
       <c r="A85" s="9" t="n"/>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="10" t="n"/>
+      <c r="B85" s="10">
+        <f>IF($A85="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A85,$K$82:$K$146,0),MATCH(IF($A85="1Y","12M",IF($A85="12M","1Y",$A85)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C85" s="11" t="n"/>
       <c r="D85" s="11" t="n"/>
-      <c r="E85" s="12">
-        <f>IF($A85="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A85,$K$82:$K$146,0),MATCH(IF($A85="1Y","12M",IF($A85="12M","1Y",$A85)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E85" s="12" t="n"/>
       <c r="F85" s="13">
+        <f>IF(OR($A85="",G85=""),"",-LN(G85)/((B85-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G85" s="14">
         <f>IF($A85="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A85,$K$82:$K$146,0),MATCH(IF($A85="1Y","12M",IF($A85="12M","1Y",$A85)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G85" s="14">
-        <f>IF(OR($A85="",F85=""),"",-LN(F85)/((E85-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H85" s="15">
-        <f>IF(OR(G85="",NOT(ISNUMBER(C85))),"",(G85-C85)*100)</f>
+        <f>IF(OR(F85="",NOT(ISNUMBER(D85))),"",(F85-D85)*100)</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>IF(OR(F85="",NOT(ISNUMBER(D85))),"",F85-D85)</f>
+        <f>IF(OR(G85="",NOT(ISNUMBER(E85))),"",G85-E85)</f>
         <v/>
       </c>
       <c r="K85" s="17" t="inlineStr">
@@ -5944,7 +5949,7 @@
         <v/>
       </c>
       <c r="S85" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("1M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("1M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("1M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U85" s="20">
@@ -5958,27 +5963,27 @@
     </row>
     <row r="86">
       <c r="A86" s="9" t="n"/>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="10" t="n"/>
+      <c r="B86" s="10">
+        <f>IF($A86="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A86,$K$82:$K$146,0),MATCH(IF($A86="1Y","12M",IF($A86="12M","1Y",$A86)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C86" s="11" t="n"/>
       <c r="D86" s="11" t="n"/>
-      <c r="E86" s="12">
-        <f>IF($A86="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A86,$K$82:$K$146,0),MATCH(IF($A86="1Y","12M",IF($A86="12M","1Y",$A86)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E86" s="12" t="n"/>
       <c r="F86" s="13">
+        <f>IF(OR($A86="",G86=""),"",-LN(G86)/((B86-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G86" s="14">
         <f>IF($A86="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A86,$K$82:$K$146,0),MATCH(IF($A86="1Y","12M",IF($A86="12M","1Y",$A86)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G86" s="14">
-        <f>IF(OR($A86="",F86=""),"",-LN(F86)/((E86-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H86" s="15">
-        <f>IF(OR(G86="",NOT(ISNUMBER(C86))),"",(G86-C86)*100)</f>
+        <f>IF(OR(F86="",NOT(ISNUMBER(D86))),"",(F86-D86)*100)</f>
         <v/>
       </c>
       <c r="I86" s="16">
-        <f>IF(OR(F86="",NOT(ISNUMBER(D86))),"",F86-D86)</f>
+        <f>IF(OR(G86="",NOT(ISNUMBER(E86))),"",G86-E86)</f>
         <v/>
       </c>
       <c r="K86" s="17" t="inlineStr">
@@ -6013,7 +6018,7 @@
         <v/>
       </c>
       <c r="S86" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("2M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("2M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U86" s="20">
@@ -6027,27 +6032,27 @@
     </row>
     <row r="87">
       <c r="A87" s="9" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
+      <c r="B87" s="10">
+        <f>IF($A87="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A87,$K$82:$K$146,0),MATCH(IF($A87="1Y","12M",IF($A87="12M","1Y",$A87)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C87" s="11" t="n"/>
       <c r="D87" s="11" t="n"/>
-      <c r="E87" s="12">
-        <f>IF($A87="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A87,$K$82:$K$146,0),MATCH(IF($A87="1Y","12M",IF($A87="12M","1Y",$A87)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E87" s="12" t="n"/>
       <c r="F87" s="13">
+        <f>IF(OR($A87="",G87=""),"",-LN(G87)/((B87-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G87" s="14">
         <f>IF($A87="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A87,$K$82:$K$146,0),MATCH(IF($A87="1Y","12M",IF($A87="12M","1Y",$A87)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G87" s="14">
-        <f>IF(OR($A87="",F87=""),"",-LN(F87)/((E87-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H87" s="15">
-        <f>IF(OR(G87="",NOT(ISNUMBER(C87))),"",(G87-C87)*100)</f>
+        <f>IF(OR(F87="",NOT(ISNUMBER(D87))),"",(F87-D87)*100)</f>
         <v/>
       </c>
       <c r="I87" s="16">
-        <f>IF(OR(F87="",NOT(ISNUMBER(D87))),"",F87-D87)</f>
+        <f>IF(OR(G87="",NOT(ISNUMBER(E87))),"",G87-E87)</f>
         <v/>
       </c>
       <c r="K87" s="17" t="inlineStr">
@@ -6082,7 +6087,7 @@
         <v/>
       </c>
       <c r="S87" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("3M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("3M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U87" s="20">
@@ -6096,27 +6101,27 @@
     </row>
     <row r="88">
       <c r="A88" s="9" t="n"/>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
+      <c r="B88" s="10">
+        <f>IF($A88="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A88,$K$82:$K$146,0),MATCH(IF($A88="1Y","12M",IF($A88="12M","1Y",$A88)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C88" s="11" t="n"/>
       <c r="D88" s="11" t="n"/>
-      <c r="E88" s="12">
-        <f>IF($A88="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A88,$K$82:$K$146,0),MATCH(IF($A88="1Y","12M",IF($A88="12M","1Y",$A88)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E88" s="12" t="n"/>
       <c r="F88" s="13">
+        <f>IF(OR($A88="",G88=""),"",-LN(G88)/((B88-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G88" s="14">
         <f>IF($A88="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A88,$K$82:$K$146,0),MATCH(IF($A88="1Y","12M",IF($A88="12M","1Y",$A88)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G88" s="14">
-        <f>IF(OR($A88="",F88=""),"",-LN(F88)/((E88-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H88" s="15">
-        <f>IF(OR(G88="",NOT(ISNUMBER(C88))),"",(G88-C88)*100)</f>
+        <f>IF(OR(F88="",NOT(ISNUMBER(D88))),"",(F88-D88)*100)</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>IF(OR(F88="",NOT(ISNUMBER(D88))),"",F88-D88)</f>
+        <f>IF(OR(G88="",NOT(ISNUMBER(E88))),"",G88-E88)</f>
         <v/>
       </c>
       <c r="K88" s="17" t="inlineStr">
@@ -6151,7 +6156,7 @@
         <v/>
       </c>
       <c r="S88" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("4M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("4M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("4M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("4M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U88" s="20">
@@ -6165,27 +6170,27 @@
     </row>
     <row r="89">
       <c r="A89" s="9" t="n"/>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="10" t="n"/>
+      <c r="B89" s="10">
+        <f>IF($A89="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A89,$K$82:$K$146,0),MATCH(IF($A89="1Y","12M",IF($A89="12M","1Y",$A89)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C89" s="11" t="n"/>
       <c r="D89" s="11" t="n"/>
-      <c r="E89" s="12">
-        <f>IF($A89="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A89,$K$82:$K$146,0),MATCH(IF($A89="1Y","12M",IF($A89="12M","1Y",$A89)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E89" s="12" t="n"/>
       <c r="F89" s="13">
+        <f>IF(OR($A89="",G89=""),"",-LN(G89)/((B89-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G89" s="14">
         <f>IF($A89="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A89,$K$82:$K$146,0),MATCH(IF($A89="1Y","12M",IF($A89="12M","1Y",$A89)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G89" s="14">
-        <f>IF(OR($A89="",F89=""),"",-LN(F89)/((E89-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H89" s="15">
-        <f>IF(OR(G89="",NOT(ISNUMBER(C89))),"",(G89-C89)*100)</f>
+        <f>IF(OR(F89="",NOT(ISNUMBER(D89))),"",(F89-D89)*100)</f>
         <v/>
       </c>
       <c r="I89" s="16">
-        <f>IF(OR(F89="",NOT(ISNUMBER(D89))),"",F89-D89)</f>
+        <f>IF(OR(G89="",NOT(ISNUMBER(E89))),"",G89-E89)</f>
         <v/>
       </c>
       <c r="K89" s="17" t="inlineStr">
@@ -6220,7 +6225,7 @@
         <v/>
       </c>
       <c r="S89" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("5M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("5M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("5M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("5M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U89" s="20">
@@ -6234,27 +6239,27 @@
     </row>
     <row r="90">
       <c r="A90" s="9" t="n"/>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
+      <c r="B90" s="10">
+        <f>IF($A90="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A90,$K$82:$K$146,0),MATCH(IF($A90="1Y","12M",IF($A90="12M","1Y",$A90)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C90" s="11" t="n"/>
       <c r="D90" s="11" t="n"/>
-      <c r="E90" s="12">
-        <f>IF($A90="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A90,$K$82:$K$146,0),MATCH(IF($A90="1Y","12M",IF($A90="12M","1Y",$A90)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E90" s="12" t="n"/>
       <c r="F90" s="13">
+        <f>IF(OR($A90="",G90=""),"",-LN(G90)/((B90-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G90" s="14">
         <f>IF($A90="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A90,$K$82:$K$146,0),MATCH(IF($A90="1Y","12M",IF($A90="12M","1Y",$A90)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G90" s="14">
-        <f>IF(OR($A90="",F90=""),"",-LN(F90)/((E90-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H90" s="15">
-        <f>IF(OR(G90="",NOT(ISNUMBER(C90))),"",(G90-C90)*100)</f>
+        <f>IF(OR(F90="",NOT(ISNUMBER(D90))),"",(F90-D90)*100)</f>
         <v/>
       </c>
       <c r="I90" s="16">
-        <f>IF(OR(F90="",NOT(ISNUMBER(D90))),"",F90-D90)</f>
+        <f>IF(OR(G90="",NOT(ISNUMBER(E90))),"",G90-E90)</f>
         <v/>
       </c>
       <c r="K90" s="17" t="inlineStr">
@@ -6289,7 +6294,7 @@
         <v/>
       </c>
       <c r="S90" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("6M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("6M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("6M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("6M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U90" s="20">
@@ -6303,27 +6308,27 @@
     </row>
     <row r="91">
       <c r="A91" s="9" t="n"/>
-      <c r="B91" s="10" t="n"/>
-      <c r="C91" s="10" t="n"/>
+      <c r="B91" s="10">
+        <f>IF($A91="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A91,$K$82:$K$146,0),MATCH(IF($A91="1Y","12M",IF($A91="12M","1Y",$A91)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C91" s="11" t="n"/>
       <c r="D91" s="11" t="n"/>
-      <c r="E91" s="12">
-        <f>IF($A91="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A91,$K$82:$K$146,0),MATCH(IF($A91="1Y","12M",IF($A91="12M","1Y",$A91)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E91" s="12" t="n"/>
       <c r="F91" s="13">
+        <f>IF(OR($A91="",G91=""),"",-LN(G91)/((B91-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G91" s="14">
         <f>IF($A91="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A91,$K$82:$K$146,0),MATCH(IF($A91="1Y","12M",IF($A91="12M","1Y",$A91)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G91" s="14">
-        <f>IF(OR($A91="",F91=""),"",-LN(F91)/((E91-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H91" s="15">
-        <f>IF(OR(G91="",NOT(ISNUMBER(C91))),"",(G91-C91)*100)</f>
+        <f>IF(OR(F91="",NOT(ISNUMBER(D91))),"",(F91-D91)*100)</f>
         <v/>
       </c>
       <c r="I91" s="16">
-        <f>IF(OR(F91="",NOT(ISNUMBER(D91))),"",F91-D91)</f>
+        <f>IF(OR(G91="",NOT(ISNUMBER(E91))),"",G91-E91)</f>
         <v/>
       </c>
       <c r="K91" s="17" t="inlineStr">
@@ -6358,7 +6363,7 @@
         <v/>
       </c>
       <c r="S91" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("7M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("7M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("7M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("7M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U91" s="20">
@@ -6372,27 +6377,27 @@
     </row>
     <row r="92">
       <c r="A92" s="9" t="n"/>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
+      <c r="B92" s="10">
+        <f>IF($A92="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A92,$K$82:$K$146,0),MATCH(IF($A92="1Y","12M",IF($A92="12M","1Y",$A92)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C92" s="11" t="n"/>
       <c r="D92" s="11" t="n"/>
-      <c r="E92" s="12">
-        <f>IF($A92="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A92,$K$82:$K$146,0),MATCH(IF($A92="1Y","12M",IF($A92="12M","1Y",$A92)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E92" s="12" t="n"/>
       <c r="F92" s="13">
+        <f>IF(OR($A92="",G92=""),"",-LN(G92)/((B92-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G92" s="14">
         <f>IF($A92="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A92,$K$82:$K$146,0),MATCH(IF($A92="1Y","12M",IF($A92="12M","1Y",$A92)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G92" s="14">
-        <f>IF(OR($A92="",F92=""),"",-LN(F92)/((E92-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H92" s="15">
-        <f>IF(OR(G92="",NOT(ISNUMBER(C92))),"",(G92-C92)*100)</f>
+        <f>IF(OR(F92="",NOT(ISNUMBER(D92))),"",(F92-D92)*100)</f>
         <v/>
       </c>
       <c r="I92" s="16">
-        <f>IF(OR(F92="",NOT(ISNUMBER(D92))),"",F92-D92)</f>
+        <f>IF(OR(G92="",NOT(ISNUMBER(E92))),"",G92-E92)</f>
         <v/>
       </c>
       <c r="K92" s="17" t="inlineStr">
@@ -6427,7 +6432,7 @@
         <v/>
       </c>
       <c r="S92" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("8M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("8M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("8M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("8M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U92" s="20">
@@ -6441,27 +6446,27 @@
     </row>
     <row r="93">
       <c r="A93" s="9" t="n"/>
-      <c r="B93" s="10" t="n"/>
-      <c r="C93" s="10" t="n"/>
+      <c r="B93" s="10">
+        <f>IF($A93="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A93,$K$82:$K$146,0),MATCH(IF($A93="1Y","12M",IF($A93="12M","1Y",$A93)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C93" s="11" t="n"/>
       <c r="D93" s="11" t="n"/>
-      <c r="E93" s="12">
-        <f>IF($A93="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A93,$K$82:$K$146,0),MATCH(IF($A93="1Y","12M",IF($A93="12M","1Y",$A93)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E93" s="12" t="n"/>
       <c r="F93" s="13">
+        <f>IF(OR($A93="",G93=""),"",-LN(G93)/((B93-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G93" s="14">
         <f>IF($A93="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A93,$K$82:$K$146,0),MATCH(IF($A93="1Y","12M",IF($A93="12M","1Y",$A93)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G93" s="14">
-        <f>IF(OR($A93="",F93=""),"",-LN(F93)/((E93-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H93" s="15">
-        <f>IF(OR(G93="",NOT(ISNUMBER(C93))),"",(G93-C93)*100)</f>
+        <f>IF(OR(F93="",NOT(ISNUMBER(D93))),"",(F93-D93)*100)</f>
         <v/>
       </c>
       <c r="I93" s="16">
-        <f>IF(OR(F93="",NOT(ISNUMBER(D93))),"",F93-D93)</f>
+        <f>IF(OR(G93="",NOT(ISNUMBER(E93))),"",G93-E93)</f>
         <v/>
       </c>
       <c r="K93" s="17" t="inlineStr">
@@ -6496,7 +6501,7 @@
         <v/>
       </c>
       <c r="S93" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("9M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("9M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("9M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("9M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U93" s="20">
@@ -6510,27 +6515,27 @@
     </row>
     <row r="94">
       <c r="A94" s="9" t="n"/>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
+      <c r="B94" s="10">
+        <f>IF($A94="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A94,$K$82:$K$146,0),MATCH(IF($A94="1Y","12M",IF($A94="12M","1Y",$A94)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C94" s="11" t="n"/>
       <c r="D94" s="11" t="n"/>
-      <c r="E94" s="12">
-        <f>IF($A94="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A94,$K$82:$K$146,0),MATCH(IF($A94="1Y","12M",IF($A94="12M","1Y",$A94)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E94" s="12" t="n"/>
       <c r="F94" s="13">
+        <f>IF(OR($A94="",G94=""),"",-LN(G94)/((B94-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G94" s="14">
         <f>IF($A94="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A94,$K$82:$K$146,0),MATCH(IF($A94="1Y","12M",IF($A94="12M","1Y",$A94)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G94" s="14">
-        <f>IF(OR($A94="",F94=""),"",-LN(F94)/((E94-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H94" s="15">
-        <f>IF(OR(G94="",NOT(ISNUMBER(C94))),"",(G94-C94)*100)</f>
+        <f>IF(OR(F94="",NOT(ISNUMBER(D94))),"",(F94-D94)*100)</f>
         <v/>
       </c>
       <c r="I94" s="16">
-        <f>IF(OR(F94="",NOT(ISNUMBER(D94))),"",F94-D94)</f>
+        <f>IF(OR(G94="",NOT(ISNUMBER(E94))),"",G94-E94)</f>
         <v/>
       </c>
       <c r="K94" s="17" t="inlineStr">
@@ -6565,7 +6570,7 @@
         <v/>
       </c>
       <c r="S94" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("10M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("10M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("10M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("10M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U94" s="20">
@@ -6579,27 +6584,27 @@
     </row>
     <row r="95">
       <c r="A95" s="9" t="n"/>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="10" t="n"/>
+      <c r="B95" s="10">
+        <f>IF($A95="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A95,$K$82:$K$146,0),MATCH(IF($A95="1Y","12M",IF($A95="12M","1Y",$A95)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C95" s="11" t="n"/>
       <c r="D95" s="11" t="n"/>
-      <c r="E95" s="12">
-        <f>IF($A95="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A95,$K$82:$K$146,0),MATCH(IF($A95="1Y","12M",IF($A95="12M","1Y",$A95)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E95" s="12" t="n"/>
       <c r="F95" s="13">
+        <f>IF(OR($A95="",G95=""),"",-LN(G95)/((B95-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G95" s="14">
         <f>IF($A95="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A95,$K$82:$K$146,0),MATCH(IF($A95="1Y","12M",IF($A95="12M","1Y",$A95)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G95" s="14">
-        <f>IF(OR($A95="",F95=""),"",-LN(F95)/((E95-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H95" s="15">
-        <f>IF(OR(G95="",NOT(ISNUMBER(C95))),"",(G95-C95)*100)</f>
+        <f>IF(OR(F95="",NOT(ISNUMBER(D95))),"",(F95-D95)*100)</f>
         <v/>
       </c>
       <c r="I95" s="16">
-        <f>IF(OR(F95="",NOT(ISNUMBER(D95))),"",F95-D95)</f>
+        <f>IF(OR(G95="",NOT(ISNUMBER(E95))),"",G95-E95)</f>
         <v/>
       </c>
       <c r="K95" s="17" t="inlineStr">
@@ -6634,7 +6639,7 @@
         <v/>
       </c>
       <c r="S95" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("11M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("11M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("11M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("11M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U95" s="20">
@@ -6648,27 +6653,27 @@
     </row>
     <row r="96">
       <c r="A96" s="9" t="n"/>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="10" t="n"/>
+      <c r="B96" s="10">
+        <f>IF($A96="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A96,$K$82:$K$146,0),MATCH(IF($A96="1Y","12M",IF($A96="12M","1Y",$A96)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C96" s="11" t="n"/>
       <c r="D96" s="11" t="n"/>
-      <c r="E96" s="12">
-        <f>IF($A96="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A96,$K$82:$K$146,0),MATCH(IF($A96="1Y","12M",IF($A96="12M","1Y",$A96)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E96" s="12" t="n"/>
       <c r="F96" s="13">
+        <f>IF(OR($A96="",G96=""),"",-LN(G96)/((B96-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G96" s="14">
         <f>IF($A96="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A96,$K$82:$K$146,0),MATCH(IF($A96="1Y","12M",IF($A96="12M","1Y",$A96)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G96" s="14">
-        <f>IF(OR($A96="",F96=""),"",-LN(F96)/((E96-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H96" s="15">
-        <f>IF(OR(G96="",NOT(ISNUMBER(C96))),"",(G96-C96)*100)</f>
+        <f>IF(OR(F96="",NOT(ISNUMBER(D96))),"",(F96-D96)*100)</f>
         <v/>
       </c>
       <c r="I96" s="16">
-        <f>IF(OR(F96="",NOT(ISNUMBER(D96))),"",F96-D96)</f>
+        <f>IF(OR(G96="",NOT(ISNUMBER(E96))),"",G96-E96)</f>
         <v/>
       </c>
       <c r="K96" s="17" t="inlineStr">
@@ -6703,7 +6708,7 @@
         <v/>
       </c>
       <c r="S96" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("12M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("1Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("12M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U96" s="20">
@@ -6717,27 +6722,27 @@
     </row>
     <row r="97">
       <c r="A97" s="9" t="n"/>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="10" t="n"/>
+      <c r="B97" s="10">
+        <f>IF($A97="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A97,$K$82:$K$146,0),MATCH(IF($A97="1Y","12M",IF($A97="12M","1Y",$A97)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C97" s="11" t="n"/>
       <c r="D97" s="11" t="n"/>
-      <c r="E97" s="12">
-        <f>IF($A97="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A97,$K$82:$K$146,0),MATCH(IF($A97="1Y","12M",IF($A97="12M","1Y",$A97)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E97" s="12" t="n"/>
       <c r="F97" s="13">
+        <f>IF(OR($A97="",G97=""),"",-LN(G97)/((B97-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G97" s="14">
         <f>IF($A97="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A97,$K$82:$K$146,0),MATCH(IF($A97="1Y","12M",IF($A97="12M","1Y",$A97)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G97" s="14">
-        <f>IF(OR($A97="",F97=""),"",-LN(F97)/((E97-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H97" s="15">
-        <f>IF(OR(G97="",NOT(ISNUMBER(C97))),"",(G97-C97)*100)</f>
+        <f>IF(OR(F97="",NOT(ISNUMBER(D97))),"",(F97-D97)*100)</f>
         <v/>
       </c>
       <c r="I97" s="16">
-        <f>IF(OR(F97="",NOT(ISNUMBER(D97))),"",F97-D97)</f>
+        <f>IF(OR(G97="",NOT(ISNUMBER(E97))),"",G97-E97)</f>
         <v/>
       </c>
       <c r="K97" s="17" t="inlineStr">
@@ -6772,7 +6777,7 @@
         <v/>
       </c>
       <c r="S97" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("18M",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("18M",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("18M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("18M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U97" s="20">
@@ -6786,27 +6791,27 @@
     </row>
     <row r="98">
       <c r="A98" s="9" t="n"/>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="10" t="n"/>
+      <c r="B98" s="10">
+        <f>IF($A98="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A98,$K$82:$K$146,0),MATCH(IF($A98="1Y","12M",IF($A98="12M","1Y",$A98)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C98" s="11" t="n"/>
       <c r="D98" s="11" t="n"/>
-      <c r="E98" s="12">
-        <f>IF($A98="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A98,$K$82:$K$146,0),MATCH(IF($A98="1Y","12M",IF($A98="12M","1Y",$A98)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E98" s="12" t="n"/>
       <c r="F98" s="13">
+        <f>IF(OR($A98="",G98=""),"",-LN(G98)/((B98-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G98" s="14">
         <f>IF($A98="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A98,$K$82:$K$146,0),MATCH(IF($A98="1Y","12M",IF($A98="12M","1Y",$A98)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G98" s="14">
-        <f>IF(OR($A98="",F98=""),"",-LN(F98)/((E98-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H98" s="15">
-        <f>IF(OR(G98="",NOT(ISNUMBER(C98))),"",(G98-C98)*100)</f>
+        <f>IF(OR(F98="",NOT(ISNUMBER(D98))),"",(F98-D98)*100)</f>
         <v/>
       </c>
       <c r="I98" s="16">
-        <f>IF(OR(F98="",NOT(ISNUMBER(D98))),"",F98-D98)</f>
+        <f>IF(OR(G98="",NOT(ISNUMBER(E98))),"",G98-E98)</f>
         <v/>
       </c>
       <c r="K98" s="17" t="inlineStr">
@@ -6841,7 +6846,7 @@
         <v/>
       </c>
       <c r="S98" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("2Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("2Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U98" s="20">
@@ -6855,27 +6860,27 @@
     </row>
     <row r="99">
       <c r="A99" s="9" t="n"/>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="10" t="n"/>
+      <c r="B99" s="10">
+        <f>IF($A99="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A99,$K$82:$K$146,0),MATCH(IF($A99="1Y","12M",IF($A99="12M","1Y",$A99)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C99" s="11" t="n"/>
       <c r="D99" s="11" t="n"/>
-      <c r="E99" s="12">
-        <f>IF($A99="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A99,$K$82:$K$146,0),MATCH(IF($A99="1Y","12M",IF($A99="12M","1Y",$A99)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E99" s="12" t="n"/>
       <c r="F99" s="13">
+        <f>IF(OR($A99="",G99=""),"",-LN(G99)/((B99-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G99" s="14">
         <f>IF($A99="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A99,$K$82:$K$146,0),MATCH(IF($A99="1Y","12M",IF($A99="12M","1Y",$A99)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G99" s="14">
-        <f>IF(OR($A99="",F99=""),"",-LN(F99)/((E99-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H99" s="15">
-        <f>IF(OR(G99="",NOT(ISNUMBER(C99))),"",(G99-C99)*100)</f>
+        <f>IF(OR(F99="",NOT(ISNUMBER(D99))),"",(F99-D99)*100)</f>
         <v/>
       </c>
       <c r="I99" s="16">
-        <f>IF(OR(F99="",NOT(ISNUMBER(D99))),"",F99-D99)</f>
+        <f>IF(OR(G99="",NOT(ISNUMBER(E99))),"",G99-E99)</f>
         <v/>
       </c>
       <c r="K99" s="17" t="inlineStr">
@@ -6910,7 +6915,7 @@
         <v/>
       </c>
       <c r="S99" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("3Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("3Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U99" s="20">
@@ -6924,27 +6929,27 @@
     </row>
     <row r="100">
       <c r="A100" s="9" t="n"/>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
+      <c r="B100" s="10">
+        <f>IF($A100="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A100,$K$82:$K$146,0),MATCH(IF($A100="1Y","12M",IF($A100="12M","1Y",$A100)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C100" s="11" t="n"/>
       <c r="D100" s="11" t="n"/>
-      <c r="E100" s="12">
-        <f>IF($A100="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A100,$K$82:$K$146,0),MATCH(IF($A100="1Y","12M",IF($A100="12M","1Y",$A100)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E100" s="12" t="n"/>
       <c r="F100" s="13">
+        <f>IF(OR($A100="",G100=""),"",-LN(G100)/((B100-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G100" s="14">
         <f>IF($A100="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A100,$K$82:$K$146,0),MATCH(IF($A100="1Y","12M",IF($A100="12M","1Y",$A100)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G100" s="14">
-        <f>IF(OR($A100="",F100=""),"",-LN(F100)/((E100-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H100" s="15">
-        <f>IF(OR(G100="",NOT(ISNUMBER(C100))),"",(G100-C100)*100)</f>
+        <f>IF(OR(F100="",NOT(ISNUMBER(D100))),"",(F100-D100)*100)</f>
         <v/>
       </c>
       <c r="I100" s="16">
-        <f>IF(OR(F100="",NOT(ISNUMBER(D100))),"",F100-D100)</f>
+        <f>IF(OR(G100="",NOT(ISNUMBER(E100))),"",G100-E100)</f>
         <v/>
       </c>
       <c r="K100" s="17" t="inlineStr">
@@ -6979,7 +6984,7 @@
         <v/>
       </c>
       <c r="S100" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("4Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("4Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("4Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("4Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U100" s="20">
@@ -6993,27 +6998,27 @@
     </row>
     <row r="101">
       <c r="A101" s="9" t="n"/>
-      <c r="B101" s="10" t="n"/>
-      <c r="C101" s="10" t="n"/>
+      <c r="B101" s="10">
+        <f>IF($A101="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A101,$K$82:$K$146,0),MATCH(IF($A101="1Y","12M",IF($A101="12M","1Y",$A101)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C101" s="11" t="n"/>
       <c r="D101" s="11" t="n"/>
-      <c r="E101" s="12">
-        <f>IF($A101="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A101,$K$82:$K$146,0),MATCH(IF($A101="1Y","12M",IF($A101="12M","1Y",$A101)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E101" s="12" t="n"/>
       <c r="F101" s="13">
+        <f>IF(OR($A101="",G101=""),"",-LN(G101)/((B101-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G101" s="14">
         <f>IF($A101="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A101,$K$82:$K$146,0),MATCH(IF($A101="1Y","12M",IF($A101="12M","1Y",$A101)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G101" s="14">
-        <f>IF(OR($A101="",F101=""),"",-LN(F101)/((E101-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H101" s="15">
-        <f>IF(OR(G101="",NOT(ISNUMBER(C101))),"",(G101-C101)*100)</f>
+        <f>IF(OR(F101="",NOT(ISNUMBER(D101))),"",(F101-D101)*100)</f>
         <v/>
       </c>
       <c r="I101" s="16">
-        <f>IF(OR(F101="",NOT(ISNUMBER(D101))),"",F101-D101)</f>
+        <f>IF(OR(G101="",NOT(ISNUMBER(E101))),"",G101-E101)</f>
         <v/>
       </c>
       <c r="K101" s="17" t="inlineStr">
@@ -7048,7 +7053,7 @@
         <v/>
       </c>
       <c r="S101" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("5Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("5Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("5Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("5Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U101" s="20">
@@ -7062,27 +7067,27 @@
     </row>
     <row r="102">
       <c r="A102" s="9" t="n"/>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="10" t="n"/>
+      <c r="B102" s="10">
+        <f>IF($A102="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A102,$K$82:$K$146,0),MATCH(IF($A102="1Y","12M",IF($A102="12M","1Y",$A102)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C102" s="11" t="n"/>
       <c r="D102" s="11" t="n"/>
-      <c r="E102" s="12">
-        <f>IF($A102="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A102,$K$82:$K$146,0),MATCH(IF($A102="1Y","12M",IF($A102="12M","1Y",$A102)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E102" s="12" t="n"/>
       <c r="F102" s="13">
+        <f>IF(OR($A102="",G102=""),"",-LN(G102)/((B102-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G102" s="14">
         <f>IF($A102="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A102,$K$82:$K$146,0),MATCH(IF($A102="1Y","12M",IF($A102="12M","1Y",$A102)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G102" s="14">
-        <f>IF(OR($A102="",F102=""),"",-LN(F102)/((E102-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H102" s="15">
-        <f>IF(OR(G102="",NOT(ISNUMBER(C102))),"",(G102-C102)*100)</f>
+        <f>IF(OR(F102="",NOT(ISNUMBER(D102))),"",(F102-D102)*100)</f>
         <v/>
       </c>
       <c r="I102" s="16">
-        <f>IF(OR(F102="",NOT(ISNUMBER(D102))),"",F102-D102)</f>
+        <f>IF(OR(G102="",NOT(ISNUMBER(E102))),"",G102-E102)</f>
         <v/>
       </c>
       <c r="K102" s="17" t="inlineStr">
@@ -7117,7 +7122,7 @@
         <v/>
       </c>
       <c r="S102" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("6Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("6Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("6Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("6Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U102" s="20">
@@ -7131,27 +7136,27 @@
     </row>
     <row r="103">
       <c r="A103" s="9" t="n"/>
-      <c r="B103" s="10" t="n"/>
-      <c r="C103" s="10" t="n"/>
+      <c r="B103" s="10">
+        <f>IF($A103="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A103,$K$82:$K$146,0),MATCH(IF($A103="1Y","12M",IF($A103="12M","1Y",$A103)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C103" s="11" t="n"/>
       <c r="D103" s="11" t="n"/>
-      <c r="E103" s="12">
-        <f>IF($A103="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A103,$K$82:$K$146,0),MATCH(IF($A103="1Y","12M",IF($A103="12M","1Y",$A103)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E103" s="12" t="n"/>
       <c r="F103" s="13">
+        <f>IF(OR($A103="",G103=""),"",-LN(G103)/((B103-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G103" s="14">
         <f>IF($A103="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A103,$K$82:$K$146,0),MATCH(IF($A103="1Y","12M",IF($A103="12M","1Y",$A103)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G103" s="14">
-        <f>IF(OR($A103="",F103=""),"",-LN(F103)/((E103-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H103" s="15">
-        <f>IF(OR(G103="",NOT(ISNUMBER(C103))),"",(G103-C103)*100)</f>
+        <f>IF(OR(F103="",NOT(ISNUMBER(D103))),"",(F103-D103)*100)</f>
         <v/>
       </c>
       <c r="I103" s="16">
-        <f>IF(OR(F103="",NOT(ISNUMBER(D103))),"",F103-D103)</f>
+        <f>IF(OR(G103="",NOT(ISNUMBER(E103))),"",G103-E103)</f>
         <v/>
       </c>
       <c r="K103" s="17" t="inlineStr">
@@ -7186,7 +7191,7 @@
         <v/>
       </c>
       <c r="S103" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("7Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("7Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("7Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("7Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U103" s="20">
@@ -7200,27 +7205,27 @@
     </row>
     <row r="104">
       <c r="A104" s="9" t="n"/>
-      <c r="B104" s="10" t="n"/>
-      <c r="C104" s="10" t="n"/>
+      <c r="B104" s="10">
+        <f>IF($A104="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A104,$K$82:$K$146,0),MATCH(IF($A104="1Y","12M",IF($A104="12M","1Y",$A104)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C104" s="11" t="n"/>
       <c r="D104" s="11" t="n"/>
-      <c r="E104" s="12">
-        <f>IF($A104="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A104,$K$82:$K$146,0),MATCH(IF($A104="1Y","12M",IF($A104="12M","1Y",$A104)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E104" s="12" t="n"/>
       <c r="F104" s="13">
+        <f>IF(OR($A104="",G104=""),"",-LN(G104)/((B104-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G104" s="14">
         <f>IF($A104="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A104,$K$82:$K$146,0),MATCH(IF($A104="1Y","12M",IF($A104="12M","1Y",$A104)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G104" s="14">
-        <f>IF(OR($A104="",F104=""),"",-LN(F104)/((E104-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H104" s="15">
-        <f>IF(OR(G104="",NOT(ISNUMBER(C104))),"",(G104-C104)*100)</f>
+        <f>IF(OR(F104="",NOT(ISNUMBER(D104))),"",(F104-D104)*100)</f>
         <v/>
       </c>
       <c r="I104" s="16">
-        <f>IF(OR(F104="",NOT(ISNUMBER(D104))),"",F104-D104)</f>
+        <f>IF(OR(G104="",NOT(ISNUMBER(E104))),"",G104-E104)</f>
         <v/>
       </c>
       <c r="K104" s="17" t="inlineStr">
@@ -7255,7 +7260,7 @@
         <v/>
       </c>
       <c r="S104" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("8Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("8Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("8Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("8Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U104" s="20">
@@ -7269,27 +7274,27 @@
     </row>
     <row r="105">
       <c r="A105" s="9" t="n"/>
-      <c r="B105" s="10" t="n"/>
-      <c r="C105" s="10" t="n"/>
+      <c r="B105" s="10">
+        <f>IF($A105="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A105,$K$82:$K$146,0),MATCH(IF($A105="1Y","12M",IF($A105="12M","1Y",$A105)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C105" s="11" t="n"/>
       <c r="D105" s="11" t="n"/>
-      <c r="E105" s="12">
-        <f>IF($A105="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A105,$K$82:$K$146,0),MATCH(IF($A105="1Y","12M",IF($A105="12M","1Y",$A105)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E105" s="12" t="n"/>
       <c r="F105" s="13">
+        <f>IF(OR($A105="",G105=""),"",-LN(G105)/((B105-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G105" s="14">
         <f>IF($A105="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A105,$K$82:$K$146,0),MATCH(IF($A105="1Y","12M",IF($A105="12M","1Y",$A105)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G105" s="14">
-        <f>IF(OR($A105="",F105=""),"",-LN(F105)/((E105-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H105" s="15">
-        <f>IF(OR(G105="",NOT(ISNUMBER(C105))),"",(G105-C105)*100)</f>
+        <f>IF(OR(F105="",NOT(ISNUMBER(D105))),"",(F105-D105)*100)</f>
         <v/>
       </c>
       <c r="I105" s="16">
-        <f>IF(OR(F105="",NOT(ISNUMBER(D105))),"",F105-D105)</f>
+        <f>IF(OR(G105="",NOT(ISNUMBER(E105))),"",G105-E105)</f>
         <v/>
       </c>
       <c r="K105" s="17" t="inlineStr">
@@ -7324,7 +7329,7 @@
         <v/>
       </c>
       <c r="S105" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("9Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("9Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("9Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("9Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U105" s="20">
@@ -7338,27 +7343,27 @@
     </row>
     <row r="106">
       <c r="A106" s="9" t="n"/>
-      <c r="B106" s="10" t="n"/>
-      <c r="C106" s="10" t="n"/>
+      <c r="B106" s="10">
+        <f>IF($A106="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A106,$K$82:$K$146,0),MATCH(IF($A106="1Y","12M",IF($A106="12M","1Y",$A106)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C106" s="11" t="n"/>
       <c r="D106" s="11" t="n"/>
-      <c r="E106" s="12">
-        <f>IF($A106="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A106,$K$82:$K$146,0),MATCH(IF($A106="1Y","12M",IF($A106="12M","1Y",$A106)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E106" s="12" t="n"/>
       <c r="F106" s="13">
+        <f>IF(OR($A106="",G106=""),"",-LN(G106)/((B106-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G106" s="14">
         <f>IF($A106="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A106,$K$82:$K$146,0),MATCH(IF($A106="1Y","12M",IF($A106="12M","1Y",$A106)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G106" s="14">
-        <f>IF(OR($A106="",F106=""),"",-LN(F106)/((E106-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H106" s="15">
-        <f>IF(OR(G106="",NOT(ISNUMBER(C106))),"",(G106-C106)*100)</f>
+        <f>IF(OR(F106="",NOT(ISNUMBER(D106))),"",(F106-D106)*100)</f>
         <v/>
       </c>
       <c r="I106" s="16">
-        <f>IF(OR(F106="",NOT(ISNUMBER(D106))),"",F106-D106)</f>
+        <f>IF(OR(G106="",NOT(ISNUMBER(E106))),"",G106-E106)</f>
         <v/>
       </c>
       <c r="K106" s="17" t="inlineStr">
@@ -7393,7 +7398,7 @@
         <v/>
       </c>
       <c r="S106" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("10Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("10Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("10Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("10Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U106" s="20">
@@ -7407,27 +7412,27 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n"/>
-      <c r="B107" s="10" t="n"/>
-      <c r="C107" s="10" t="n"/>
+      <c r="B107" s="10">
+        <f>IF($A107="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A107,$K$82:$K$146,0),MATCH(IF($A107="1Y","12M",IF($A107="12M","1Y",$A107)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C107" s="11" t="n"/>
       <c r="D107" s="11" t="n"/>
-      <c r="E107" s="12">
-        <f>IF($A107="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A107,$K$82:$K$146,0),MATCH(IF($A107="1Y","12M",IF($A107="12M","1Y",$A107)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E107" s="12" t="n"/>
       <c r="F107" s="13">
+        <f>IF(OR($A107="",G107=""),"",-LN(G107)/((B107-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G107" s="14">
         <f>IF($A107="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A107,$K$82:$K$146,0),MATCH(IF($A107="1Y","12M",IF($A107="12M","1Y",$A107)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G107" s="14">
-        <f>IF(OR($A107="",F107=""),"",-LN(F107)/((E107-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H107" s="15">
-        <f>IF(OR(G107="",NOT(ISNUMBER(C107))),"",(G107-C107)*100)</f>
+        <f>IF(OR(F107="",NOT(ISNUMBER(D107))),"",(F107-D107)*100)</f>
         <v/>
       </c>
       <c r="I107" s="16">
-        <f>IF(OR(F107="",NOT(ISNUMBER(D107))),"",F107-D107)</f>
+        <f>IF(OR(G107="",NOT(ISNUMBER(E107))),"",G107-E107)</f>
         <v/>
       </c>
       <c r="K107" s="17" t="inlineStr">
@@ -7462,7 +7467,7 @@
         <v/>
       </c>
       <c r="S107" s="19">
-        <f>IFERROR(IF(R107=1,IFERROR(INDEX($B$82:$B$133,MATCH("11Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("11Y",$A$82:$A$133,0))),S106+(S108-S106)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R107=1,IFERROR(INDEX($C$82:$C$133,MATCH("11Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("11Y",$A$82:$A$133,0))),S106+(S108-S106)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T107">
@@ -7480,27 +7485,27 @@
     </row>
     <row r="108">
       <c r="A108" s="9" t="n"/>
-      <c r="B108" s="10" t="n"/>
-      <c r="C108" s="10" t="n"/>
+      <c r="B108" s="10">
+        <f>IF($A108="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A108,$K$82:$K$146,0),MATCH(IF($A108="1Y","12M",IF($A108="12M","1Y",$A108)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C108" s="11" t="n"/>
       <c r="D108" s="11" t="n"/>
-      <c r="E108" s="12">
-        <f>IF($A108="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A108,$K$82:$K$146,0),MATCH(IF($A108="1Y","12M",IF($A108="12M","1Y",$A108)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E108" s="12" t="n"/>
       <c r="F108" s="13">
+        <f>IF(OR($A108="",G108=""),"",-LN(G108)/((B108-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G108" s="14">
         <f>IF($A108="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A108,$K$82:$K$146,0),MATCH(IF($A108="1Y","12M",IF($A108="12M","1Y",$A108)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G108" s="14">
-        <f>IF(OR($A108="",F108=""),"",-LN(F108)/((E108-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H108" s="15">
-        <f>IF(OR(G108="",NOT(ISNUMBER(C108))),"",(G108-C108)*100)</f>
+        <f>IF(OR(F108="",NOT(ISNUMBER(D108))),"",(F108-D108)*100)</f>
         <v/>
       </c>
       <c r="I108" s="16">
-        <f>IF(OR(F108="",NOT(ISNUMBER(D108))),"",F108-D108)</f>
+        <f>IF(OR(G108="",NOT(ISNUMBER(E108))),"",G108-E108)</f>
         <v/>
       </c>
       <c r="K108" s="17" t="inlineStr">
@@ -7535,7 +7540,7 @@
         <v/>
       </c>
       <c r="S108" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("12Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("12Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("12Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("12Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U108" s="20">
@@ -7613,27 +7618,27 @@
     </row>
     <row r="109">
       <c r="A109" s="9" t="n"/>
-      <c r="B109" s="10" t="n"/>
-      <c r="C109" s="10" t="n"/>
+      <c r="B109" s="10">
+        <f>IF($A109="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A109,$K$82:$K$146,0),MATCH(IF($A109="1Y","12M",IF($A109="12M","1Y",$A109)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C109" s="11" t="n"/>
       <c r="D109" s="11" t="n"/>
-      <c r="E109" s="12">
-        <f>IF($A109="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A109,$K$82:$K$146,0),MATCH(IF($A109="1Y","12M",IF($A109="12M","1Y",$A109)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E109" s="12" t="n"/>
       <c r="F109" s="13">
+        <f>IF(OR($A109="",G109=""),"",-LN(G109)/((B109-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G109" s="14">
         <f>IF($A109="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A109,$K$82:$K$146,0),MATCH(IF($A109="1Y","12M",IF($A109="12M","1Y",$A109)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G109" s="14">
-        <f>IF(OR($A109="",F109=""),"",-LN(F109)/((E109-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H109" s="15">
-        <f>IF(OR(G109="",NOT(ISNUMBER(C109))),"",(G109-C109)*100)</f>
+        <f>IF(OR(F109="",NOT(ISNUMBER(D109))),"",(F109-D109)*100)</f>
         <v/>
       </c>
       <c r="I109" s="16">
-        <f>IF(OR(F109="",NOT(ISNUMBER(D109))),"",F109-D109)</f>
+        <f>IF(OR(G109="",NOT(ISNUMBER(E109))),"",G109-E109)</f>
         <v/>
       </c>
       <c r="K109" s="17" t="inlineStr">
@@ -7668,7 +7673,7 @@
         <v/>
       </c>
       <c r="S109" s="19">
-        <f>IFERROR(IF(R109=1,IFERROR(INDEX($B$82:$B$133,MATCH("13Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("13Y",$A$82:$A$133,0))),S108+(S111-S108)*0.3333333333),"")</f>
+        <f>IFERROR(IF(R109=1,IFERROR(INDEX($C$82:$C$133,MATCH("13Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("13Y",$A$82:$A$133,0))),S108+(S111-S108)*0.3333333333),"")</f>
         <v/>
       </c>
       <c r="T109">
@@ -7686,27 +7691,27 @@
     </row>
     <row r="110">
       <c r="A110" s="9" t="n"/>
-      <c r="B110" s="10" t="n"/>
-      <c r="C110" s="10" t="n"/>
+      <c r="B110" s="10">
+        <f>IF($A110="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A110,$K$82:$K$146,0),MATCH(IF($A110="1Y","12M",IF($A110="12M","1Y",$A110)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C110" s="11" t="n"/>
       <c r="D110" s="11" t="n"/>
-      <c r="E110" s="12">
-        <f>IF($A110="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A110,$K$82:$K$146,0),MATCH(IF($A110="1Y","12M",IF($A110="12M","1Y",$A110)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E110" s="12" t="n"/>
       <c r="F110" s="13">
+        <f>IF(OR($A110="",G110=""),"",-LN(G110)/((B110-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G110" s="14">
         <f>IF($A110="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A110,$K$82:$K$146,0),MATCH(IF($A110="1Y","12M",IF($A110="12M","1Y",$A110)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G110" s="14">
-        <f>IF(OR($A110="",F110=""),"",-LN(F110)/((E110-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H110" s="15">
-        <f>IF(OR(G110="",NOT(ISNUMBER(C110))),"",(G110-C110)*100)</f>
+        <f>IF(OR(F110="",NOT(ISNUMBER(D110))),"",(F110-D110)*100)</f>
         <v/>
       </c>
       <c r="I110" s="16">
-        <f>IF(OR(F110="",NOT(ISNUMBER(D110))),"",F110-D110)</f>
+        <f>IF(OR(G110="",NOT(ISNUMBER(E110))),"",G110-E110)</f>
         <v/>
       </c>
       <c r="K110" s="17" t="inlineStr">
@@ -7741,7 +7746,7 @@
         <v/>
       </c>
       <c r="S110" s="19">
-        <f>IFERROR(IF(R110=1,IFERROR(INDEX($B$82:$B$133,MATCH("14Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("14Y",$A$82:$A$133,0))),S108+(S111-S108)*0.6666666667),"")</f>
+        <f>IFERROR(IF(R110=1,IFERROR(INDEX($C$82:$C$133,MATCH("14Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("14Y",$A$82:$A$133,0))),S108+(S111-S108)*0.6666666667),"")</f>
         <v/>
       </c>
       <c r="T110">
@@ -7759,27 +7764,27 @@
     </row>
     <row r="111">
       <c r="A111" s="9" t="n"/>
-      <c r="B111" s="10" t="n"/>
-      <c r="C111" s="10" t="n"/>
+      <c r="B111" s="10">
+        <f>IF($A111="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A111,$K$82:$K$146,0),MATCH(IF($A111="1Y","12M",IF($A111="12M","1Y",$A111)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C111" s="11" t="n"/>
       <c r="D111" s="11" t="n"/>
-      <c r="E111" s="12">
-        <f>IF($A111="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A111,$K$82:$K$146,0),MATCH(IF($A111="1Y","12M",IF($A111="12M","1Y",$A111)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E111" s="12" t="n"/>
       <c r="F111" s="13">
+        <f>IF(OR($A111="",G111=""),"",-LN(G111)/((B111-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G111" s="14">
         <f>IF($A111="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A111,$K$82:$K$146,0),MATCH(IF($A111="1Y","12M",IF($A111="12M","1Y",$A111)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G111" s="14">
-        <f>IF(OR($A111="",F111=""),"",-LN(F111)/((E111-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H111" s="15">
-        <f>IF(OR(G111="",NOT(ISNUMBER(C111))),"",(G111-C111)*100)</f>
+        <f>IF(OR(F111="",NOT(ISNUMBER(D111))),"",(F111-D111)*100)</f>
         <v/>
       </c>
       <c r="I111" s="16">
-        <f>IF(OR(F111="",NOT(ISNUMBER(D111))),"",F111-D111)</f>
+        <f>IF(OR(G111="",NOT(ISNUMBER(E111))),"",G111-E111)</f>
         <v/>
       </c>
       <c r="K111" s="17" t="inlineStr">
@@ -7814,7 +7819,7 @@
         <v/>
       </c>
       <c r="S111" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("15Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("15Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("15Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("15Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U111" s="20">
@@ -7892,27 +7897,27 @@
     </row>
     <row r="112">
       <c r="A112" s="9" t="n"/>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
+      <c r="B112" s="10">
+        <f>IF($A112="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A112,$K$82:$K$146,0),MATCH(IF($A112="1Y","12M",IF($A112="12M","1Y",$A112)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C112" s="11" t="n"/>
       <c r="D112" s="11" t="n"/>
-      <c r="E112" s="12">
-        <f>IF($A112="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A112,$K$82:$K$146,0),MATCH(IF($A112="1Y","12M",IF($A112="12M","1Y",$A112)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E112" s="12" t="n"/>
       <c r="F112" s="13">
+        <f>IF(OR($A112="",G112=""),"",-LN(G112)/((B112-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G112" s="14">
         <f>IF($A112="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A112,$K$82:$K$146,0),MATCH(IF($A112="1Y","12M",IF($A112="12M","1Y",$A112)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G112" s="14">
-        <f>IF(OR($A112="",F112=""),"",-LN(F112)/((E112-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H112" s="15">
-        <f>IF(OR(G112="",NOT(ISNUMBER(C112))),"",(G112-C112)*100)</f>
+        <f>IF(OR(F112="",NOT(ISNUMBER(D112))),"",(F112-D112)*100)</f>
         <v/>
       </c>
       <c r="I112" s="16">
-        <f>IF(OR(F112="",NOT(ISNUMBER(D112))),"",F112-D112)</f>
+        <f>IF(OR(G112="",NOT(ISNUMBER(E112))),"",G112-E112)</f>
         <v/>
       </c>
       <c r="K112" s="17" t="inlineStr">
@@ -7947,7 +7952,7 @@
         <v/>
       </c>
       <c r="S112" s="19">
-        <f>IFERROR(IF(R112=1,IFERROR(INDEX($B$82:$B$133,MATCH("16Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("16Y",$A$82:$A$133,0))),S111+(S116-S111)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R112=1,IFERROR(INDEX($C$82:$C$133,MATCH("16Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("16Y",$A$82:$A$133,0))),S111+(S116-S111)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T112">
@@ -7965,27 +7970,27 @@
     </row>
     <row r="113">
       <c r="A113" s="9" t="n"/>
-      <c r="B113" s="10" t="n"/>
-      <c r="C113" s="10" t="n"/>
+      <c r="B113" s="10">
+        <f>IF($A113="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A113,$K$82:$K$146,0),MATCH(IF($A113="1Y","12M",IF($A113="12M","1Y",$A113)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C113" s="11" t="n"/>
       <c r="D113" s="11" t="n"/>
-      <c r="E113" s="12">
-        <f>IF($A113="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A113,$K$82:$K$146,0),MATCH(IF($A113="1Y","12M",IF($A113="12M","1Y",$A113)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E113" s="12" t="n"/>
       <c r="F113" s="13">
+        <f>IF(OR($A113="",G113=""),"",-LN(G113)/((B113-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G113" s="14">
         <f>IF($A113="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A113,$K$82:$K$146,0),MATCH(IF($A113="1Y","12M",IF($A113="12M","1Y",$A113)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G113" s="14">
-        <f>IF(OR($A113="",F113=""),"",-LN(F113)/((E113-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H113" s="15">
-        <f>IF(OR(G113="",NOT(ISNUMBER(C113))),"",(G113-C113)*100)</f>
+        <f>IF(OR(F113="",NOT(ISNUMBER(D113))),"",(F113-D113)*100)</f>
         <v/>
       </c>
       <c r="I113" s="16">
-        <f>IF(OR(F113="",NOT(ISNUMBER(D113))),"",F113-D113)</f>
+        <f>IF(OR(G113="",NOT(ISNUMBER(E113))),"",G113-E113)</f>
         <v/>
       </c>
       <c r="K113" s="17" t="inlineStr">
@@ -8020,7 +8025,7 @@
         <v/>
       </c>
       <c r="S113" s="19">
-        <f>IFERROR(IF(R113=1,IFERROR(INDEX($B$82:$B$133,MATCH("17Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("17Y",$A$82:$A$133,0))),S111+(S116-S111)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R113=1,IFERROR(INDEX($C$82:$C$133,MATCH("17Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("17Y",$A$82:$A$133,0))),S111+(S116-S111)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T113">
@@ -8038,27 +8043,27 @@
     </row>
     <row r="114">
       <c r="A114" s="9" t="n"/>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
+      <c r="B114" s="10">
+        <f>IF($A114="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A114,$K$82:$K$146,0),MATCH(IF($A114="1Y","12M",IF($A114="12M","1Y",$A114)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C114" s="11" t="n"/>
       <c r="D114" s="11" t="n"/>
-      <c r="E114" s="12">
-        <f>IF($A114="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A114,$K$82:$K$146,0),MATCH(IF($A114="1Y","12M",IF($A114="12M","1Y",$A114)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E114" s="12" t="n"/>
       <c r="F114" s="13">
+        <f>IF(OR($A114="",G114=""),"",-LN(G114)/((B114-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G114" s="14">
         <f>IF($A114="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A114,$K$82:$K$146,0),MATCH(IF($A114="1Y","12M",IF($A114="12M","1Y",$A114)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G114" s="14">
-        <f>IF(OR($A114="",F114=""),"",-LN(F114)/((E114-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H114" s="15">
-        <f>IF(OR(G114="",NOT(ISNUMBER(C114))),"",(G114-C114)*100)</f>
+        <f>IF(OR(F114="",NOT(ISNUMBER(D114))),"",(F114-D114)*100)</f>
         <v/>
       </c>
       <c r="I114" s="16">
-        <f>IF(OR(F114="",NOT(ISNUMBER(D114))),"",F114-D114)</f>
+        <f>IF(OR(G114="",NOT(ISNUMBER(E114))),"",G114-E114)</f>
         <v/>
       </c>
       <c r="K114" s="17" t="inlineStr">
@@ -8093,7 +8098,7 @@
         <v/>
       </c>
       <c r="S114" s="19">
-        <f>IFERROR(IF(R114=1,IFERROR(INDEX($B$82:$B$133,MATCH("18Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("18Y",$A$82:$A$133,0))),S111+(S116-S111)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R114=1,IFERROR(INDEX($C$82:$C$133,MATCH("18Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("18Y",$A$82:$A$133,0))),S111+(S116-S111)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T114">
@@ -8111,27 +8116,27 @@
     </row>
     <row r="115">
       <c r="A115" s="9" t="n"/>
-      <c r="B115" s="10" t="n"/>
-      <c r="C115" s="10" t="n"/>
+      <c r="B115" s="10">
+        <f>IF($A115="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A115,$K$82:$K$146,0),MATCH(IF($A115="1Y","12M",IF($A115="12M","1Y",$A115)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C115" s="11" t="n"/>
       <c r="D115" s="11" t="n"/>
-      <c r="E115" s="12">
-        <f>IF($A115="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A115,$K$82:$K$146,0),MATCH(IF($A115="1Y","12M",IF($A115="12M","1Y",$A115)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E115" s="12" t="n"/>
       <c r="F115" s="13">
+        <f>IF(OR($A115="",G115=""),"",-LN(G115)/((B115-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G115" s="14">
         <f>IF($A115="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A115,$K$82:$K$146,0),MATCH(IF($A115="1Y","12M",IF($A115="12M","1Y",$A115)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G115" s="14">
-        <f>IF(OR($A115="",F115=""),"",-LN(F115)/((E115-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H115" s="15">
-        <f>IF(OR(G115="",NOT(ISNUMBER(C115))),"",(G115-C115)*100)</f>
+        <f>IF(OR(F115="",NOT(ISNUMBER(D115))),"",(F115-D115)*100)</f>
         <v/>
       </c>
       <c r="I115" s="16">
-        <f>IF(OR(F115="",NOT(ISNUMBER(D115))),"",F115-D115)</f>
+        <f>IF(OR(G115="",NOT(ISNUMBER(E115))),"",G115-E115)</f>
         <v/>
       </c>
       <c r="K115" s="17" t="inlineStr">
@@ -8166,7 +8171,7 @@
         <v/>
       </c>
       <c r="S115" s="19">
-        <f>IFERROR(IF(R115=1,IFERROR(INDEX($B$82:$B$133,MATCH("19Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("19Y",$A$82:$A$133,0))),S111+(S116-S111)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R115=1,IFERROR(INDEX($C$82:$C$133,MATCH("19Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("19Y",$A$82:$A$133,0))),S111+(S116-S111)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T115">
@@ -8184,27 +8189,27 @@
     </row>
     <row r="116">
       <c r="A116" s="9" t="n"/>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
+      <c r="B116" s="10">
+        <f>IF($A116="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A116,$K$82:$K$146,0),MATCH(IF($A116="1Y","12M",IF($A116="12M","1Y",$A116)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C116" s="11" t="n"/>
       <c r="D116" s="11" t="n"/>
-      <c r="E116" s="12">
-        <f>IF($A116="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A116,$K$82:$K$146,0),MATCH(IF($A116="1Y","12M",IF($A116="12M","1Y",$A116)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E116" s="12" t="n"/>
       <c r="F116" s="13">
+        <f>IF(OR($A116="",G116=""),"",-LN(G116)/((B116-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G116" s="14">
         <f>IF($A116="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A116,$K$82:$K$146,0),MATCH(IF($A116="1Y","12M",IF($A116="12M","1Y",$A116)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G116" s="14">
-        <f>IF(OR($A116="",F116=""),"",-LN(F116)/((E116-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H116" s="15">
-        <f>IF(OR(G116="",NOT(ISNUMBER(C116))),"",(G116-C116)*100)</f>
+        <f>IF(OR(F116="",NOT(ISNUMBER(D116))),"",(F116-D116)*100)</f>
         <v/>
       </c>
       <c r="I116" s="16">
-        <f>IF(OR(F116="",NOT(ISNUMBER(D116))),"",F116-D116)</f>
+        <f>IF(OR(G116="",NOT(ISNUMBER(E116))),"",G116-E116)</f>
         <v/>
       </c>
       <c r="K116" s="17" t="inlineStr">
@@ -8239,7 +8244,7 @@
         <v/>
       </c>
       <c r="S116" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("20Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("20Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("20Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("20Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U116" s="20">
@@ -8317,27 +8322,27 @@
     </row>
     <row r="117">
       <c r="A117" s="9" t="n"/>
-      <c r="B117" s="10" t="n"/>
-      <c r="C117" s="10" t="n"/>
+      <c r="B117" s="10">
+        <f>IF($A117="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A117,$K$82:$K$146,0),MATCH(IF($A117="1Y","12M",IF($A117="12M","1Y",$A117)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C117" s="11" t="n"/>
       <c r="D117" s="11" t="n"/>
-      <c r="E117" s="12">
-        <f>IF($A117="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A117,$K$82:$K$146,0),MATCH(IF($A117="1Y","12M",IF($A117="12M","1Y",$A117)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E117" s="12" t="n"/>
       <c r="F117" s="13">
+        <f>IF(OR($A117="",G117=""),"",-LN(G117)/((B117-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G117" s="14">
         <f>IF($A117="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A117,$K$82:$K$146,0),MATCH(IF($A117="1Y","12M",IF($A117="12M","1Y",$A117)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G117" s="14">
-        <f>IF(OR($A117="",F117=""),"",-LN(F117)/((E117-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H117" s="15">
-        <f>IF(OR(G117="",NOT(ISNUMBER(C117))),"",(G117-C117)*100)</f>
+        <f>IF(OR(F117="",NOT(ISNUMBER(D117))),"",(F117-D117)*100)</f>
         <v/>
       </c>
       <c r="I117" s="16">
-        <f>IF(OR(F117="",NOT(ISNUMBER(D117))),"",F117-D117)</f>
+        <f>IF(OR(G117="",NOT(ISNUMBER(E117))),"",G117-E117)</f>
         <v/>
       </c>
       <c r="K117" s="17" t="inlineStr">
@@ -8372,7 +8377,7 @@
         <v/>
       </c>
       <c r="S117" s="19">
-        <f>IFERROR(IF(R117=1,IFERROR(INDEX($B$82:$B$133,MATCH("21Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("21Y",$A$82:$A$133,0))),S116+(S121-S116)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R117=1,IFERROR(INDEX($C$82:$C$133,MATCH("21Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("21Y",$A$82:$A$133,0))),S116+(S121-S116)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T117">
@@ -8390,27 +8395,27 @@
     </row>
     <row r="118">
       <c r="A118" s="9" t="n"/>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="10" t="n"/>
+      <c r="B118" s="10">
+        <f>IF($A118="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A118,$K$82:$K$146,0),MATCH(IF($A118="1Y","12M",IF($A118="12M","1Y",$A118)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C118" s="11" t="n"/>
       <c r="D118" s="11" t="n"/>
-      <c r="E118" s="12">
-        <f>IF($A118="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A118,$K$82:$K$146,0),MATCH(IF($A118="1Y","12M",IF($A118="12M","1Y",$A118)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E118" s="12" t="n"/>
       <c r="F118" s="13">
+        <f>IF(OR($A118="",G118=""),"",-LN(G118)/((B118-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G118" s="14">
         <f>IF($A118="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A118,$K$82:$K$146,0),MATCH(IF($A118="1Y","12M",IF($A118="12M","1Y",$A118)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G118" s="14">
-        <f>IF(OR($A118="",F118=""),"",-LN(F118)/((E118-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H118" s="15">
-        <f>IF(OR(G118="",NOT(ISNUMBER(C118))),"",(G118-C118)*100)</f>
+        <f>IF(OR(F118="",NOT(ISNUMBER(D118))),"",(F118-D118)*100)</f>
         <v/>
       </c>
       <c r="I118" s="16">
-        <f>IF(OR(F118="",NOT(ISNUMBER(D118))),"",F118-D118)</f>
+        <f>IF(OR(G118="",NOT(ISNUMBER(E118))),"",G118-E118)</f>
         <v/>
       </c>
       <c r="K118" s="17" t="inlineStr">
@@ -8445,7 +8450,7 @@
         <v/>
       </c>
       <c r="S118" s="19">
-        <f>IFERROR(IF(R118=1,IFERROR(INDEX($B$82:$B$133,MATCH("22Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("22Y",$A$82:$A$133,0))),S116+(S121-S116)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R118=1,IFERROR(INDEX($C$82:$C$133,MATCH("22Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("22Y",$A$82:$A$133,0))),S116+(S121-S116)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T118">
@@ -8463,27 +8468,27 @@
     </row>
     <row r="119">
       <c r="A119" s="9" t="n"/>
-      <c r="B119" s="10" t="n"/>
-      <c r="C119" s="10" t="n"/>
+      <c r="B119" s="10">
+        <f>IF($A119="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A119,$K$82:$K$146,0),MATCH(IF($A119="1Y","12M",IF($A119="12M","1Y",$A119)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C119" s="11" t="n"/>
       <c r="D119" s="11" t="n"/>
-      <c r="E119" s="12">
-        <f>IF($A119="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A119,$K$82:$K$146,0),MATCH(IF($A119="1Y","12M",IF($A119="12M","1Y",$A119)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E119" s="12" t="n"/>
       <c r="F119" s="13">
+        <f>IF(OR($A119="",G119=""),"",-LN(G119)/((B119-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G119" s="14">
         <f>IF($A119="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A119,$K$82:$K$146,0),MATCH(IF($A119="1Y","12M",IF($A119="12M","1Y",$A119)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G119" s="14">
-        <f>IF(OR($A119="",F119=""),"",-LN(F119)/((E119-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H119" s="15">
-        <f>IF(OR(G119="",NOT(ISNUMBER(C119))),"",(G119-C119)*100)</f>
+        <f>IF(OR(F119="",NOT(ISNUMBER(D119))),"",(F119-D119)*100)</f>
         <v/>
       </c>
       <c r="I119" s="16">
-        <f>IF(OR(F119="",NOT(ISNUMBER(D119))),"",F119-D119)</f>
+        <f>IF(OR(G119="",NOT(ISNUMBER(E119))),"",G119-E119)</f>
         <v/>
       </c>
       <c r="K119" s="17" t="inlineStr">
@@ -8518,7 +8523,7 @@
         <v/>
       </c>
       <c r="S119" s="19">
-        <f>IFERROR(IF(R119=1,IFERROR(INDEX($B$82:$B$133,MATCH("23Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("23Y",$A$82:$A$133,0))),S116+(S121-S116)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R119=1,IFERROR(INDEX($C$82:$C$133,MATCH("23Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("23Y",$A$82:$A$133,0))),S116+(S121-S116)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T119">
@@ -8536,27 +8541,27 @@
     </row>
     <row r="120">
       <c r="A120" s="9" t="n"/>
-      <c r="B120" s="10" t="n"/>
-      <c r="C120" s="10" t="n"/>
+      <c r="B120" s="10">
+        <f>IF($A120="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A120,$K$82:$K$146,0),MATCH(IF($A120="1Y","12M",IF($A120="12M","1Y",$A120)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C120" s="11" t="n"/>
       <c r="D120" s="11" t="n"/>
-      <c r="E120" s="12">
-        <f>IF($A120="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A120,$K$82:$K$146,0),MATCH(IF($A120="1Y","12M",IF($A120="12M","1Y",$A120)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E120" s="12" t="n"/>
       <c r="F120" s="13">
+        <f>IF(OR($A120="",G120=""),"",-LN(G120)/((B120-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G120" s="14">
         <f>IF($A120="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A120,$K$82:$K$146,0),MATCH(IF($A120="1Y","12M",IF($A120="12M","1Y",$A120)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G120" s="14">
-        <f>IF(OR($A120="",F120=""),"",-LN(F120)/((E120-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H120" s="15">
-        <f>IF(OR(G120="",NOT(ISNUMBER(C120))),"",(G120-C120)*100)</f>
+        <f>IF(OR(F120="",NOT(ISNUMBER(D120))),"",(F120-D120)*100)</f>
         <v/>
       </c>
       <c r="I120" s="16">
-        <f>IF(OR(F120="",NOT(ISNUMBER(D120))),"",F120-D120)</f>
+        <f>IF(OR(G120="",NOT(ISNUMBER(E120))),"",G120-E120)</f>
         <v/>
       </c>
       <c r="K120" s="17" t="inlineStr">
@@ -8591,7 +8596,7 @@
         <v/>
       </c>
       <c r="S120" s="19">
-        <f>IFERROR(IF(R120=1,IFERROR(INDEX($B$82:$B$133,MATCH("24Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("24Y",$A$82:$A$133,0))),S116+(S121-S116)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R120=1,IFERROR(INDEX($C$82:$C$133,MATCH("24Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("24Y",$A$82:$A$133,0))),S116+(S121-S116)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T120">
@@ -8609,27 +8614,27 @@
     </row>
     <row r="121">
       <c r="A121" s="9" t="n"/>
-      <c r="B121" s="10" t="n"/>
-      <c r="C121" s="10" t="n"/>
+      <c r="B121" s="10">
+        <f>IF($A121="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A121,$K$82:$K$146,0),MATCH(IF($A121="1Y","12M",IF($A121="12M","1Y",$A121)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C121" s="11" t="n"/>
       <c r="D121" s="11" t="n"/>
-      <c r="E121" s="12">
-        <f>IF($A121="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A121,$K$82:$K$146,0),MATCH(IF($A121="1Y","12M",IF($A121="12M","1Y",$A121)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E121" s="12" t="n"/>
       <c r="F121" s="13">
+        <f>IF(OR($A121="",G121=""),"",-LN(G121)/((B121-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G121" s="14">
         <f>IF($A121="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A121,$K$82:$K$146,0),MATCH(IF($A121="1Y","12M",IF($A121="12M","1Y",$A121)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G121" s="14">
-        <f>IF(OR($A121="",F121=""),"",-LN(F121)/((E121-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H121" s="15">
-        <f>IF(OR(G121="",NOT(ISNUMBER(C121))),"",(G121-C121)*100)</f>
+        <f>IF(OR(F121="",NOT(ISNUMBER(D121))),"",(F121-D121)*100)</f>
         <v/>
       </c>
       <c r="I121" s="16">
-        <f>IF(OR(F121="",NOT(ISNUMBER(D121))),"",F121-D121)</f>
+        <f>IF(OR(G121="",NOT(ISNUMBER(E121))),"",G121-E121)</f>
         <v/>
       </c>
       <c r="K121" s="17" t="inlineStr">
@@ -8664,7 +8669,7 @@
         <v/>
       </c>
       <c r="S121" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("25Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("25Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("25Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("25Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U121" s="20">
@@ -8742,27 +8747,27 @@
     </row>
     <row r="122">
       <c r="A122" s="9" t="n"/>
-      <c r="B122" s="10" t="n"/>
-      <c r="C122" s="10" t="n"/>
+      <c r="B122" s="10">
+        <f>IF($A122="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A122,$K$82:$K$146,0),MATCH(IF($A122="1Y","12M",IF($A122="12M","1Y",$A122)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C122" s="11" t="n"/>
       <c r="D122" s="11" t="n"/>
-      <c r="E122" s="12">
-        <f>IF($A122="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A122,$K$82:$K$146,0),MATCH(IF($A122="1Y","12M",IF($A122="12M","1Y",$A122)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E122" s="12" t="n"/>
       <c r="F122" s="13">
+        <f>IF(OR($A122="",G122=""),"",-LN(G122)/((B122-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G122" s="14">
         <f>IF($A122="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A122,$K$82:$K$146,0),MATCH(IF($A122="1Y","12M",IF($A122="12M","1Y",$A122)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G122" s="14">
-        <f>IF(OR($A122="",F122=""),"",-LN(F122)/((E122-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H122" s="15">
-        <f>IF(OR(G122="",NOT(ISNUMBER(C122))),"",(G122-C122)*100)</f>
+        <f>IF(OR(F122="",NOT(ISNUMBER(D122))),"",(F122-D122)*100)</f>
         <v/>
       </c>
       <c r="I122" s="16">
-        <f>IF(OR(F122="",NOT(ISNUMBER(D122))),"",F122-D122)</f>
+        <f>IF(OR(G122="",NOT(ISNUMBER(E122))),"",G122-E122)</f>
         <v/>
       </c>
       <c r="K122" s="17" t="inlineStr">
@@ -8797,7 +8802,7 @@
         <v/>
       </c>
       <c r="S122" s="19">
-        <f>IFERROR(IF(R122=1,IFERROR(INDEX($B$82:$B$133,MATCH("26Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("26Y",$A$82:$A$133,0))),S121+(S126-S121)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R122=1,IFERROR(INDEX($C$82:$C$133,MATCH("26Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("26Y",$A$82:$A$133,0))),S121+(S126-S121)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T122">
@@ -8815,27 +8820,27 @@
     </row>
     <row r="123">
       <c r="A123" s="9" t="n"/>
-      <c r="B123" s="10" t="n"/>
-      <c r="C123" s="10" t="n"/>
+      <c r="B123" s="10">
+        <f>IF($A123="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A123,$K$82:$K$146,0),MATCH(IF($A123="1Y","12M",IF($A123="12M","1Y",$A123)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C123" s="11" t="n"/>
       <c r="D123" s="11" t="n"/>
-      <c r="E123" s="12">
-        <f>IF($A123="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A123,$K$82:$K$146,0),MATCH(IF($A123="1Y","12M",IF($A123="12M","1Y",$A123)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E123" s="12" t="n"/>
       <c r="F123" s="13">
+        <f>IF(OR($A123="",G123=""),"",-LN(G123)/((B123-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G123" s="14">
         <f>IF($A123="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A123,$K$82:$K$146,0),MATCH(IF($A123="1Y","12M",IF($A123="12M","1Y",$A123)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G123" s="14">
-        <f>IF(OR($A123="",F123=""),"",-LN(F123)/((E123-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H123" s="15">
-        <f>IF(OR(G123="",NOT(ISNUMBER(C123))),"",(G123-C123)*100)</f>
+        <f>IF(OR(F123="",NOT(ISNUMBER(D123))),"",(F123-D123)*100)</f>
         <v/>
       </c>
       <c r="I123" s="16">
-        <f>IF(OR(F123="",NOT(ISNUMBER(D123))),"",F123-D123)</f>
+        <f>IF(OR(G123="",NOT(ISNUMBER(E123))),"",G123-E123)</f>
         <v/>
       </c>
       <c r="K123" s="17" t="inlineStr">
@@ -8870,7 +8875,7 @@
         <v/>
       </c>
       <c r="S123" s="19">
-        <f>IFERROR(IF(R123=1,IFERROR(INDEX($B$82:$B$133,MATCH("27Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("27Y",$A$82:$A$133,0))),S121+(S126-S121)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R123=1,IFERROR(INDEX($C$82:$C$133,MATCH("27Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("27Y",$A$82:$A$133,0))),S121+(S126-S121)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T123">
@@ -8888,27 +8893,27 @@
     </row>
     <row r="124">
       <c r="A124" s="9" t="n"/>
-      <c r="B124" s="10" t="n"/>
-      <c r="C124" s="10" t="n"/>
+      <c r="B124" s="10">
+        <f>IF($A124="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A124,$K$82:$K$146,0),MATCH(IF($A124="1Y","12M",IF($A124="12M","1Y",$A124)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C124" s="11" t="n"/>
       <c r="D124" s="11" t="n"/>
-      <c r="E124" s="12">
-        <f>IF($A124="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A124,$K$82:$K$146,0),MATCH(IF($A124="1Y","12M",IF($A124="12M","1Y",$A124)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E124" s="12" t="n"/>
       <c r="F124" s="13">
+        <f>IF(OR($A124="",G124=""),"",-LN(G124)/((B124-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G124" s="14">
         <f>IF($A124="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A124,$K$82:$K$146,0),MATCH(IF($A124="1Y","12M",IF($A124="12M","1Y",$A124)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G124" s="14">
-        <f>IF(OR($A124="",F124=""),"",-LN(F124)/((E124-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H124" s="15">
-        <f>IF(OR(G124="",NOT(ISNUMBER(C124))),"",(G124-C124)*100)</f>
+        <f>IF(OR(F124="",NOT(ISNUMBER(D124))),"",(F124-D124)*100)</f>
         <v/>
       </c>
       <c r="I124" s="16">
-        <f>IF(OR(F124="",NOT(ISNUMBER(D124))),"",F124-D124)</f>
+        <f>IF(OR(G124="",NOT(ISNUMBER(E124))),"",G124-E124)</f>
         <v/>
       </c>
       <c r="K124" s="17" t="inlineStr">
@@ -8943,7 +8948,7 @@
         <v/>
       </c>
       <c r="S124" s="19">
-        <f>IFERROR(IF(R124=1,IFERROR(INDEX($B$82:$B$133,MATCH("28Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("28Y",$A$82:$A$133,0))),S121+(S126-S121)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R124=1,IFERROR(INDEX($C$82:$C$133,MATCH("28Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("28Y",$A$82:$A$133,0))),S121+(S126-S121)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T124">
@@ -8961,27 +8966,27 @@
     </row>
     <row r="125">
       <c r="A125" s="9" t="n"/>
-      <c r="B125" s="10" t="n"/>
-      <c r="C125" s="10" t="n"/>
+      <c r="B125" s="10">
+        <f>IF($A125="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A125,$K$82:$K$146,0),MATCH(IF($A125="1Y","12M",IF($A125="12M","1Y",$A125)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C125" s="11" t="n"/>
       <c r="D125" s="11" t="n"/>
-      <c r="E125" s="12">
-        <f>IF($A125="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A125,$K$82:$K$146,0),MATCH(IF($A125="1Y","12M",IF($A125="12M","1Y",$A125)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E125" s="12" t="n"/>
       <c r="F125" s="13">
+        <f>IF(OR($A125="",G125=""),"",-LN(G125)/((B125-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G125" s="14">
         <f>IF($A125="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A125,$K$82:$K$146,0),MATCH(IF($A125="1Y","12M",IF($A125="12M","1Y",$A125)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G125" s="14">
-        <f>IF(OR($A125="",F125=""),"",-LN(F125)/((E125-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H125" s="15">
-        <f>IF(OR(G125="",NOT(ISNUMBER(C125))),"",(G125-C125)*100)</f>
+        <f>IF(OR(F125="",NOT(ISNUMBER(D125))),"",(F125-D125)*100)</f>
         <v/>
       </c>
       <c r="I125" s="16">
-        <f>IF(OR(F125="",NOT(ISNUMBER(D125))),"",F125-D125)</f>
+        <f>IF(OR(G125="",NOT(ISNUMBER(E125))),"",G125-E125)</f>
         <v/>
       </c>
       <c r="K125" s="17" t="inlineStr">
@@ -9016,7 +9021,7 @@
         <v/>
       </c>
       <c r="S125" s="19">
-        <f>IFERROR(IF(R125=1,IFERROR(INDEX($B$82:$B$133,MATCH("29Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("29Y",$A$82:$A$133,0))),S121+(S126-S121)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R125=1,IFERROR(INDEX($C$82:$C$133,MATCH("29Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("29Y",$A$82:$A$133,0))),S121+(S126-S121)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T125">
@@ -9034,27 +9039,27 @@
     </row>
     <row r="126">
       <c r="A126" s="9" t="n"/>
-      <c r="B126" s="10" t="n"/>
-      <c r="C126" s="10" t="n"/>
+      <c r="B126" s="10">
+        <f>IF($A126="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A126,$K$82:$K$146,0),MATCH(IF($A126="1Y","12M",IF($A126="12M","1Y",$A126)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C126" s="11" t="n"/>
       <c r="D126" s="11" t="n"/>
-      <c r="E126" s="12">
-        <f>IF($A126="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A126,$K$82:$K$146,0),MATCH(IF($A126="1Y","12M",IF($A126="12M","1Y",$A126)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E126" s="12" t="n"/>
       <c r="F126" s="13">
+        <f>IF(OR($A126="",G126=""),"",-LN(G126)/((B126-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G126" s="14">
         <f>IF($A126="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A126,$K$82:$K$146,0),MATCH(IF($A126="1Y","12M",IF($A126="12M","1Y",$A126)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G126" s="14">
-        <f>IF(OR($A126="",F126=""),"",-LN(F126)/((E126-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H126" s="15">
-        <f>IF(OR(G126="",NOT(ISNUMBER(C126))),"",(G126-C126)*100)</f>
+        <f>IF(OR(F126="",NOT(ISNUMBER(D126))),"",(F126-D126)*100)</f>
         <v/>
       </c>
       <c r="I126" s="16">
-        <f>IF(OR(F126="",NOT(ISNUMBER(D126))),"",F126-D126)</f>
+        <f>IF(OR(G126="",NOT(ISNUMBER(E126))),"",G126-E126)</f>
         <v/>
       </c>
       <c r="K126" s="17" t="inlineStr">
@@ -9089,7 +9094,7 @@
         <v/>
       </c>
       <c r="S126" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("30Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("30Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("30Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("30Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U126" s="20">
@@ -9167,27 +9172,27 @@
     </row>
     <row r="127">
       <c r="A127" s="9" t="n"/>
-      <c r="B127" s="10" t="n"/>
-      <c r="C127" s="10" t="n"/>
+      <c r="B127" s="10">
+        <f>IF($A127="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A127,$K$82:$K$146,0),MATCH(IF($A127="1Y","12M",IF($A127="12M","1Y",$A127)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C127" s="11" t="n"/>
       <c r="D127" s="11" t="n"/>
-      <c r="E127" s="12">
-        <f>IF($A127="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A127,$K$82:$K$146,0),MATCH(IF($A127="1Y","12M",IF($A127="12M","1Y",$A127)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E127" s="12" t="n"/>
       <c r="F127" s="13">
+        <f>IF(OR($A127="",G127=""),"",-LN(G127)/((B127-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G127" s="14">
         <f>IF($A127="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A127,$K$82:$K$146,0),MATCH(IF($A127="1Y","12M",IF($A127="12M","1Y",$A127)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G127" s="14">
-        <f>IF(OR($A127="",F127=""),"",-LN(F127)/((E127-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H127" s="15">
-        <f>IF(OR(G127="",NOT(ISNUMBER(C127))),"",(G127-C127)*100)</f>
+        <f>IF(OR(F127="",NOT(ISNUMBER(D127))),"",(F127-D127)*100)</f>
         <v/>
       </c>
       <c r="I127" s="16">
-        <f>IF(OR(F127="",NOT(ISNUMBER(D127))),"",F127-D127)</f>
+        <f>IF(OR(G127="",NOT(ISNUMBER(E127))),"",G127-E127)</f>
         <v/>
       </c>
       <c r="K127" s="17" t="inlineStr">
@@ -9222,7 +9227,7 @@
         <v/>
       </c>
       <c r="S127" s="19">
-        <f>IFERROR(IF(R127=1,IFERROR(INDEX($B$82:$B$133,MATCH("31Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("31Y",$A$82:$A$133,0))),S126+(S136-S126)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R127=1,IFERROR(INDEX($C$82:$C$133,MATCH("31Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("31Y",$A$82:$A$133,0))),S126+(S136-S126)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T127">
@@ -9240,27 +9245,27 @@
     </row>
     <row r="128">
       <c r="A128" s="9" t="n"/>
-      <c r="B128" s="10" t="n"/>
-      <c r="C128" s="10" t="n"/>
+      <c r="B128" s="10">
+        <f>IF($A128="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A128,$K$82:$K$146,0),MATCH(IF($A128="1Y","12M",IF($A128="12M","1Y",$A128)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C128" s="11" t="n"/>
       <c r="D128" s="11" t="n"/>
-      <c r="E128" s="12">
-        <f>IF($A128="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A128,$K$82:$K$146,0),MATCH(IF($A128="1Y","12M",IF($A128="12M","1Y",$A128)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E128" s="12" t="n"/>
       <c r="F128" s="13">
+        <f>IF(OR($A128="",G128=""),"",-LN(G128)/((B128-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G128" s="14">
         <f>IF($A128="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A128,$K$82:$K$146,0),MATCH(IF($A128="1Y","12M",IF($A128="12M","1Y",$A128)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G128" s="14">
-        <f>IF(OR($A128="",F128=""),"",-LN(F128)/((E128-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H128" s="15">
-        <f>IF(OR(G128="",NOT(ISNUMBER(C128))),"",(G128-C128)*100)</f>
+        <f>IF(OR(F128="",NOT(ISNUMBER(D128))),"",(F128-D128)*100)</f>
         <v/>
       </c>
       <c r="I128" s="16">
-        <f>IF(OR(F128="",NOT(ISNUMBER(D128))),"",F128-D128)</f>
+        <f>IF(OR(G128="",NOT(ISNUMBER(E128))),"",G128-E128)</f>
         <v/>
       </c>
       <c r="K128" s="17" t="inlineStr">
@@ -9295,7 +9300,7 @@
         <v/>
       </c>
       <c r="S128" s="19">
-        <f>IFERROR(IF(R128=1,IFERROR(INDEX($B$82:$B$133,MATCH("32Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("32Y",$A$82:$A$133,0))),S126+(S136-S126)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R128=1,IFERROR(INDEX($C$82:$C$133,MATCH("32Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("32Y",$A$82:$A$133,0))),S126+(S136-S126)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T128">
@@ -9313,27 +9318,27 @@
     </row>
     <row r="129">
       <c r="A129" s="9" t="n"/>
-      <c r="B129" s="10" t="n"/>
-      <c r="C129" s="10" t="n"/>
+      <c r="B129" s="10">
+        <f>IF($A129="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A129,$K$82:$K$146,0),MATCH(IF($A129="1Y","12M",IF($A129="12M","1Y",$A129)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C129" s="11" t="n"/>
       <c r="D129" s="11" t="n"/>
-      <c r="E129" s="12">
-        <f>IF($A129="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A129,$K$82:$K$146,0),MATCH(IF($A129="1Y","12M",IF($A129="12M","1Y",$A129)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E129" s="12" t="n"/>
       <c r="F129" s="13">
+        <f>IF(OR($A129="",G129=""),"",-LN(G129)/((B129-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G129" s="14">
         <f>IF($A129="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A129,$K$82:$K$146,0),MATCH(IF($A129="1Y","12M",IF($A129="12M","1Y",$A129)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G129" s="14">
-        <f>IF(OR($A129="",F129=""),"",-LN(F129)/((E129-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H129" s="15">
-        <f>IF(OR(G129="",NOT(ISNUMBER(C129))),"",(G129-C129)*100)</f>
+        <f>IF(OR(F129="",NOT(ISNUMBER(D129))),"",(F129-D129)*100)</f>
         <v/>
       </c>
       <c r="I129" s="16">
-        <f>IF(OR(F129="",NOT(ISNUMBER(D129))),"",F129-D129)</f>
+        <f>IF(OR(G129="",NOT(ISNUMBER(E129))),"",G129-E129)</f>
         <v/>
       </c>
       <c r="K129" s="17" t="inlineStr">
@@ -9368,7 +9373,7 @@
         <v/>
       </c>
       <c r="S129" s="19">
-        <f>IFERROR(IF(R129=1,IFERROR(INDEX($B$82:$B$133,MATCH("33Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("33Y",$A$82:$A$133,0))),S126+(S136-S126)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R129=1,IFERROR(INDEX($C$82:$C$133,MATCH("33Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("33Y",$A$82:$A$133,0))),S126+(S136-S126)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T129">
@@ -9386,27 +9391,27 @@
     </row>
     <row r="130">
       <c r="A130" s="9" t="n"/>
-      <c r="B130" s="10" t="n"/>
-      <c r="C130" s="10" t="n"/>
+      <c r="B130" s="10">
+        <f>IF($A130="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A130,$K$82:$K$146,0),MATCH(IF($A130="1Y","12M",IF($A130="12M","1Y",$A130)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C130" s="11" t="n"/>
       <c r="D130" s="11" t="n"/>
-      <c r="E130" s="12">
-        <f>IF($A130="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A130,$K$82:$K$146,0),MATCH(IF($A130="1Y","12M",IF($A130="12M","1Y",$A130)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E130" s="12" t="n"/>
       <c r="F130" s="13">
+        <f>IF(OR($A130="",G130=""),"",-LN(G130)/((B130-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G130" s="14">
         <f>IF($A130="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A130,$K$82:$K$146,0),MATCH(IF($A130="1Y","12M",IF($A130="12M","1Y",$A130)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G130" s="14">
-        <f>IF(OR($A130="",F130=""),"",-LN(F130)/((E130-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H130" s="15">
-        <f>IF(OR(G130="",NOT(ISNUMBER(C130))),"",(G130-C130)*100)</f>
+        <f>IF(OR(F130="",NOT(ISNUMBER(D130))),"",(F130-D130)*100)</f>
         <v/>
       </c>
       <c r="I130" s="16">
-        <f>IF(OR(F130="",NOT(ISNUMBER(D130))),"",F130-D130)</f>
+        <f>IF(OR(G130="",NOT(ISNUMBER(E130))),"",G130-E130)</f>
         <v/>
       </c>
       <c r="K130" s="17" t="inlineStr">
@@ -9441,7 +9446,7 @@
         <v/>
       </c>
       <c r="S130" s="19">
-        <f>IFERROR(IF(R130=1,IFERROR(INDEX($B$82:$B$133,MATCH("34Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("34Y",$A$82:$A$133,0))),S126+(S136-S126)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R130=1,IFERROR(INDEX($C$82:$C$133,MATCH("34Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("34Y",$A$82:$A$133,0))),S126+(S136-S126)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T130">
@@ -9459,27 +9464,27 @@
     </row>
     <row r="131">
       <c r="A131" s="9" t="n"/>
-      <c r="B131" s="10" t="n"/>
-      <c r="C131" s="10" t="n"/>
+      <c r="B131" s="10">
+        <f>IF($A131="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A131,$K$82:$K$146,0),MATCH(IF($A131="1Y","12M",IF($A131="12M","1Y",$A131)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C131" s="11" t="n"/>
       <c r="D131" s="11" t="n"/>
-      <c r="E131" s="12">
-        <f>IF($A131="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A131,$K$82:$K$146,0),MATCH(IF($A131="1Y","12M",IF($A131="12M","1Y",$A131)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E131" s="12" t="n"/>
       <c r="F131" s="13">
+        <f>IF(OR($A131="",G131=""),"",-LN(G131)/((B131-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G131" s="14">
         <f>IF($A131="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A131,$K$82:$K$146,0),MATCH(IF($A131="1Y","12M",IF($A131="12M","1Y",$A131)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G131" s="14">
-        <f>IF(OR($A131="",F131=""),"",-LN(F131)/((E131-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H131" s="15">
-        <f>IF(OR(G131="",NOT(ISNUMBER(C131))),"",(G131-C131)*100)</f>
+        <f>IF(OR(F131="",NOT(ISNUMBER(D131))),"",(F131-D131)*100)</f>
         <v/>
       </c>
       <c r="I131" s="16">
-        <f>IF(OR(F131="",NOT(ISNUMBER(D131))),"",F131-D131)</f>
+        <f>IF(OR(G131="",NOT(ISNUMBER(E131))),"",G131-E131)</f>
         <v/>
       </c>
       <c r="K131" s="17" t="inlineStr">
@@ -9514,7 +9519,7 @@
         <v/>
       </c>
       <c r="S131" s="19">
-        <f>IFERROR(IF(R131=1,IFERROR(INDEX($B$82:$B$133,MATCH("35Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("35Y",$A$82:$A$133,0))),S126+(S136-S126)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R131=1,IFERROR(INDEX($C$82:$C$133,MATCH("35Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("35Y",$A$82:$A$133,0))),S126+(S136-S126)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T131">
@@ -9532,27 +9537,27 @@
     </row>
     <row r="132">
       <c r="A132" s="9" t="n"/>
-      <c r="B132" s="10" t="n"/>
-      <c r="C132" s="10" t="n"/>
+      <c r="B132" s="10">
+        <f>IF($A132="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A132,$K$82:$K$146,0),MATCH(IF($A132="1Y","12M",IF($A132="12M","1Y",$A132)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C132" s="11" t="n"/>
       <c r="D132" s="11" t="n"/>
-      <c r="E132" s="12">
-        <f>IF($A132="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A132,$K$82:$K$146,0),MATCH(IF($A132="1Y","12M",IF($A132="12M","1Y",$A132)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E132" s="12" t="n"/>
       <c r="F132" s="13">
+        <f>IF(OR($A132="",G132=""),"",-LN(G132)/((B132-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G132" s="14">
         <f>IF($A132="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A132,$K$82:$K$146,0),MATCH(IF($A132="1Y","12M",IF($A132="12M","1Y",$A132)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G132" s="14">
-        <f>IF(OR($A132="",F132=""),"",-LN(F132)/((E132-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H132" s="15">
-        <f>IF(OR(G132="",NOT(ISNUMBER(C132))),"",(G132-C132)*100)</f>
+        <f>IF(OR(F132="",NOT(ISNUMBER(D132))),"",(F132-D132)*100)</f>
         <v/>
       </c>
       <c r="I132" s="16">
-        <f>IF(OR(F132="",NOT(ISNUMBER(D132))),"",F132-D132)</f>
+        <f>IF(OR(G132="",NOT(ISNUMBER(E132))),"",G132-E132)</f>
         <v/>
       </c>
       <c r="K132" s="17" t="inlineStr">
@@ -9587,7 +9592,7 @@
         <v/>
       </c>
       <c r="S132" s="19">
-        <f>IFERROR(IF(R132=1,IFERROR(INDEX($B$82:$B$133,MATCH("36Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("36Y",$A$82:$A$133,0))),S126+(S136-S126)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R132=1,IFERROR(INDEX($C$82:$C$133,MATCH("36Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("36Y",$A$82:$A$133,0))),S126+(S136-S126)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T132">
@@ -9605,27 +9610,27 @@
     </row>
     <row r="133">
       <c r="A133" s="9" t="n"/>
-      <c r="B133" s="10" t="n"/>
-      <c r="C133" s="10" t="n"/>
+      <c r="B133" s="10">
+        <f>IF($A133="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A133,$K$82:$K$146,0),MATCH(IF($A133="1Y","12M",IF($A133="12M","1Y",$A133)),$K$82:$K$146,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C133" s="11" t="n"/>
       <c r="D133" s="11" t="n"/>
-      <c r="E133" s="12">
-        <f>IF($A133="","",IFERROR(INDEX($M$82:$M$146,IFERROR(MATCH($A133,$K$82:$K$146,0),MATCH(IF($A133="1Y","12M",IF($A133="12M","1Y",$A133)),$K$82:$K$146,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E133" s="12" t="n"/>
       <c r="F133" s="13">
+        <f>IF(OR($A133="",G133=""),"",-LN(G133)/((B133-$C$77)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G133" s="14">
         <f>IF($A133="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A133,$K$82:$K$146,0),MATCH(IF($A133="1Y","12M",IF($A133="12M","1Y",$A133)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="G133" s="14">
-        <f>IF(OR($A133="",F133=""),"",-LN(F133)/((E133-$C$77)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H133" s="15">
-        <f>IF(OR(G133="",NOT(ISNUMBER(C133))),"",(G133-C133)*100)</f>
+        <f>IF(OR(F133="",NOT(ISNUMBER(D133))),"",(F133-D133)*100)</f>
         <v/>
       </c>
       <c r="I133" s="16">
-        <f>IF(OR(F133="",NOT(ISNUMBER(D133))),"",F133-D133)</f>
+        <f>IF(OR(G133="",NOT(ISNUMBER(E133))),"",G133-E133)</f>
         <v/>
       </c>
       <c r="K133" s="17" t="inlineStr">
@@ -9660,7 +9665,7 @@
         <v/>
       </c>
       <c r="S133" s="19">
-        <f>IFERROR(IF(R133=1,IFERROR(INDEX($B$82:$B$133,MATCH("37Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("37Y",$A$82:$A$133,0))),S126+(S136-S126)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R133=1,IFERROR(INDEX($C$82:$C$133,MATCH("37Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("37Y",$A$82:$A$133,0))),S126+(S136-S126)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T133">
@@ -9709,7 +9714,7 @@
         <v/>
       </c>
       <c r="S134" s="19">
-        <f>IFERROR(IF(R134=1,IFERROR(INDEX($B$82:$B$133,MATCH("38Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("38Y",$A$82:$A$133,0))),S126+(S136-S126)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R134=1,IFERROR(INDEX($C$82:$C$133,MATCH("38Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("38Y",$A$82:$A$133,0))),S126+(S136-S126)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T134">
@@ -9741,7 +9746,7 @@
         </is>
       </c>
       <c r="F135" s="22">
-        <f>COUNT($G$82:$G$133)</f>
+        <f>COUNT($F$82:$F$133)</f>
         <v/>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9785,7 +9790,7 @@
         <v/>
       </c>
       <c r="S135" s="19">
-        <f>IFERROR(IF(R135=1,IFERROR(INDEX($B$82:$B$133,MATCH("39Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("39Y",$A$82:$A$133,0))),S126+(S136-S126)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R135=1,IFERROR(INDEX($C$82:$C$133,MATCH("39Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("39Y",$A$82:$A$133,0))),S126+(S136-S126)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T135">
@@ -9843,7 +9848,7 @@
         <v/>
       </c>
       <c r="S136" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("40Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("40Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("40Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("40Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U136" s="20">
@@ -9957,7 +9962,7 @@
         <v/>
       </c>
       <c r="S137" s="19">
-        <f>IFERROR(IF(R137=1,IFERROR(INDEX($B$82:$B$133,MATCH("41Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("41Y",$A$82:$A$133,0))),S136+(S146-S136)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R137=1,IFERROR(INDEX($C$82:$C$133,MATCH("41Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("41Y",$A$82:$A$133,0))),S136+(S146-S136)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T137">
@@ -10006,7 +10011,7 @@
         <v/>
       </c>
       <c r="S138" s="19">
-        <f>IFERROR(IF(R138=1,IFERROR(INDEX($B$82:$B$133,MATCH("42Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("42Y",$A$82:$A$133,0))),S136+(S146-S136)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R138=1,IFERROR(INDEX($C$82:$C$133,MATCH("42Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("42Y",$A$82:$A$133,0))),S136+(S146-S136)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T138">
@@ -10055,7 +10060,7 @@
         <v/>
       </c>
       <c r="S139" s="19">
-        <f>IFERROR(IF(R139=1,IFERROR(INDEX($B$82:$B$133,MATCH("43Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("43Y",$A$82:$A$133,0))),S136+(S146-S136)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R139=1,IFERROR(INDEX($C$82:$C$133,MATCH("43Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("43Y",$A$82:$A$133,0))),S136+(S146-S136)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T139">
@@ -10104,7 +10109,7 @@
         <v/>
       </c>
       <c r="S140" s="19">
-        <f>IFERROR(IF(R140=1,IFERROR(INDEX($B$82:$B$133,MATCH("44Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("44Y",$A$82:$A$133,0))),S136+(S146-S136)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R140=1,IFERROR(INDEX($C$82:$C$133,MATCH("44Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("44Y",$A$82:$A$133,0))),S136+(S146-S136)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T140">
@@ -10153,7 +10158,7 @@
         <v/>
       </c>
       <c r="S141" s="19">
-        <f>IFERROR(IF(R141=1,IFERROR(INDEX($B$82:$B$133,MATCH("45Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("45Y",$A$82:$A$133,0))),S136+(S146-S136)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R141=1,IFERROR(INDEX($C$82:$C$133,MATCH("45Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("45Y",$A$82:$A$133,0))),S136+(S146-S136)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T141">
@@ -10202,7 +10207,7 @@
         <v/>
       </c>
       <c r="S142" s="19">
-        <f>IFERROR(IF(R142=1,IFERROR(INDEX($B$82:$B$133,MATCH("46Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("46Y",$A$82:$A$133,0))),S136+(S146-S136)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R142=1,IFERROR(INDEX($C$82:$C$133,MATCH("46Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("46Y",$A$82:$A$133,0))),S136+(S146-S136)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T142">
@@ -10251,7 +10256,7 @@
         <v/>
       </c>
       <c r="S143" s="19">
-        <f>IFERROR(IF(R143=1,IFERROR(INDEX($B$82:$B$133,MATCH("47Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("47Y",$A$82:$A$133,0))),S136+(S146-S136)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R143=1,IFERROR(INDEX($C$82:$C$133,MATCH("47Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("47Y",$A$82:$A$133,0))),S136+(S146-S136)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T143">
@@ -10300,7 +10305,7 @@
         <v/>
       </c>
       <c r="S144" s="19">
-        <f>IFERROR(IF(R144=1,IFERROR(INDEX($B$82:$B$133,MATCH("48Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("48Y",$A$82:$A$133,0))),S136+(S146-S136)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R144=1,IFERROR(INDEX($C$82:$C$133,MATCH("48Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("48Y",$A$82:$A$133,0))),S136+(S146-S136)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T144">
@@ -10349,7 +10354,7 @@
         <v/>
       </c>
       <c r="S145" s="19">
-        <f>IFERROR(IF(R145=1,IFERROR(INDEX($B$82:$B$133,MATCH("49Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("49Y",$A$82:$A$133,0))),S136+(S146-S136)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R145=1,IFERROR(INDEX($C$82:$C$133,MATCH("49Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("49Y",$A$82:$A$133,0))),S136+(S146-S136)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T145">
@@ -10398,7 +10403,7 @@
         <v/>
       </c>
       <c r="S146" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$82:$B$133,MATCH("50Y",$A$82:$A$133,0)),INDEX($B$82:$B$133,MATCH("50Y",$A$82:$A$133,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("50Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("50Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
       <c r="U146" s="20">
@@ -10484,7 +10489,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Paste the yellow columns. Everything green is computed on this sheet — nothing here points at another sheet.</t>
+          <t>Paste YELLOW: tenor into A, then swap mid / BBG zero / BBG discount into C:E. Green is computed here — this sheet points at nothing outside itself.</t>
         </is>
       </c>
     </row>
@@ -10520,32 +10525,32 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
           <t>Swap rate (mid) %</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t>BBG zero %</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="E155" s="6" t="inlineStr">
         <is>
           <t>BBG discount</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>our DF</t>
+          <t>Our zero %</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>our zero %</t>
+          <t>Our discount</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
@@ -10626,27 +10631,27 @@
     </row>
     <row r="156">
       <c r="A156" s="9" t="n"/>
-      <c r="B156" s="10" t="n"/>
-      <c r="C156" s="10" t="n"/>
+      <c r="B156" s="10">
+        <f>IF($A156="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A156,$K$156:$K$220,0),MATCH(IF($A156="1Y","12M",IF($A156="12M","1Y",$A156)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C156" s="11" t="n"/>
       <c r="D156" s="11" t="n"/>
-      <c r="E156" s="12">
-        <f>IF($A156="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A156,$K$156:$K$220,0),MATCH(IF($A156="1Y","12M",IF($A156="12M","1Y",$A156)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E156" s="12" t="n"/>
       <c r="F156" s="13">
+        <f>IF(OR($A156="",G156=""),"",-LN(G156)/((B156-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G156" s="14">
         <f>IF($A156="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A156,$K$156:$K$220,0),MATCH(IF($A156="1Y","12M",IF($A156="12M","1Y",$A156)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G156" s="14">
-        <f>IF(OR($A156="",F156=""),"",-LN(F156)/((E156-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H156" s="15">
-        <f>IF(OR(G156="",NOT(ISNUMBER(C156))),"",(G156-C156)*100)</f>
+        <f>IF(OR(F156="",NOT(ISNUMBER(D156))),"",(F156-D156)*100)</f>
         <v/>
       </c>
       <c r="I156" s="16">
-        <f>IF(OR(F156="",NOT(ISNUMBER(D156))),"",F156-D156)</f>
+        <f>IF(OR(G156="",NOT(ISNUMBER(E156))),"",G156-E156)</f>
         <v/>
       </c>
       <c r="K156" s="17" t="inlineStr">
@@ -10681,7 +10686,7 @@
         <v/>
       </c>
       <c r="S156" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("1W",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("1W",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("1W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U156" s="20">
@@ -10695,27 +10700,27 @@
     </row>
     <row r="157">
       <c r="A157" s="9" t="n"/>
-      <c r="B157" s="10" t="n"/>
-      <c r="C157" s="10" t="n"/>
+      <c r="B157" s="10">
+        <f>IF($A157="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A157,$K$156:$K$220,0),MATCH(IF($A157="1Y","12M",IF($A157="12M","1Y",$A157)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C157" s="11" t="n"/>
       <c r="D157" s="11" t="n"/>
-      <c r="E157" s="12">
-        <f>IF($A157="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A157,$K$156:$K$220,0),MATCH(IF($A157="1Y","12M",IF($A157="12M","1Y",$A157)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E157" s="12" t="n"/>
       <c r="F157" s="13">
+        <f>IF(OR($A157="",G157=""),"",-LN(G157)/((B157-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G157" s="14">
         <f>IF($A157="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A157,$K$156:$K$220,0),MATCH(IF($A157="1Y","12M",IF($A157="12M","1Y",$A157)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G157" s="14">
-        <f>IF(OR($A157="",F157=""),"",-LN(F157)/((E157-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H157" s="15">
-        <f>IF(OR(G157="",NOT(ISNUMBER(C157))),"",(G157-C157)*100)</f>
+        <f>IF(OR(F157="",NOT(ISNUMBER(D157))),"",(F157-D157)*100)</f>
         <v/>
       </c>
       <c r="I157" s="16">
-        <f>IF(OR(F157="",NOT(ISNUMBER(D157))),"",F157-D157)</f>
+        <f>IF(OR(G157="",NOT(ISNUMBER(E157))),"",G157-E157)</f>
         <v/>
       </c>
       <c r="K157" s="17" t="inlineStr">
@@ -10750,7 +10755,7 @@
         <v/>
       </c>
       <c r="S157" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("2W",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("2W",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U157" s="20">
@@ -10764,27 +10769,27 @@
     </row>
     <row r="158">
       <c r="A158" s="9" t="n"/>
-      <c r="B158" s="10" t="n"/>
-      <c r="C158" s="10" t="n"/>
+      <c r="B158" s="10">
+        <f>IF($A158="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A158,$K$156:$K$220,0),MATCH(IF($A158="1Y","12M",IF($A158="12M","1Y",$A158)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C158" s="11" t="n"/>
       <c r="D158" s="11" t="n"/>
-      <c r="E158" s="12">
-        <f>IF($A158="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A158,$K$156:$K$220,0),MATCH(IF($A158="1Y","12M",IF($A158="12M","1Y",$A158)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E158" s="12" t="n"/>
       <c r="F158" s="13">
+        <f>IF(OR($A158="",G158=""),"",-LN(G158)/((B158-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G158" s="14">
         <f>IF($A158="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A158,$K$156:$K$220,0),MATCH(IF($A158="1Y","12M",IF($A158="12M","1Y",$A158)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G158" s="14">
-        <f>IF(OR($A158="",F158=""),"",-LN(F158)/((E158-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H158" s="15">
-        <f>IF(OR(G158="",NOT(ISNUMBER(C158))),"",(G158-C158)*100)</f>
+        <f>IF(OR(F158="",NOT(ISNUMBER(D158))),"",(F158-D158)*100)</f>
         <v/>
       </c>
       <c r="I158" s="16">
-        <f>IF(OR(F158="",NOT(ISNUMBER(D158))),"",F158-D158)</f>
+        <f>IF(OR(G158="",NOT(ISNUMBER(E158))),"",G158-E158)</f>
         <v/>
       </c>
       <c r="K158" s="17" t="inlineStr">
@@ -10819,7 +10824,7 @@
         <v/>
       </c>
       <c r="S158" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("3W",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("3W",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U158" s="20">
@@ -10833,27 +10838,27 @@
     </row>
     <row r="159">
       <c r="A159" s="9" t="n"/>
-      <c r="B159" s="10" t="n"/>
-      <c r="C159" s="10" t="n"/>
+      <c r="B159" s="10">
+        <f>IF($A159="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A159,$K$156:$K$220,0),MATCH(IF($A159="1Y","12M",IF($A159="12M","1Y",$A159)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C159" s="11" t="n"/>
       <c r="D159" s="11" t="n"/>
-      <c r="E159" s="12">
-        <f>IF($A159="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A159,$K$156:$K$220,0),MATCH(IF($A159="1Y","12M",IF($A159="12M","1Y",$A159)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E159" s="12" t="n"/>
       <c r="F159" s="13">
+        <f>IF(OR($A159="",G159=""),"",-LN(G159)/((B159-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G159" s="14">
         <f>IF($A159="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A159,$K$156:$K$220,0),MATCH(IF($A159="1Y","12M",IF($A159="12M","1Y",$A159)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G159" s="14">
-        <f>IF(OR($A159="",F159=""),"",-LN(F159)/((E159-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H159" s="15">
-        <f>IF(OR(G159="",NOT(ISNUMBER(C159))),"",(G159-C159)*100)</f>
+        <f>IF(OR(F159="",NOT(ISNUMBER(D159))),"",(F159-D159)*100)</f>
         <v/>
       </c>
       <c r="I159" s="16">
-        <f>IF(OR(F159="",NOT(ISNUMBER(D159))),"",F159-D159)</f>
+        <f>IF(OR(G159="",NOT(ISNUMBER(E159))),"",G159-E159)</f>
         <v/>
       </c>
       <c r="K159" s="17" t="inlineStr">
@@ -10888,7 +10893,7 @@
         <v/>
       </c>
       <c r="S159" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("1M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("1M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("1M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U159" s="20">
@@ -10902,27 +10907,27 @@
     </row>
     <row r="160">
       <c r="A160" s="9" t="n"/>
-      <c r="B160" s="10" t="n"/>
-      <c r="C160" s="10" t="n"/>
+      <c r="B160" s="10">
+        <f>IF($A160="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A160,$K$156:$K$220,0),MATCH(IF($A160="1Y","12M",IF($A160="12M","1Y",$A160)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C160" s="11" t="n"/>
       <c r="D160" s="11" t="n"/>
-      <c r="E160" s="12">
-        <f>IF($A160="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A160,$K$156:$K$220,0),MATCH(IF($A160="1Y","12M",IF($A160="12M","1Y",$A160)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E160" s="12" t="n"/>
       <c r="F160" s="13">
+        <f>IF(OR($A160="",G160=""),"",-LN(G160)/((B160-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G160" s="14">
         <f>IF($A160="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A160,$K$156:$K$220,0),MATCH(IF($A160="1Y","12M",IF($A160="12M","1Y",$A160)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G160" s="14">
-        <f>IF(OR($A160="",F160=""),"",-LN(F160)/((E160-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H160" s="15">
-        <f>IF(OR(G160="",NOT(ISNUMBER(C160))),"",(G160-C160)*100)</f>
+        <f>IF(OR(F160="",NOT(ISNUMBER(D160))),"",(F160-D160)*100)</f>
         <v/>
       </c>
       <c r="I160" s="16">
-        <f>IF(OR(F160="",NOT(ISNUMBER(D160))),"",F160-D160)</f>
+        <f>IF(OR(G160="",NOT(ISNUMBER(E160))),"",G160-E160)</f>
         <v/>
       </c>
       <c r="K160" s="17" t="inlineStr">
@@ -10957,7 +10962,7 @@
         <v/>
       </c>
       <c r="S160" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("2M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("2M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U160" s="20">
@@ -10971,27 +10976,27 @@
     </row>
     <row r="161">
       <c r="A161" s="9" t="n"/>
-      <c r="B161" s="10" t="n"/>
-      <c r="C161" s="10" t="n"/>
+      <c r="B161" s="10">
+        <f>IF($A161="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A161,$K$156:$K$220,0),MATCH(IF($A161="1Y","12M",IF($A161="12M","1Y",$A161)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C161" s="11" t="n"/>
       <c r="D161" s="11" t="n"/>
-      <c r="E161" s="12">
-        <f>IF($A161="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A161,$K$156:$K$220,0),MATCH(IF($A161="1Y","12M",IF($A161="12M","1Y",$A161)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E161" s="12" t="n"/>
       <c r="F161" s="13">
+        <f>IF(OR($A161="",G161=""),"",-LN(G161)/((B161-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G161" s="14">
         <f>IF($A161="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A161,$K$156:$K$220,0),MATCH(IF($A161="1Y","12M",IF($A161="12M","1Y",$A161)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G161" s="14">
-        <f>IF(OR($A161="",F161=""),"",-LN(F161)/((E161-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H161" s="15">
-        <f>IF(OR(G161="",NOT(ISNUMBER(C161))),"",(G161-C161)*100)</f>
+        <f>IF(OR(F161="",NOT(ISNUMBER(D161))),"",(F161-D161)*100)</f>
         <v/>
       </c>
       <c r="I161" s="16">
-        <f>IF(OR(F161="",NOT(ISNUMBER(D161))),"",F161-D161)</f>
+        <f>IF(OR(G161="",NOT(ISNUMBER(E161))),"",G161-E161)</f>
         <v/>
       </c>
       <c r="K161" s="17" t="inlineStr">
@@ -11026,7 +11031,7 @@
         <v/>
       </c>
       <c r="S161" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("3M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("3M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U161" s="20">
@@ -11040,27 +11045,27 @@
     </row>
     <row r="162">
       <c r="A162" s="9" t="n"/>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="10" t="n"/>
+      <c r="B162" s="10">
+        <f>IF($A162="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A162,$K$156:$K$220,0),MATCH(IF($A162="1Y","12M",IF($A162="12M","1Y",$A162)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C162" s="11" t="n"/>
       <c r="D162" s="11" t="n"/>
-      <c r="E162" s="12">
-        <f>IF($A162="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A162,$K$156:$K$220,0),MATCH(IF($A162="1Y","12M",IF($A162="12M","1Y",$A162)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E162" s="12" t="n"/>
       <c r="F162" s="13">
+        <f>IF(OR($A162="",G162=""),"",-LN(G162)/((B162-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G162" s="14">
         <f>IF($A162="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A162,$K$156:$K$220,0),MATCH(IF($A162="1Y","12M",IF($A162="12M","1Y",$A162)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G162" s="14">
-        <f>IF(OR($A162="",F162=""),"",-LN(F162)/((E162-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H162" s="15">
-        <f>IF(OR(G162="",NOT(ISNUMBER(C162))),"",(G162-C162)*100)</f>
+        <f>IF(OR(F162="",NOT(ISNUMBER(D162))),"",(F162-D162)*100)</f>
         <v/>
       </c>
       <c r="I162" s="16">
-        <f>IF(OR(F162="",NOT(ISNUMBER(D162))),"",F162-D162)</f>
+        <f>IF(OR(G162="",NOT(ISNUMBER(E162))),"",G162-E162)</f>
         <v/>
       </c>
       <c r="K162" s="17" t="inlineStr">
@@ -11095,7 +11100,7 @@
         <v/>
       </c>
       <c r="S162" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("4M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("4M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("4M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("4M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U162" s="20">
@@ -11109,27 +11114,27 @@
     </row>
     <row r="163">
       <c r="A163" s="9" t="n"/>
-      <c r="B163" s="10" t="n"/>
-      <c r="C163" s="10" t="n"/>
+      <c r="B163" s="10">
+        <f>IF($A163="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A163,$K$156:$K$220,0),MATCH(IF($A163="1Y","12M",IF($A163="12M","1Y",$A163)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C163" s="11" t="n"/>
       <c r="D163" s="11" t="n"/>
-      <c r="E163" s="12">
-        <f>IF($A163="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A163,$K$156:$K$220,0),MATCH(IF($A163="1Y","12M",IF($A163="12M","1Y",$A163)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E163" s="12" t="n"/>
       <c r="F163" s="13">
+        <f>IF(OR($A163="",G163=""),"",-LN(G163)/((B163-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G163" s="14">
         <f>IF($A163="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A163,$K$156:$K$220,0),MATCH(IF($A163="1Y","12M",IF($A163="12M","1Y",$A163)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G163" s="14">
-        <f>IF(OR($A163="",F163=""),"",-LN(F163)/((E163-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H163" s="15">
-        <f>IF(OR(G163="",NOT(ISNUMBER(C163))),"",(G163-C163)*100)</f>
+        <f>IF(OR(F163="",NOT(ISNUMBER(D163))),"",(F163-D163)*100)</f>
         <v/>
       </c>
       <c r="I163" s="16">
-        <f>IF(OR(F163="",NOT(ISNUMBER(D163))),"",F163-D163)</f>
+        <f>IF(OR(G163="",NOT(ISNUMBER(E163))),"",G163-E163)</f>
         <v/>
       </c>
       <c r="K163" s="17" t="inlineStr">
@@ -11164,7 +11169,7 @@
         <v/>
       </c>
       <c r="S163" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("5M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("5M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("5M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("5M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U163" s="20">
@@ -11178,27 +11183,27 @@
     </row>
     <row r="164">
       <c r="A164" s="9" t="n"/>
-      <c r="B164" s="10" t="n"/>
-      <c r="C164" s="10" t="n"/>
+      <c r="B164" s="10">
+        <f>IF($A164="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A164,$K$156:$K$220,0),MATCH(IF($A164="1Y","12M",IF($A164="12M","1Y",$A164)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C164" s="11" t="n"/>
       <c r="D164" s="11" t="n"/>
-      <c r="E164" s="12">
-        <f>IF($A164="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A164,$K$156:$K$220,0),MATCH(IF($A164="1Y","12M",IF($A164="12M","1Y",$A164)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E164" s="12" t="n"/>
       <c r="F164" s="13">
+        <f>IF(OR($A164="",G164=""),"",-LN(G164)/((B164-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G164" s="14">
         <f>IF($A164="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A164,$K$156:$K$220,0),MATCH(IF($A164="1Y","12M",IF($A164="12M","1Y",$A164)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G164" s="14">
-        <f>IF(OR($A164="",F164=""),"",-LN(F164)/((E164-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H164" s="15">
-        <f>IF(OR(G164="",NOT(ISNUMBER(C164))),"",(G164-C164)*100)</f>
+        <f>IF(OR(F164="",NOT(ISNUMBER(D164))),"",(F164-D164)*100)</f>
         <v/>
       </c>
       <c r="I164" s="16">
-        <f>IF(OR(F164="",NOT(ISNUMBER(D164))),"",F164-D164)</f>
+        <f>IF(OR(G164="",NOT(ISNUMBER(E164))),"",G164-E164)</f>
         <v/>
       </c>
       <c r="K164" s="17" t="inlineStr">
@@ -11233,7 +11238,7 @@
         <v/>
       </c>
       <c r="S164" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("6M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("6M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("6M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("6M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U164" s="20">
@@ -11247,27 +11252,27 @@
     </row>
     <row r="165">
       <c r="A165" s="9" t="n"/>
-      <c r="B165" s="10" t="n"/>
-      <c r="C165" s="10" t="n"/>
+      <c r="B165" s="10">
+        <f>IF($A165="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A165,$K$156:$K$220,0),MATCH(IF($A165="1Y","12M",IF($A165="12M","1Y",$A165)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C165" s="11" t="n"/>
       <c r="D165" s="11" t="n"/>
-      <c r="E165" s="12">
-        <f>IF($A165="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A165,$K$156:$K$220,0),MATCH(IF($A165="1Y","12M",IF($A165="12M","1Y",$A165)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E165" s="12" t="n"/>
       <c r="F165" s="13">
+        <f>IF(OR($A165="",G165=""),"",-LN(G165)/((B165-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G165" s="14">
         <f>IF($A165="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A165,$K$156:$K$220,0),MATCH(IF($A165="1Y","12M",IF($A165="12M","1Y",$A165)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G165" s="14">
-        <f>IF(OR($A165="",F165=""),"",-LN(F165)/((E165-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H165" s="15">
-        <f>IF(OR(G165="",NOT(ISNUMBER(C165))),"",(G165-C165)*100)</f>
+        <f>IF(OR(F165="",NOT(ISNUMBER(D165))),"",(F165-D165)*100)</f>
         <v/>
       </c>
       <c r="I165" s="16">
-        <f>IF(OR(F165="",NOT(ISNUMBER(D165))),"",F165-D165)</f>
+        <f>IF(OR(G165="",NOT(ISNUMBER(E165))),"",G165-E165)</f>
         <v/>
       </c>
       <c r="K165" s="17" t="inlineStr">
@@ -11302,7 +11307,7 @@
         <v/>
       </c>
       <c r="S165" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("7M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("7M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("7M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("7M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U165" s="20">
@@ -11316,27 +11321,27 @@
     </row>
     <row r="166">
       <c r="A166" s="9" t="n"/>
-      <c r="B166" s="10" t="n"/>
-      <c r="C166" s="10" t="n"/>
+      <c r="B166" s="10">
+        <f>IF($A166="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A166,$K$156:$K$220,0),MATCH(IF($A166="1Y","12M",IF($A166="12M","1Y",$A166)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C166" s="11" t="n"/>
       <c r="D166" s="11" t="n"/>
-      <c r="E166" s="12">
-        <f>IF($A166="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A166,$K$156:$K$220,0),MATCH(IF($A166="1Y","12M",IF($A166="12M","1Y",$A166)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E166" s="12" t="n"/>
       <c r="F166" s="13">
+        <f>IF(OR($A166="",G166=""),"",-LN(G166)/((B166-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G166" s="14">
         <f>IF($A166="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A166,$K$156:$K$220,0),MATCH(IF($A166="1Y","12M",IF($A166="12M","1Y",$A166)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G166" s="14">
-        <f>IF(OR($A166="",F166=""),"",-LN(F166)/((E166-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H166" s="15">
-        <f>IF(OR(G166="",NOT(ISNUMBER(C166))),"",(G166-C166)*100)</f>
+        <f>IF(OR(F166="",NOT(ISNUMBER(D166))),"",(F166-D166)*100)</f>
         <v/>
       </c>
       <c r="I166" s="16">
-        <f>IF(OR(F166="",NOT(ISNUMBER(D166))),"",F166-D166)</f>
+        <f>IF(OR(G166="",NOT(ISNUMBER(E166))),"",G166-E166)</f>
         <v/>
       </c>
       <c r="K166" s="17" t="inlineStr">
@@ -11371,7 +11376,7 @@
         <v/>
       </c>
       <c r="S166" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("8M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("8M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("8M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("8M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U166" s="20">
@@ -11385,27 +11390,27 @@
     </row>
     <row r="167">
       <c r="A167" s="9" t="n"/>
-      <c r="B167" s="10" t="n"/>
-      <c r="C167" s="10" t="n"/>
+      <c r="B167" s="10">
+        <f>IF($A167="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A167,$K$156:$K$220,0),MATCH(IF($A167="1Y","12M",IF($A167="12M","1Y",$A167)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C167" s="11" t="n"/>
       <c r="D167" s="11" t="n"/>
-      <c r="E167" s="12">
-        <f>IF($A167="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A167,$K$156:$K$220,0),MATCH(IF($A167="1Y","12M",IF($A167="12M","1Y",$A167)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E167" s="12" t="n"/>
       <c r="F167" s="13">
+        <f>IF(OR($A167="",G167=""),"",-LN(G167)/((B167-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G167" s="14">
         <f>IF($A167="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A167,$K$156:$K$220,0),MATCH(IF($A167="1Y","12M",IF($A167="12M","1Y",$A167)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G167" s="14">
-        <f>IF(OR($A167="",F167=""),"",-LN(F167)/((E167-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H167" s="15">
-        <f>IF(OR(G167="",NOT(ISNUMBER(C167))),"",(G167-C167)*100)</f>
+        <f>IF(OR(F167="",NOT(ISNUMBER(D167))),"",(F167-D167)*100)</f>
         <v/>
       </c>
       <c r="I167" s="16">
-        <f>IF(OR(F167="",NOT(ISNUMBER(D167))),"",F167-D167)</f>
+        <f>IF(OR(G167="",NOT(ISNUMBER(E167))),"",G167-E167)</f>
         <v/>
       </c>
       <c r="K167" s="17" t="inlineStr">
@@ -11440,7 +11445,7 @@
         <v/>
       </c>
       <c r="S167" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("9M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("9M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("9M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("9M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U167" s="20">
@@ -11454,27 +11459,27 @@
     </row>
     <row r="168">
       <c r="A168" s="9" t="n"/>
-      <c r="B168" s="10" t="n"/>
-      <c r="C168" s="10" t="n"/>
+      <c r="B168" s="10">
+        <f>IF($A168="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A168,$K$156:$K$220,0),MATCH(IF($A168="1Y","12M",IF($A168="12M","1Y",$A168)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C168" s="11" t="n"/>
       <c r="D168" s="11" t="n"/>
-      <c r="E168" s="12">
-        <f>IF($A168="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A168,$K$156:$K$220,0),MATCH(IF($A168="1Y","12M",IF($A168="12M","1Y",$A168)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E168" s="12" t="n"/>
       <c r="F168" s="13">
+        <f>IF(OR($A168="",G168=""),"",-LN(G168)/((B168-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G168" s="14">
         <f>IF($A168="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A168,$K$156:$K$220,0),MATCH(IF($A168="1Y","12M",IF($A168="12M","1Y",$A168)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G168" s="14">
-        <f>IF(OR($A168="",F168=""),"",-LN(F168)/((E168-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H168" s="15">
-        <f>IF(OR(G168="",NOT(ISNUMBER(C168))),"",(G168-C168)*100)</f>
+        <f>IF(OR(F168="",NOT(ISNUMBER(D168))),"",(F168-D168)*100)</f>
         <v/>
       </c>
       <c r="I168" s="16">
-        <f>IF(OR(F168="",NOT(ISNUMBER(D168))),"",F168-D168)</f>
+        <f>IF(OR(G168="",NOT(ISNUMBER(E168))),"",G168-E168)</f>
         <v/>
       </c>
       <c r="K168" s="17" t="inlineStr">
@@ -11509,7 +11514,7 @@
         <v/>
       </c>
       <c r="S168" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("10M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("10M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("10M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("10M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U168" s="20">
@@ -11523,27 +11528,27 @@
     </row>
     <row r="169">
       <c r="A169" s="9" t="n"/>
-      <c r="B169" s="10" t="n"/>
-      <c r="C169" s="10" t="n"/>
+      <c r="B169" s="10">
+        <f>IF($A169="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A169,$K$156:$K$220,0),MATCH(IF($A169="1Y","12M",IF($A169="12M","1Y",$A169)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C169" s="11" t="n"/>
       <c r="D169" s="11" t="n"/>
-      <c r="E169" s="12">
-        <f>IF($A169="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A169,$K$156:$K$220,0),MATCH(IF($A169="1Y","12M",IF($A169="12M","1Y",$A169)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E169" s="12" t="n"/>
       <c r="F169" s="13">
+        <f>IF(OR($A169="",G169=""),"",-LN(G169)/((B169-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G169" s="14">
         <f>IF($A169="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A169,$K$156:$K$220,0),MATCH(IF($A169="1Y","12M",IF($A169="12M","1Y",$A169)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G169" s="14">
-        <f>IF(OR($A169="",F169=""),"",-LN(F169)/((E169-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H169" s="15">
-        <f>IF(OR(G169="",NOT(ISNUMBER(C169))),"",(G169-C169)*100)</f>
+        <f>IF(OR(F169="",NOT(ISNUMBER(D169))),"",(F169-D169)*100)</f>
         <v/>
       </c>
       <c r="I169" s="16">
-        <f>IF(OR(F169="",NOT(ISNUMBER(D169))),"",F169-D169)</f>
+        <f>IF(OR(G169="",NOT(ISNUMBER(E169))),"",G169-E169)</f>
         <v/>
       </c>
       <c r="K169" s="17" t="inlineStr">
@@ -11578,7 +11583,7 @@
         <v/>
       </c>
       <c r="S169" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("11M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("11M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("11M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("11M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U169" s="20">
@@ -11592,27 +11597,27 @@
     </row>
     <row r="170">
       <c r="A170" s="9" t="n"/>
-      <c r="B170" s="10" t="n"/>
-      <c r="C170" s="10" t="n"/>
+      <c r="B170" s="10">
+        <f>IF($A170="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A170,$K$156:$K$220,0),MATCH(IF($A170="1Y","12M",IF($A170="12M","1Y",$A170)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C170" s="11" t="n"/>
       <c r="D170" s="11" t="n"/>
-      <c r="E170" s="12">
-        <f>IF($A170="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A170,$K$156:$K$220,0),MATCH(IF($A170="1Y","12M",IF($A170="12M","1Y",$A170)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E170" s="12" t="n"/>
       <c r="F170" s="13">
+        <f>IF(OR($A170="",G170=""),"",-LN(G170)/((B170-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G170" s="14">
         <f>IF($A170="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A170,$K$156:$K$220,0),MATCH(IF($A170="1Y","12M",IF($A170="12M","1Y",$A170)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G170" s="14">
-        <f>IF(OR($A170="",F170=""),"",-LN(F170)/((E170-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H170" s="15">
-        <f>IF(OR(G170="",NOT(ISNUMBER(C170))),"",(G170-C170)*100)</f>
+        <f>IF(OR(F170="",NOT(ISNUMBER(D170))),"",(F170-D170)*100)</f>
         <v/>
       </c>
       <c r="I170" s="16">
-        <f>IF(OR(F170="",NOT(ISNUMBER(D170))),"",F170-D170)</f>
+        <f>IF(OR(G170="",NOT(ISNUMBER(E170))),"",G170-E170)</f>
         <v/>
       </c>
       <c r="K170" s="17" t="inlineStr">
@@ -11647,7 +11652,7 @@
         <v/>
       </c>
       <c r="S170" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("12M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("1Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("12M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U170" s="20">
@@ -11661,27 +11666,27 @@
     </row>
     <row r="171">
       <c r="A171" s="9" t="n"/>
-      <c r="B171" s="10" t="n"/>
-      <c r="C171" s="10" t="n"/>
+      <c r="B171" s="10">
+        <f>IF($A171="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A171,$K$156:$K$220,0),MATCH(IF($A171="1Y","12M",IF($A171="12M","1Y",$A171)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C171" s="11" t="n"/>
       <c r="D171" s="11" t="n"/>
-      <c r="E171" s="12">
-        <f>IF($A171="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A171,$K$156:$K$220,0),MATCH(IF($A171="1Y","12M",IF($A171="12M","1Y",$A171)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E171" s="12" t="n"/>
       <c r="F171" s="13">
+        <f>IF(OR($A171="",G171=""),"",-LN(G171)/((B171-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G171" s="14">
         <f>IF($A171="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A171,$K$156:$K$220,0),MATCH(IF($A171="1Y","12M",IF($A171="12M","1Y",$A171)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G171" s="14">
-        <f>IF(OR($A171="",F171=""),"",-LN(F171)/((E171-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H171" s="15">
-        <f>IF(OR(G171="",NOT(ISNUMBER(C171))),"",(G171-C171)*100)</f>
+        <f>IF(OR(F171="",NOT(ISNUMBER(D171))),"",(F171-D171)*100)</f>
         <v/>
       </c>
       <c r="I171" s="16">
-        <f>IF(OR(F171="",NOT(ISNUMBER(D171))),"",F171-D171)</f>
+        <f>IF(OR(G171="",NOT(ISNUMBER(E171))),"",G171-E171)</f>
         <v/>
       </c>
       <c r="K171" s="17" t="inlineStr">
@@ -11716,7 +11721,7 @@
         <v/>
       </c>
       <c r="S171" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("18M",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("18M",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("18M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("18M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U171" s="20">
@@ -11730,27 +11735,27 @@
     </row>
     <row r="172">
       <c r="A172" s="9" t="n"/>
-      <c r="B172" s="10" t="n"/>
-      <c r="C172" s="10" t="n"/>
+      <c r="B172" s="10">
+        <f>IF($A172="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A172,$K$156:$K$220,0),MATCH(IF($A172="1Y","12M",IF($A172="12M","1Y",$A172)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C172" s="11" t="n"/>
       <c r="D172" s="11" t="n"/>
-      <c r="E172" s="12">
-        <f>IF($A172="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A172,$K$156:$K$220,0),MATCH(IF($A172="1Y","12M",IF($A172="12M","1Y",$A172)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E172" s="12" t="n"/>
       <c r="F172" s="13">
+        <f>IF(OR($A172="",G172=""),"",-LN(G172)/((B172-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G172" s="14">
         <f>IF($A172="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A172,$K$156:$K$220,0),MATCH(IF($A172="1Y","12M",IF($A172="12M","1Y",$A172)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G172" s="14">
-        <f>IF(OR($A172="",F172=""),"",-LN(F172)/((E172-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H172" s="15">
-        <f>IF(OR(G172="",NOT(ISNUMBER(C172))),"",(G172-C172)*100)</f>
+        <f>IF(OR(F172="",NOT(ISNUMBER(D172))),"",(F172-D172)*100)</f>
         <v/>
       </c>
       <c r="I172" s="16">
-        <f>IF(OR(F172="",NOT(ISNUMBER(D172))),"",F172-D172)</f>
+        <f>IF(OR(G172="",NOT(ISNUMBER(E172))),"",G172-E172)</f>
         <v/>
       </c>
       <c r="K172" s="17" t="inlineStr">
@@ -11785,7 +11790,7 @@
         <v/>
       </c>
       <c r="S172" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("2Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("2Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U172" s="20">
@@ -11799,27 +11804,27 @@
     </row>
     <row r="173">
       <c r="A173" s="9" t="n"/>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="10" t="n"/>
+      <c r="B173" s="10">
+        <f>IF($A173="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A173,$K$156:$K$220,0),MATCH(IF($A173="1Y","12M",IF($A173="12M","1Y",$A173)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C173" s="11" t="n"/>
       <c r="D173" s="11" t="n"/>
-      <c r="E173" s="12">
-        <f>IF($A173="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A173,$K$156:$K$220,0),MATCH(IF($A173="1Y","12M",IF($A173="12M","1Y",$A173)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E173" s="12" t="n"/>
       <c r="F173" s="13">
+        <f>IF(OR($A173="",G173=""),"",-LN(G173)/((B173-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G173" s="14">
         <f>IF($A173="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A173,$K$156:$K$220,0),MATCH(IF($A173="1Y","12M",IF($A173="12M","1Y",$A173)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G173" s="14">
-        <f>IF(OR($A173="",F173=""),"",-LN(F173)/((E173-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H173" s="15">
-        <f>IF(OR(G173="",NOT(ISNUMBER(C173))),"",(G173-C173)*100)</f>
+        <f>IF(OR(F173="",NOT(ISNUMBER(D173))),"",(F173-D173)*100)</f>
         <v/>
       </c>
       <c r="I173" s="16">
-        <f>IF(OR(F173="",NOT(ISNUMBER(D173))),"",F173-D173)</f>
+        <f>IF(OR(G173="",NOT(ISNUMBER(E173))),"",G173-E173)</f>
         <v/>
       </c>
       <c r="K173" s="17" t="inlineStr">
@@ -11854,7 +11859,7 @@
         <v/>
       </c>
       <c r="S173" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("3Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("3Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U173" s="20">
@@ -11868,27 +11873,27 @@
     </row>
     <row r="174">
       <c r="A174" s="9" t="n"/>
-      <c r="B174" s="10" t="n"/>
-      <c r="C174" s="10" t="n"/>
+      <c r="B174" s="10">
+        <f>IF($A174="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A174,$K$156:$K$220,0),MATCH(IF($A174="1Y","12M",IF($A174="12M","1Y",$A174)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C174" s="11" t="n"/>
       <c r="D174" s="11" t="n"/>
-      <c r="E174" s="12">
-        <f>IF($A174="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A174,$K$156:$K$220,0),MATCH(IF($A174="1Y","12M",IF($A174="12M","1Y",$A174)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E174" s="12" t="n"/>
       <c r="F174" s="13">
+        <f>IF(OR($A174="",G174=""),"",-LN(G174)/((B174-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G174" s="14">
         <f>IF($A174="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A174,$K$156:$K$220,0),MATCH(IF($A174="1Y","12M",IF($A174="12M","1Y",$A174)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G174" s="14">
-        <f>IF(OR($A174="",F174=""),"",-LN(F174)/((E174-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H174" s="15">
-        <f>IF(OR(G174="",NOT(ISNUMBER(C174))),"",(G174-C174)*100)</f>
+        <f>IF(OR(F174="",NOT(ISNUMBER(D174))),"",(F174-D174)*100)</f>
         <v/>
       </c>
       <c r="I174" s="16">
-        <f>IF(OR(F174="",NOT(ISNUMBER(D174))),"",F174-D174)</f>
+        <f>IF(OR(G174="",NOT(ISNUMBER(E174))),"",G174-E174)</f>
         <v/>
       </c>
       <c r="K174" s="17" t="inlineStr">
@@ -11923,7 +11928,7 @@
         <v/>
       </c>
       <c r="S174" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("4Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("4Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("4Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("4Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U174" s="20">
@@ -11937,27 +11942,27 @@
     </row>
     <row r="175">
       <c r="A175" s="9" t="n"/>
-      <c r="B175" s="10" t="n"/>
-      <c r="C175" s="10" t="n"/>
+      <c r="B175" s="10">
+        <f>IF($A175="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A175,$K$156:$K$220,0),MATCH(IF($A175="1Y","12M",IF($A175="12M","1Y",$A175)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C175" s="11" t="n"/>
       <c r="D175" s="11" t="n"/>
-      <c r="E175" s="12">
-        <f>IF($A175="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A175,$K$156:$K$220,0),MATCH(IF($A175="1Y","12M",IF($A175="12M","1Y",$A175)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E175" s="12" t="n"/>
       <c r="F175" s="13">
+        <f>IF(OR($A175="",G175=""),"",-LN(G175)/((B175-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G175" s="14">
         <f>IF($A175="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A175,$K$156:$K$220,0),MATCH(IF($A175="1Y","12M",IF($A175="12M","1Y",$A175)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G175" s="14">
-        <f>IF(OR($A175="",F175=""),"",-LN(F175)/((E175-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H175" s="15">
-        <f>IF(OR(G175="",NOT(ISNUMBER(C175))),"",(G175-C175)*100)</f>
+        <f>IF(OR(F175="",NOT(ISNUMBER(D175))),"",(F175-D175)*100)</f>
         <v/>
       </c>
       <c r="I175" s="16">
-        <f>IF(OR(F175="",NOT(ISNUMBER(D175))),"",F175-D175)</f>
+        <f>IF(OR(G175="",NOT(ISNUMBER(E175))),"",G175-E175)</f>
         <v/>
       </c>
       <c r="K175" s="17" t="inlineStr">
@@ -11992,7 +11997,7 @@
         <v/>
       </c>
       <c r="S175" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("5Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("5Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("5Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("5Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U175" s="20">
@@ -12006,27 +12011,27 @@
     </row>
     <row r="176">
       <c r="A176" s="9" t="n"/>
-      <c r="B176" s="10" t="n"/>
-      <c r="C176" s="10" t="n"/>
+      <c r="B176" s="10">
+        <f>IF($A176="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A176,$K$156:$K$220,0),MATCH(IF($A176="1Y","12M",IF($A176="12M","1Y",$A176)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C176" s="11" t="n"/>
       <c r="D176" s="11" t="n"/>
-      <c r="E176" s="12">
-        <f>IF($A176="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A176,$K$156:$K$220,0),MATCH(IF($A176="1Y","12M",IF($A176="12M","1Y",$A176)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E176" s="12" t="n"/>
       <c r="F176" s="13">
+        <f>IF(OR($A176="",G176=""),"",-LN(G176)/((B176-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G176" s="14">
         <f>IF($A176="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A176,$K$156:$K$220,0),MATCH(IF($A176="1Y","12M",IF($A176="12M","1Y",$A176)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G176" s="14">
-        <f>IF(OR($A176="",F176=""),"",-LN(F176)/((E176-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H176" s="15">
-        <f>IF(OR(G176="",NOT(ISNUMBER(C176))),"",(G176-C176)*100)</f>
+        <f>IF(OR(F176="",NOT(ISNUMBER(D176))),"",(F176-D176)*100)</f>
         <v/>
       </c>
       <c r="I176" s="16">
-        <f>IF(OR(F176="",NOT(ISNUMBER(D176))),"",F176-D176)</f>
+        <f>IF(OR(G176="",NOT(ISNUMBER(E176))),"",G176-E176)</f>
         <v/>
       </c>
       <c r="K176" s="17" t="inlineStr">
@@ -12061,7 +12066,7 @@
         <v/>
       </c>
       <c r="S176" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("6Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("6Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("6Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("6Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U176" s="20">
@@ -12075,27 +12080,27 @@
     </row>
     <row r="177">
       <c r="A177" s="9" t="n"/>
-      <c r="B177" s="10" t="n"/>
-      <c r="C177" s="10" t="n"/>
+      <c r="B177" s="10">
+        <f>IF($A177="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A177,$K$156:$K$220,0),MATCH(IF($A177="1Y","12M",IF($A177="12M","1Y",$A177)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C177" s="11" t="n"/>
       <c r="D177" s="11" t="n"/>
-      <c r="E177" s="12">
-        <f>IF($A177="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A177,$K$156:$K$220,0),MATCH(IF($A177="1Y","12M",IF($A177="12M","1Y",$A177)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E177" s="12" t="n"/>
       <c r="F177" s="13">
+        <f>IF(OR($A177="",G177=""),"",-LN(G177)/((B177-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G177" s="14">
         <f>IF($A177="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A177,$K$156:$K$220,0),MATCH(IF($A177="1Y","12M",IF($A177="12M","1Y",$A177)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G177" s="14">
-        <f>IF(OR($A177="",F177=""),"",-LN(F177)/((E177-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H177" s="15">
-        <f>IF(OR(G177="",NOT(ISNUMBER(C177))),"",(G177-C177)*100)</f>
+        <f>IF(OR(F177="",NOT(ISNUMBER(D177))),"",(F177-D177)*100)</f>
         <v/>
       </c>
       <c r="I177" s="16">
-        <f>IF(OR(F177="",NOT(ISNUMBER(D177))),"",F177-D177)</f>
+        <f>IF(OR(G177="",NOT(ISNUMBER(E177))),"",G177-E177)</f>
         <v/>
       </c>
       <c r="K177" s="17" t="inlineStr">
@@ -12130,7 +12135,7 @@
         <v/>
       </c>
       <c r="S177" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("7Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("7Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("7Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("7Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U177" s="20">
@@ -12144,27 +12149,27 @@
     </row>
     <row r="178">
       <c r="A178" s="9" t="n"/>
-      <c r="B178" s="10" t="n"/>
-      <c r="C178" s="10" t="n"/>
+      <c r="B178" s="10">
+        <f>IF($A178="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A178,$K$156:$K$220,0),MATCH(IF($A178="1Y","12M",IF($A178="12M","1Y",$A178)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C178" s="11" t="n"/>
       <c r="D178" s="11" t="n"/>
-      <c r="E178" s="12">
-        <f>IF($A178="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A178,$K$156:$K$220,0),MATCH(IF($A178="1Y","12M",IF($A178="12M","1Y",$A178)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E178" s="12" t="n"/>
       <c r="F178" s="13">
+        <f>IF(OR($A178="",G178=""),"",-LN(G178)/((B178-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G178" s="14">
         <f>IF($A178="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A178,$K$156:$K$220,0),MATCH(IF($A178="1Y","12M",IF($A178="12M","1Y",$A178)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G178" s="14">
-        <f>IF(OR($A178="",F178=""),"",-LN(F178)/((E178-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H178" s="15">
-        <f>IF(OR(G178="",NOT(ISNUMBER(C178))),"",(G178-C178)*100)</f>
+        <f>IF(OR(F178="",NOT(ISNUMBER(D178))),"",(F178-D178)*100)</f>
         <v/>
       </c>
       <c r="I178" s="16">
-        <f>IF(OR(F178="",NOT(ISNUMBER(D178))),"",F178-D178)</f>
+        <f>IF(OR(G178="",NOT(ISNUMBER(E178))),"",G178-E178)</f>
         <v/>
       </c>
       <c r="K178" s="17" t="inlineStr">
@@ -12199,7 +12204,7 @@
         <v/>
       </c>
       <c r="S178" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("8Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("8Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("8Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("8Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U178" s="20">
@@ -12213,27 +12218,27 @@
     </row>
     <row r="179">
       <c r="A179" s="9" t="n"/>
-      <c r="B179" s="10" t="n"/>
-      <c r="C179" s="10" t="n"/>
+      <c r="B179" s="10">
+        <f>IF($A179="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A179,$K$156:$K$220,0),MATCH(IF($A179="1Y","12M",IF($A179="12M","1Y",$A179)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C179" s="11" t="n"/>
       <c r="D179" s="11" t="n"/>
-      <c r="E179" s="12">
-        <f>IF($A179="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A179,$K$156:$K$220,0),MATCH(IF($A179="1Y","12M",IF($A179="12M","1Y",$A179)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E179" s="12" t="n"/>
       <c r="F179" s="13">
+        <f>IF(OR($A179="",G179=""),"",-LN(G179)/((B179-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G179" s="14">
         <f>IF($A179="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A179,$K$156:$K$220,0),MATCH(IF($A179="1Y","12M",IF($A179="12M","1Y",$A179)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G179" s="14">
-        <f>IF(OR($A179="",F179=""),"",-LN(F179)/((E179-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H179" s="15">
-        <f>IF(OR(G179="",NOT(ISNUMBER(C179))),"",(G179-C179)*100)</f>
+        <f>IF(OR(F179="",NOT(ISNUMBER(D179))),"",(F179-D179)*100)</f>
         <v/>
       </c>
       <c r="I179" s="16">
-        <f>IF(OR(F179="",NOT(ISNUMBER(D179))),"",F179-D179)</f>
+        <f>IF(OR(G179="",NOT(ISNUMBER(E179))),"",G179-E179)</f>
         <v/>
       </c>
       <c r="K179" s="17" t="inlineStr">
@@ -12268,7 +12273,7 @@
         <v/>
       </c>
       <c r="S179" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("9Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("9Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("9Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("9Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U179" s="20">
@@ -12282,27 +12287,27 @@
     </row>
     <row r="180">
       <c r="A180" s="9" t="n"/>
-      <c r="B180" s="10" t="n"/>
-      <c r="C180" s="10" t="n"/>
+      <c r="B180" s="10">
+        <f>IF($A180="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A180,$K$156:$K$220,0),MATCH(IF($A180="1Y","12M",IF($A180="12M","1Y",$A180)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C180" s="11" t="n"/>
       <c r="D180" s="11" t="n"/>
-      <c r="E180" s="12">
-        <f>IF($A180="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A180,$K$156:$K$220,0),MATCH(IF($A180="1Y","12M",IF($A180="12M","1Y",$A180)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E180" s="12" t="n"/>
       <c r="F180" s="13">
+        <f>IF(OR($A180="",G180=""),"",-LN(G180)/((B180-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G180" s="14">
         <f>IF($A180="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A180,$K$156:$K$220,0),MATCH(IF($A180="1Y","12M",IF($A180="12M","1Y",$A180)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G180" s="14">
-        <f>IF(OR($A180="",F180=""),"",-LN(F180)/((E180-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H180" s="15">
-        <f>IF(OR(G180="",NOT(ISNUMBER(C180))),"",(G180-C180)*100)</f>
+        <f>IF(OR(F180="",NOT(ISNUMBER(D180))),"",(F180-D180)*100)</f>
         <v/>
       </c>
       <c r="I180" s="16">
-        <f>IF(OR(F180="",NOT(ISNUMBER(D180))),"",F180-D180)</f>
+        <f>IF(OR(G180="",NOT(ISNUMBER(E180))),"",G180-E180)</f>
         <v/>
       </c>
       <c r="K180" s="17" t="inlineStr">
@@ -12337,7 +12342,7 @@
         <v/>
       </c>
       <c r="S180" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("10Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("10Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("10Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("10Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U180" s="20">
@@ -12351,27 +12356,27 @@
     </row>
     <row r="181">
       <c r="A181" s="9" t="n"/>
-      <c r="B181" s="10" t="n"/>
-      <c r="C181" s="10" t="n"/>
+      <c r="B181" s="10">
+        <f>IF($A181="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A181,$K$156:$K$220,0),MATCH(IF($A181="1Y","12M",IF($A181="12M","1Y",$A181)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C181" s="11" t="n"/>
       <c r="D181" s="11" t="n"/>
-      <c r="E181" s="12">
-        <f>IF($A181="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A181,$K$156:$K$220,0),MATCH(IF($A181="1Y","12M",IF($A181="12M","1Y",$A181)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E181" s="12" t="n"/>
       <c r="F181" s="13">
+        <f>IF(OR($A181="",G181=""),"",-LN(G181)/((B181-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G181" s="14">
         <f>IF($A181="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A181,$K$156:$K$220,0),MATCH(IF($A181="1Y","12M",IF($A181="12M","1Y",$A181)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G181" s="14">
-        <f>IF(OR($A181="",F181=""),"",-LN(F181)/((E181-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H181" s="15">
-        <f>IF(OR(G181="",NOT(ISNUMBER(C181))),"",(G181-C181)*100)</f>
+        <f>IF(OR(F181="",NOT(ISNUMBER(D181))),"",(F181-D181)*100)</f>
         <v/>
       </c>
       <c r="I181" s="16">
-        <f>IF(OR(F181="",NOT(ISNUMBER(D181))),"",F181-D181)</f>
+        <f>IF(OR(G181="",NOT(ISNUMBER(E181))),"",G181-E181)</f>
         <v/>
       </c>
       <c r="K181" s="17" t="inlineStr">
@@ -12406,7 +12411,7 @@
         <v/>
       </c>
       <c r="S181" s="19">
-        <f>IFERROR(IF(R181=1,IFERROR(INDEX($B$156:$B$207,MATCH("11Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("11Y",$A$156:$A$207,0))),S180+(S182-S180)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R181=1,IFERROR(INDEX($C$156:$C$207,MATCH("11Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("11Y",$A$156:$A$207,0))),S180+(S182-S180)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T181">
@@ -12424,27 +12429,27 @@
     </row>
     <row r="182">
       <c r="A182" s="9" t="n"/>
-      <c r="B182" s="10" t="n"/>
-      <c r="C182" s="10" t="n"/>
+      <c r="B182" s="10">
+        <f>IF($A182="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A182,$K$156:$K$220,0),MATCH(IF($A182="1Y","12M",IF($A182="12M","1Y",$A182)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C182" s="11" t="n"/>
       <c r="D182" s="11" t="n"/>
-      <c r="E182" s="12">
-        <f>IF($A182="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A182,$K$156:$K$220,0),MATCH(IF($A182="1Y","12M",IF($A182="12M","1Y",$A182)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E182" s="12" t="n"/>
       <c r="F182" s="13">
+        <f>IF(OR($A182="",G182=""),"",-LN(G182)/((B182-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G182" s="14">
         <f>IF($A182="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A182,$K$156:$K$220,0),MATCH(IF($A182="1Y","12M",IF($A182="12M","1Y",$A182)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G182" s="14">
-        <f>IF(OR($A182="",F182=""),"",-LN(F182)/((E182-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H182" s="15">
-        <f>IF(OR(G182="",NOT(ISNUMBER(C182))),"",(G182-C182)*100)</f>
+        <f>IF(OR(F182="",NOT(ISNUMBER(D182))),"",(F182-D182)*100)</f>
         <v/>
       </c>
       <c r="I182" s="16">
-        <f>IF(OR(F182="",NOT(ISNUMBER(D182))),"",F182-D182)</f>
+        <f>IF(OR(G182="",NOT(ISNUMBER(E182))),"",G182-E182)</f>
         <v/>
       </c>
       <c r="K182" s="17" t="inlineStr">
@@ -12479,7 +12484,7 @@
         <v/>
       </c>
       <c r="S182" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("12Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("12Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("12Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("12Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U182" s="20">
@@ -12557,27 +12562,27 @@
     </row>
     <row r="183">
       <c r="A183" s="9" t="n"/>
-      <c r="B183" s="10" t="n"/>
-      <c r="C183" s="10" t="n"/>
+      <c r="B183" s="10">
+        <f>IF($A183="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A183,$K$156:$K$220,0),MATCH(IF($A183="1Y","12M",IF($A183="12M","1Y",$A183)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C183" s="11" t="n"/>
       <c r="D183" s="11" t="n"/>
-      <c r="E183" s="12">
-        <f>IF($A183="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A183,$K$156:$K$220,0),MATCH(IF($A183="1Y","12M",IF($A183="12M","1Y",$A183)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E183" s="12" t="n"/>
       <c r="F183" s="13">
+        <f>IF(OR($A183="",G183=""),"",-LN(G183)/((B183-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G183" s="14">
         <f>IF($A183="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A183,$K$156:$K$220,0),MATCH(IF($A183="1Y","12M",IF($A183="12M","1Y",$A183)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G183" s="14">
-        <f>IF(OR($A183="",F183=""),"",-LN(F183)/((E183-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H183" s="15">
-        <f>IF(OR(G183="",NOT(ISNUMBER(C183))),"",(G183-C183)*100)</f>
+        <f>IF(OR(F183="",NOT(ISNUMBER(D183))),"",(F183-D183)*100)</f>
         <v/>
       </c>
       <c r="I183" s="16">
-        <f>IF(OR(F183="",NOT(ISNUMBER(D183))),"",F183-D183)</f>
+        <f>IF(OR(G183="",NOT(ISNUMBER(E183))),"",G183-E183)</f>
         <v/>
       </c>
       <c r="K183" s="17" t="inlineStr">
@@ -12612,7 +12617,7 @@
         <v/>
       </c>
       <c r="S183" s="19">
-        <f>IFERROR(IF(R183=1,IFERROR(INDEX($B$156:$B$207,MATCH("13Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("13Y",$A$156:$A$207,0))),S182+(S185-S182)*0.3333333333),"")</f>
+        <f>IFERROR(IF(R183=1,IFERROR(INDEX($C$156:$C$207,MATCH("13Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("13Y",$A$156:$A$207,0))),S182+(S185-S182)*0.3333333333),"")</f>
         <v/>
       </c>
       <c r="T183">
@@ -12630,27 +12635,27 @@
     </row>
     <row r="184">
       <c r="A184" s="9" t="n"/>
-      <c r="B184" s="10" t="n"/>
-      <c r="C184" s="10" t="n"/>
+      <c r="B184" s="10">
+        <f>IF($A184="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A184,$K$156:$K$220,0),MATCH(IF($A184="1Y","12M",IF($A184="12M","1Y",$A184)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C184" s="11" t="n"/>
       <c r="D184" s="11" t="n"/>
-      <c r="E184" s="12">
-        <f>IF($A184="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A184,$K$156:$K$220,0),MATCH(IF($A184="1Y","12M",IF($A184="12M","1Y",$A184)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E184" s="12" t="n"/>
       <c r="F184" s="13">
+        <f>IF(OR($A184="",G184=""),"",-LN(G184)/((B184-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G184" s="14">
         <f>IF($A184="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A184,$K$156:$K$220,0),MATCH(IF($A184="1Y","12M",IF($A184="12M","1Y",$A184)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G184" s="14">
-        <f>IF(OR($A184="",F184=""),"",-LN(F184)/((E184-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H184" s="15">
-        <f>IF(OR(G184="",NOT(ISNUMBER(C184))),"",(G184-C184)*100)</f>
+        <f>IF(OR(F184="",NOT(ISNUMBER(D184))),"",(F184-D184)*100)</f>
         <v/>
       </c>
       <c r="I184" s="16">
-        <f>IF(OR(F184="",NOT(ISNUMBER(D184))),"",F184-D184)</f>
+        <f>IF(OR(G184="",NOT(ISNUMBER(E184))),"",G184-E184)</f>
         <v/>
       </c>
       <c r="K184" s="17" t="inlineStr">
@@ -12685,7 +12690,7 @@
         <v/>
       </c>
       <c r="S184" s="19">
-        <f>IFERROR(IF(R184=1,IFERROR(INDEX($B$156:$B$207,MATCH("14Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("14Y",$A$156:$A$207,0))),S182+(S185-S182)*0.6666666667),"")</f>
+        <f>IFERROR(IF(R184=1,IFERROR(INDEX($C$156:$C$207,MATCH("14Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("14Y",$A$156:$A$207,0))),S182+(S185-S182)*0.6666666667),"")</f>
         <v/>
       </c>
       <c r="T184">
@@ -12703,27 +12708,27 @@
     </row>
     <row r="185">
       <c r="A185" s="9" t="n"/>
-      <c r="B185" s="10" t="n"/>
-      <c r="C185" s="10" t="n"/>
+      <c r="B185" s="10">
+        <f>IF($A185="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A185,$K$156:$K$220,0),MATCH(IF($A185="1Y","12M",IF($A185="12M","1Y",$A185)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C185" s="11" t="n"/>
       <c r="D185" s="11" t="n"/>
-      <c r="E185" s="12">
-        <f>IF($A185="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A185,$K$156:$K$220,0),MATCH(IF($A185="1Y","12M",IF($A185="12M","1Y",$A185)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E185" s="12" t="n"/>
       <c r="F185" s="13">
+        <f>IF(OR($A185="",G185=""),"",-LN(G185)/((B185-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G185" s="14">
         <f>IF($A185="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A185,$K$156:$K$220,0),MATCH(IF($A185="1Y","12M",IF($A185="12M","1Y",$A185)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G185" s="14">
-        <f>IF(OR($A185="",F185=""),"",-LN(F185)/((E185-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H185" s="15">
-        <f>IF(OR(G185="",NOT(ISNUMBER(C185))),"",(G185-C185)*100)</f>
+        <f>IF(OR(F185="",NOT(ISNUMBER(D185))),"",(F185-D185)*100)</f>
         <v/>
       </c>
       <c r="I185" s="16">
-        <f>IF(OR(F185="",NOT(ISNUMBER(D185))),"",F185-D185)</f>
+        <f>IF(OR(G185="",NOT(ISNUMBER(E185))),"",G185-E185)</f>
         <v/>
       </c>
       <c r="K185" s="17" t="inlineStr">
@@ -12758,7 +12763,7 @@
         <v/>
       </c>
       <c r="S185" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("15Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("15Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("15Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("15Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U185" s="20">
@@ -12836,27 +12841,27 @@
     </row>
     <row r="186">
       <c r="A186" s="9" t="n"/>
-      <c r="B186" s="10" t="n"/>
-      <c r="C186" s="10" t="n"/>
+      <c r="B186" s="10">
+        <f>IF($A186="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A186,$K$156:$K$220,0),MATCH(IF($A186="1Y","12M",IF($A186="12M","1Y",$A186)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C186" s="11" t="n"/>
       <c r="D186" s="11" t="n"/>
-      <c r="E186" s="12">
-        <f>IF($A186="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A186,$K$156:$K$220,0),MATCH(IF($A186="1Y","12M",IF($A186="12M","1Y",$A186)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E186" s="12" t="n"/>
       <c r="F186" s="13">
+        <f>IF(OR($A186="",G186=""),"",-LN(G186)/((B186-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G186" s="14">
         <f>IF($A186="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A186,$K$156:$K$220,0),MATCH(IF($A186="1Y","12M",IF($A186="12M","1Y",$A186)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G186" s="14">
-        <f>IF(OR($A186="",F186=""),"",-LN(F186)/((E186-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H186" s="15">
-        <f>IF(OR(G186="",NOT(ISNUMBER(C186))),"",(G186-C186)*100)</f>
+        <f>IF(OR(F186="",NOT(ISNUMBER(D186))),"",(F186-D186)*100)</f>
         <v/>
       </c>
       <c r="I186" s="16">
-        <f>IF(OR(F186="",NOT(ISNUMBER(D186))),"",F186-D186)</f>
+        <f>IF(OR(G186="",NOT(ISNUMBER(E186))),"",G186-E186)</f>
         <v/>
       </c>
       <c r="K186" s="17" t="inlineStr">
@@ -12891,7 +12896,7 @@
         <v/>
       </c>
       <c r="S186" s="19">
-        <f>IFERROR(IF(R186=1,IFERROR(INDEX($B$156:$B$207,MATCH("16Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("16Y",$A$156:$A$207,0))),S185+(S190-S185)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R186=1,IFERROR(INDEX($C$156:$C$207,MATCH("16Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("16Y",$A$156:$A$207,0))),S185+(S190-S185)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T186">
@@ -12909,27 +12914,27 @@
     </row>
     <row r="187">
       <c r="A187" s="9" t="n"/>
-      <c r="B187" s="10" t="n"/>
-      <c r="C187" s="10" t="n"/>
+      <c r="B187" s="10">
+        <f>IF($A187="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A187,$K$156:$K$220,0),MATCH(IF($A187="1Y","12M",IF($A187="12M","1Y",$A187)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C187" s="11" t="n"/>
       <c r="D187" s="11" t="n"/>
-      <c r="E187" s="12">
-        <f>IF($A187="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A187,$K$156:$K$220,0),MATCH(IF($A187="1Y","12M",IF($A187="12M","1Y",$A187)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E187" s="12" t="n"/>
       <c r="F187" s="13">
+        <f>IF(OR($A187="",G187=""),"",-LN(G187)/((B187-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G187" s="14">
         <f>IF($A187="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A187,$K$156:$K$220,0),MATCH(IF($A187="1Y","12M",IF($A187="12M","1Y",$A187)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G187" s="14">
-        <f>IF(OR($A187="",F187=""),"",-LN(F187)/((E187-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H187" s="15">
-        <f>IF(OR(G187="",NOT(ISNUMBER(C187))),"",(G187-C187)*100)</f>
+        <f>IF(OR(F187="",NOT(ISNUMBER(D187))),"",(F187-D187)*100)</f>
         <v/>
       </c>
       <c r="I187" s="16">
-        <f>IF(OR(F187="",NOT(ISNUMBER(D187))),"",F187-D187)</f>
+        <f>IF(OR(G187="",NOT(ISNUMBER(E187))),"",G187-E187)</f>
         <v/>
       </c>
       <c r="K187" s="17" t="inlineStr">
@@ -12964,7 +12969,7 @@
         <v/>
       </c>
       <c r="S187" s="19">
-        <f>IFERROR(IF(R187=1,IFERROR(INDEX($B$156:$B$207,MATCH("17Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("17Y",$A$156:$A$207,0))),S185+(S190-S185)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R187=1,IFERROR(INDEX($C$156:$C$207,MATCH("17Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("17Y",$A$156:$A$207,0))),S185+(S190-S185)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T187">
@@ -12982,27 +12987,27 @@
     </row>
     <row r="188">
       <c r="A188" s="9" t="n"/>
-      <c r="B188" s="10" t="n"/>
-      <c r="C188" s="10" t="n"/>
+      <c r="B188" s="10">
+        <f>IF($A188="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A188,$K$156:$K$220,0),MATCH(IF($A188="1Y","12M",IF($A188="12M","1Y",$A188)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C188" s="11" t="n"/>
       <c r="D188" s="11" t="n"/>
-      <c r="E188" s="12">
-        <f>IF($A188="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A188,$K$156:$K$220,0),MATCH(IF($A188="1Y","12M",IF($A188="12M","1Y",$A188)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E188" s="12" t="n"/>
       <c r="F188" s="13">
+        <f>IF(OR($A188="",G188=""),"",-LN(G188)/((B188-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G188" s="14">
         <f>IF($A188="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A188,$K$156:$K$220,0),MATCH(IF($A188="1Y","12M",IF($A188="12M","1Y",$A188)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G188" s="14">
-        <f>IF(OR($A188="",F188=""),"",-LN(F188)/((E188-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H188" s="15">
-        <f>IF(OR(G188="",NOT(ISNUMBER(C188))),"",(G188-C188)*100)</f>
+        <f>IF(OR(F188="",NOT(ISNUMBER(D188))),"",(F188-D188)*100)</f>
         <v/>
       </c>
       <c r="I188" s="16">
-        <f>IF(OR(F188="",NOT(ISNUMBER(D188))),"",F188-D188)</f>
+        <f>IF(OR(G188="",NOT(ISNUMBER(E188))),"",G188-E188)</f>
         <v/>
       </c>
       <c r="K188" s="17" t="inlineStr">
@@ -13037,7 +13042,7 @@
         <v/>
       </c>
       <c r="S188" s="19">
-        <f>IFERROR(IF(R188=1,IFERROR(INDEX($B$156:$B$207,MATCH("18Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("18Y",$A$156:$A$207,0))),S185+(S190-S185)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R188=1,IFERROR(INDEX($C$156:$C$207,MATCH("18Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("18Y",$A$156:$A$207,0))),S185+(S190-S185)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T188">
@@ -13055,27 +13060,27 @@
     </row>
     <row r="189">
       <c r="A189" s="9" t="n"/>
-      <c r="B189" s="10" t="n"/>
-      <c r="C189" s="10" t="n"/>
+      <c r="B189" s="10">
+        <f>IF($A189="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A189,$K$156:$K$220,0),MATCH(IF($A189="1Y","12M",IF($A189="12M","1Y",$A189)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C189" s="11" t="n"/>
       <c r="D189" s="11" t="n"/>
-      <c r="E189" s="12">
-        <f>IF($A189="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A189,$K$156:$K$220,0),MATCH(IF($A189="1Y","12M",IF($A189="12M","1Y",$A189)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E189" s="12" t="n"/>
       <c r="F189" s="13">
+        <f>IF(OR($A189="",G189=""),"",-LN(G189)/((B189-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G189" s="14">
         <f>IF($A189="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A189,$K$156:$K$220,0),MATCH(IF($A189="1Y","12M",IF($A189="12M","1Y",$A189)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G189" s="14">
-        <f>IF(OR($A189="",F189=""),"",-LN(F189)/((E189-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H189" s="15">
-        <f>IF(OR(G189="",NOT(ISNUMBER(C189))),"",(G189-C189)*100)</f>
+        <f>IF(OR(F189="",NOT(ISNUMBER(D189))),"",(F189-D189)*100)</f>
         <v/>
       </c>
       <c r="I189" s="16">
-        <f>IF(OR(F189="",NOT(ISNUMBER(D189))),"",F189-D189)</f>
+        <f>IF(OR(G189="",NOT(ISNUMBER(E189))),"",G189-E189)</f>
         <v/>
       </c>
       <c r="K189" s="17" t="inlineStr">
@@ -13110,7 +13115,7 @@
         <v/>
       </c>
       <c r="S189" s="19">
-        <f>IFERROR(IF(R189=1,IFERROR(INDEX($B$156:$B$207,MATCH("19Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("19Y",$A$156:$A$207,0))),S185+(S190-S185)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R189=1,IFERROR(INDEX($C$156:$C$207,MATCH("19Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("19Y",$A$156:$A$207,0))),S185+(S190-S185)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T189">
@@ -13128,27 +13133,27 @@
     </row>
     <row r="190">
       <c r="A190" s="9" t="n"/>
-      <c r="B190" s="10" t="n"/>
-      <c r="C190" s="10" t="n"/>
+      <c r="B190" s="10">
+        <f>IF($A190="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A190,$K$156:$K$220,0),MATCH(IF($A190="1Y","12M",IF($A190="12M","1Y",$A190)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C190" s="11" t="n"/>
       <c r="D190" s="11" t="n"/>
-      <c r="E190" s="12">
-        <f>IF($A190="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A190,$K$156:$K$220,0),MATCH(IF($A190="1Y","12M",IF($A190="12M","1Y",$A190)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E190" s="12" t="n"/>
       <c r="F190" s="13">
+        <f>IF(OR($A190="",G190=""),"",-LN(G190)/((B190-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G190" s="14">
         <f>IF($A190="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A190,$K$156:$K$220,0),MATCH(IF($A190="1Y","12M",IF($A190="12M","1Y",$A190)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G190" s="14">
-        <f>IF(OR($A190="",F190=""),"",-LN(F190)/((E190-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H190" s="15">
-        <f>IF(OR(G190="",NOT(ISNUMBER(C190))),"",(G190-C190)*100)</f>
+        <f>IF(OR(F190="",NOT(ISNUMBER(D190))),"",(F190-D190)*100)</f>
         <v/>
       </c>
       <c r="I190" s="16">
-        <f>IF(OR(F190="",NOT(ISNUMBER(D190))),"",F190-D190)</f>
+        <f>IF(OR(G190="",NOT(ISNUMBER(E190))),"",G190-E190)</f>
         <v/>
       </c>
       <c r="K190" s="17" t="inlineStr">
@@ -13183,7 +13188,7 @@
         <v/>
       </c>
       <c r="S190" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("20Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("20Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("20Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("20Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U190" s="20">
@@ -13261,27 +13266,27 @@
     </row>
     <row r="191">
       <c r="A191" s="9" t="n"/>
-      <c r="B191" s="10" t="n"/>
-      <c r="C191" s="10" t="n"/>
+      <c r="B191" s="10">
+        <f>IF($A191="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A191,$K$156:$K$220,0),MATCH(IF($A191="1Y","12M",IF($A191="12M","1Y",$A191)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C191" s="11" t="n"/>
       <c r="D191" s="11" t="n"/>
-      <c r="E191" s="12">
-        <f>IF($A191="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A191,$K$156:$K$220,0),MATCH(IF($A191="1Y","12M",IF($A191="12M","1Y",$A191)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E191" s="12" t="n"/>
       <c r="F191" s="13">
+        <f>IF(OR($A191="",G191=""),"",-LN(G191)/((B191-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G191" s="14">
         <f>IF($A191="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A191,$K$156:$K$220,0),MATCH(IF($A191="1Y","12M",IF($A191="12M","1Y",$A191)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G191" s="14">
-        <f>IF(OR($A191="",F191=""),"",-LN(F191)/((E191-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H191" s="15">
-        <f>IF(OR(G191="",NOT(ISNUMBER(C191))),"",(G191-C191)*100)</f>
+        <f>IF(OR(F191="",NOT(ISNUMBER(D191))),"",(F191-D191)*100)</f>
         <v/>
       </c>
       <c r="I191" s="16">
-        <f>IF(OR(F191="",NOT(ISNUMBER(D191))),"",F191-D191)</f>
+        <f>IF(OR(G191="",NOT(ISNUMBER(E191))),"",G191-E191)</f>
         <v/>
       </c>
       <c r="K191" s="17" t="inlineStr">
@@ -13316,7 +13321,7 @@
         <v/>
       </c>
       <c r="S191" s="19">
-        <f>IFERROR(IF(R191=1,IFERROR(INDEX($B$156:$B$207,MATCH("21Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("21Y",$A$156:$A$207,0))),S190+(S195-S190)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R191=1,IFERROR(INDEX($C$156:$C$207,MATCH("21Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("21Y",$A$156:$A$207,0))),S190+(S195-S190)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T191">
@@ -13334,27 +13339,27 @@
     </row>
     <row r="192">
       <c r="A192" s="9" t="n"/>
-      <c r="B192" s="10" t="n"/>
-      <c r="C192" s="10" t="n"/>
+      <c r="B192" s="10">
+        <f>IF($A192="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A192,$K$156:$K$220,0),MATCH(IF($A192="1Y","12M",IF($A192="12M","1Y",$A192)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C192" s="11" t="n"/>
       <c r="D192" s="11" t="n"/>
-      <c r="E192" s="12">
-        <f>IF($A192="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A192,$K$156:$K$220,0),MATCH(IF($A192="1Y","12M",IF($A192="12M","1Y",$A192)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E192" s="12" t="n"/>
       <c r="F192" s="13">
+        <f>IF(OR($A192="",G192=""),"",-LN(G192)/((B192-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G192" s="14">
         <f>IF($A192="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A192,$K$156:$K$220,0),MATCH(IF($A192="1Y","12M",IF($A192="12M","1Y",$A192)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G192" s="14">
-        <f>IF(OR($A192="",F192=""),"",-LN(F192)/((E192-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H192" s="15">
-        <f>IF(OR(G192="",NOT(ISNUMBER(C192))),"",(G192-C192)*100)</f>
+        <f>IF(OR(F192="",NOT(ISNUMBER(D192))),"",(F192-D192)*100)</f>
         <v/>
       </c>
       <c r="I192" s="16">
-        <f>IF(OR(F192="",NOT(ISNUMBER(D192))),"",F192-D192)</f>
+        <f>IF(OR(G192="",NOT(ISNUMBER(E192))),"",G192-E192)</f>
         <v/>
       </c>
       <c r="K192" s="17" t="inlineStr">
@@ -13389,7 +13394,7 @@
         <v/>
       </c>
       <c r="S192" s="19">
-        <f>IFERROR(IF(R192=1,IFERROR(INDEX($B$156:$B$207,MATCH("22Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("22Y",$A$156:$A$207,0))),S190+(S195-S190)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R192=1,IFERROR(INDEX($C$156:$C$207,MATCH("22Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("22Y",$A$156:$A$207,0))),S190+(S195-S190)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T192">
@@ -13407,27 +13412,27 @@
     </row>
     <row r="193">
       <c r="A193" s="9" t="n"/>
-      <c r="B193" s="10" t="n"/>
-      <c r="C193" s="10" t="n"/>
+      <c r="B193" s="10">
+        <f>IF($A193="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A193,$K$156:$K$220,0),MATCH(IF($A193="1Y","12M",IF($A193="12M","1Y",$A193)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C193" s="11" t="n"/>
       <c r="D193" s="11" t="n"/>
-      <c r="E193" s="12">
-        <f>IF($A193="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A193,$K$156:$K$220,0),MATCH(IF($A193="1Y","12M",IF($A193="12M","1Y",$A193)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E193" s="12" t="n"/>
       <c r="F193" s="13">
+        <f>IF(OR($A193="",G193=""),"",-LN(G193)/((B193-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G193" s="14">
         <f>IF($A193="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A193,$K$156:$K$220,0),MATCH(IF($A193="1Y","12M",IF($A193="12M","1Y",$A193)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G193" s="14">
-        <f>IF(OR($A193="",F193=""),"",-LN(F193)/((E193-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H193" s="15">
-        <f>IF(OR(G193="",NOT(ISNUMBER(C193))),"",(G193-C193)*100)</f>
+        <f>IF(OR(F193="",NOT(ISNUMBER(D193))),"",(F193-D193)*100)</f>
         <v/>
       </c>
       <c r="I193" s="16">
-        <f>IF(OR(F193="",NOT(ISNUMBER(D193))),"",F193-D193)</f>
+        <f>IF(OR(G193="",NOT(ISNUMBER(E193))),"",G193-E193)</f>
         <v/>
       </c>
       <c r="K193" s="17" t="inlineStr">
@@ -13462,7 +13467,7 @@
         <v/>
       </c>
       <c r="S193" s="19">
-        <f>IFERROR(IF(R193=1,IFERROR(INDEX($B$156:$B$207,MATCH("23Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("23Y",$A$156:$A$207,0))),S190+(S195-S190)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R193=1,IFERROR(INDEX($C$156:$C$207,MATCH("23Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("23Y",$A$156:$A$207,0))),S190+(S195-S190)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T193">
@@ -13480,27 +13485,27 @@
     </row>
     <row r="194">
       <c r="A194" s="9" t="n"/>
-      <c r="B194" s="10" t="n"/>
-      <c r="C194" s="10" t="n"/>
+      <c r="B194" s="10">
+        <f>IF($A194="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A194,$K$156:$K$220,0),MATCH(IF($A194="1Y","12M",IF($A194="12M","1Y",$A194)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C194" s="11" t="n"/>
       <c r="D194" s="11" t="n"/>
-      <c r="E194" s="12">
-        <f>IF($A194="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A194,$K$156:$K$220,0),MATCH(IF($A194="1Y","12M",IF($A194="12M","1Y",$A194)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E194" s="12" t="n"/>
       <c r="F194" s="13">
+        <f>IF(OR($A194="",G194=""),"",-LN(G194)/((B194-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G194" s="14">
         <f>IF($A194="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A194,$K$156:$K$220,0),MATCH(IF($A194="1Y","12M",IF($A194="12M","1Y",$A194)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G194" s="14">
-        <f>IF(OR($A194="",F194=""),"",-LN(F194)/((E194-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H194" s="15">
-        <f>IF(OR(G194="",NOT(ISNUMBER(C194))),"",(G194-C194)*100)</f>
+        <f>IF(OR(F194="",NOT(ISNUMBER(D194))),"",(F194-D194)*100)</f>
         <v/>
       </c>
       <c r="I194" s="16">
-        <f>IF(OR(F194="",NOT(ISNUMBER(D194))),"",F194-D194)</f>
+        <f>IF(OR(G194="",NOT(ISNUMBER(E194))),"",G194-E194)</f>
         <v/>
       </c>
       <c r="K194" s="17" t="inlineStr">
@@ -13535,7 +13540,7 @@
         <v/>
       </c>
       <c r="S194" s="19">
-        <f>IFERROR(IF(R194=1,IFERROR(INDEX($B$156:$B$207,MATCH("24Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("24Y",$A$156:$A$207,0))),S190+(S195-S190)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R194=1,IFERROR(INDEX($C$156:$C$207,MATCH("24Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("24Y",$A$156:$A$207,0))),S190+(S195-S190)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T194">
@@ -13553,27 +13558,27 @@
     </row>
     <row r="195">
       <c r="A195" s="9" t="n"/>
-      <c r="B195" s="10" t="n"/>
-      <c r="C195" s="10" t="n"/>
+      <c r="B195" s="10">
+        <f>IF($A195="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A195,$K$156:$K$220,0),MATCH(IF($A195="1Y","12M",IF($A195="12M","1Y",$A195)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C195" s="11" t="n"/>
       <c r="D195" s="11" t="n"/>
-      <c r="E195" s="12">
-        <f>IF($A195="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A195,$K$156:$K$220,0),MATCH(IF($A195="1Y","12M",IF($A195="12M","1Y",$A195)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E195" s="12" t="n"/>
       <c r="F195" s="13">
+        <f>IF(OR($A195="",G195=""),"",-LN(G195)/((B195-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G195" s="14">
         <f>IF($A195="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A195,$K$156:$K$220,0),MATCH(IF($A195="1Y","12M",IF($A195="12M","1Y",$A195)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G195" s="14">
-        <f>IF(OR($A195="",F195=""),"",-LN(F195)/((E195-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H195" s="15">
-        <f>IF(OR(G195="",NOT(ISNUMBER(C195))),"",(G195-C195)*100)</f>
+        <f>IF(OR(F195="",NOT(ISNUMBER(D195))),"",(F195-D195)*100)</f>
         <v/>
       </c>
       <c r="I195" s="16">
-        <f>IF(OR(F195="",NOT(ISNUMBER(D195))),"",F195-D195)</f>
+        <f>IF(OR(G195="",NOT(ISNUMBER(E195))),"",G195-E195)</f>
         <v/>
       </c>
       <c r="K195" s="17" t="inlineStr">
@@ -13608,7 +13613,7 @@
         <v/>
       </c>
       <c r="S195" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("25Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("25Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("25Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("25Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U195" s="20">
@@ -13686,27 +13691,27 @@
     </row>
     <row r="196">
       <c r="A196" s="9" t="n"/>
-      <c r="B196" s="10" t="n"/>
-      <c r="C196" s="10" t="n"/>
+      <c r="B196" s="10">
+        <f>IF($A196="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A196,$K$156:$K$220,0),MATCH(IF($A196="1Y","12M",IF($A196="12M","1Y",$A196)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C196" s="11" t="n"/>
       <c r="D196" s="11" t="n"/>
-      <c r="E196" s="12">
-        <f>IF($A196="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A196,$K$156:$K$220,0),MATCH(IF($A196="1Y","12M",IF($A196="12M","1Y",$A196)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E196" s="12" t="n"/>
       <c r="F196" s="13">
+        <f>IF(OR($A196="",G196=""),"",-LN(G196)/((B196-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G196" s="14">
         <f>IF($A196="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A196,$K$156:$K$220,0),MATCH(IF($A196="1Y","12M",IF($A196="12M","1Y",$A196)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G196" s="14">
-        <f>IF(OR($A196="",F196=""),"",-LN(F196)/((E196-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H196" s="15">
-        <f>IF(OR(G196="",NOT(ISNUMBER(C196))),"",(G196-C196)*100)</f>
+        <f>IF(OR(F196="",NOT(ISNUMBER(D196))),"",(F196-D196)*100)</f>
         <v/>
       </c>
       <c r="I196" s="16">
-        <f>IF(OR(F196="",NOT(ISNUMBER(D196))),"",F196-D196)</f>
+        <f>IF(OR(G196="",NOT(ISNUMBER(E196))),"",G196-E196)</f>
         <v/>
       </c>
       <c r="K196" s="17" t="inlineStr">
@@ -13741,7 +13746,7 @@
         <v/>
       </c>
       <c r="S196" s="19">
-        <f>IFERROR(IF(R196=1,IFERROR(INDEX($B$156:$B$207,MATCH("26Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("26Y",$A$156:$A$207,0))),S195+(S200-S195)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R196=1,IFERROR(INDEX($C$156:$C$207,MATCH("26Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("26Y",$A$156:$A$207,0))),S195+(S200-S195)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T196">
@@ -13759,27 +13764,27 @@
     </row>
     <row r="197">
       <c r="A197" s="9" t="n"/>
-      <c r="B197" s="10" t="n"/>
-      <c r="C197" s="10" t="n"/>
+      <c r="B197" s="10">
+        <f>IF($A197="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A197,$K$156:$K$220,0),MATCH(IF($A197="1Y","12M",IF($A197="12M","1Y",$A197)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C197" s="11" t="n"/>
       <c r="D197" s="11" t="n"/>
-      <c r="E197" s="12">
-        <f>IF($A197="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A197,$K$156:$K$220,0),MATCH(IF($A197="1Y","12M",IF($A197="12M","1Y",$A197)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E197" s="12" t="n"/>
       <c r="F197" s="13">
+        <f>IF(OR($A197="",G197=""),"",-LN(G197)/((B197-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G197" s="14">
         <f>IF($A197="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A197,$K$156:$K$220,0),MATCH(IF($A197="1Y","12M",IF($A197="12M","1Y",$A197)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G197" s="14">
-        <f>IF(OR($A197="",F197=""),"",-LN(F197)/((E197-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H197" s="15">
-        <f>IF(OR(G197="",NOT(ISNUMBER(C197))),"",(G197-C197)*100)</f>
+        <f>IF(OR(F197="",NOT(ISNUMBER(D197))),"",(F197-D197)*100)</f>
         <v/>
       </c>
       <c r="I197" s="16">
-        <f>IF(OR(F197="",NOT(ISNUMBER(D197))),"",F197-D197)</f>
+        <f>IF(OR(G197="",NOT(ISNUMBER(E197))),"",G197-E197)</f>
         <v/>
       </c>
       <c r="K197" s="17" t="inlineStr">
@@ -13814,7 +13819,7 @@
         <v/>
       </c>
       <c r="S197" s="19">
-        <f>IFERROR(IF(R197=1,IFERROR(INDEX($B$156:$B$207,MATCH("27Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("27Y",$A$156:$A$207,0))),S195+(S200-S195)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R197=1,IFERROR(INDEX($C$156:$C$207,MATCH("27Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("27Y",$A$156:$A$207,0))),S195+(S200-S195)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T197">
@@ -13832,27 +13837,27 @@
     </row>
     <row r="198">
       <c r="A198" s="9" t="n"/>
-      <c r="B198" s="10" t="n"/>
-      <c r="C198" s="10" t="n"/>
+      <c r="B198" s="10">
+        <f>IF($A198="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A198,$K$156:$K$220,0),MATCH(IF($A198="1Y","12M",IF($A198="12M","1Y",$A198)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C198" s="11" t="n"/>
       <c r="D198" s="11" t="n"/>
-      <c r="E198" s="12">
-        <f>IF($A198="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A198,$K$156:$K$220,0),MATCH(IF($A198="1Y","12M",IF($A198="12M","1Y",$A198)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E198" s="12" t="n"/>
       <c r="F198" s="13">
+        <f>IF(OR($A198="",G198=""),"",-LN(G198)/((B198-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G198" s="14">
         <f>IF($A198="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A198,$K$156:$K$220,0),MATCH(IF($A198="1Y","12M",IF($A198="12M","1Y",$A198)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G198" s="14">
-        <f>IF(OR($A198="",F198=""),"",-LN(F198)/((E198-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H198" s="15">
-        <f>IF(OR(G198="",NOT(ISNUMBER(C198))),"",(G198-C198)*100)</f>
+        <f>IF(OR(F198="",NOT(ISNUMBER(D198))),"",(F198-D198)*100)</f>
         <v/>
       </c>
       <c r="I198" s="16">
-        <f>IF(OR(F198="",NOT(ISNUMBER(D198))),"",F198-D198)</f>
+        <f>IF(OR(G198="",NOT(ISNUMBER(E198))),"",G198-E198)</f>
         <v/>
       </c>
       <c r="K198" s="17" t="inlineStr">
@@ -13887,7 +13892,7 @@
         <v/>
       </c>
       <c r="S198" s="19">
-        <f>IFERROR(IF(R198=1,IFERROR(INDEX($B$156:$B$207,MATCH("28Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("28Y",$A$156:$A$207,0))),S195+(S200-S195)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R198=1,IFERROR(INDEX($C$156:$C$207,MATCH("28Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("28Y",$A$156:$A$207,0))),S195+(S200-S195)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T198">
@@ -13905,27 +13910,27 @@
     </row>
     <row r="199">
       <c r="A199" s="9" t="n"/>
-      <c r="B199" s="10" t="n"/>
-      <c r="C199" s="10" t="n"/>
+      <c r="B199" s="10">
+        <f>IF($A199="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A199,$K$156:$K$220,0),MATCH(IF($A199="1Y","12M",IF($A199="12M","1Y",$A199)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C199" s="11" t="n"/>
       <c r="D199" s="11" t="n"/>
-      <c r="E199" s="12">
-        <f>IF($A199="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A199,$K$156:$K$220,0),MATCH(IF($A199="1Y","12M",IF($A199="12M","1Y",$A199)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E199" s="12" t="n"/>
       <c r="F199" s="13">
+        <f>IF(OR($A199="",G199=""),"",-LN(G199)/((B199-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G199" s="14">
         <f>IF($A199="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A199,$K$156:$K$220,0),MATCH(IF($A199="1Y","12M",IF($A199="12M","1Y",$A199)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G199" s="14">
-        <f>IF(OR($A199="",F199=""),"",-LN(F199)/((E199-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H199" s="15">
-        <f>IF(OR(G199="",NOT(ISNUMBER(C199))),"",(G199-C199)*100)</f>
+        <f>IF(OR(F199="",NOT(ISNUMBER(D199))),"",(F199-D199)*100)</f>
         <v/>
       </c>
       <c r="I199" s="16">
-        <f>IF(OR(F199="",NOT(ISNUMBER(D199))),"",F199-D199)</f>
+        <f>IF(OR(G199="",NOT(ISNUMBER(E199))),"",G199-E199)</f>
         <v/>
       </c>
       <c r="K199" s="17" t="inlineStr">
@@ -13960,7 +13965,7 @@
         <v/>
       </c>
       <c r="S199" s="19">
-        <f>IFERROR(IF(R199=1,IFERROR(INDEX($B$156:$B$207,MATCH("29Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("29Y",$A$156:$A$207,0))),S195+(S200-S195)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R199=1,IFERROR(INDEX($C$156:$C$207,MATCH("29Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("29Y",$A$156:$A$207,0))),S195+(S200-S195)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T199">
@@ -13978,27 +13983,27 @@
     </row>
     <row r="200">
       <c r="A200" s="9" t="n"/>
-      <c r="B200" s="10" t="n"/>
-      <c r="C200" s="10" t="n"/>
+      <c r="B200" s="10">
+        <f>IF($A200="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A200,$K$156:$K$220,0),MATCH(IF($A200="1Y","12M",IF($A200="12M","1Y",$A200)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C200" s="11" t="n"/>
       <c r="D200" s="11" t="n"/>
-      <c r="E200" s="12">
-        <f>IF($A200="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A200,$K$156:$K$220,0),MATCH(IF($A200="1Y","12M",IF($A200="12M","1Y",$A200)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E200" s="12" t="n"/>
       <c r="F200" s="13">
+        <f>IF(OR($A200="",G200=""),"",-LN(G200)/((B200-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G200" s="14">
         <f>IF($A200="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A200,$K$156:$K$220,0),MATCH(IF($A200="1Y","12M",IF($A200="12M","1Y",$A200)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G200" s="14">
-        <f>IF(OR($A200="",F200=""),"",-LN(F200)/((E200-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H200" s="15">
-        <f>IF(OR(G200="",NOT(ISNUMBER(C200))),"",(G200-C200)*100)</f>
+        <f>IF(OR(F200="",NOT(ISNUMBER(D200))),"",(F200-D200)*100)</f>
         <v/>
       </c>
       <c r="I200" s="16">
-        <f>IF(OR(F200="",NOT(ISNUMBER(D200))),"",F200-D200)</f>
+        <f>IF(OR(G200="",NOT(ISNUMBER(E200))),"",G200-E200)</f>
         <v/>
       </c>
       <c r="K200" s="17" t="inlineStr">
@@ -14033,7 +14038,7 @@
         <v/>
       </c>
       <c r="S200" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("30Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("30Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("30Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("30Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U200" s="20">
@@ -14111,27 +14116,27 @@
     </row>
     <row r="201">
       <c r="A201" s="9" t="n"/>
-      <c r="B201" s="10" t="n"/>
-      <c r="C201" s="10" t="n"/>
+      <c r="B201" s="10">
+        <f>IF($A201="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A201,$K$156:$K$220,0),MATCH(IF($A201="1Y","12M",IF($A201="12M","1Y",$A201)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C201" s="11" t="n"/>
       <c r="D201" s="11" t="n"/>
-      <c r="E201" s="12">
-        <f>IF($A201="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A201,$K$156:$K$220,0),MATCH(IF($A201="1Y","12M",IF($A201="12M","1Y",$A201)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E201" s="12" t="n"/>
       <c r="F201" s="13">
+        <f>IF(OR($A201="",G201=""),"",-LN(G201)/((B201-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G201" s="14">
         <f>IF($A201="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A201,$K$156:$K$220,0),MATCH(IF($A201="1Y","12M",IF($A201="12M","1Y",$A201)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G201" s="14">
-        <f>IF(OR($A201="",F201=""),"",-LN(F201)/((E201-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H201" s="15">
-        <f>IF(OR(G201="",NOT(ISNUMBER(C201))),"",(G201-C201)*100)</f>
+        <f>IF(OR(F201="",NOT(ISNUMBER(D201))),"",(F201-D201)*100)</f>
         <v/>
       </c>
       <c r="I201" s="16">
-        <f>IF(OR(F201="",NOT(ISNUMBER(D201))),"",F201-D201)</f>
+        <f>IF(OR(G201="",NOT(ISNUMBER(E201))),"",G201-E201)</f>
         <v/>
       </c>
       <c r="K201" s="17" t="inlineStr">
@@ -14166,7 +14171,7 @@
         <v/>
       </c>
       <c r="S201" s="19">
-        <f>IFERROR(IF(R201=1,IFERROR(INDEX($B$156:$B$207,MATCH("31Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("31Y",$A$156:$A$207,0))),S200+(S210-S200)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R201=1,IFERROR(INDEX($C$156:$C$207,MATCH("31Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("31Y",$A$156:$A$207,0))),S200+(S210-S200)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T201">
@@ -14184,27 +14189,27 @@
     </row>
     <row r="202">
       <c r="A202" s="9" t="n"/>
-      <c r="B202" s="10" t="n"/>
-      <c r="C202" s="10" t="n"/>
+      <c r="B202" s="10">
+        <f>IF($A202="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A202,$K$156:$K$220,0),MATCH(IF($A202="1Y","12M",IF($A202="12M","1Y",$A202)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C202" s="11" t="n"/>
       <c r="D202" s="11" t="n"/>
-      <c r="E202" s="12">
-        <f>IF($A202="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A202,$K$156:$K$220,0),MATCH(IF($A202="1Y","12M",IF($A202="12M","1Y",$A202)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E202" s="12" t="n"/>
       <c r="F202" s="13">
+        <f>IF(OR($A202="",G202=""),"",-LN(G202)/((B202-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G202" s="14">
         <f>IF($A202="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A202,$K$156:$K$220,0),MATCH(IF($A202="1Y","12M",IF($A202="12M","1Y",$A202)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G202" s="14">
-        <f>IF(OR($A202="",F202=""),"",-LN(F202)/((E202-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H202" s="15">
-        <f>IF(OR(G202="",NOT(ISNUMBER(C202))),"",(G202-C202)*100)</f>
+        <f>IF(OR(F202="",NOT(ISNUMBER(D202))),"",(F202-D202)*100)</f>
         <v/>
       </c>
       <c r="I202" s="16">
-        <f>IF(OR(F202="",NOT(ISNUMBER(D202))),"",F202-D202)</f>
+        <f>IF(OR(G202="",NOT(ISNUMBER(E202))),"",G202-E202)</f>
         <v/>
       </c>
       <c r="K202" s="17" t="inlineStr">
@@ -14239,7 +14244,7 @@
         <v/>
       </c>
       <c r="S202" s="19">
-        <f>IFERROR(IF(R202=1,IFERROR(INDEX($B$156:$B$207,MATCH("32Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("32Y",$A$156:$A$207,0))),S200+(S210-S200)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R202=1,IFERROR(INDEX($C$156:$C$207,MATCH("32Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("32Y",$A$156:$A$207,0))),S200+(S210-S200)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T202">
@@ -14257,27 +14262,27 @@
     </row>
     <row r="203">
       <c r="A203" s="9" t="n"/>
-      <c r="B203" s="10" t="n"/>
-      <c r="C203" s="10" t="n"/>
+      <c r="B203" s="10">
+        <f>IF($A203="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A203,$K$156:$K$220,0),MATCH(IF($A203="1Y","12M",IF($A203="12M","1Y",$A203)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C203" s="11" t="n"/>
       <c r="D203" s="11" t="n"/>
-      <c r="E203" s="12">
-        <f>IF($A203="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A203,$K$156:$K$220,0),MATCH(IF($A203="1Y","12M",IF($A203="12M","1Y",$A203)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E203" s="12" t="n"/>
       <c r="F203" s="13">
+        <f>IF(OR($A203="",G203=""),"",-LN(G203)/((B203-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G203" s="14">
         <f>IF($A203="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A203,$K$156:$K$220,0),MATCH(IF($A203="1Y","12M",IF($A203="12M","1Y",$A203)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G203" s="14">
-        <f>IF(OR($A203="",F203=""),"",-LN(F203)/((E203-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H203" s="15">
-        <f>IF(OR(G203="",NOT(ISNUMBER(C203))),"",(G203-C203)*100)</f>
+        <f>IF(OR(F203="",NOT(ISNUMBER(D203))),"",(F203-D203)*100)</f>
         <v/>
       </c>
       <c r="I203" s="16">
-        <f>IF(OR(F203="",NOT(ISNUMBER(D203))),"",F203-D203)</f>
+        <f>IF(OR(G203="",NOT(ISNUMBER(E203))),"",G203-E203)</f>
         <v/>
       </c>
       <c r="K203" s="17" t="inlineStr">
@@ -14312,7 +14317,7 @@
         <v/>
       </c>
       <c r="S203" s="19">
-        <f>IFERROR(IF(R203=1,IFERROR(INDEX($B$156:$B$207,MATCH("33Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("33Y",$A$156:$A$207,0))),S200+(S210-S200)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R203=1,IFERROR(INDEX($C$156:$C$207,MATCH("33Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("33Y",$A$156:$A$207,0))),S200+(S210-S200)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T203">
@@ -14330,27 +14335,27 @@
     </row>
     <row r="204">
       <c r="A204" s="9" t="n"/>
-      <c r="B204" s="10" t="n"/>
-      <c r="C204" s="10" t="n"/>
+      <c r="B204" s="10">
+        <f>IF($A204="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A204,$K$156:$K$220,0),MATCH(IF($A204="1Y","12M",IF($A204="12M","1Y",$A204)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C204" s="11" t="n"/>
       <c r="D204" s="11" t="n"/>
-      <c r="E204" s="12">
-        <f>IF($A204="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A204,$K$156:$K$220,0),MATCH(IF($A204="1Y","12M",IF($A204="12M","1Y",$A204)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E204" s="12" t="n"/>
       <c r="F204" s="13">
+        <f>IF(OR($A204="",G204=""),"",-LN(G204)/((B204-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G204" s="14">
         <f>IF($A204="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A204,$K$156:$K$220,0),MATCH(IF($A204="1Y","12M",IF($A204="12M","1Y",$A204)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G204" s="14">
-        <f>IF(OR($A204="",F204=""),"",-LN(F204)/((E204-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H204" s="15">
-        <f>IF(OR(G204="",NOT(ISNUMBER(C204))),"",(G204-C204)*100)</f>
+        <f>IF(OR(F204="",NOT(ISNUMBER(D204))),"",(F204-D204)*100)</f>
         <v/>
       </c>
       <c r="I204" s="16">
-        <f>IF(OR(F204="",NOT(ISNUMBER(D204))),"",F204-D204)</f>
+        <f>IF(OR(G204="",NOT(ISNUMBER(E204))),"",G204-E204)</f>
         <v/>
       </c>
       <c r="K204" s="17" t="inlineStr">
@@ -14385,7 +14390,7 @@
         <v/>
       </c>
       <c r="S204" s="19">
-        <f>IFERROR(IF(R204=1,IFERROR(INDEX($B$156:$B$207,MATCH("34Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("34Y",$A$156:$A$207,0))),S200+(S210-S200)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R204=1,IFERROR(INDEX($C$156:$C$207,MATCH("34Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("34Y",$A$156:$A$207,0))),S200+(S210-S200)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T204">
@@ -14403,27 +14408,27 @@
     </row>
     <row r="205">
       <c r="A205" s="9" t="n"/>
-      <c r="B205" s="10" t="n"/>
-      <c r="C205" s="10" t="n"/>
+      <c r="B205" s="10">
+        <f>IF($A205="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A205,$K$156:$K$220,0),MATCH(IF($A205="1Y","12M",IF($A205="12M","1Y",$A205)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C205" s="11" t="n"/>
       <c r="D205" s="11" t="n"/>
-      <c r="E205" s="12">
-        <f>IF($A205="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A205,$K$156:$K$220,0),MATCH(IF($A205="1Y","12M",IF($A205="12M","1Y",$A205)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E205" s="12" t="n"/>
       <c r="F205" s="13">
+        <f>IF(OR($A205="",G205=""),"",-LN(G205)/((B205-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G205" s="14">
         <f>IF($A205="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A205,$K$156:$K$220,0),MATCH(IF($A205="1Y","12M",IF($A205="12M","1Y",$A205)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G205" s="14">
-        <f>IF(OR($A205="",F205=""),"",-LN(F205)/((E205-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H205" s="15">
-        <f>IF(OR(G205="",NOT(ISNUMBER(C205))),"",(G205-C205)*100)</f>
+        <f>IF(OR(F205="",NOT(ISNUMBER(D205))),"",(F205-D205)*100)</f>
         <v/>
       </c>
       <c r="I205" s="16">
-        <f>IF(OR(F205="",NOT(ISNUMBER(D205))),"",F205-D205)</f>
+        <f>IF(OR(G205="",NOT(ISNUMBER(E205))),"",G205-E205)</f>
         <v/>
       </c>
       <c r="K205" s="17" t="inlineStr">
@@ -14458,7 +14463,7 @@
         <v/>
       </c>
       <c r="S205" s="19">
-        <f>IFERROR(IF(R205=1,IFERROR(INDEX($B$156:$B$207,MATCH("35Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("35Y",$A$156:$A$207,0))),S200+(S210-S200)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R205=1,IFERROR(INDEX($C$156:$C$207,MATCH("35Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("35Y",$A$156:$A$207,0))),S200+(S210-S200)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T205">
@@ -14476,27 +14481,27 @@
     </row>
     <row r="206">
       <c r="A206" s="9" t="n"/>
-      <c r="B206" s="10" t="n"/>
-      <c r="C206" s="10" t="n"/>
+      <c r="B206" s="10">
+        <f>IF($A206="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A206,$K$156:$K$220,0),MATCH(IF($A206="1Y","12M",IF($A206="12M","1Y",$A206)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C206" s="11" t="n"/>
       <c r="D206" s="11" t="n"/>
-      <c r="E206" s="12">
-        <f>IF($A206="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A206,$K$156:$K$220,0),MATCH(IF($A206="1Y","12M",IF($A206="12M","1Y",$A206)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E206" s="12" t="n"/>
       <c r="F206" s="13">
+        <f>IF(OR($A206="",G206=""),"",-LN(G206)/((B206-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G206" s="14">
         <f>IF($A206="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A206,$K$156:$K$220,0),MATCH(IF($A206="1Y","12M",IF($A206="12M","1Y",$A206)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G206" s="14">
-        <f>IF(OR($A206="",F206=""),"",-LN(F206)/((E206-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H206" s="15">
-        <f>IF(OR(G206="",NOT(ISNUMBER(C206))),"",(G206-C206)*100)</f>
+        <f>IF(OR(F206="",NOT(ISNUMBER(D206))),"",(F206-D206)*100)</f>
         <v/>
       </c>
       <c r="I206" s="16">
-        <f>IF(OR(F206="",NOT(ISNUMBER(D206))),"",F206-D206)</f>
+        <f>IF(OR(G206="",NOT(ISNUMBER(E206))),"",G206-E206)</f>
         <v/>
       </c>
       <c r="K206" s="17" t="inlineStr">
@@ -14531,7 +14536,7 @@
         <v/>
       </c>
       <c r="S206" s="19">
-        <f>IFERROR(IF(R206=1,IFERROR(INDEX($B$156:$B$207,MATCH("36Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("36Y",$A$156:$A$207,0))),S200+(S210-S200)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R206=1,IFERROR(INDEX($C$156:$C$207,MATCH("36Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("36Y",$A$156:$A$207,0))),S200+(S210-S200)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T206">
@@ -14549,27 +14554,27 @@
     </row>
     <row r="207">
       <c r="A207" s="9" t="n"/>
-      <c r="B207" s="10" t="n"/>
-      <c r="C207" s="10" t="n"/>
+      <c r="B207" s="10">
+        <f>IF($A207="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A207,$K$156:$K$220,0),MATCH(IF($A207="1Y","12M",IF($A207="12M","1Y",$A207)),$K$156:$K$220,0))),""))</f>
+        <v/>
+      </c>
+      <c r="C207" s="11" t="n"/>
       <c r="D207" s="11" t="n"/>
-      <c r="E207" s="12">
-        <f>IF($A207="","",IFERROR(INDEX($M$156:$M$220,IFERROR(MATCH($A207,$K$156:$K$220,0),MATCH(IF($A207="1Y","12M",IF($A207="12M","1Y",$A207)),$K$156:$K$220,0))),""))</f>
-        <v/>
-      </c>
+      <c r="E207" s="12" t="n"/>
       <c r="F207" s="13">
+        <f>IF(OR($A207="",G207=""),"",-LN(G207)/((B207-$C$151)/365)*100)</f>
+        <v/>
+      </c>
+      <c r="G207" s="14">
         <f>IF($A207="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A207,$K$156:$K$220,0),MATCH(IF($A207="1Y","12M",IF($A207="12M","1Y",$A207)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="G207" s="14">
-        <f>IF(OR($A207="",F207=""),"",-LN(F207)/((E207-$C$151)/365)*100)</f>
-        <v/>
-      </c>
       <c r="H207" s="15">
-        <f>IF(OR(G207="",NOT(ISNUMBER(C207))),"",(G207-C207)*100)</f>
+        <f>IF(OR(F207="",NOT(ISNUMBER(D207))),"",(F207-D207)*100)</f>
         <v/>
       </c>
       <c r="I207" s="16">
-        <f>IF(OR(F207="",NOT(ISNUMBER(D207))),"",F207-D207)</f>
+        <f>IF(OR(G207="",NOT(ISNUMBER(E207))),"",G207-E207)</f>
         <v/>
       </c>
       <c r="K207" s="17" t="inlineStr">
@@ -14604,7 +14609,7 @@
         <v/>
       </c>
       <c r="S207" s="19">
-        <f>IFERROR(IF(R207=1,IFERROR(INDEX($B$156:$B$207,MATCH("37Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("37Y",$A$156:$A$207,0))),S200+(S210-S200)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R207=1,IFERROR(INDEX($C$156:$C$207,MATCH("37Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("37Y",$A$156:$A$207,0))),S200+(S210-S200)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T207">
@@ -14653,7 +14658,7 @@
         <v/>
       </c>
       <c r="S208" s="19">
-        <f>IFERROR(IF(R208=1,IFERROR(INDEX($B$156:$B$207,MATCH("38Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("38Y",$A$156:$A$207,0))),S200+(S210-S200)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R208=1,IFERROR(INDEX($C$156:$C$207,MATCH("38Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("38Y",$A$156:$A$207,0))),S200+(S210-S200)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T208">
@@ -14685,7 +14690,7 @@
         </is>
       </c>
       <c r="F209" s="22">
-        <f>COUNT($G$156:$G$207)</f>
+        <f>COUNT($F$156:$F$207)</f>
         <v/>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14729,7 +14734,7 @@
         <v/>
       </c>
       <c r="S209" s="19">
-        <f>IFERROR(IF(R209=1,IFERROR(INDEX($B$156:$B$207,MATCH("39Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("39Y",$A$156:$A$207,0))),S200+(S210-S200)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R209=1,IFERROR(INDEX($C$156:$C$207,MATCH("39Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("39Y",$A$156:$A$207,0))),S200+(S210-S200)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T209">
@@ -14787,7 +14792,7 @@
         <v/>
       </c>
       <c r="S210" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("40Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("40Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("40Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("40Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U210" s="20">
@@ -14901,7 +14906,7 @@
         <v/>
       </c>
       <c r="S211" s="19">
-        <f>IFERROR(IF(R211=1,IFERROR(INDEX($B$156:$B$207,MATCH("41Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("41Y",$A$156:$A$207,0))),S210+(S220-S210)*0.1000000000),"")</f>
+        <f>IFERROR(IF(R211=1,IFERROR(INDEX($C$156:$C$207,MATCH("41Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("41Y",$A$156:$A$207,0))),S210+(S220-S210)*0.1000000000),"")</f>
         <v/>
       </c>
       <c r="T211">
@@ -14950,7 +14955,7 @@
         <v/>
       </c>
       <c r="S212" s="19">
-        <f>IFERROR(IF(R212=1,IFERROR(INDEX($B$156:$B$207,MATCH("42Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("42Y",$A$156:$A$207,0))),S210+(S220-S210)*0.2000000000),"")</f>
+        <f>IFERROR(IF(R212=1,IFERROR(INDEX($C$156:$C$207,MATCH("42Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("42Y",$A$156:$A$207,0))),S210+(S220-S210)*0.2000000000),"")</f>
         <v/>
       </c>
       <c r="T212">
@@ -14999,7 +15004,7 @@
         <v/>
       </c>
       <c r="S213" s="19">
-        <f>IFERROR(IF(R213=1,IFERROR(INDEX($B$156:$B$207,MATCH("43Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("43Y",$A$156:$A$207,0))),S210+(S220-S210)*0.3000000000),"")</f>
+        <f>IFERROR(IF(R213=1,IFERROR(INDEX($C$156:$C$207,MATCH("43Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("43Y",$A$156:$A$207,0))),S210+(S220-S210)*0.3000000000),"")</f>
         <v/>
       </c>
       <c r="T213">
@@ -15048,7 +15053,7 @@
         <v/>
       </c>
       <c r="S214" s="19">
-        <f>IFERROR(IF(R214=1,IFERROR(INDEX($B$156:$B$207,MATCH("44Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("44Y",$A$156:$A$207,0))),S210+(S220-S210)*0.4000000000),"")</f>
+        <f>IFERROR(IF(R214=1,IFERROR(INDEX($C$156:$C$207,MATCH("44Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("44Y",$A$156:$A$207,0))),S210+(S220-S210)*0.4000000000),"")</f>
         <v/>
       </c>
       <c r="T214">
@@ -15097,7 +15102,7 @@
         <v/>
       </c>
       <c r="S215" s="19">
-        <f>IFERROR(IF(R215=1,IFERROR(INDEX($B$156:$B$207,MATCH("45Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("45Y",$A$156:$A$207,0))),S210+(S220-S210)*0.5000000000),"")</f>
+        <f>IFERROR(IF(R215=1,IFERROR(INDEX($C$156:$C$207,MATCH("45Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("45Y",$A$156:$A$207,0))),S210+(S220-S210)*0.5000000000),"")</f>
         <v/>
       </c>
       <c r="T215">
@@ -15146,7 +15151,7 @@
         <v/>
       </c>
       <c r="S216" s="19">
-        <f>IFERROR(IF(R216=1,IFERROR(INDEX($B$156:$B$207,MATCH("46Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("46Y",$A$156:$A$207,0))),S210+(S220-S210)*0.6000000000),"")</f>
+        <f>IFERROR(IF(R216=1,IFERROR(INDEX($C$156:$C$207,MATCH("46Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("46Y",$A$156:$A$207,0))),S210+(S220-S210)*0.6000000000),"")</f>
         <v/>
       </c>
       <c r="T216">
@@ -15195,7 +15200,7 @@
         <v/>
       </c>
       <c r="S217" s="19">
-        <f>IFERROR(IF(R217=1,IFERROR(INDEX($B$156:$B$207,MATCH("47Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("47Y",$A$156:$A$207,0))),S210+(S220-S210)*0.7000000000),"")</f>
+        <f>IFERROR(IF(R217=1,IFERROR(INDEX($C$156:$C$207,MATCH("47Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("47Y",$A$156:$A$207,0))),S210+(S220-S210)*0.7000000000),"")</f>
         <v/>
       </c>
       <c r="T217">
@@ -15244,7 +15249,7 @@
         <v/>
       </c>
       <c r="S218" s="19">
-        <f>IFERROR(IF(R218=1,IFERROR(INDEX($B$156:$B$207,MATCH("48Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("48Y",$A$156:$A$207,0))),S210+(S220-S210)*0.8000000000),"")</f>
+        <f>IFERROR(IF(R218=1,IFERROR(INDEX($C$156:$C$207,MATCH("48Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("48Y",$A$156:$A$207,0))),S210+(S220-S210)*0.8000000000),"")</f>
         <v/>
       </c>
       <c r="T218">
@@ -15293,7 +15298,7 @@
         <v/>
       </c>
       <c r="S219" s="19">
-        <f>IFERROR(IF(R219=1,IFERROR(INDEX($B$156:$B$207,MATCH("49Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("49Y",$A$156:$A$207,0))),S210+(S220-S210)*0.9000000000),"")</f>
+        <f>IFERROR(IF(R219=1,IFERROR(INDEX($C$156:$C$207,MATCH("49Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("49Y",$A$156:$A$207,0))),S210+(S220-S210)*0.9000000000),"")</f>
         <v/>
       </c>
       <c r="T219">
@@ -15342,7 +15347,7 @@
         <v/>
       </c>
       <c r="S220" s="19">
-        <f>IFERROR(IFERROR(INDEX($B$156:$B$207,MATCH("50Y",$A$156:$A$207,0)),INDEX($B$156:$B$207,MATCH("50Y",$A$156:$A$207,0))),"")</f>
+        <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("50Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("50Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
       <c r="U220" s="20">

--- a/bloomberg/Bootstrap_Check.xlsx
+++ b/bloomberg/Bootstrap_Check.xlsx
@@ -19,9 +19,9 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.00000000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.00000000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,19 +162,25 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -596,19 +602,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CURVE TEST CASE 1 — paste and read</t>
+          <t>CURVE TEST CASE 1: paste and read</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>WORKING — the bootstrap itself, left visible so every step can be audited: dates, taus, annuity, then the 16 solver passes</t>
+          <t>WORKING: the bootstrap itself, left visible so every step can be audited: dates, taus, annuity, then the 16 solver passes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Paste YELLOW A:E straight off the capture — tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed here; this sheet points at nothing outside itself.</t>
+          <t>Paste A:E off the capture: tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed on this sheet.</t>
         </is>
       </c>
     </row>
@@ -635,6 +641,8 @@
         <v/>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
@@ -757,16 +765,16 @@
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="n"/>
+      <c r="E8" s="26" t="n"/>
       <c r="F8" s="14">
         <f>IF(OR($A8="",G8=""),"",-LN(G8)/INDEX($N$8:$N$72,IFERROR(MATCH($A8,$K$8:$K$72,0),MATCH(IF($A8="1Y","12M",IF($A8="12M","1Y",$A8)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="27">
         <f>IF($A8="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A8,$K$8:$K$72,0),MATCH(IF($A8="1Y","12M",IF($A8="12M","1Y",$A8)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="28">
         <f>IF(OR(F8="",NOT(ISNUMBER(D8))),"",(F8-D8)*100)</f>
         <v/>
       </c>
@@ -813,7 +821,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("1W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U8" s="22">
+      <c r="U8" s="29">
         <f>IFERROR(IF(S8="","",1/(1+(S8/100)*O8)),"")</f>
         <v/>
       </c>
@@ -827,16 +835,16 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="12" t="n"/>
-      <c r="E9" s="13" t="n"/>
+      <c r="E9" s="26" t="n"/>
       <c r="F9" s="14">
         <f>IF(OR($A9="",G9=""),"",-LN(G9)/INDEX($N$8:$N$72,IFERROR(MATCH($A9,$K$8:$K$72,0),MATCH(IF($A9="1Y","12M",IF($A9="12M","1Y",$A9)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="27">
         <f>IF($A9="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A9,$K$8:$K$72,0),MATCH(IF($A9="1Y","12M",IF($A9="12M","1Y",$A9)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="28">
         <f>IF(OR(F9="",NOT(ISNUMBER(D9))),"",(F9-D9)*100)</f>
         <v/>
       </c>
@@ -883,7 +891,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U9" s="22">
+      <c r="U9" s="29">
         <f>IFERROR(IF(S9="","",1/(1+(S9/100)*O9)),"")</f>
         <v/>
       </c>
@@ -897,16 +905,16 @@
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="E10" s="26" t="n"/>
       <c r="F10" s="14">
         <f>IF(OR($A10="",G10=""),"",-LN(G10)/INDEX($N$8:$N$72,IFERROR(MATCH($A10,$K$8:$K$72,0),MATCH(IF($A10="1Y","12M",IF($A10="12M","1Y",$A10)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="27">
         <f>IF($A10="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A10,$K$8:$K$72,0),MATCH(IF($A10="1Y","12M",IF($A10="12M","1Y",$A10)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="28">
         <f>IF(OR(F10="",NOT(ISNUMBER(D10))),"",(F10-D10)*100)</f>
         <v/>
       </c>
@@ -953,7 +961,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3W",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3W",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U10" s="22">
+      <c r="U10" s="29">
         <f>IFERROR(IF(S10="","",1/(1+(S10/100)*O10)),"")</f>
         <v/>
       </c>
@@ -967,16 +975,16 @@
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="E11" s="26" t="n"/>
       <c r="F11" s="14">
         <f>IF(OR($A11="",G11=""),"",-LN(G11)/INDEX($N$8:$N$72,IFERROR(MATCH($A11,$K$8:$K$72,0),MATCH(IF($A11="1Y","12M",IF($A11="12M","1Y",$A11)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="27">
         <f>IF($A11="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A11,$K$8:$K$72,0),MATCH(IF($A11="1Y","12M",IF($A11="12M","1Y",$A11)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="28">
         <f>IF(OR(F11="",NOT(ISNUMBER(D11))),"",(F11-D11)*100)</f>
         <v/>
       </c>
@@ -1023,7 +1031,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("1M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U11" s="22">
+      <c r="U11" s="29">
         <f>IFERROR(IF(S11="","",1/(1+(S11/100)*O11)),"")</f>
         <v/>
       </c>
@@ -1037,16 +1045,16 @@
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="n"/>
       <c r="D12" s="12" t="n"/>
-      <c r="E12" s="13" t="n"/>
+      <c r="E12" s="26" t="n"/>
       <c r="F12" s="14">
         <f>IF(OR($A12="",G12=""),"",-LN(G12)/INDEX($N$8:$N$72,IFERROR(MATCH($A12,$K$8:$K$72,0),MATCH(IF($A12="1Y","12M",IF($A12="12M","1Y",$A12)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="27">
         <f>IF($A12="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A12,$K$8:$K$72,0),MATCH(IF($A12="1Y","12M",IF($A12="12M","1Y",$A12)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="28">
         <f>IF(OR(F12="",NOT(ISNUMBER(D12))),"",(F12-D12)*100)</f>
         <v/>
       </c>
@@ -1093,7 +1101,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U12" s="22">
+      <c r="U12" s="29">
         <f>IFERROR(IF(S12="","",1/(1+(S12/100)*O12)),"")</f>
         <v/>
       </c>
@@ -1107,16 +1115,16 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="12" t="n"/>
-      <c r="E13" s="13" t="n"/>
+      <c r="E13" s="26" t="n"/>
       <c r="F13" s="14">
         <f>IF(OR($A13="",G13=""),"",-LN(G13)/INDEX($N$8:$N$72,IFERROR(MATCH($A13,$K$8:$K$72,0),MATCH(IF($A13="1Y","12M",IF($A13="12M","1Y",$A13)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="27">
         <f>IF($A13="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A13,$K$8:$K$72,0),MATCH(IF($A13="1Y","12M",IF($A13="12M","1Y",$A13)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="28">
         <f>IF(OR(F13="",NOT(ISNUMBER(D13))),"",(F13-D13)*100)</f>
         <v/>
       </c>
@@ -1163,7 +1171,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U13" s="22">
+      <c r="U13" s="29">
         <f>IFERROR(IF(S13="","",1/(1+(S13/100)*O13)),"")</f>
         <v/>
       </c>
@@ -1177,16 +1185,16 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="12" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="E14" s="26" t="n"/>
       <c r="F14" s="14">
         <f>IF(OR($A14="",G14=""),"",-LN(G14)/INDEX($N$8:$N$72,IFERROR(MATCH($A14,$K$8:$K$72,0),MATCH(IF($A14="1Y","12M",IF($A14="12M","1Y",$A14)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="27">
         <f>IF($A14="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A14,$K$8:$K$72,0),MATCH(IF($A14="1Y","12M",IF($A14="12M","1Y",$A14)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="28">
         <f>IF(OR(F14="",NOT(ISNUMBER(D14))),"",(F14-D14)*100)</f>
         <v/>
       </c>
@@ -1233,7 +1241,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("4M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("4M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U14" s="22">
+      <c r="U14" s="29">
         <f>IFERROR(IF(S14="","",1/(1+(S14/100)*O14)),"")</f>
         <v/>
       </c>
@@ -1247,16 +1255,16 @@
       <c r="B15" s="11" t="n"/>
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="13" t="n"/>
+      <c r="E15" s="26" t="n"/>
       <c r="F15" s="14">
         <f>IF(OR($A15="",G15=""),"",-LN(G15)/INDEX($N$8:$N$72,IFERROR(MATCH($A15,$K$8:$K$72,0),MATCH(IF($A15="1Y","12M",IF($A15="12M","1Y",$A15)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="27">
         <f>IF($A15="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A15,$K$8:$K$72,0),MATCH(IF($A15="1Y","12M",IF($A15="12M","1Y",$A15)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="28">
         <f>IF(OR(F15="",NOT(ISNUMBER(D15))),"",(F15-D15)*100)</f>
         <v/>
       </c>
@@ -1303,7 +1311,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("5M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("5M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U15" s="22">
+      <c r="U15" s="29">
         <f>IFERROR(IF(S15="","",1/(1+(S15/100)*O15)),"")</f>
         <v/>
       </c>
@@ -1317,16 +1325,16 @@
       <c r="B16" s="11" t="n"/>
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="13" t="n"/>
+      <c r="E16" s="26" t="n"/>
       <c r="F16" s="14">
         <f>IF(OR($A16="",G16=""),"",-LN(G16)/INDEX($N$8:$N$72,IFERROR(MATCH($A16,$K$8:$K$72,0),MATCH(IF($A16="1Y","12M",IF($A16="12M","1Y",$A16)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="27">
         <f>IF($A16="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A16,$K$8:$K$72,0),MATCH(IF($A16="1Y","12M",IF($A16="12M","1Y",$A16)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="28">
         <f>IF(OR(F16="",NOT(ISNUMBER(D16))),"",(F16-D16)*100)</f>
         <v/>
       </c>
@@ -1373,7 +1381,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("6M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("6M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U16" s="22">
+      <c r="U16" s="29">
         <f>IFERROR(IF(S16="","",1/(1+(S16/100)*O16)),"")</f>
         <v/>
       </c>
@@ -1387,16 +1395,16 @@
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="13" t="n"/>
+      <c r="E17" s="26" t="n"/>
       <c r="F17" s="14">
         <f>IF(OR($A17="",G17=""),"",-LN(G17)/INDEX($N$8:$N$72,IFERROR(MATCH($A17,$K$8:$K$72,0),MATCH(IF($A17="1Y","12M",IF($A17="12M","1Y",$A17)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="27">
         <f>IF($A17="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A17,$K$8:$K$72,0),MATCH(IF($A17="1Y","12M",IF($A17="12M","1Y",$A17)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="28">
         <f>IF(OR(F17="",NOT(ISNUMBER(D17))),"",(F17-D17)*100)</f>
         <v/>
       </c>
@@ -1443,7 +1451,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("7M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("7M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U17" s="22">
+      <c r="U17" s="29">
         <f>IFERROR(IF(S17="","",1/(1+(S17/100)*O17)),"")</f>
         <v/>
       </c>
@@ -1457,16 +1465,16 @@
       <c r="B18" s="11" t="n"/>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="12" t="n"/>
-      <c r="E18" s="13" t="n"/>
+      <c r="E18" s="26" t="n"/>
       <c r="F18" s="14">
         <f>IF(OR($A18="",G18=""),"",-LN(G18)/INDEX($N$8:$N$72,IFERROR(MATCH($A18,$K$8:$K$72,0),MATCH(IF($A18="1Y","12M",IF($A18="12M","1Y",$A18)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="27">
         <f>IF($A18="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A18,$K$8:$K$72,0),MATCH(IF($A18="1Y","12M",IF($A18="12M","1Y",$A18)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="28">
         <f>IF(OR(F18="",NOT(ISNUMBER(D18))),"",(F18-D18)*100)</f>
         <v/>
       </c>
@@ -1513,7 +1521,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("8M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("8M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U18" s="22">
+      <c r="U18" s="29">
         <f>IFERROR(IF(S18="","",1/(1+(S18/100)*O18)),"")</f>
         <v/>
       </c>
@@ -1527,16 +1535,16 @@
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="12" t="n"/>
-      <c r="E19" s="13" t="n"/>
+      <c r="E19" s="26" t="n"/>
       <c r="F19" s="14">
         <f>IF(OR($A19="",G19=""),"",-LN(G19)/INDEX($N$8:$N$72,IFERROR(MATCH($A19,$K$8:$K$72,0),MATCH(IF($A19="1Y","12M",IF($A19="12M","1Y",$A19)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="27">
         <f>IF($A19="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A19,$K$8:$K$72,0),MATCH(IF($A19="1Y","12M",IF($A19="12M","1Y",$A19)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="28">
         <f>IF(OR(F19="",NOT(ISNUMBER(D19))),"",(F19-D19)*100)</f>
         <v/>
       </c>
@@ -1583,7 +1591,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("9M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("9M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U19" s="22">
+      <c r="U19" s="29">
         <f>IFERROR(IF(S19="","",1/(1+(S19/100)*O19)),"")</f>
         <v/>
       </c>
@@ -1597,16 +1605,16 @@
       <c r="B20" s="11" t="n"/>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="12" t="n"/>
-      <c r="E20" s="13" t="n"/>
+      <c r="E20" s="26" t="n"/>
       <c r="F20" s="14">
         <f>IF(OR($A20="",G20=""),"",-LN(G20)/INDEX($N$8:$N$72,IFERROR(MATCH($A20,$K$8:$K$72,0),MATCH(IF($A20="1Y","12M",IF($A20="12M","1Y",$A20)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="27">
         <f>IF($A20="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A20,$K$8:$K$72,0),MATCH(IF($A20="1Y","12M",IF($A20="12M","1Y",$A20)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="28">
         <f>IF(OR(F20="",NOT(ISNUMBER(D20))),"",(F20-D20)*100)</f>
         <v/>
       </c>
@@ -1653,7 +1661,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("10M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("10M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="29">
         <f>IFERROR(IF(S20="","",1/(1+(S20/100)*O20)),"")</f>
         <v/>
       </c>
@@ -1667,16 +1675,16 @@
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="12" t="n"/>
-      <c r="E21" s="13" t="n"/>
+      <c r="E21" s="26" t="n"/>
       <c r="F21" s="14">
         <f>IF(OR($A21="",G21=""),"",-LN(G21)/INDEX($N$8:$N$72,IFERROR(MATCH($A21,$K$8:$K$72,0),MATCH(IF($A21="1Y","12M",IF($A21="12M","1Y",$A21)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="27">
         <f>IF($A21="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A21,$K$8:$K$72,0),MATCH(IF($A21="1Y","12M",IF($A21="12M","1Y",$A21)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="28">
         <f>IF(OR(F21="",NOT(ISNUMBER(D21))),"",(F21-D21)*100)</f>
         <v/>
       </c>
@@ -1723,7 +1731,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("11M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("11M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U21" s="22">
+      <c r="U21" s="29">
         <f>IFERROR(IF(S21="","",1/(1+(S21/100)*O21)),"")</f>
         <v/>
       </c>
@@ -1737,16 +1745,16 @@
       <c r="B22" s="11" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="12" t="n"/>
-      <c r="E22" s="13" t="n"/>
+      <c r="E22" s="26" t="n"/>
       <c r="F22" s="14">
         <f>IF(OR($A22="",G22=""),"",-LN(G22)/INDEX($N$8:$N$72,IFERROR(MATCH($A22,$K$8:$K$72,0),MATCH(IF($A22="1Y","12M",IF($A22="12M","1Y",$A22)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="27">
         <f>IF($A22="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A22,$K$8:$K$72,0),MATCH(IF($A22="1Y","12M",IF($A22="12M","1Y",$A22)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="28">
         <f>IF(OR(F22="",NOT(ISNUMBER(D22))),"",(F22-D22)*100)</f>
         <v/>
       </c>
@@ -1793,7 +1801,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("12M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("1Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U22" s="22">
+      <c r="U22" s="29">
         <f>IFERROR(IF(S22="","",1/(1+(S22/100)*O22)),"")</f>
         <v/>
       </c>
@@ -1807,16 +1815,16 @@
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
+      <c r="E23" s="26" t="n"/>
       <c r="F23" s="14">
         <f>IF(OR($A23="",G23=""),"",-LN(G23)/INDEX($N$8:$N$72,IFERROR(MATCH($A23,$K$8:$K$72,0),MATCH(IF($A23="1Y","12M",IF($A23="12M","1Y",$A23)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="27">
         <f>IF($A23="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A23,$K$8:$K$72,0),MATCH(IF($A23="1Y","12M",IF($A23="12M","1Y",$A23)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="28">
         <f>IF(OR(F23="",NOT(ISNUMBER(D23))),"",(F23-D23)*100)</f>
         <v/>
       </c>
@@ -1863,7 +1871,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("18M",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("18M",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U23" s="22">
+      <c r="U23" s="29">
         <f>IFERROR(IF(S23="","",(1-(S23/100)*SUM($V$8:V22))/(1+(S23/100)*P23)),"")</f>
         <v/>
       </c>
@@ -1877,16 +1885,16 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="13" t="n"/>
+      <c r="E24" s="26" t="n"/>
       <c r="F24" s="14">
         <f>IF(OR($A24="",G24=""),"",-LN(G24)/INDEX($N$8:$N$72,IFERROR(MATCH($A24,$K$8:$K$72,0),MATCH(IF($A24="1Y","12M",IF($A24="12M","1Y",$A24)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="27">
         <f>IF($A24="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A24,$K$8:$K$72,0),MATCH(IF($A24="1Y","12M",IF($A24="12M","1Y",$A24)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="28">
         <f>IF(OR(F24="",NOT(ISNUMBER(D24))),"",(F24-D24)*100)</f>
         <v/>
       </c>
@@ -1933,7 +1941,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("2Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("2Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U24" s="22">
+      <c r="U24" s="29">
         <f>IFERROR(IF(S24="","",(1-(S24/100)*SUM($V$8:V23))/(1+(S24/100)*P24)),"")</f>
         <v/>
       </c>
@@ -1947,16 +1955,16 @@
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="13" t="n"/>
+      <c r="E25" s="26" t="n"/>
       <c r="F25" s="14">
         <f>IF(OR($A25="",G25=""),"",-LN(G25)/INDEX($N$8:$N$72,IFERROR(MATCH($A25,$K$8:$K$72,0),MATCH(IF($A25="1Y","12M",IF($A25="12M","1Y",$A25)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="27">
         <f>IF($A25="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A25,$K$8:$K$72,0),MATCH(IF($A25="1Y","12M",IF($A25="12M","1Y",$A25)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="28">
         <f>IF(OR(F25="",NOT(ISNUMBER(D25))),"",(F25-D25)*100)</f>
         <v/>
       </c>
@@ -2003,7 +2011,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("3Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("3Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U25" s="22">
+      <c r="U25" s="29">
         <f>IFERROR(IF(S25="","",(1-(S25/100)*SUM($V$8:V24))/(1+(S25/100)*P25)),"")</f>
         <v/>
       </c>
@@ -2017,16 +2025,16 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="12" t="n"/>
       <c r="D26" s="12" t="n"/>
-      <c r="E26" s="13" t="n"/>
+      <c r="E26" s="26" t="n"/>
       <c r="F26" s="14">
         <f>IF(OR($A26="",G26=""),"",-LN(G26)/INDEX($N$8:$N$72,IFERROR(MATCH($A26,$K$8:$K$72,0),MATCH(IF($A26="1Y","12M",IF($A26="12M","1Y",$A26)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="27">
         <f>IF($A26="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A26,$K$8:$K$72,0),MATCH(IF($A26="1Y","12M",IF($A26="12M","1Y",$A26)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="28">
         <f>IF(OR(F26="",NOT(ISNUMBER(D26))),"",(F26-D26)*100)</f>
         <v/>
       </c>
@@ -2073,7 +2081,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("4Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("4Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U26" s="22">
+      <c r="U26" s="29">
         <f>IFERROR(IF(S26="","",(1-(S26/100)*SUM($V$8:V25))/(1+(S26/100)*P26)),"")</f>
         <v/>
       </c>
@@ -2087,16 +2095,16 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="12" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="13" t="n"/>
+      <c r="E27" s="26" t="n"/>
       <c r="F27" s="14">
         <f>IF(OR($A27="",G27=""),"",-LN(G27)/INDEX($N$8:$N$72,IFERROR(MATCH($A27,$K$8:$K$72,0),MATCH(IF($A27="1Y","12M",IF($A27="12M","1Y",$A27)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="27">
         <f>IF($A27="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A27,$K$8:$K$72,0),MATCH(IF($A27="1Y","12M",IF($A27="12M","1Y",$A27)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="28">
         <f>IF(OR(F27="",NOT(ISNUMBER(D27))),"",(F27-D27)*100)</f>
         <v/>
       </c>
@@ -2143,7 +2151,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("5Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("5Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U27" s="22">
+      <c r="U27" s="29">
         <f>IFERROR(IF(S27="","",(1-(S27/100)*SUM($V$8:V26))/(1+(S27/100)*P27)),"")</f>
         <v/>
       </c>
@@ -2157,16 +2165,16 @@
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="12" t="n"/>
-      <c r="E28" s="13" t="n"/>
+      <c r="E28" s="26" t="n"/>
       <c r="F28" s="14">
         <f>IF(OR($A28="",G28=""),"",-LN(G28)/INDEX($N$8:$N$72,IFERROR(MATCH($A28,$K$8:$K$72,0),MATCH(IF($A28="1Y","12M",IF($A28="12M","1Y",$A28)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="27">
         <f>IF($A28="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A28,$K$8:$K$72,0),MATCH(IF($A28="1Y","12M",IF($A28="12M","1Y",$A28)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="28">
         <f>IF(OR(F28="",NOT(ISNUMBER(D28))),"",(F28-D28)*100)</f>
         <v/>
       </c>
@@ -2213,7 +2221,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("6Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("6Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U28" s="22">
+      <c r="U28" s="29">
         <f>IFERROR(IF(S28="","",(1-(S28/100)*SUM($V$8:V27))/(1+(S28/100)*P28)),"")</f>
         <v/>
       </c>
@@ -2227,16 +2235,16 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="13" t="n"/>
+      <c r="E29" s="26" t="n"/>
       <c r="F29" s="14">
         <f>IF(OR($A29="",G29=""),"",-LN(G29)/INDEX($N$8:$N$72,IFERROR(MATCH($A29,$K$8:$K$72,0),MATCH(IF($A29="1Y","12M",IF($A29="12M","1Y",$A29)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="27">
         <f>IF($A29="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A29,$K$8:$K$72,0),MATCH(IF($A29="1Y","12M",IF($A29="12M","1Y",$A29)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="28">
         <f>IF(OR(F29="",NOT(ISNUMBER(D29))),"",(F29-D29)*100)</f>
         <v/>
       </c>
@@ -2283,7 +2291,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("7Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("7Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U29" s="22">
+      <c r="U29" s="29">
         <f>IFERROR(IF(S29="","",(1-(S29/100)*SUM($V$8:V28))/(1+(S29/100)*P29)),"")</f>
         <v/>
       </c>
@@ -2297,16 +2305,16 @@
       <c r="B30" s="11" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="12" t="n"/>
-      <c r="E30" s="13" t="n"/>
+      <c r="E30" s="26" t="n"/>
       <c r="F30" s="14">
         <f>IF(OR($A30="",G30=""),"",-LN(G30)/INDEX($N$8:$N$72,IFERROR(MATCH($A30,$K$8:$K$72,0),MATCH(IF($A30="1Y","12M",IF($A30="12M","1Y",$A30)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="27">
         <f>IF($A30="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A30,$K$8:$K$72,0),MATCH(IF($A30="1Y","12M",IF($A30="12M","1Y",$A30)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="28">
         <f>IF(OR(F30="",NOT(ISNUMBER(D30))),"",(F30-D30)*100)</f>
         <v/>
       </c>
@@ -2353,7 +2361,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("8Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("8Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U30" s="22">
+      <c r="U30" s="29">
         <f>IFERROR(IF(S30="","",(1-(S30/100)*SUM($V$8:V29))/(1+(S30/100)*P30)),"")</f>
         <v/>
       </c>
@@ -2367,16 +2375,16 @@
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="12" t="n"/>
-      <c r="E31" s="13" t="n"/>
+      <c r="E31" s="26" t="n"/>
       <c r="F31" s="14">
         <f>IF(OR($A31="",G31=""),"",-LN(G31)/INDEX($N$8:$N$72,IFERROR(MATCH($A31,$K$8:$K$72,0),MATCH(IF($A31="1Y","12M",IF($A31="12M","1Y",$A31)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="27">
         <f>IF($A31="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A31,$K$8:$K$72,0),MATCH(IF($A31="1Y","12M",IF($A31="12M","1Y",$A31)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="28">
         <f>IF(OR(F31="",NOT(ISNUMBER(D31))),"",(F31-D31)*100)</f>
         <v/>
       </c>
@@ -2423,7 +2431,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("9Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("9Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U31" s="22">
+      <c r="U31" s="29">
         <f>IFERROR(IF(S31="","",(1-(S31/100)*SUM($V$8:V30))/(1+(S31/100)*P31)),"")</f>
         <v/>
       </c>
@@ -2437,16 +2445,16 @@
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="12" t="n"/>
-      <c r="E32" s="13" t="n"/>
+      <c r="E32" s="26" t="n"/>
       <c r="F32" s="14">
         <f>IF(OR($A32="",G32=""),"",-LN(G32)/INDEX($N$8:$N$72,IFERROR(MATCH($A32,$K$8:$K$72,0),MATCH(IF($A32="1Y","12M",IF($A32="12M","1Y",$A32)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="27">
         <f>IF($A32="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A32,$K$8:$K$72,0),MATCH(IF($A32="1Y","12M",IF($A32="12M","1Y",$A32)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="28">
         <f>IF(OR(F32="",NOT(ISNUMBER(D32))),"",(F32-D32)*100)</f>
         <v/>
       </c>
@@ -2493,7 +2501,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("10Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("10Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U32" s="22">
+      <c r="U32" s="29">
         <f>IFERROR(IF(S32="","",(1-(S32/100)*SUM($V$8:V31))/(1+(S32/100)*P32)),"")</f>
         <v/>
       </c>
@@ -2507,16 +2515,16 @@
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="12" t="n"/>
-      <c r="E33" s="13" t="n"/>
+      <c r="E33" s="26" t="n"/>
       <c r="F33" s="14">
         <f>IF(OR($A33="",G33=""),"",-LN(G33)/INDEX($N$8:$N$72,IFERROR(MATCH($A33,$K$8:$K$72,0),MATCH(IF($A33="1Y","12M",IF($A33="12M","1Y",$A33)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="27">
         <f>IF($A33="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A33,$K$8:$K$72,0),MATCH(IF($A33="1Y","12M",IF($A33="12M","1Y",$A33)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="28">
         <f>IF(OR(F33="",NOT(ISNUMBER(D33))),"",(F33-D33)*100)</f>
         <v/>
       </c>
@@ -2567,7 +2575,7 @@
         <f>IFERROR(IF(OR(N33="",N34=""),"",(N33-N32)/(N34-N32)),"")</f>
         <v/>
       </c>
-      <c r="U33" s="22">
+      <c r="U33" s="29">
         <f>IFERROR(IF(OR(T33="",U34=""),"",U32*(U34/U32)^T33),"")</f>
         <v/>
       </c>
@@ -2581,16 +2589,16 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="E34" s="26" t="n"/>
       <c r="F34" s="14">
         <f>IF(OR($A34="",G34=""),"",-LN(G34)/INDEX($N$8:$N$72,IFERROR(MATCH($A34,$K$8:$K$72,0),MATCH(IF($A34="1Y","12M",IF($A34="12M","1Y",$A34)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="27">
         <f>IF($A34="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A34,$K$8:$K$72,0),MATCH(IF($A34="1Y","12M",IF($A34="12M","1Y",$A34)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="28">
         <f>IF(OR(F34="",NOT(ISNUMBER(D34))),"",(F34-D34)*100)</f>
         <v/>
       </c>
@@ -2637,7 +2645,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("12Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("12Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U34" s="22">
+      <c r="U34" s="29">
         <f>IFERROR(IF(S34="","",AM34),"")</f>
         <v/>
       </c>
@@ -2645,67 +2653,67 @@
         <f>IFERROR(IF(OR(U34="",Q34=0),0,P34*U34),"")</f>
         <v/>
       </c>
-      <c r="X34" s="23">
+      <c r="X34" s="30">
         <f>IFERROR(IF(S34="","",U32*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y34" s="23">
+      <c r="Y34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(X34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="Z34" s="23">
+      <c r="Z34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(Y34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AA34" s="23">
+      <c r="AA34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(Z34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AB34" s="23">
+      <c r="AB34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AA34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AC34" s="23">
+      <c r="AC34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AB34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AD34" s="23">
+      <c r="AD34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AC34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AE34" s="23">
+      <c r="AE34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AD34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AF34" s="23">
+      <c r="AF34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AE34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AG34" s="23">
+      <c r="AG34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AF34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AH34" s="23">
+      <c r="AH34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AG34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AI34" s="23">
+      <c r="AI34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AH34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AJ34" s="23">
+      <c r="AJ34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AI34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AK34" s="23">
+      <c r="AK34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AJ34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AL34" s="23">
+      <c r="AL34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AK34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
-      <c r="AM34" s="23">
+      <c r="AM34" s="30">
         <f>IFERROR(IF(S34="","",(1-(S34/100)*(SUM($V$8:V32)+SUMPRODUCT($P$33:$P$33,$Q$33:$Q$33,U32*(AL34/U32)^$T$33:$T$33)))/(1+(S34/100)*P34)),"")</f>
         <v/>
       </c>
@@ -2715,16 +2723,16 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="13" t="n"/>
+      <c r="E35" s="26" t="n"/>
       <c r="F35" s="14">
         <f>IF(OR($A35="",G35=""),"",-LN(G35)/INDEX($N$8:$N$72,IFERROR(MATCH($A35,$K$8:$K$72,0),MATCH(IF($A35="1Y","12M",IF($A35="12M","1Y",$A35)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="27">
         <f>IF($A35="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A35,$K$8:$K$72,0),MATCH(IF($A35="1Y","12M",IF($A35="12M","1Y",$A35)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="28">
         <f>IF(OR(F35="",NOT(ISNUMBER(D35))),"",(F35-D35)*100)</f>
         <v/>
       </c>
@@ -2775,7 +2783,7 @@
         <f>IFERROR(IF(OR(N35="",N37=""),"",(N35-N34)/(N37-N34)),"")</f>
         <v/>
       </c>
-      <c r="U35" s="22">
+      <c r="U35" s="29">
         <f>IFERROR(IF(OR(T35="",U37=""),"",U34*(U37/U34)^T35),"")</f>
         <v/>
       </c>
@@ -2789,16 +2797,16 @@
       <c r="B36" s="11" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="12" t="n"/>
-      <c r="E36" s="13" t="n"/>
+      <c r="E36" s="26" t="n"/>
       <c r="F36" s="14">
         <f>IF(OR($A36="",G36=""),"",-LN(G36)/INDEX($N$8:$N$72,IFERROR(MATCH($A36,$K$8:$K$72,0),MATCH(IF($A36="1Y","12M",IF($A36="12M","1Y",$A36)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="27">
         <f>IF($A36="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A36,$K$8:$K$72,0),MATCH(IF($A36="1Y","12M",IF($A36="12M","1Y",$A36)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="28">
         <f>IF(OR(F36="",NOT(ISNUMBER(D36))),"",(F36-D36)*100)</f>
         <v/>
       </c>
@@ -2849,7 +2857,7 @@
         <f>IFERROR(IF(OR(N36="",N37=""),"",(N36-N34)/(N37-N34)),"")</f>
         <v/>
       </c>
-      <c r="U36" s="22">
+      <c r="U36" s="29">
         <f>IFERROR(IF(OR(T36="",U37=""),"",U34*(U37/U34)^T36),"")</f>
         <v/>
       </c>
@@ -2863,16 +2871,16 @@
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="12" t="n"/>
-      <c r="E37" s="13" t="n"/>
+      <c r="E37" s="26" t="n"/>
       <c r="F37" s="14">
         <f>IF(OR($A37="",G37=""),"",-LN(G37)/INDEX($N$8:$N$72,IFERROR(MATCH($A37,$K$8:$K$72,0),MATCH(IF($A37="1Y","12M",IF($A37="12M","1Y",$A37)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="27">
         <f>IF($A37="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A37,$K$8:$K$72,0),MATCH(IF($A37="1Y","12M",IF($A37="12M","1Y",$A37)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="28">
         <f>IF(OR(F37="",NOT(ISNUMBER(D37))),"",(F37-D37)*100)</f>
         <v/>
       </c>
@@ -2919,7 +2927,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("15Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("15Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U37" s="22">
+      <c r="U37" s="29">
         <f>IFERROR(IF(S37="","",AM37),"")</f>
         <v/>
       </c>
@@ -2927,67 +2935,67 @@
         <f>IFERROR(IF(OR(U37="",Q37=0),0,P37*U37),"")</f>
         <v/>
       </c>
-      <c r="X37" s="23">
+      <c r="X37" s="30">
         <f>IFERROR(IF(S37="","",U34*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y37" s="23">
+      <c r="Y37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(X37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="Z37" s="23">
+      <c r="Z37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(Y37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AA37" s="23">
+      <c r="AA37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(Z37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AB37" s="23">
+      <c r="AB37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AA37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AC37" s="23">
+      <c r="AC37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AB37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AD37" s="23">
+      <c r="AD37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AC37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AE37" s="23">
+      <c r="AE37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AD37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AF37" s="23">
+      <c r="AF37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AE37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AG37" s="23">
+      <c r="AG37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AF37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AH37" s="23">
+      <c r="AH37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AG37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AI37" s="23">
+      <c r="AI37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AH37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AJ37" s="23">
+      <c r="AJ37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AI37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AK37" s="23">
+      <c r="AK37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AJ37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AL37" s="23">
+      <c r="AL37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AK37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
-      <c r="AM37" s="23">
+      <c r="AM37" s="30">
         <f>IFERROR(IF(S37="","",(1-(S37/100)*(SUM($V$8:V34)+SUMPRODUCT($P$35:$P$36,$Q$35:$Q$36,U34*(AL37/U34)^$T$35:$T$36)))/(1+(S37/100)*P37)),"")</f>
         <v/>
       </c>
@@ -2997,16 +3005,16 @@
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="12" t="n"/>
       <c r="D38" s="12" t="n"/>
-      <c r="E38" s="13" t="n"/>
+      <c r="E38" s="26" t="n"/>
       <c r="F38" s="14">
         <f>IF(OR($A38="",G38=""),"",-LN(G38)/INDEX($N$8:$N$72,IFERROR(MATCH($A38,$K$8:$K$72,0),MATCH(IF($A38="1Y","12M",IF($A38="12M","1Y",$A38)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="27">
         <f>IF($A38="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A38,$K$8:$K$72,0),MATCH(IF($A38="1Y","12M",IF($A38="12M","1Y",$A38)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="28">
         <f>IF(OR(F38="",NOT(ISNUMBER(D38))),"",(F38-D38)*100)</f>
         <v/>
       </c>
@@ -3057,7 +3065,7 @@
         <f>IFERROR(IF(OR(N38="",N42=""),"",(N38-N37)/(N42-N37)),"")</f>
         <v/>
       </c>
-      <c r="U38" s="22">
+      <c r="U38" s="29">
         <f>IFERROR(IF(OR(T38="",U42=""),"",U37*(U42/U37)^T38),"")</f>
         <v/>
       </c>
@@ -3071,16 +3079,16 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="13" t="n"/>
+      <c r="E39" s="26" t="n"/>
       <c r="F39" s="14">
         <f>IF(OR($A39="",G39=""),"",-LN(G39)/INDEX($N$8:$N$72,IFERROR(MATCH($A39,$K$8:$K$72,0),MATCH(IF($A39="1Y","12M",IF($A39="12M","1Y",$A39)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="27">
         <f>IF($A39="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A39,$K$8:$K$72,0),MATCH(IF($A39="1Y","12M",IF($A39="12M","1Y",$A39)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="28">
         <f>IF(OR(F39="",NOT(ISNUMBER(D39))),"",(F39-D39)*100)</f>
         <v/>
       </c>
@@ -3131,7 +3139,7 @@
         <f>IFERROR(IF(OR(N39="",N42=""),"",(N39-N37)/(N42-N37)),"")</f>
         <v/>
       </c>
-      <c r="U39" s="22">
+      <c r="U39" s="29">
         <f>IFERROR(IF(OR(T39="",U42=""),"",U37*(U42/U37)^T39),"")</f>
         <v/>
       </c>
@@ -3145,16 +3153,16 @@
       <c r="B40" s="11" t="n"/>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="12" t="n"/>
-      <c r="E40" s="13" t="n"/>
+      <c r="E40" s="26" t="n"/>
       <c r="F40" s="14">
         <f>IF(OR($A40="",G40=""),"",-LN(G40)/INDEX($N$8:$N$72,IFERROR(MATCH($A40,$K$8:$K$72,0),MATCH(IF($A40="1Y","12M",IF($A40="12M","1Y",$A40)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="27">
         <f>IF($A40="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A40,$K$8:$K$72,0),MATCH(IF($A40="1Y","12M",IF($A40="12M","1Y",$A40)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="28">
         <f>IF(OR(F40="",NOT(ISNUMBER(D40))),"",(F40-D40)*100)</f>
         <v/>
       </c>
@@ -3205,7 +3213,7 @@
         <f>IFERROR(IF(OR(N40="",N42=""),"",(N40-N37)/(N42-N37)),"")</f>
         <v/>
       </c>
-      <c r="U40" s="22">
+      <c r="U40" s="29">
         <f>IFERROR(IF(OR(T40="",U42=""),"",U37*(U42/U37)^T40),"")</f>
         <v/>
       </c>
@@ -3219,16 +3227,16 @@
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="12" t="n"/>
-      <c r="E41" s="13" t="n"/>
+      <c r="E41" s="26" t="n"/>
       <c r="F41" s="14">
         <f>IF(OR($A41="",G41=""),"",-LN(G41)/INDEX($N$8:$N$72,IFERROR(MATCH($A41,$K$8:$K$72,0),MATCH(IF($A41="1Y","12M",IF($A41="12M","1Y",$A41)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="27">
         <f>IF($A41="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A41,$K$8:$K$72,0),MATCH(IF($A41="1Y","12M",IF($A41="12M","1Y",$A41)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="28">
         <f>IF(OR(F41="",NOT(ISNUMBER(D41))),"",(F41-D41)*100)</f>
         <v/>
       </c>
@@ -3279,7 +3287,7 @@
         <f>IFERROR(IF(OR(N41="",N42=""),"",(N41-N37)/(N42-N37)),"")</f>
         <v/>
       </c>
-      <c r="U41" s="22">
+      <c r="U41" s="29">
         <f>IFERROR(IF(OR(T41="",U42=""),"",U37*(U42/U37)^T41),"")</f>
         <v/>
       </c>
@@ -3293,16 +3301,16 @@
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="12" t="n"/>
-      <c r="E42" s="13" t="n"/>
+      <c r="E42" s="26" t="n"/>
       <c r="F42" s="14">
         <f>IF(OR($A42="",G42=""),"",-LN(G42)/INDEX($N$8:$N$72,IFERROR(MATCH($A42,$K$8:$K$72,0),MATCH(IF($A42="1Y","12M",IF($A42="12M","1Y",$A42)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="27">
         <f>IF($A42="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A42,$K$8:$K$72,0),MATCH(IF($A42="1Y","12M",IF($A42="12M","1Y",$A42)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="28">
         <f>IF(OR(F42="",NOT(ISNUMBER(D42))),"",(F42-D42)*100)</f>
         <v/>
       </c>
@@ -3349,7 +3357,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("20Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("20Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U42" s="22">
+      <c r="U42" s="29">
         <f>IFERROR(IF(S42="","",AM42),"")</f>
         <v/>
       </c>
@@ -3357,67 +3365,67 @@
         <f>IFERROR(IF(OR(U42="",Q42=0),0,P42*U42),"")</f>
         <v/>
       </c>
-      <c r="X42" s="23">
+      <c r="X42" s="30">
         <f>IFERROR(IF(S42="","",U37*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y42" s="23">
+      <c r="Y42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(X42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="Z42" s="23">
+      <c r="Z42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(Y42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AA42" s="23">
+      <c r="AA42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(Z42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AB42" s="23">
+      <c r="AB42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AA42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AC42" s="23">
+      <c r="AC42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AB42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AD42" s="23">
+      <c r="AD42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AC42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AE42" s="23">
+      <c r="AE42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AD42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AF42" s="23">
+      <c r="AF42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AE42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AG42" s="23">
+      <c r="AG42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AF42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AH42" s="23">
+      <c r="AH42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AG42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AI42" s="23">
+      <c r="AI42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AH42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AJ42" s="23">
+      <c r="AJ42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AI42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AK42" s="23">
+      <c r="AK42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AJ42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AL42" s="23">
+      <c r="AL42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AK42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
-      <c r="AM42" s="23">
+      <c r="AM42" s="30">
         <f>IFERROR(IF(S42="","",(1-(S42/100)*(SUM($V$8:V37)+SUMPRODUCT($P$38:$P$41,$Q$38:$Q$41,U37*(AL42/U37)^$T$38:$T$41)))/(1+(S42/100)*P42)),"")</f>
         <v/>
       </c>
@@ -3427,16 +3435,16 @@
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="12" t="n"/>
-      <c r="E43" s="13" t="n"/>
+      <c r="E43" s="26" t="n"/>
       <c r="F43" s="14">
         <f>IF(OR($A43="",G43=""),"",-LN(G43)/INDEX($N$8:$N$72,IFERROR(MATCH($A43,$K$8:$K$72,0),MATCH(IF($A43="1Y","12M",IF($A43="12M","1Y",$A43)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="27">
         <f>IF($A43="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A43,$K$8:$K$72,0),MATCH(IF($A43="1Y","12M",IF($A43="12M","1Y",$A43)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="28">
         <f>IF(OR(F43="",NOT(ISNUMBER(D43))),"",(F43-D43)*100)</f>
         <v/>
       </c>
@@ -3487,7 +3495,7 @@
         <f>IFERROR(IF(OR(N43="",N47=""),"",(N43-N42)/(N47-N42)),"")</f>
         <v/>
       </c>
-      <c r="U43" s="22">
+      <c r="U43" s="29">
         <f>IFERROR(IF(OR(T43="",U47=""),"",U42*(U47/U42)^T43),"")</f>
         <v/>
       </c>
@@ -3501,16 +3509,16 @@
       <c r="B44" s="11" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="12" t="n"/>
-      <c r="E44" s="13" t="n"/>
+      <c r="E44" s="26" t="n"/>
       <c r="F44" s="14">
         <f>IF(OR($A44="",G44=""),"",-LN(G44)/INDEX($N$8:$N$72,IFERROR(MATCH($A44,$K$8:$K$72,0),MATCH(IF($A44="1Y","12M",IF($A44="12M","1Y",$A44)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="27">
         <f>IF($A44="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A44,$K$8:$K$72,0),MATCH(IF($A44="1Y","12M",IF($A44="12M","1Y",$A44)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="28">
         <f>IF(OR(F44="",NOT(ISNUMBER(D44))),"",(F44-D44)*100)</f>
         <v/>
       </c>
@@ -3561,7 +3569,7 @@
         <f>IFERROR(IF(OR(N44="",N47=""),"",(N44-N42)/(N47-N42)),"")</f>
         <v/>
       </c>
-      <c r="U44" s="22">
+      <c r="U44" s="29">
         <f>IFERROR(IF(OR(T44="",U47=""),"",U42*(U47/U42)^T44),"")</f>
         <v/>
       </c>
@@ -3575,16 +3583,16 @@
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="12" t="n"/>
-      <c r="E45" s="13" t="n"/>
+      <c r="E45" s="26" t="n"/>
       <c r="F45" s="14">
         <f>IF(OR($A45="",G45=""),"",-LN(G45)/INDEX($N$8:$N$72,IFERROR(MATCH($A45,$K$8:$K$72,0),MATCH(IF($A45="1Y","12M",IF($A45="12M","1Y",$A45)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="27">
         <f>IF($A45="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A45,$K$8:$K$72,0),MATCH(IF($A45="1Y","12M",IF($A45="12M","1Y",$A45)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="28">
         <f>IF(OR(F45="",NOT(ISNUMBER(D45))),"",(F45-D45)*100)</f>
         <v/>
       </c>
@@ -3635,7 +3643,7 @@
         <f>IFERROR(IF(OR(N45="",N47=""),"",(N45-N42)/(N47-N42)),"")</f>
         <v/>
       </c>
-      <c r="U45" s="22">
+      <c r="U45" s="29">
         <f>IFERROR(IF(OR(T45="",U47=""),"",U42*(U47/U42)^T45),"")</f>
         <v/>
       </c>
@@ -3649,16 +3657,16 @@
       <c r="B46" s="11" t="n"/>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="12" t="n"/>
-      <c r="E46" s="13" t="n"/>
+      <c r="E46" s="26" t="n"/>
       <c r="F46" s="14">
         <f>IF(OR($A46="",G46=""),"",-LN(G46)/INDEX($N$8:$N$72,IFERROR(MATCH($A46,$K$8:$K$72,0),MATCH(IF($A46="1Y","12M",IF($A46="12M","1Y",$A46)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="27">
         <f>IF($A46="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A46,$K$8:$K$72,0),MATCH(IF($A46="1Y","12M",IF($A46="12M","1Y",$A46)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="28">
         <f>IF(OR(F46="",NOT(ISNUMBER(D46))),"",(F46-D46)*100)</f>
         <v/>
       </c>
@@ -3709,7 +3717,7 @@
         <f>IFERROR(IF(OR(N46="",N47=""),"",(N46-N42)/(N47-N42)),"")</f>
         <v/>
       </c>
-      <c r="U46" s="22">
+      <c r="U46" s="29">
         <f>IFERROR(IF(OR(T46="",U47=""),"",U42*(U47/U42)^T46),"")</f>
         <v/>
       </c>
@@ -3723,16 +3731,16 @@
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="12" t="n"/>
-      <c r="E47" s="13" t="n"/>
+      <c r="E47" s="26" t="n"/>
       <c r="F47" s="14">
         <f>IF(OR($A47="",G47=""),"",-LN(G47)/INDEX($N$8:$N$72,IFERROR(MATCH($A47,$K$8:$K$72,0),MATCH(IF($A47="1Y","12M",IF($A47="12M","1Y",$A47)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="27">
         <f>IF($A47="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A47,$K$8:$K$72,0),MATCH(IF($A47="1Y","12M",IF($A47="12M","1Y",$A47)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="28">
         <f>IF(OR(F47="",NOT(ISNUMBER(D47))),"",(F47-D47)*100)</f>
         <v/>
       </c>
@@ -3779,7 +3787,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("25Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("25Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U47" s="22">
+      <c r="U47" s="29">
         <f>IFERROR(IF(S47="","",AM47),"")</f>
         <v/>
       </c>
@@ -3787,67 +3795,67 @@
         <f>IFERROR(IF(OR(U47="",Q47=0),0,P47*U47),"")</f>
         <v/>
       </c>
-      <c r="X47" s="23">
+      <c r="X47" s="30">
         <f>IFERROR(IF(S47="","",U42*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y47" s="23">
+      <c r="Y47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(X47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="Z47" s="23">
+      <c r="Z47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(Y47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AA47" s="23">
+      <c r="AA47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(Z47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AB47" s="23">
+      <c r="AB47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AA47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AC47" s="23">
+      <c r="AC47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AB47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AD47" s="23">
+      <c r="AD47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AC47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AE47" s="23">
+      <c r="AE47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AD47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AF47" s="23">
+      <c r="AF47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AE47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AG47" s="23">
+      <c r="AG47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AF47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AH47" s="23">
+      <c r="AH47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AG47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AI47" s="23">
+      <c r="AI47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AH47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AJ47" s="23">
+      <c r="AJ47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AI47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AK47" s="23">
+      <c r="AK47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AJ47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AL47" s="23">
+      <c r="AL47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AK47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
-      <c r="AM47" s="23">
+      <c r="AM47" s="30">
         <f>IFERROR(IF(S47="","",(1-(S47/100)*(SUM($V$8:V42)+SUMPRODUCT($P$43:$P$46,$Q$43:$Q$46,U42*(AL47/U42)^$T$43:$T$46)))/(1+(S47/100)*P47)),"")</f>
         <v/>
       </c>
@@ -3857,16 +3865,16 @@
       <c r="B48" s="11" t="n"/>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="12" t="n"/>
-      <c r="E48" s="13" t="n"/>
+      <c r="E48" s="26" t="n"/>
       <c r="F48" s="14">
         <f>IF(OR($A48="",G48=""),"",-LN(G48)/INDEX($N$8:$N$72,IFERROR(MATCH($A48,$K$8:$K$72,0),MATCH(IF($A48="1Y","12M",IF($A48="12M","1Y",$A48)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="27">
         <f>IF($A48="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A48,$K$8:$K$72,0),MATCH(IF($A48="1Y","12M",IF($A48="12M","1Y",$A48)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="28">
         <f>IF(OR(F48="",NOT(ISNUMBER(D48))),"",(F48-D48)*100)</f>
         <v/>
       </c>
@@ -3917,7 +3925,7 @@
         <f>IFERROR(IF(OR(N48="",N52=""),"",(N48-N47)/(N52-N47)),"")</f>
         <v/>
       </c>
-      <c r="U48" s="22">
+      <c r="U48" s="29">
         <f>IFERROR(IF(OR(T48="",U52=""),"",U47*(U52/U47)^T48),"")</f>
         <v/>
       </c>
@@ -3931,16 +3939,16 @@
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="n"/>
-      <c r="E49" s="13" t="n"/>
+      <c r="E49" s="26" t="n"/>
       <c r="F49" s="14">
         <f>IF(OR($A49="",G49=""),"",-LN(G49)/INDEX($N$8:$N$72,IFERROR(MATCH($A49,$K$8:$K$72,0),MATCH(IF($A49="1Y","12M",IF($A49="12M","1Y",$A49)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="27">
         <f>IF($A49="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A49,$K$8:$K$72,0),MATCH(IF($A49="1Y","12M",IF($A49="12M","1Y",$A49)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="28">
         <f>IF(OR(F49="",NOT(ISNUMBER(D49))),"",(F49-D49)*100)</f>
         <v/>
       </c>
@@ -3991,7 +3999,7 @@
         <f>IFERROR(IF(OR(N49="",N52=""),"",(N49-N47)/(N52-N47)),"")</f>
         <v/>
       </c>
-      <c r="U49" s="22">
+      <c r="U49" s="29">
         <f>IFERROR(IF(OR(T49="",U52=""),"",U47*(U52/U47)^T49),"")</f>
         <v/>
       </c>
@@ -4005,16 +4013,16 @@
       <c r="B50" s="11" t="n"/>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="12" t="n"/>
-      <c r="E50" s="13" t="n"/>
+      <c r="E50" s="26" t="n"/>
       <c r="F50" s="14">
         <f>IF(OR($A50="",G50=""),"",-LN(G50)/INDEX($N$8:$N$72,IFERROR(MATCH($A50,$K$8:$K$72,0),MATCH(IF($A50="1Y","12M",IF($A50="12M","1Y",$A50)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="27">
         <f>IF($A50="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A50,$K$8:$K$72,0),MATCH(IF($A50="1Y","12M",IF($A50="12M","1Y",$A50)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="28">
         <f>IF(OR(F50="",NOT(ISNUMBER(D50))),"",(F50-D50)*100)</f>
         <v/>
       </c>
@@ -4065,7 +4073,7 @@
         <f>IFERROR(IF(OR(N50="",N52=""),"",(N50-N47)/(N52-N47)),"")</f>
         <v/>
       </c>
-      <c r="U50" s="22">
+      <c r="U50" s="29">
         <f>IFERROR(IF(OR(T50="",U52=""),"",U47*(U52/U47)^T50),"")</f>
         <v/>
       </c>
@@ -4079,16 +4087,16 @@
       <c r="B51" s="11" t="n"/>
       <c r="C51" s="12" t="n"/>
       <c r="D51" s="12" t="n"/>
-      <c r="E51" s="13" t="n"/>
+      <c r="E51" s="26" t="n"/>
       <c r="F51" s="14">
         <f>IF(OR($A51="",G51=""),"",-LN(G51)/INDEX($N$8:$N$72,IFERROR(MATCH($A51,$K$8:$K$72,0),MATCH(IF($A51="1Y","12M",IF($A51="12M","1Y",$A51)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="27">
         <f>IF($A51="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A51,$K$8:$K$72,0),MATCH(IF($A51="1Y","12M",IF($A51="12M","1Y",$A51)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H51" s="16">
+      <c r="H51" s="28">
         <f>IF(OR(F51="",NOT(ISNUMBER(D51))),"",(F51-D51)*100)</f>
         <v/>
       </c>
@@ -4139,7 +4147,7 @@
         <f>IFERROR(IF(OR(N51="",N52=""),"",(N51-N47)/(N52-N47)),"")</f>
         <v/>
       </c>
-      <c r="U51" s="22">
+      <c r="U51" s="29">
         <f>IFERROR(IF(OR(T51="",U52=""),"",U47*(U52/U47)^T51),"")</f>
         <v/>
       </c>
@@ -4153,16 +4161,16 @@
       <c r="B52" s="11" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="12" t="n"/>
-      <c r="E52" s="13" t="n"/>
+      <c r="E52" s="26" t="n"/>
       <c r="F52" s="14">
         <f>IF(OR($A52="",G52=""),"",-LN(G52)/INDEX($N$8:$N$72,IFERROR(MATCH($A52,$K$8:$K$72,0),MATCH(IF($A52="1Y","12M",IF($A52="12M","1Y",$A52)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="27">
         <f>IF($A52="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A52,$K$8:$K$72,0),MATCH(IF($A52="1Y","12M",IF($A52="12M","1Y",$A52)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="28">
         <f>IF(OR(F52="",NOT(ISNUMBER(D52))),"",(F52-D52)*100)</f>
         <v/>
       </c>
@@ -4209,7 +4217,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("30Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("30Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U52" s="22">
+      <c r="U52" s="29">
         <f>IFERROR(IF(S52="","",AM52),"")</f>
         <v/>
       </c>
@@ -4217,67 +4225,67 @@
         <f>IFERROR(IF(OR(U52="",Q52=0),0,P52*U52),"")</f>
         <v/>
       </c>
-      <c r="X52" s="23">
+      <c r="X52" s="30">
         <f>IFERROR(IF(S52="","",U47*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y52" s="23">
+      <c r="Y52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(X52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="Z52" s="23">
+      <c r="Z52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(Y52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AA52" s="23">
+      <c r="AA52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(Z52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AB52" s="23">
+      <c r="AB52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AA52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AC52" s="23">
+      <c r="AC52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AB52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AD52" s="23">
+      <c r="AD52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AC52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AE52" s="23">
+      <c r="AE52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AD52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AF52" s="23">
+      <c r="AF52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AE52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AG52" s="23">
+      <c r="AG52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AF52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AH52" s="23">
+      <c r="AH52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AG52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AI52" s="23">
+      <c r="AI52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AH52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AJ52" s="23">
+      <c r="AJ52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AI52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AK52" s="23">
+      <c r="AK52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AJ52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AL52" s="23">
+      <c r="AL52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AK52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
-      <c r="AM52" s="23">
+      <c r="AM52" s="30">
         <f>IFERROR(IF(S52="","",(1-(S52/100)*(SUM($V$8:V47)+SUMPRODUCT($P$48:$P$51,$Q$48:$Q$51,U47*(AL52/U47)^$T$48:$T$51)))/(1+(S52/100)*P52)),"")</f>
         <v/>
       </c>
@@ -4287,16 +4295,16 @@
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="12" t="n"/>
-      <c r="E53" s="13" t="n"/>
+      <c r="E53" s="26" t="n"/>
       <c r="F53" s="14">
         <f>IF(OR($A53="",G53=""),"",-LN(G53)/INDEX($N$8:$N$72,IFERROR(MATCH($A53,$K$8:$K$72,0),MATCH(IF($A53="1Y","12M",IF($A53="12M","1Y",$A53)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="27">
         <f>IF($A53="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A53,$K$8:$K$72,0),MATCH(IF($A53="1Y","12M",IF($A53="12M","1Y",$A53)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="28">
         <f>IF(OR(F53="",NOT(ISNUMBER(D53))),"",(F53-D53)*100)</f>
         <v/>
       </c>
@@ -4347,7 +4355,7 @@
         <f>IFERROR(IF(OR(N53="",N62=""),"",(N53-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U53" s="22">
+      <c r="U53" s="29">
         <f>IFERROR(IF(OR(T53="",U62=""),"",U52*(U62/U52)^T53),"")</f>
         <v/>
       </c>
@@ -4361,16 +4369,16 @@
       <c r="B54" s="11" t="n"/>
       <c r="C54" s="12" t="n"/>
       <c r="D54" s="12" t="n"/>
-      <c r="E54" s="13" t="n"/>
+      <c r="E54" s="26" t="n"/>
       <c r="F54" s="14">
         <f>IF(OR($A54="",G54=""),"",-LN(G54)/INDEX($N$8:$N$72,IFERROR(MATCH($A54,$K$8:$K$72,0),MATCH(IF($A54="1Y","12M",IF($A54="12M","1Y",$A54)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="27">
         <f>IF($A54="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A54,$K$8:$K$72,0),MATCH(IF($A54="1Y","12M",IF($A54="12M","1Y",$A54)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="28">
         <f>IF(OR(F54="",NOT(ISNUMBER(D54))),"",(F54-D54)*100)</f>
         <v/>
       </c>
@@ -4421,7 +4429,7 @@
         <f>IFERROR(IF(OR(N54="",N62=""),"",(N54-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U54" s="22">
+      <c r="U54" s="29">
         <f>IFERROR(IF(OR(T54="",U62=""),"",U52*(U62/U52)^T54),"")</f>
         <v/>
       </c>
@@ -4435,16 +4443,16 @@
       <c r="B55" s="11" t="n"/>
       <c r="C55" s="12" t="n"/>
       <c r="D55" s="12" t="n"/>
-      <c r="E55" s="13" t="n"/>
+      <c r="E55" s="26" t="n"/>
       <c r="F55" s="14">
         <f>IF(OR($A55="",G55=""),"",-LN(G55)/INDEX($N$8:$N$72,IFERROR(MATCH($A55,$K$8:$K$72,0),MATCH(IF($A55="1Y","12M",IF($A55="12M","1Y",$A55)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="27">
         <f>IF($A55="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A55,$K$8:$K$72,0),MATCH(IF($A55="1Y","12M",IF($A55="12M","1Y",$A55)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H55" s="16">
+      <c r="H55" s="28">
         <f>IF(OR(F55="",NOT(ISNUMBER(D55))),"",(F55-D55)*100)</f>
         <v/>
       </c>
@@ -4495,7 +4503,7 @@
         <f>IFERROR(IF(OR(N55="",N62=""),"",(N55-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U55" s="22">
+      <c r="U55" s="29">
         <f>IFERROR(IF(OR(T55="",U62=""),"",U52*(U62/U52)^T55),"")</f>
         <v/>
       </c>
@@ -4509,16 +4517,16 @@
       <c r="B56" s="11" t="n"/>
       <c r="C56" s="12" t="n"/>
       <c r="D56" s="12" t="n"/>
-      <c r="E56" s="13" t="n"/>
+      <c r="E56" s="26" t="n"/>
       <c r="F56" s="14">
         <f>IF(OR($A56="",G56=""),"",-LN(G56)/INDEX($N$8:$N$72,IFERROR(MATCH($A56,$K$8:$K$72,0),MATCH(IF($A56="1Y","12M",IF($A56="12M","1Y",$A56)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="27">
         <f>IF($A56="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A56,$K$8:$K$72,0),MATCH(IF($A56="1Y","12M",IF($A56="12M","1Y",$A56)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H56" s="16">
+      <c r="H56" s="28">
         <f>IF(OR(F56="",NOT(ISNUMBER(D56))),"",(F56-D56)*100)</f>
         <v/>
       </c>
@@ -4569,7 +4577,7 @@
         <f>IFERROR(IF(OR(N56="",N62=""),"",(N56-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U56" s="22">
+      <c r="U56" s="29">
         <f>IFERROR(IF(OR(T56="",U62=""),"",U52*(U62/U52)^T56),"")</f>
         <v/>
       </c>
@@ -4583,16 +4591,16 @@
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="12" t="n"/>
-      <c r="E57" s="13" t="n"/>
+      <c r="E57" s="26" t="n"/>
       <c r="F57" s="14">
         <f>IF(OR($A57="",G57=""),"",-LN(G57)/INDEX($N$8:$N$72,IFERROR(MATCH($A57,$K$8:$K$72,0),MATCH(IF($A57="1Y","12M",IF($A57="12M","1Y",$A57)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="27">
         <f>IF($A57="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A57,$K$8:$K$72,0),MATCH(IF($A57="1Y","12M",IF($A57="12M","1Y",$A57)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H57" s="16">
+      <c r="H57" s="28">
         <f>IF(OR(F57="",NOT(ISNUMBER(D57))),"",(F57-D57)*100)</f>
         <v/>
       </c>
@@ -4643,7 +4651,7 @@
         <f>IFERROR(IF(OR(N57="",N62=""),"",(N57-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U57" s="22">
+      <c r="U57" s="29">
         <f>IFERROR(IF(OR(T57="",U62=""),"",U52*(U62/U52)^T57),"")</f>
         <v/>
       </c>
@@ -4657,16 +4665,16 @@
       <c r="B58" s="11" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="12" t="n"/>
-      <c r="E58" s="13" t="n"/>
+      <c r="E58" s="26" t="n"/>
       <c r="F58" s="14">
         <f>IF(OR($A58="",G58=""),"",-LN(G58)/INDEX($N$8:$N$72,IFERROR(MATCH($A58,$K$8:$K$72,0),MATCH(IF($A58="1Y","12M",IF($A58="12M","1Y",$A58)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="27">
         <f>IF($A58="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A58,$K$8:$K$72,0),MATCH(IF($A58="1Y","12M",IF($A58="12M","1Y",$A58)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H58" s="16">
+      <c r="H58" s="28">
         <f>IF(OR(F58="",NOT(ISNUMBER(D58))),"",(F58-D58)*100)</f>
         <v/>
       </c>
@@ -4717,7 +4725,7 @@
         <f>IFERROR(IF(OR(N58="",N62=""),"",(N58-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U58" s="22">
+      <c r="U58" s="29">
         <f>IFERROR(IF(OR(T58="",U62=""),"",U52*(U62/U52)^T58),"")</f>
         <v/>
       </c>
@@ -4731,16 +4739,16 @@
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="12" t="n"/>
-      <c r="E59" s="13" t="n"/>
+      <c r="E59" s="26" t="n"/>
       <c r="F59" s="14">
         <f>IF(OR($A59="",G59=""),"",-LN(G59)/INDEX($N$8:$N$72,IFERROR(MATCH($A59,$K$8:$K$72,0),MATCH(IF($A59="1Y","12M",IF($A59="12M","1Y",$A59)),$K$8:$K$72,0)))*100)</f>
         <v/>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="27">
         <f>IF($A59="","",IFERROR(INDEX($U$8:$U$72,IFERROR(MATCH($A59,$K$8:$K$72,0),MATCH(IF($A59="1Y","12M",IF($A59="12M","1Y",$A59)),$K$8:$K$72,0))),""))</f>
         <v/>
       </c>
-      <c r="H59" s="16">
+      <c r="H59" s="28">
         <f>IF(OR(F59="",NOT(ISNUMBER(D59))),"",(F59-D59)*100)</f>
         <v/>
       </c>
@@ -4791,7 +4799,7 @@
         <f>IFERROR(IF(OR(N59="",N62=""),"",(N59-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U59" s="22">
+      <c r="U59" s="29">
         <f>IFERROR(IF(OR(T59="",U62=""),"",U52*(U62/U52)^T59),"")</f>
         <v/>
       </c>
@@ -4840,7 +4848,7 @@
         <f>IFERROR(IF(OR(N60="",N62=""),"",(N60-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U60" s="22">
+      <c r="U60" s="29">
         <f>IFERROR(IF(OR(T60="",U62=""),"",U52*(U62/U52)^T60),"")</f>
         <v/>
       </c>
@@ -4873,7 +4881,7 @@
           <t>max |d zero| bp</t>
         </is>
       </c>
-      <c r="H61" s="24">
+      <c r="H61" s="31">
         <f>IF(COUNT($H$8:$H$59)=0,"",MAX(MAX($H$8:$H$59),-MIN($H$8:$H$59)))</f>
         <v/>
       </c>
@@ -4920,7 +4928,7 @@
         <f>IFERROR(IF(OR(N61="",N62=""),"",(N61-N52)/(N62-N52)),"")</f>
         <v/>
       </c>
-      <c r="U61" s="22">
+      <c r="U61" s="29">
         <f>IFERROR(IF(OR(T61="",U62=""),"",U52*(U62/U52)^T61),"")</f>
         <v/>
       </c>
@@ -4974,7 +4982,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("40Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("40Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U62" s="22">
+      <c r="U62" s="29">
         <f>IFERROR(IF(S62="","",AM62),"")</f>
         <v/>
       </c>
@@ -4982,67 +4990,67 @@
         <f>IFERROR(IF(OR(U62="",Q62=0),0,P62*U62),"")</f>
         <v/>
       </c>
-      <c r="X62" s="23">
+      <c r="X62" s="30">
         <f>IFERROR(IF(S62="","",U52*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y62" s="23">
+      <c r="Y62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(X62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="Z62" s="23">
+      <c r="Z62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(Y62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AA62" s="23">
+      <c r="AA62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(Z62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AB62" s="23">
+      <c r="AB62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AA62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AC62" s="23">
+      <c r="AC62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AB62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AD62" s="23">
+      <c r="AD62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AC62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AE62" s="23">
+      <c r="AE62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AD62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AF62" s="23">
+      <c r="AF62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AE62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AG62" s="23">
+      <c r="AG62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AF62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AH62" s="23">
+      <c r="AH62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AG62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AI62" s="23">
+      <c r="AI62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AH62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AJ62" s="23">
+      <c r="AJ62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AI62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AK62" s="23">
+      <c r="AK62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AJ62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AL62" s="23">
+      <c r="AL62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AK62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
-      <c r="AM62" s="23">
+      <c r="AM62" s="30">
         <f>IFERROR(IF(S62="","",(1-(S62/100)*(SUM($V$8:V52)+SUMPRODUCT($P$53:$P$61,$Q$53:$Q$61,U52*(AL62/U52)^$T$53:$T$61)))/(1+(S62/100)*P62)),"")</f>
         <v/>
       </c>
@@ -5092,7 +5100,7 @@
         <f>IFERROR(IF(OR(N63="",N72=""),"",(N63-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U63" s="22">
+      <c r="U63" s="29">
         <f>IFERROR(IF(OR(T63="",U72=""),"",U62*(U72/U62)^T63),"")</f>
         <v/>
       </c>
@@ -5141,7 +5149,7 @@
         <f>IFERROR(IF(OR(N64="",N72=""),"",(N64-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U64" s="22">
+      <c r="U64" s="29">
         <f>IFERROR(IF(OR(T64="",U72=""),"",U62*(U72/U62)^T64),"")</f>
         <v/>
       </c>
@@ -5190,7 +5198,7 @@
         <f>IFERROR(IF(OR(N65="",N72=""),"",(N65-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U65" s="22">
+      <c r="U65" s="29">
         <f>IFERROR(IF(OR(T65="",U72=""),"",U62*(U72/U62)^T65),"")</f>
         <v/>
       </c>
@@ -5239,7 +5247,7 @@
         <f>IFERROR(IF(OR(N66="",N72=""),"",(N66-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U66" s="22">
+      <c r="U66" s="29">
         <f>IFERROR(IF(OR(T66="",U72=""),"",U62*(U72/U62)^T66),"")</f>
         <v/>
       </c>
@@ -5288,7 +5296,7 @@
         <f>IFERROR(IF(OR(N67="",N72=""),"",(N67-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U67" s="22">
+      <c r="U67" s="29">
         <f>IFERROR(IF(OR(T67="",U72=""),"",U62*(U72/U62)^T67),"")</f>
         <v/>
       </c>
@@ -5337,7 +5345,7 @@
         <f>IFERROR(IF(OR(N68="",N72=""),"",(N68-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U68" s="22">
+      <c r="U68" s="29">
         <f>IFERROR(IF(OR(T68="",U72=""),"",U62*(U72/U62)^T68),"")</f>
         <v/>
       </c>
@@ -5386,7 +5394,7 @@
         <f>IFERROR(IF(OR(N69="",N72=""),"",(N69-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U69" s="22">
+      <c r="U69" s="29">
         <f>IFERROR(IF(OR(T69="",U72=""),"",U62*(U72/U62)^T69),"")</f>
         <v/>
       </c>
@@ -5435,7 +5443,7 @@
         <f>IFERROR(IF(OR(N70="",N72=""),"",(N70-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U70" s="22">
+      <c r="U70" s="29">
         <f>IFERROR(IF(OR(T70="",U72=""),"",U62*(U72/U62)^T70),"")</f>
         <v/>
       </c>
@@ -5484,7 +5492,7 @@
         <f>IFERROR(IF(OR(N71="",N72=""),"",(N71-N62)/(N72-N62)),"")</f>
         <v/>
       </c>
-      <c r="U71" s="22">
+      <c r="U71" s="29">
         <f>IFERROR(IF(OR(T71="",U72=""),"",U62*(U72/U62)^T71),"")</f>
         <v/>
       </c>
@@ -5529,7 +5537,7 @@
         <f>IFERROR(IFERROR(INDEX($C$8:$C$59,MATCH("50Y",$A$8:$A$59,0)),INDEX($C$8:$C$59,MATCH("50Y",$A$8:$A$59,0))),"")</f>
         <v/>
       </c>
-      <c r="U72" s="22">
+      <c r="U72" s="29">
         <f>IFERROR(IF(S72="","",AM72),"")</f>
         <v/>
       </c>
@@ -5537,82 +5545,84 @@
         <f>IFERROR(IF(OR(U72="",Q72=0),0,P72*U72),"")</f>
         <v/>
       </c>
-      <c r="X72" s="23">
+      <c r="X72" s="30">
         <f>IFERROR(IF(S72="","",U62*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y72" s="23">
+      <c r="Y72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(X72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="Z72" s="23">
+      <c r="Z72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(Y72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AA72" s="23">
+      <c r="AA72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(Z72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AB72" s="23">
+      <c r="AB72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AA72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AC72" s="23">
+      <c r="AC72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AB72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AD72" s="23">
+      <c r="AD72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AC72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AE72" s="23">
+      <c r="AE72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AD72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AF72" s="23">
+      <c r="AF72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AE72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AG72" s="23">
+      <c r="AG72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AF72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AH72" s="23">
+      <c r="AH72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AG72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AI72" s="23">
+      <c r="AI72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AH72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AJ72" s="23">
+      <c r="AJ72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AI72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AK72" s="23">
+      <c r="AK72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AJ72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AL72" s="23">
+      <c r="AL72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AK72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
-      <c r="AM72" s="23">
+      <c r="AM72" s="30">
         <f>IFERROR(IF(S72="","",(1-(S72/100)*(SUM($V$8:V62)+SUMPRODUCT($P$63:$P$71,$Q$63:$Q$71,U62*(AL72/U62)^$T$63:$T$71)))/(1+(S72/100)*P72)),"")</f>
         <v/>
       </c>
     </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>CURVE TEST CASE 2 — paste and read</t>
+          <t>CURVE TEST CASE 2: paste and read</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Paste YELLOW A:E straight off the capture — tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed here; this sheet points at nothing outside itself.</t>
+          <t>Paste A:E off the capture: tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed on this sheet.</t>
         </is>
       </c>
     </row>
@@ -5639,6 +5649,8 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
+    <row r="80"/>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
@@ -5761,16 +5773,16 @@
       <c r="B82" s="11" t="n"/>
       <c r="C82" s="12" t="n"/>
       <c r="D82" s="12" t="n"/>
-      <c r="E82" s="13" t="n"/>
+      <c r="E82" s="26" t="n"/>
       <c r="F82" s="14">
         <f>IF(OR($A82="",G82=""),"",-LN(G82)/INDEX($N$82:$N$146,IFERROR(MATCH($A82,$K$82:$K$146,0),MATCH(IF($A82="1Y","12M",IF($A82="12M","1Y",$A82)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G82" s="15">
+      <c r="G82" s="27">
         <f>IF($A82="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A82,$K$82:$K$146,0),MATCH(IF($A82="1Y","12M",IF($A82="12M","1Y",$A82)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H82" s="16">
+      <c r="H82" s="28">
         <f>IF(OR(F82="",NOT(ISNUMBER(D82))),"",(F82-D82)*100)</f>
         <v/>
       </c>
@@ -5817,7 +5829,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("1W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U82" s="22">
+      <c r="U82" s="29">
         <f>IFERROR(IF(S82="","",1/(1+(S82/100)*O82)),"")</f>
         <v/>
       </c>
@@ -5831,16 +5843,16 @@
       <c r="B83" s="11" t="n"/>
       <c r="C83" s="12" t="n"/>
       <c r="D83" s="12" t="n"/>
-      <c r="E83" s="13" t="n"/>
+      <c r="E83" s="26" t="n"/>
       <c r="F83" s="14">
         <f>IF(OR($A83="",G83=""),"",-LN(G83)/INDEX($N$82:$N$146,IFERROR(MATCH($A83,$K$82:$K$146,0),MATCH(IF($A83="1Y","12M",IF($A83="12M","1Y",$A83)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G83" s="15">
+      <c r="G83" s="27">
         <f>IF($A83="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A83,$K$82:$K$146,0),MATCH(IF($A83="1Y","12M",IF($A83="12M","1Y",$A83)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H83" s="16">
+      <c r="H83" s="28">
         <f>IF(OR(F83="",NOT(ISNUMBER(D83))),"",(F83-D83)*100)</f>
         <v/>
       </c>
@@ -5887,7 +5899,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U83" s="22">
+      <c r="U83" s="29">
         <f>IFERROR(IF(S83="","",1/(1+(S83/100)*O83)),"")</f>
         <v/>
       </c>
@@ -5901,16 +5913,16 @@
       <c r="B84" s="11" t="n"/>
       <c r="C84" s="12" t="n"/>
       <c r="D84" s="12" t="n"/>
-      <c r="E84" s="13" t="n"/>
+      <c r="E84" s="26" t="n"/>
       <c r="F84" s="14">
         <f>IF(OR($A84="",G84=""),"",-LN(G84)/INDEX($N$82:$N$146,IFERROR(MATCH($A84,$K$82:$K$146,0),MATCH(IF($A84="1Y","12M",IF($A84="12M","1Y",$A84)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G84" s="15">
+      <c r="G84" s="27">
         <f>IF($A84="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A84,$K$82:$K$146,0),MATCH(IF($A84="1Y","12M",IF($A84="12M","1Y",$A84)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H84" s="16">
+      <c r="H84" s="28">
         <f>IF(OR(F84="",NOT(ISNUMBER(D84))),"",(F84-D84)*100)</f>
         <v/>
       </c>
@@ -5957,7 +5969,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3W",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3W",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U84" s="22">
+      <c r="U84" s="29">
         <f>IFERROR(IF(S84="","",1/(1+(S84/100)*O84)),"")</f>
         <v/>
       </c>
@@ -5971,16 +5983,16 @@
       <c r="B85" s="11" t="n"/>
       <c r="C85" s="12" t="n"/>
       <c r="D85" s="12" t="n"/>
-      <c r="E85" s="13" t="n"/>
+      <c r="E85" s="26" t="n"/>
       <c r="F85" s="14">
         <f>IF(OR($A85="",G85=""),"",-LN(G85)/INDEX($N$82:$N$146,IFERROR(MATCH($A85,$K$82:$K$146,0),MATCH(IF($A85="1Y","12M",IF($A85="12M","1Y",$A85)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G85" s="15">
+      <c r="G85" s="27">
         <f>IF($A85="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A85,$K$82:$K$146,0),MATCH(IF($A85="1Y","12M",IF($A85="12M","1Y",$A85)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H85" s="16">
+      <c r="H85" s="28">
         <f>IF(OR(F85="",NOT(ISNUMBER(D85))),"",(F85-D85)*100)</f>
         <v/>
       </c>
@@ -6027,7 +6039,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("1M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U85" s="22">
+      <c r="U85" s="29">
         <f>IFERROR(IF(S85="","",1/(1+(S85/100)*O85)),"")</f>
         <v/>
       </c>
@@ -6041,16 +6053,16 @@
       <c r="B86" s="11" t="n"/>
       <c r="C86" s="12" t="n"/>
       <c r="D86" s="12" t="n"/>
-      <c r="E86" s="13" t="n"/>
+      <c r="E86" s="26" t="n"/>
       <c r="F86" s="14">
         <f>IF(OR($A86="",G86=""),"",-LN(G86)/INDEX($N$82:$N$146,IFERROR(MATCH($A86,$K$82:$K$146,0),MATCH(IF($A86="1Y","12M",IF($A86="12M","1Y",$A86)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G86" s="15">
+      <c r="G86" s="27">
         <f>IF($A86="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A86,$K$82:$K$146,0),MATCH(IF($A86="1Y","12M",IF($A86="12M","1Y",$A86)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H86" s="16">
+      <c r="H86" s="28">
         <f>IF(OR(F86="",NOT(ISNUMBER(D86))),"",(F86-D86)*100)</f>
         <v/>
       </c>
@@ -6097,7 +6109,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U86" s="22">
+      <c r="U86" s="29">
         <f>IFERROR(IF(S86="","",1/(1+(S86/100)*O86)),"")</f>
         <v/>
       </c>
@@ -6111,16 +6123,16 @@
       <c r="B87" s="11" t="n"/>
       <c r="C87" s="12" t="n"/>
       <c r="D87" s="12" t="n"/>
-      <c r="E87" s="13" t="n"/>
+      <c r="E87" s="26" t="n"/>
       <c r="F87" s="14">
         <f>IF(OR($A87="",G87=""),"",-LN(G87)/INDEX($N$82:$N$146,IFERROR(MATCH($A87,$K$82:$K$146,0),MATCH(IF($A87="1Y","12M",IF($A87="12M","1Y",$A87)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G87" s="15">
+      <c r="G87" s="27">
         <f>IF($A87="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A87,$K$82:$K$146,0),MATCH(IF($A87="1Y","12M",IF($A87="12M","1Y",$A87)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H87" s="16">
+      <c r="H87" s="28">
         <f>IF(OR(F87="",NOT(ISNUMBER(D87))),"",(F87-D87)*100)</f>
         <v/>
       </c>
@@ -6167,7 +6179,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U87" s="22">
+      <c r="U87" s="29">
         <f>IFERROR(IF(S87="","",1/(1+(S87/100)*O87)),"")</f>
         <v/>
       </c>
@@ -6181,16 +6193,16 @@
       <c r="B88" s="11" t="n"/>
       <c r="C88" s="12" t="n"/>
       <c r="D88" s="12" t="n"/>
-      <c r="E88" s="13" t="n"/>
+      <c r="E88" s="26" t="n"/>
       <c r="F88" s="14">
         <f>IF(OR($A88="",G88=""),"",-LN(G88)/INDEX($N$82:$N$146,IFERROR(MATCH($A88,$K$82:$K$146,0),MATCH(IF($A88="1Y","12M",IF($A88="12M","1Y",$A88)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G88" s="15">
+      <c r="G88" s="27">
         <f>IF($A88="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A88,$K$82:$K$146,0),MATCH(IF($A88="1Y","12M",IF($A88="12M","1Y",$A88)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H88" s="16">
+      <c r="H88" s="28">
         <f>IF(OR(F88="",NOT(ISNUMBER(D88))),"",(F88-D88)*100)</f>
         <v/>
       </c>
@@ -6237,7 +6249,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("4M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("4M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U88" s="22">
+      <c r="U88" s="29">
         <f>IFERROR(IF(S88="","",1/(1+(S88/100)*O88)),"")</f>
         <v/>
       </c>
@@ -6251,16 +6263,16 @@
       <c r="B89" s="11" t="n"/>
       <c r="C89" s="12" t="n"/>
       <c r="D89" s="12" t="n"/>
-      <c r="E89" s="13" t="n"/>
+      <c r="E89" s="26" t="n"/>
       <c r="F89" s="14">
         <f>IF(OR($A89="",G89=""),"",-LN(G89)/INDEX($N$82:$N$146,IFERROR(MATCH($A89,$K$82:$K$146,0),MATCH(IF($A89="1Y","12M",IF($A89="12M","1Y",$A89)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G89" s="15">
+      <c r="G89" s="27">
         <f>IF($A89="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A89,$K$82:$K$146,0),MATCH(IF($A89="1Y","12M",IF($A89="12M","1Y",$A89)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H89" s="16">
+      <c r="H89" s="28">
         <f>IF(OR(F89="",NOT(ISNUMBER(D89))),"",(F89-D89)*100)</f>
         <v/>
       </c>
@@ -6307,7 +6319,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("5M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("5M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U89" s="22">
+      <c r="U89" s="29">
         <f>IFERROR(IF(S89="","",1/(1+(S89/100)*O89)),"")</f>
         <v/>
       </c>
@@ -6321,16 +6333,16 @@
       <c r="B90" s="11" t="n"/>
       <c r="C90" s="12" t="n"/>
       <c r="D90" s="12" t="n"/>
-      <c r="E90" s="13" t="n"/>
+      <c r="E90" s="26" t="n"/>
       <c r="F90" s="14">
         <f>IF(OR($A90="",G90=""),"",-LN(G90)/INDEX($N$82:$N$146,IFERROR(MATCH($A90,$K$82:$K$146,0),MATCH(IF($A90="1Y","12M",IF($A90="12M","1Y",$A90)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G90" s="15">
+      <c r="G90" s="27">
         <f>IF($A90="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A90,$K$82:$K$146,0),MATCH(IF($A90="1Y","12M",IF($A90="12M","1Y",$A90)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H90" s="16">
+      <c r="H90" s="28">
         <f>IF(OR(F90="",NOT(ISNUMBER(D90))),"",(F90-D90)*100)</f>
         <v/>
       </c>
@@ -6377,7 +6389,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("6M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("6M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U90" s="22">
+      <c r="U90" s="29">
         <f>IFERROR(IF(S90="","",1/(1+(S90/100)*O90)),"")</f>
         <v/>
       </c>
@@ -6391,16 +6403,16 @@
       <c r="B91" s="11" t="n"/>
       <c r="C91" s="12" t="n"/>
       <c r="D91" s="12" t="n"/>
-      <c r="E91" s="13" t="n"/>
+      <c r="E91" s="26" t="n"/>
       <c r="F91" s="14">
         <f>IF(OR($A91="",G91=""),"",-LN(G91)/INDEX($N$82:$N$146,IFERROR(MATCH($A91,$K$82:$K$146,0),MATCH(IF($A91="1Y","12M",IF($A91="12M","1Y",$A91)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G91" s="15">
+      <c r="G91" s="27">
         <f>IF($A91="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A91,$K$82:$K$146,0),MATCH(IF($A91="1Y","12M",IF($A91="12M","1Y",$A91)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H91" s="16">
+      <c r="H91" s="28">
         <f>IF(OR(F91="",NOT(ISNUMBER(D91))),"",(F91-D91)*100)</f>
         <v/>
       </c>
@@ -6447,7 +6459,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("7M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("7M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U91" s="22">
+      <c r="U91" s="29">
         <f>IFERROR(IF(S91="","",1/(1+(S91/100)*O91)),"")</f>
         <v/>
       </c>
@@ -6461,16 +6473,16 @@
       <c r="B92" s="11" t="n"/>
       <c r="C92" s="12" t="n"/>
       <c r="D92" s="12" t="n"/>
-      <c r="E92" s="13" t="n"/>
+      <c r="E92" s="26" t="n"/>
       <c r="F92" s="14">
         <f>IF(OR($A92="",G92=""),"",-LN(G92)/INDEX($N$82:$N$146,IFERROR(MATCH($A92,$K$82:$K$146,0),MATCH(IF($A92="1Y","12M",IF($A92="12M","1Y",$A92)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G92" s="15">
+      <c r="G92" s="27">
         <f>IF($A92="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A92,$K$82:$K$146,0),MATCH(IF($A92="1Y","12M",IF($A92="12M","1Y",$A92)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H92" s="16">
+      <c r="H92" s="28">
         <f>IF(OR(F92="",NOT(ISNUMBER(D92))),"",(F92-D92)*100)</f>
         <v/>
       </c>
@@ -6517,7 +6529,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("8M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("8M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U92" s="22">
+      <c r="U92" s="29">
         <f>IFERROR(IF(S92="","",1/(1+(S92/100)*O92)),"")</f>
         <v/>
       </c>
@@ -6531,16 +6543,16 @@
       <c r="B93" s="11" t="n"/>
       <c r="C93" s="12" t="n"/>
       <c r="D93" s="12" t="n"/>
-      <c r="E93" s="13" t="n"/>
+      <c r="E93" s="26" t="n"/>
       <c r="F93" s="14">
         <f>IF(OR($A93="",G93=""),"",-LN(G93)/INDEX($N$82:$N$146,IFERROR(MATCH($A93,$K$82:$K$146,0),MATCH(IF($A93="1Y","12M",IF($A93="12M","1Y",$A93)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G93" s="15">
+      <c r="G93" s="27">
         <f>IF($A93="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A93,$K$82:$K$146,0),MATCH(IF($A93="1Y","12M",IF($A93="12M","1Y",$A93)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H93" s="16">
+      <c r="H93" s="28">
         <f>IF(OR(F93="",NOT(ISNUMBER(D93))),"",(F93-D93)*100)</f>
         <v/>
       </c>
@@ -6587,7 +6599,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("9M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("9M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U93" s="22">
+      <c r="U93" s="29">
         <f>IFERROR(IF(S93="","",1/(1+(S93/100)*O93)),"")</f>
         <v/>
       </c>
@@ -6601,16 +6613,16 @@
       <c r="B94" s="11" t="n"/>
       <c r="C94" s="12" t="n"/>
       <c r="D94" s="12" t="n"/>
-      <c r="E94" s="13" t="n"/>
+      <c r="E94" s="26" t="n"/>
       <c r="F94" s="14">
         <f>IF(OR($A94="",G94=""),"",-LN(G94)/INDEX($N$82:$N$146,IFERROR(MATCH($A94,$K$82:$K$146,0),MATCH(IF($A94="1Y","12M",IF($A94="12M","1Y",$A94)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G94" s="15">
+      <c r="G94" s="27">
         <f>IF($A94="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A94,$K$82:$K$146,0),MATCH(IF($A94="1Y","12M",IF($A94="12M","1Y",$A94)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H94" s="16">
+      <c r="H94" s="28">
         <f>IF(OR(F94="",NOT(ISNUMBER(D94))),"",(F94-D94)*100)</f>
         <v/>
       </c>
@@ -6657,7 +6669,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("10M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("10M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U94" s="22">
+      <c r="U94" s="29">
         <f>IFERROR(IF(S94="","",1/(1+(S94/100)*O94)),"")</f>
         <v/>
       </c>
@@ -6671,16 +6683,16 @@
       <c r="B95" s="11" t="n"/>
       <c r="C95" s="12" t="n"/>
       <c r="D95" s="12" t="n"/>
-      <c r="E95" s="13" t="n"/>
+      <c r="E95" s="26" t="n"/>
       <c r="F95" s="14">
         <f>IF(OR($A95="",G95=""),"",-LN(G95)/INDEX($N$82:$N$146,IFERROR(MATCH($A95,$K$82:$K$146,0),MATCH(IF($A95="1Y","12M",IF($A95="12M","1Y",$A95)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G95" s="15">
+      <c r="G95" s="27">
         <f>IF($A95="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A95,$K$82:$K$146,0),MATCH(IF($A95="1Y","12M",IF($A95="12M","1Y",$A95)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H95" s="16">
+      <c r="H95" s="28">
         <f>IF(OR(F95="",NOT(ISNUMBER(D95))),"",(F95-D95)*100)</f>
         <v/>
       </c>
@@ -6727,7 +6739,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("11M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("11M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U95" s="22">
+      <c r="U95" s="29">
         <f>IFERROR(IF(S95="","",1/(1+(S95/100)*O95)),"")</f>
         <v/>
       </c>
@@ -6741,16 +6753,16 @@
       <c r="B96" s="11" t="n"/>
       <c r="C96" s="12" t="n"/>
       <c r="D96" s="12" t="n"/>
-      <c r="E96" s="13" t="n"/>
+      <c r="E96" s="26" t="n"/>
       <c r="F96" s="14">
         <f>IF(OR($A96="",G96=""),"",-LN(G96)/INDEX($N$82:$N$146,IFERROR(MATCH($A96,$K$82:$K$146,0),MATCH(IF($A96="1Y","12M",IF($A96="12M","1Y",$A96)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="27">
         <f>IF($A96="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A96,$K$82:$K$146,0),MATCH(IF($A96="1Y","12M",IF($A96="12M","1Y",$A96)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H96" s="16">
+      <c r="H96" s="28">
         <f>IF(OR(F96="",NOT(ISNUMBER(D96))),"",(F96-D96)*100)</f>
         <v/>
       </c>
@@ -6797,7 +6809,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("12M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("1Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U96" s="22">
+      <c r="U96" s="29">
         <f>IFERROR(IF(S96="","",1/(1+(S96/100)*O96)),"")</f>
         <v/>
       </c>
@@ -6811,16 +6823,16 @@
       <c r="B97" s="11" t="n"/>
       <c r="C97" s="12" t="n"/>
       <c r="D97" s="12" t="n"/>
-      <c r="E97" s="13" t="n"/>
+      <c r="E97" s="26" t="n"/>
       <c r="F97" s="14">
         <f>IF(OR($A97="",G97=""),"",-LN(G97)/INDEX($N$82:$N$146,IFERROR(MATCH($A97,$K$82:$K$146,0),MATCH(IF($A97="1Y","12M",IF($A97="12M","1Y",$A97)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="27">
         <f>IF($A97="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A97,$K$82:$K$146,0),MATCH(IF($A97="1Y","12M",IF($A97="12M","1Y",$A97)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H97" s="16">
+      <c r="H97" s="28">
         <f>IF(OR(F97="",NOT(ISNUMBER(D97))),"",(F97-D97)*100)</f>
         <v/>
       </c>
@@ -6867,7 +6879,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("18M",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("18M",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U97" s="22">
+      <c r="U97" s="29">
         <f>IFERROR(IF(S97="","",(1-(S97/100)*SUM($V$82:V96))/(1+(S97/100)*P97)),"")</f>
         <v/>
       </c>
@@ -6881,16 +6893,16 @@
       <c r="B98" s="11" t="n"/>
       <c r="C98" s="12" t="n"/>
       <c r="D98" s="12" t="n"/>
-      <c r="E98" s="13" t="n"/>
+      <c r="E98" s="26" t="n"/>
       <c r="F98" s="14">
         <f>IF(OR($A98="",G98=""),"",-LN(G98)/INDEX($N$82:$N$146,IFERROR(MATCH($A98,$K$82:$K$146,0),MATCH(IF($A98="1Y","12M",IF($A98="12M","1Y",$A98)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G98" s="15">
+      <c r="G98" s="27">
         <f>IF($A98="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A98,$K$82:$K$146,0),MATCH(IF($A98="1Y","12M",IF($A98="12M","1Y",$A98)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H98" s="16">
+      <c r="H98" s="28">
         <f>IF(OR(F98="",NOT(ISNUMBER(D98))),"",(F98-D98)*100)</f>
         <v/>
       </c>
@@ -6937,7 +6949,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("2Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("2Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U98" s="22">
+      <c r="U98" s="29">
         <f>IFERROR(IF(S98="","",(1-(S98/100)*SUM($V$82:V97))/(1+(S98/100)*P98)),"")</f>
         <v/>
       </c>
@@ -6951,16 +6963,16 @@
       <c r="B99" s="11" t="n"/>
       <c r="C99" s="12" t="n"/>
       <c r="D99" s="12" t="n"/>
-      <c r="E99" s="13" t="n"/>
+      <c r="E99" s="26" t="n"/>
       <c r="F99" s="14">
         <f>IF(OR($A99="",G99=""),"",-LN(G99)/INDEX($N$82:$N$146,IFERROR(MATCH($A99,$K$82:$K$146,0),MATCH(IF($A99="1Y","12M",IF($A99="12M","1Y",$A99)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G99" s="15">
+      <c r="G99" s="27">
         <f>IF($A99="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A99,$K$82:$K$146,0),MATCH(IF($A99="1Y","12M",IF($A99="12M","1Y",$A99)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H99" s="16">
+      <c r="H99" s="28">
         <f>IF(OR(F99="",NOT(ISNUMBER(D99))),"",(F99-D99)*100)</f>
         <v/>
       </c>
@@ -7007,7 +7019,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("3Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("3Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U99" s="22">
+      <c r="U99" s="29">
         <f>IFERROR(IF(S99="","",(1-(S99/100)*SUM($V$82:V98))/(1+(S99/100)*P99)),"")</f>
         <v/>
       </c>
@@ -7021,16 +7033,16 @@
       <c r="B100" s="11" t="n"/>
       <c r="C100" s="12" t="n"/>
       <c r="D100" s="12" t="n"/>
-      <c r="E100" s="13" t="n"/>
+      <c r="E100" s="26" t="n"/>
       <c r="F100" s="14">
         <f>IF(OR($A100="",G100=""),"",-LN(G100)/INDEX($N$82:$N$146,IFERROR(MATCH($A100,$K$82:$K$146,0),MATCH(IF($A100="1Y","12M",IF($A100="12M","1Y",$A100)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G100" s="15">
+      <c r="G100" s="27">
         <f>IF($A100="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A100,$K$82:$K$146,0),MATCH(IF($A100="1Y","12M",IF($A100="12M","1Y",$A100)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H100" s="16">
+      <c r="H100" s="28">
         <f>IF(OR(F100="",NOT(ISNUMBER(D100))),"",(F100-D100)*100)</f>
         <v/>
       </c>
@@ -7077,7 +7089,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("4Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("4Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U100" s="22">
+      <c r="U100" s="29">
         <f>IFERROR(IF(S100="","",(1-(S100/100)*SUM($V$82:V99))/(1+(S100/100)*P100)),"")</f>
         <v/>
       </c>
@@ -7091,16 +7103,16 @@
       <c r="B101" s="11" t="n"/>
       <c r="C101" s="12" t="n"/>
       <c r="D101" s="12" t="n"/>
-      <c r="E101" s="13" t="n"/>
+      <c r="E101" s="26" t="n"/>
       <c r="F101" s="14">
         <f>IF(OR($A101="",G101=""),"",-LN(G101)/INDEX($N$82:$N$146,IFERROR(MATCH($A101,$K$82:$K$146,0),MATCH(IF($A101="1Y","12M",IF($A101="12M","1Y",$A101)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G101" s="15">
+      <c r="G101" s="27">
         <f>IF($A101="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A101,$K$82:$K$146,0),MATCH(IF($A101="1Y","12M",IF($A101="12M","1Y",$A101)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H101" s="16">
+      <c r="H101" s="28">
         <f>IF(OR(F101="",NOT(ISNUMBER(D101))),"",(F101-D101)*100)</f>
         <v/>
       </c>
@@ -7147,7 +7159,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("5Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("5Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U101" s="22">
+      <c r="U101" s="29">
         <f>IFERROR(IF(S101="","",(1-(S101/100)*SUM($V$82:V100))/(1+(S101/100)*P101)),"")</f>
         <v/>
       </c>
@@ -7161,16 +7173,16 @@
       <c r="B102" s="11" t="n"/>
       <c r="C102" s="12" t="n"/>
       <c r="D102" s="12" t="n"/>
-      <c r="E102" s="13" t="n"/>
+      <c r="E102" s="26" t="n"/>
       <c r="F102" s="14">
         <f>IF(OR($A102="",G102=""),"",-LN(G102)/INDEX($N$82:$N$146,IFERROR(MATCH($A102,$K$82:$K$146,0),MATCH(IF($A102="1Y","12M",IF($A102="12M","1Y",$A102)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G102" s="15">
+      <c r="G102" s="27">
         <f>IF($A102="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A102,$K$82:$K$146,0),MATCH(IF($A102="1Y","12M",IF($A102="12M","1Y",$A102)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H102" s="16">
+      <c r="H102" s="28">
         <f>IF(OR(F102="",NOT(ISNUMBER(D102))),"",(F102-D102)*100)</f>
         <v/>
       </c>
@@ -7217,7 +7229,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("6Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("6Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U102" s="22">
+      <c r="U102" s="29">
         <f>IFERROR(IF(S102="","",(1-(S102/100)*SUM($V$82:V101))/(1+(S102/100)*P102)),"")</f>
         <v/>
       </c>
@@ -7231,16 +7243,16 @@
       <c r="B103" s="11" t="n"/>
       <c r="C103" s="12" t="n"/>
       <c r="D103" s="12" t="n"/>
-      <c r="E103" s="13" t="n"/>
+      <c r="E103" s="26" t="n"/>
       <c r="F103" s="14">
         <f>IF(OR($A103="",G103=""),"",-LN(G103)/INDEX($N$82:$N$146,IFERROR(MATCH($A103,$K$82:$K$146,0),MATCH(IF($A103="1Y","12M",IF($A103="12M","1Y",$A103)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G103" s="15">
+      <c r="G103" s="27">
         <f>IF($A103="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A103,$K$82:$K$146,0),MATCH(IF($A103="1Y","12M",IF($A103="12M","1Y",$A103)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H103" s="16">
+      <c r="H103" s="28">
         <f>IF(OR(F103="",NOT(ISNUMBER(D103))),"",(F103-D103)*100)</f>
         <v/>
       </c>
@@ -7287,7 +7299,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("7Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("7Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U103" s="22">
+      <c r="U103" s="29">
         <f>IFERROR(IF(S103="","",(1-(S103/100)*SUM($V$82:V102))/(1+(S103/100)*P103)),"")</f>
         <v/>
       </c>
@@ -7301,16 +7313,16 @@
       <c r="B104" s="11" t="n"/>
       <c r="C104" s="12" t="n"/>
       <c r="D104" s="12" t="n"/>
-      <c r="E104" s="13" t="n"/>
+      <c r="E104" s="26" t="n"/>
       <c r="F104" s="14">
         <f>IF(OR($A104="",G104=""),"",-LN(G104)/INDEX($N$82:$N$146,IFERROR(MATCH($A104,$K$82:$K$146,0),MATCH(IF($A104="1Y","12M",IF($A104="12M","1Y",$A104)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G104" s="15">
+      <c r="G104" s="27">
         <f>IF($A104="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A104,$K$82:$K$146,0),MATCH(IF($A104="1Y","12M",IF($A104="12M","1Y",$A104)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H104" s="16">
+      <c r="H104" s="28">
         <f>IF(OR(F104="",NOT(ISNUMBER(D104))),"",(F104-D104)*100)</f>
         <v/>
       </c>
@@ -7357,7 +7369,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("8Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("8Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U104" s="22">
+      <c r="U104" s="29">
         <f>IFERROR(IF(S104="","",(1-(S104/100)*SUM($V$82:V103))/(1+(S104/100)*P104)),"")</f>
         <v/>
       </c>
@@ -7371,16 +7383,16 @@
       <c r="B105" s="11" t="n"/>
       <c r="C105" s="12" t="n"/>
       <c r="D105" s="12" t="n"/>
-      <c r="E105" s="13" t="n"/>
+      <c r="E105" s="26" t="n"/>
       <c r="F105" s="14">
         <f>IF(OR($A105="",G105=""),"",-LN(G105)/INDEX($N$82:$N$146,IFERROR(MATCH($A105,$K$82:$K$146,0),MATCH(IF($A105="1Y","12M",IF($A105="12M","1Y",$A105)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G105" s="15">
+      <c r="G105" s="27">
         <f>IF($A105="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A105,$K$82:$K$146,0),MATCH(IF($A105="1Y","12M",IF($A105="12M","1Y",$A105)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H105" s="16">
+      <c r="H105" s="28">
         <f>IF(OR(F105="",NOT(ISNUMBER(D105))),"",(F105-D105)*100)</f>
         <v/>
       </c>
@@ -7427,7 +7439,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("9Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("9Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U105" s="22">
+      <c r="U105" s="29">
         <f>IFERROR(IF(S105="","",(1-(S105/100)*SUM($V$82:V104))/(1+(S105/100)*P105)),"")</f>
         <v/>
       </c>
@@ -7441,16 +7453,16 @@
       <c r="B106" s="11" t="n"/>
       <c r="C106" s="12" t="n"/>
       <c r="D106" s="12" t="n"/>
-      <c r="E106" s="13" t="n"/>
+      <c r="E106" s="26" t="n"/>
       <c r="F106" s="14">
         <f>IF(OR($A106="",G106=""),"",-LN(G106)/INDEX($N$82:$N$146,IFERROR(MATCH($A106,$K$82:$K$146,0),MATCH(IF($A106="1Y","12M",IF($A106="12M","1Y",$A106)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G106" s="15">
+      <c r="G106" s="27">
         <f>IF($A106="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A106,$K$82:$K$146,0),MATCH(IF($A106="1Y","12M",IF($A106="12M","1Y",$A106)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H106" s="16">
+      <c r="H106" s="28">
         <f>IF(OR(F106="",NOT(ISNUMBER(D106))),"",(F106-D106)*100)</f>
         <v/>
       </c>
@@ -7497,7 +7509,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("10Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("10Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U106" s="22">
+      <c r="U106" s="29">
         <f>IFERROR(IF(S106="","",(1-(S106/100)*SUM($V$82:V105))/(1+(S106/100)*P106)),"")</f>
         <v/>
       </c>
@@ -7511,16 +7523,16 @@
       <c r="B107" s="11" t="n"/>
       <c r="C107" s="12" t="n"/>
       <c r="D107" s="12" t="n"/>
-      <c r="E107" s="13" t="n"/>
+      <c r="E107" s="26" t="n"/>
       <c r="F107" s="14">
         <f>IF(OR($A107="",G107=""),"",-LN(G107)/INDEX($N$82:$N$146,IFERROR(MATCH($A107,$K$82:$K$146,0),MATCH(IF($A107="1Y","12M",IF($A107="12M","1Y",$A107)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G107" s="15">
+      <c r="G107" s="27">
         <f>IF($A107="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A107,$K$82:$K$146,0),MATCH(IF($A107="1Y","12M",IF($A107="12M","1Y",$A107)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H107" s="16">
+      <c r="H107" s="28">
         <f>IF(OR(F107="",NOT(ISNUMBER(D107))),"",(F107-D107)*100)</f>
         <v/>
       </c>
@@ -7571,7 +7583,7 @@
         <f>IFERROR(IF(OR(N107="",N108=""),"",(N107-N106)/(N108-N106)),"")</f>
         <v/>
       </c>
-      <c r="U107" s="22">
+      <c r="U107" s="29">
         <f>IFERROR(IF(OR(T107="",U108=""),"",U106*(U108/U106)^T107),"")</f>
         <v/>
       </c>
@@ -7585,16 +7597,16 @@
       <c r="B108" s="11" t="n"/>
       <c r="C108" s="12" t="n"/>
       <c r="D108" s="12" t="n"/>
-      <c r="E108" s="13" t="n"/>
+      <c r="E108" s="26" t="n"/>
       <c r="F108" s="14">
         <f>IF(OR($A108="",G108=""),"",-LN(G108)/INDEX($N$82:$N$146,IFERROR(MATCH($A108,$K$82:$K$146,0),MATCH(IF($A108="1Y","12M",IF($A108="12M","1Y",$A108)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G108" s="15">
+      <c r="G108" s="27">
         <f>IF($A108="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A108,$K$82:$K$146,0),MATCH(IF($A108="1Y","12M",IF($A108="12M","1Y",$A108)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H108" s="16">
+      <c r="H108" s="28">
         <f>IF(OR(F108="",NOT(ISNUMBER(D108))),"",(F108-D108)*100)</f>
         <v/>
       </c>
@@ -7641,7 +7653,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("12Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("12Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U108" s="22">
+      <c r="U108" s="29">
         <f>IFERROR(IF(S108="","",AM108),"")</f>
         <v/>
       </c>
@@ -7649,67 +7661,67 @@
         <f>IFERROR(IF(OR(U108="",Q108=0),0,P108*U108),"")</f>
         <v/>
       </c>
-      <c r="X108" s="23">
+      <c r="X108" s="30">
         <f>IFERROR(IF(S108="","",U106*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y108" s="23">
+      <c r="Y108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(X108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="Z108" s="23">
+      <c r="Z108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(Y108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AA108" s="23">
+      <c r="AA108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(Z108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AB108" s="23">
+      <c r="AB108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AA108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AC108" s="23">
+      <c r="AC108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AB108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AD108" s="23">
+      <c r="AD108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AC108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AE108" s="23">
+      <c r="AE108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AD108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AF108" s="23">
+      <c r="AF108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AE108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AG108" s="23">
+      <c r="AG108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AF108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AH108" s="23">
+      <c r="AH108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AG108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AI108" s="23">
+      <c r="AI108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AH108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AJ108" s="23">
+      <c r="AJ108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AI108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AK108" s="23">
+      <c r="AK108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AJ108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AL108" s="23">
+      <c r="AL108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AK108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
-      <c r="AM108" s="23">
+      <c r="AM108" s="30">
         <f>IFERROR(IF(S108="","",(1-(S108/100)*(SUM($V$82:V106)+SUMPRODUCT($P$107:$P$107,$Q$107:$Q$107,U106*(AL108/U106)^$T$107:$T$107)))/(1+(S108/100)*P108)),"")</f>
         <v/>
       </c>
@@ -7719,16 +7731,16 @@
       <c r="B109" s="11" t="n"/>
       <c r="C109" s="12" t="n"/>
       <c r="D109" s="12" t="n"/>
-      <c r="E109" s="13" t="n"/>
+      <c r="E109" s="26" t="n"/>
       <c r="F109" s="14">
         <f>IF(OR($A109="",G109=""),"",-LN(G109)/INDEX($N$82:$N$146,IFERROR(MATCH($A109,$K$82:$K$146,0),MATCH(IF($A109="1Y","12M",IF($A109="12M","1Y",$A109)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G109" s="15">
+      <c r="G109" s="27">
         <f>IF($A109="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A109,$K$82:$K$146,0),MATCH(IF($A109="1Y","12M",IF($A109="12M","1Y",$A109)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H109" s="16">
+      <c r="H109" s="28">
         <f>IF(OR(F109="",NOT(ISNUMBER(D109))),"",(F109-D109)*100)</f>
         <v/>
       </c>
@@ -7779,7 +7791,7 @@
         <f>IFERROR(IF(OR(N109="",N111=""),"",(N109-N108)/(N111-N108)),"")</f>
         <v/>
       </c>
-      <c r="U109" s="22">
+      <c r="U109" s="29">
         <f>IFERROR(IF(OR(T109="",U111=""),"",U108*(U111/U108)^T109),"")</f>
         <v/>
       </c>
@@ -7793,16 +7805,16 @@
       <c r="B110" s="11" t="n"/>
       <c r="C110" s="12" t="n"/>
       <c r="D110" s="12" t="n"/>
-      <c r="E110" s="13" t="n"/>
+      <c r="E110" s="26" t="n"/>
       <c r="F110" s="14">
         <f>IF(OR($A110="",G110=""),"",-LN(G110)/INDEX($N$82:$N$146,IFERROR(MATCH($A110,$K$82:$K$146,0),MATCH(IF($A110="1Y","12M",IF($A110="12M","1Y",$A110)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G110" s="15">
+      <c r="G110" s="27">
         <f>IF($A110="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A110,$K$82:$K$146,0),MATCH(IF($A110="1Y","12M",IF($A110="12M","1Y",$A110)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H110" s="16">
+      <c r="H110" s="28">
         <f>IF(OR(F110="",NOT(ISNUMBER(D110))),"",(F110-D110)*100)</f>
         <v/>
       </c>
@@ -7853,7 +7865,7 @@
         <f>IFERROR(IF(OR(N110="",N111=""),"",(N110-N108)/(N111-N108)),"")</f>
         <v/>
       </c>
-      <c r="U110" s="22">
+      <c r="U110" s="29">
         <f>IFERROR(IF(OR(T110="",U111=""),"",U108*(U111/U108)^T110),"")</f>
         <v/>
       </c>
@@ -7867,16 +7879,16 @@
       <c r="B111" s="11" t="n"/>
       <c r="C111" s="12" t="n"/>
       <c r="D111" s="12" t="n"/>
-      <c r="E111" s="13" t="n"/>
+      <c r="E111" s="26" t="n"/>
       <c r="F111" s="14">
         <f>IF(OR($A111="",G111=""),"",-LN(G111)/INDEX($N$82:$N$146,IFERROR(MATCH($A111,$K$82:$K$146,0),MATCH(IF($A111="1Y","12M",IF($A111="12M","1Y",$A111)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G111" s="15">
+      <c r="G111" s="27">
         <f>IF($A111="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A111,$K$82:$K$146,0),MATCH(IF($A111="1Y","12M",IF($A111="12M","1Y",$A111)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H111" s="16">
+      <c r="H111" s="28">
         <f>IF(OR(F111="",NOT(ISNUMBER(D111))),"",(F111-D111)*100)</f>
         <v/>
       </c>
@@ -7923,7 +7935,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("15Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("15Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U111" s="22">
+      <c r="U111" s="29">
         <f>IFERROR(IF(S111="","",AM111),"")</f>
         <v/>
       </c>
@@ -7931,67 +7943,67 @@
         <f>IFERROR(IF(OR(U111="",Q111=0),0,P111*U111),"")</f>
         <v/>
       </c>
-      <c r="X111" s="23">
+      <c r="X111" s="30">
         <f>IFERROR(IF(S111="","",U108*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y111" s="23">
+      <c r="Y111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(X111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="Z111" s="23">
+      <c r="Z111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(Y111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AA111" s="23">
+      <c r="AA111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(Z111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AB111" s="23">
+      <c r="AB111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AA111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AC111" s="23">
+      <c r="AC111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AB111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AD111" s="23">
+      <c r="AD111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AC111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AE111" s="23">
+      <c r="AE111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AD111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AF111" s="23">
+      <c r="AF111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AE111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AG111" s="23">
+      <c r="AG111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AF111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AH111" s="23">
+      <c r="AH111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AG111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AI111" s="23">
+      <c r="AI111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AH111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AJ111" s="23">
+      <c r="AJ111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AI111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AK111" s="23">
+      <c r="AK111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AJ111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AL111" s="23">
+      <c r="AL111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AK111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
-      <c r="AM111" s="23">
+      <c r="AM111" s="30">
         <f>IFERROR(IF(S111="","",(1-(S111/100)*(SUM($V$82:V108)+SUMPRODUCT($P$109:$P$110,$Q$109:$Q$110,U108*(AL111/U108)^$T$109:$T$110)))/(1+(S111/100)*P111)),"")</f>
         <v/>
       </c>
@@ -8001,16 +8013,16 @@
       <c r="B112" s="11" t="n"/>
       <c r="C112" s="12" t="n"/>
       <c r="D112" s="12" t="n"/>
-      <c r="E112" s="13" t="n"/>
+      <c r="E112" s="26" t="n"/>
       <c r="F112" s="14">
         <f>IF(OR($A112="",G112=""),"",-LN(G112)/INDEX($N$82:$N$146,IFERROR(MATCH($A112,$K$82:$K$146,0),MATCH(IF($A112="1Y","12M",IF($A112="12M","1Y",$A112)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G112" s="15">
+      <c r="G112" s="27">
         <f>IF($A112="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A112,$K$82:$K$146,0),MATCH(IF($A112="1Y","12M",IF($A112="12M","1Y",$A112)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H112" s="16">
+      <c r="H112" s="28">
         <f>IF(OR(F112="",NOT(ISNUMBER(D112))),"",(F112-D112)*100)</f>
         <v/>
       </c>
@@ -8061,7 +8073,7 @@
         <f>IFERROR(IF(OR(N112="",N116=""),"",(N112-N111)/(N116-N111)),"")</f>
         <v/>
       </c>
-      <c r="U112" s="22">
+      <c r="U112" s="29">
         <f>IFERROR(IF(OR(T112="",U116=""),"",U111*(U116/U111)^T112),"")</f>
         <v/>
       </c>
@@ -8075,16 +8087,16 @@
       <c r="B113" s="11" t="n"/>
       <c r="C113" s="12" t="n"/>
       <c r="D113" s="12" t="n"/>
-      <c r="E113" s="13" t="n"/>
+      <c r="E113" s="26" t="n"/>
       <c r="F113" s="14">
         <f>IF(OR($A113="",G113=""),"",-LN(G113)/INDEX($N$82:$N$146,IFERROR(MATCH($A113,$K$82:$K$146,0),MATCH(IF($A113="1Y","12M",IF($A113="12M","1Y",$A113)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G113" s="15">
+      <c r="G113" s="27">
         <f>IF($A113="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A113,$K$82:$K$146,0),MATCH(IF($A113="1Y","12M",IF($A113="12M","1Y",$A113)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H113" s="16">
+      <c r="H113" s="28">
         <f>IF(OR(F113="",NOT(ISNUMBER(D113))),"",(F113-D113)*100)</f>
         <v/>
       </c>
@@ -8135,7 +8147,7 @@
         <f>IFERROR(IF(OR(N113="",N116=""),"",(N113-N111)/(N116-N111)),"")</f>
         <v/>
       </c>
-      <c r="U113" s="22">
+      <c r="U113" s="29">
         <f>IFERROR(IF(OR(T113="",U116=""),"",U111*(U116/U111)^T113),"")</f>
         <v/>
       </c>
@@ -8149,16 +8161,16 @@
       <c r="B114" s="11" t="n"/>
       <c r="C114" s="12" t="n"/>
       <c r="D114" s="12" t="n"/>
-      <c r="E114" s="13" t="n"/>
+      <c r="E114" s="26" t="n"/>
       <c r="F114" s="14">
         <f>IF(OR($A114="",G114=""),"",-LN(G114)/INDEX($N$82:$N$146,IFERROR(MATCH($A114,$K$82:$K$146,0),MATCH(IF($A114="1Y","12M",IF($A114="12M","1Y",$A114)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G114" s="15">
+      <c r="G114" s="27">
         <f>IF($A114="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A114,$K$82:$K$146,0),MATCH(IF($A114="1Y","12M",IF($A114="12M","1Y",$A114)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H114" s="16">
+      <c r="H114" s="28">
         <f>IF(OR(F114="",NOT(ISNUMBER(D114))),"",(F114-D114)*100)</f>
         <v/>
       </c>
@@ -8209,7 +8221,7 @@
         <f>IFERROR(IF(OR(N114="",N116=""),"",(N114-N111)/(N116-N111)),"")</f>
         <v/>
       </c>
-      <c r="U114" s="22">
+      <c r="U114" s="29">
         <f>IFERROR(IF(OR(T114="",U116=""),"",U111*(U116/U111)^T114),"")</f>
         <v/>
       </c>
@@ -8223,16 +8235,16 @@
       <c r="B115" s="11" t="n"/>
       <c r="C115" s="12" t="n"/>
       <c r="D115" s="12" t="n"/>
-      <c r="E115" s="13" t="n"/>
+      <c r="E115" s="26" t="n"/>
       <c r="F115" s="14">
         <f>IF(OR($A115="",G115=""),"",-LN(G115)/INDEX($N$82:$N$146,IFERROR(MATCH($A115,$K$82:$K$146,0),MATCH(IF($A115="1Y","12M",IF($A115="12M","1Y",$A115)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G115" s="15">
+      <c r="G115" s="27">
         <f>IF($A115="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A115,$K$82:$K$146,0),MATCH(IF($A115="1Y","12M",IF($A115="12M","1Y",$A115)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H115" s="16">
+      <c r="H115" s="28">
         <f>IF(OR(F115="",NOT(ISNUMBER(D115))),"",(F115-D115)*100)</f>
         <v/>
       </c>
@@ -8283,7 +8295,7 @@
         <f>IFERROR(IF(OR(N115="",N116=""),"",(N115-N111)/(N116-N111)),"")</f>
         <v/>
       </c>
-      <c r="U115" s="22">
+      <c r="U115" s="29">
         <f>IFERROR(IF(OR(T115="",U116=""),"",U111*(U116/U111)^T115),"")</f>
         <v/>
       </c>
@@ -8297,16 +8309,16 @@
       <c r="B116" s="11" t="n"/>
       <c r="C116" s="12" t="n"/>
       <c r="D116" s="12" t="n"/>
-      <c r="E116" s="13" t="n"/>
+      <c r="E116" s="26" t="n"/>
       <c r="F116" s="14">
         <f>IF(OR($A116="",G116=""),"",-LN(G116)/INDEX($N$82:$N$146,IFERROR(MATCH($A116,$K$82:$K$146,0),MATCH(IF($A116="1Y","12M",IF($A116="12M","1Y",$A116)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G116" s="15">
+      <c r="G116" s="27">
         <f>IF($A116="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A116,$K$82:$K$146,0),MATCH(IF($A116="1Y","12M",IF($A116="12M","1Y",$A116)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H116" s="16">
+      <c r="H116" s="28">
         <f>IF(OR(F116="",NOT(ISNUMBER(D116))),"",(F116-D116)*100)</f>
         <v/>
       </c>
@@ -8353,7 +8365,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("20Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("20Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U116" s="22">
+      <c r="U116" s="29">
         <f>IFERROR(IF(S116="","",AM116),"")</f>
         <v/>
       </c>
@@ -8361,67 +8373,67 @@
         <f>IFERROR(IF(OR(U116="",Q116=0),0,P116*U116),"")</f>
         <v/>
       </c>
-      <c r="X116" s="23">
+      <c r="X116" s="30">
         <f>IFERROR(IF(S116="","",U111*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y116" s="23">
+      <c r="Y116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(X116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="Z116" s="23">
+      <c r="Z116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(Y116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AA116" s="23">
+      <c r="AA116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(Z116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AB116" s="23">
+      <c r="AB116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AA116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AC116" s="23">
+      <c r="AC116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AB116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AD116" s="23">
+      <c r="AD116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AC116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AE116" s="23">
+      <c r="AE116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AD116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AF116" s="23">
+      <c r="AF116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AE116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AG116" s="23">
+      <c r="AG116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AF116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AH116" s="23">
+      <c r="AH116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AG116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AI116" s="23">
+      <c r="AI116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AH116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AJ116" s="23">
+      <c r="AJ116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AI116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AK116" s="23">
+      <c r="AK116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AJ116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AL116" s="23">
+      <c r="AL116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AK116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
-      <c r="AM116" s="23">
+      <c r="AM116" s="30">
         <f>IFERROR(IF(S116="","",(1-(S116/100)*(SUM($V$82:V111)+SUMPRODUCT($P$112:$P$115,$Q$112:$Q$115,U111*(AL116/U111)^$T$112:$T$115)))/(1+(S116/100)*P116)),"")</f>
         <v/>
       </c>
@@ -8431,16 +8443,16 @@
       <c r="B117" s="11" t="n"/>
       <c r="C117" s="12" t="n"/>
       <c r="D117" s="12" t="n"/>
-      <c r="E117" s="13" t="n"/>
+      <c r="E117" s="26" t="n"/>
       <c r="F117" s="14">
         <f>IF(OR($A117="",G117=""),"",-LN(G117)/INDEX($N$82:$N$146,IFERROR(MATCH($A117,$K$82:$K$146,0),MATCH(IF($A117="1Y","12M",IF($A117="12M","1Y",$A117)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G117" s="15">
+      <c r="G117" s="27">
         <f>IF($A117="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A117,$K$82:$K$146,0),MATCH(IF($A117="1Y","12M",IF($A117="12M","1Y",$A117)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H117" s="16">
+      <c r="H117" s="28">
         <f>IF(OR(F117="",NOT(ISNUMBER(D117))),"",(F117-D117)*100)</f>
         <v/>
       </c>
@@ -8491,7 +8503,7 @@
         <f>IFERROR(IF(OR(N117="",N121=""),"",(N117-N116)/(N121-N116)),"")</f>
         <v/>
       </c>
-      <c r="U117" s="22">
+      <c r="U117" s="29">
         <f>IFERROR(IF(OR(T117="",U121=""),"",U116*(U121/U116)^T117),"")</f>
         <v/>
       </c>
@@ -8505,16 +8517,16 @@
       <c r="B118" s="11" t="n"/>
       <c r="C118" s="12" t="n"/>
       <c r="D118" s="12" t="n"/>
-      <c r="E118" s="13" t="n"/>
+      <c r="E118" s="26" t="n"/>
       <c r="F118" s="14">
         <f>IF(OR($A118="",G118=""),"",-LN(G118)/INDEX($N$82:$N$146,IFERROR(MATCH($A118,$K$82:$K$146,0),MATCH(IF($A118="1Y","12M",IF($A118="12M","1Y",$A118)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G118" s="15">
+      <c r="G118" s="27">
         <f>IF($A118="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A118,$K$82:$K$146,0),MATCH(IF($A118="1Y","12M",IF($A118="12M","1Y",$A118)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H118" s="16">
+      <c r="H118" s="28">
         <f>IF(OR(F118="",NOT(ISNUMBER(D118))),"",(F118-D118)*100)</f>
         <v/>
       </c>
@@ -8565,7 +8577,7 @@
         <f>IFERROR(IF(OR(N118="",N121=""),"",(N118-N116)/(N121-N116)),"")</f>
         <v/>
       </c>
-      <c r="U118" s="22">
+      <c r="U118" s="29">
         <f>IFERROR(IF(OR(T118="",U121=""),"",U116*(U121/U116)^T118),"")</f>
         <v/>
       </c>
@@ -8579,16 +8591,16 @@
       <c r="B119" s="11" t="n"/>
       <c r="C119" s="12" t="n"/>
       <c r="D119" s="12" t="n"/>
-      <c r="E119" s="13" t="n"/>
+      <c r="E119" s="26" t="n"/>
       <c r="F119" s="14">
         <f>IF(OR($A119="",G119=""),"",-LN(G119)/INDEX($N$82:$N$146,IFERROR(MATCH($A119,$K$82:$K$146,0),MATCH(IF($A119="1Y","12M",IF($A119="12M","1Y",$A119)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G119" s="15">
+      <c r="G119" s="27">
         <f>IF($A119="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A119,$K$82:$K$146,0),MATCH(IF($A119="1Y","12M",IF($A119="12M","1Y",$A119)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H119" s="16">
+      <c r="H119" s="28">
         <f>IF(OR(F119="",NOT(ISNUMBER(D119))),"",(F119-D119)*100)</f>
         <v/>
       </c>
@@ -8639,7 +8651,7 @@
         <f>IFERROR(IF(OR(N119="",N121=""),"",(N119-N116)/(N121-N116)),"")</f>
         <v/>
       </c>
-      <c r="U119" s="22">
+      <c r="U119" s="29">
         <f>IFERROR(IF(OR(T119="",U121=""),"",U116*(U121/U116)^T119),"")</f>
         <v/>
       </c>
@@ -8653,16 +8665,16 @@
       <c r="B120" s="11" t="n"/>
       <c r="C120" s="12" t="n"/>
       <c r="D120" s="12" t="n"/>
-      <c r="E120" s="13" t="n"/>
+      <c r="E120" s="26" t="n"/>
       <c r="F120" s="14">
         <f>IF(OR($A120="",G120=""),"",-LN(G120)/INDEX($N$82:$N$146,IFERROR(MATCH($A120,$K$82:$K$146,0),MATCH(IF($A120="1Y","12M",IF($A120="12M","1Y",$A120)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G120" s="15">
+      <c r="G120" s="27">
         <f>IF($A120="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A120,$K$82:$K$146,0),MATCH(IF($A120="1Y","12M",IF($A120="12M","1Y",$A120)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H120" s="16">
+      <c r="H120" s="28">
         <f>IF(OR(F120="",NOT(ISNUMBER(D120))),"",(F120-D120)*100)</f>
         <v/>
       </c>
@@ -8713,7 +8725,7 @@
         <f>IFERROR(IF(OR(N120="",N121=""),"",(N120-N116)/(N121-N116)),"")</f>
         <v/>
       </c>
-      <c r="U120" s="22">
+      <c r="U120" s="29">
         <f>IFERROR(IF(OR(T120="",U121=""),"",U116*(U121/U116)^T120),"")</f>
         <v/>
       </c>
@@ -8727,16 +8739,16 @@
       <c r="B121" s="11" t="n"/>
       <c r="C121" s="12" t="n"/>
       <c r="D121" s="12" t="n"/>
-      <c r="E121" s="13" t="n"/>
+      <c r="E121" s="26" t="n"/>
       <c r="F121" s="14">
         <f>IF(OR($A121="",G121=""),"",-LN(G121)/INDEX($N$82:$N$146,IFERROR(MATCH($A121,$K$82:$K$146,0),MATCH(IF($A121="1Y","12M",IF($A121="12M","1Y",$A121)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G121" s="15">
+      <c r="G121" s="27">
         <f>IF($A121="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A121,$K$82:$K$146,0),MATCH(IF($A121="1Y","12M",IF($A121="12M","1Y",$A121)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H121" s="16">
+      <c r="H121" s="28">
         <f>IF(OR(F121="",NOT(ISNUMBER(D121))),"",(F121-D121)*100)</f>
         <v/>
       </c>
@@ -8783,7 +8795,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("25Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("25Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U121" s="22">
+      <c r="U121" s="29">
         <f>IFERROR(IF(S121="","",AM121),"")</f>
         <v/>
       </c>
@@ -8791,67 +8803,67 @@
         <f>IFERROR(IF(OR(U121="",Q121=0),0,P121*U121),"")</f>
         <v/>
       </c>
-      <c r="X121" s="23">
+      <c r="X121" s="30">
         <f>IFERROR(IF(S121="","",U116*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y121" s="23">
+      <c r="Y121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(X121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="Z121" s="23">
+      <c r="Z121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(Y121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AA121" s="23">
+      <c r="AA121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(Z121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AB121" s="23">
+      <c r="AB121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AA121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AC121" s="23">
+      <c r="AC121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AB121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AD121" s="23">
+      <c r="AD121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AC121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AE121" s="23">
+      <c r="AE121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AD121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AF121" s="23">
+      <c r="AF121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AE121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AG121" s="23">
+      <c r="AG121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AF121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AH121" s="23">
+      <c r="AH121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AG121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AI121" s="23">
+      <c r="AI121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AH121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AJ121" s="23">
+      <c r="AJ121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AI121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AK121" s="23">
+      <c r="AK121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AJ121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AL121" s="23">
+      <c r="AL121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AK121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
-      <c r="AM121" s="23">
+      <c r="AM121" s="30">
         <f>IFERROR(IF(S121="","",(1-(S121/100)*(SUM($V$82:V116)+SUMPRODUCT($P$117:$P$120,$Q$117:$Q$120,U116*(AL121/U116)^$T$117:$T$120)))/(1+(S121/100)*P121)),"")</f>
         <v/>
       </c>
@@ -8861,16 +8873,16 @@
       <c r="B122" s="11" t="n"/>
       <c r="C122" s="12" t="n"/>
       <c r="D122" s="12" t="n"/>
-      <c r="E122" s="13" t="n"/>
+      <c r="E122" s="26" t="n"/>
       <c r="F122" s="14">
         <f>IF(OR($A122="",G122=""),"",-LN(G122)/INDEX($N$82:$N$146,IFERROR(MATCH($A122,$K$82:$K$146,0),MATCH(IF($A122="1Y","12M",IF($A122="12M","1Y",$A122)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G122" s="15">
+      <c r="G122" s="27">
         <f>IF($A122="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A122,$K$82:$K$146,0),MATCH(IF($A122="1Y","12M",IF($A122="12M","1Y",$A122)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H122" s="16">
+      <c r="H122" s="28">
         <f>IF(OR(F122="",NOT(ISNUMBER(D122))),"",(F122-D122)*100)</f>
         <v/>
       </c>
@@ -8921,7 +8933,7 @@
         <f>IFERROR(IF(OR(N122="",N126=""),"",(N122-N121)/(N126-N121)),"")</f>
         <v/>
       </c>
-      <c r="U122" s="22">
+      <c r="U122" s="29">
         <f>IFERROR(IF(OR(T122="",U126=""),"",U121*(U126/U121)^T122),"")</f>
         <v/>
       </c>
@@ -8935,16 +8947,16 @@
       <c r="B123" s="11" t="n"/>
       <c r="C123" s="12" t="n"/>
       <c r="D123" s="12" t="n"/>
-      <c r="E123" s="13" t="n"/>
+      <c r="E123" s="26" t="n"/>
       <c r="F123" s="14">
         <f>IF(OR($A123="",G123=""),"",-LN(G123)/INDEX($N$82:$N$146,IFERROR(MATCH($A123,$K$82:$K$146,0),MATCH(IF($A123="1Y","12M",IF($A123="12M","1Y",$A123)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G123" s="15">
+      <c r="G123" s="27">
         <f>IF($A123="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A123,$K$82:$K$146,0),MATCH(IF($A123="1Y","12M",IF($A123="12M","1Y",$A123)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H123" s="16">
+      <c r="H123" s="28">
         <f>IF(OR(F123="",NOT(ISNUMBER(D123))),"",(F123-D123)*100)</f>
         <v/>
       </c>
@@ -8995,7 +9007,7 @@
         <f>IFERROR(IF(OR(N123="",N126=""),"",(N123-N121)/(N126-N121)),"")</f>
         <v/>
       </c>
-      <c r="U123" s="22">
+      <c r="U123" s="29">
         <f>IFERROR(IF(OR(T123="",U126=""),"",U121*(U126/U121)^T123),"")</f>
         <v/>
       </c>
@@ -9009,16 +9021,16 @@
       <c r="B124" s="11" t="n"/>
       <c r="C124" s="12" t="n"/>
       <c r="D124" s="12" t="n"/>
-      <c r="E124" s="13" t="n"/>
+      <c r="E124" s="26" t="n"/>
       <c r="F124" s="14">
         <f>IF(OR($A124="",G124=""),"",-LN(G124)/INDEX($N$82:$N$146,IFERROR(MATCH($A124,$K$82:$K$146,0),MATCH(IF($A124="1Y","12M",IF($A124="12M","1Y",$A124)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G124" s="15">
+      <c r="G124" s="27">
         <f>IF($A124="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A124,$K$82:$K$146,0),MATCH(IF($A124="1Y","12M",IF($A124="12M","1Y",$A124)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H124" s="16">
+      <c r="H124" s="28">
         <f>IF(OR(F124="",NOT(ISNUMBER(D124))),"",(F124-D124)*100)</f>
         <v/>
       </c>
@@ -9069,7 +9081,7 @@
         <f>IFERROR(IF(OR(N124="",N126=""),"",(N124-N121)/(N126-N121)),"")</f>
         <v/>
       </c>
-      <c r="U124" s="22">
+      <c r="U124" s="29">
         <f>IFERROR(IF(OR(T124="",U126=""),"",U121*(U126/U121)^T124),"")</f>
         <v/>
       </c>
@@ -9083,16 +9095,16 @@
       <c r="B125" s="11" t="n"/>
       <c r="C125" s="12" t="n"/>
       <c r="D125" s="12" t="n"/>
-      <c r="E125" s="13" t="n"/>
+      <c r="E125" s="26" t="n"/>
       <c r="F125" s="14">
         <f>IF(OR($A125="",G125=""),"",-LN(G125)/INDEX($N$82:$N$146,IFERROR(MATCH($A125,$K$82:$K$146,0),MATCH(IF($A125="1Y","12M",IF($A125="12M","1Y",$A125)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G125" s="15">
+      <c r="G125" s="27">
         <f>IF($A125="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A125,$K$82:$K$146,0),MATCH(IF($A125="1Y","12M",IF($A125="12M","1Y",$A125)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H125" s="16">
+      <c r="H125" s="28">
         <f>IF(OR(F125="",NOT(ISNUMBER(D125))),"",(F125-D125)*100)</f>
         <v/>
       </c>
@@ -9143,7 +9155,7 @@
         <f>IFERROR(IF(OR(N125="",N126=""),"",(N125-N121)/(N126-N121)),"")</f>
         <v/>
       </c>
-      <c r="U125" s="22">
+      <c r="U125" s="29">
         <f>IFERROR(IF(OR(T125="",U126=""),"",U121*(U126/U121)^T125),"")</f>
         <v/>
       </c>
@@ -9157,16 +9169,16 @@
       <c r="B126" s="11" t="n"/>
       <c r="C126" s="12" t="n"/>
       <c r="D126" s="12" t="n"/>
-      <c r="E126" s="13" t="n"/>
+      <c r="E126" s="26" t="n"/>
       <c r="F126" s="14">
         <f>IF(OR($A126="",G126=""),"",-LN(G126)/INDEX($N$82:$N$146,IFERROR(MATCH($A126,$K$82:$K$146,0),MATCH(IF($A126="1Y","12M",IF($A126="12M","1Y",$A126)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G126" s="15">
+      <c r="G126" s="27">
         <f>IF($A126="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A126,$K$82:$K$146,0),MATCH(IF($A126="1Y","12M",IF($A126="12M","1Y",$A126)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H126" s="16">
+      <c r="H126" s="28">
         <f>IF(OR(F126="",NOT(ISNUMBER(D126))),"",(F126-D126)*100)</f>
         <v/>
       </c>
@@ -9213,7 +9225,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("30Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("30Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U126" s="22">
+      <c r="U126" s="29">
         <f>IFERROR(IF(S126="","",AM126),"")</f>
         <v/>
       </c>
@@ -9221,67 +9233,67 @@
         <f>IFERROR(IF(OR(U126="",Q126=0),0,P126*U126),"")</f>
         <v/>
       </c>
-      <c r="X126" s="23">
+      <c r="X126" s="30">
         <f>IFERROR(IF(S126="","",U121*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y126" s="23">
+      <c r="Y126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(X126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="Z126" s="23">
+      <c r="Z126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(Y126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AA126" s="23">
+      <c r="AA126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(Z126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AB126" s="23">
+      <c r="AB126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AA126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AC126" s="23">
+      <c r="AC126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AB126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AD126" s="23">
+      <c r="AD126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AC126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AE126" s="23">
+      <c r="AE126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AD126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AF126" s="23">
+      <c r="AF126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AE126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AG126" s="23">
+      <c r="AG126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AF126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AH126" s="23">
+      <c r="AH126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AG126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AI126" s="23">
+      <c r="AI126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AH126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AJ126" s="23">
+      <c r="AJ126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AI126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AK126" s="23">
+      <c r="AK126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AJ126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AL126" s="23">
+      <c r="AL126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AK126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
-      <c r="AM126" s="23">
+      <c r="AM126" s="30">
         <f>IFERROR(IF(S126="","",(1-(S126/100)*(SUM($V$82:V121)+SUMPRODUCT($P$122:$P$125,$Q$122:$Q$125,U121*(AL126/U121)^$T$122:$T$125)))/(1+(S126/100)*P126)),"")</f>
         <v/>
       </c>
@@ -9291,16 +9303,16 @@
       <c r="B127" s="11" t="n"/>
       <c r="C127" s="12" t="n"/>
       <c r="D127" s="12" t="n"/>
-      <c r="E127" s="13" t="n"/>
+      <c r="E127" s="26" t="n"/>
       <c r="F127" s="14">
         <f>IF(OR($A127="",G127=""),"",-LN(G127)/INDEX($N$82:$N$146,IFERROR(MATCH($A127,$K$82:$K$146,0),MATCH(IF($A127="1Y","12M",IF($A127="12M","1Y",$A127)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G127" s="15">
+      <c r="G127" s="27">
         <f>IF($A127="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A127,$K$82:$K$146,0),MATCH(IF($A127="1Y","12M",IF($A127="12M","1Y",$A127)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H127" s="16">
+      <c r="H127" s="28">
         <f>IF(OR(F127="",NOT(ISNUMBER(D127))),"",(F127-D127)*100)</f>
         <v/>
       </c>
@@ -9351,7 +9363,7 @@
         <f>IFERROR(IF(OR(N127="",N136=""),"",(N127-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U127" s="22">
+      <c r="U127" s="29">
         <f>IFERROR(IF(OR(T127="",U136=""),"",U126*(U136/U126)^T127),"")</f>
         <v/>
       </c>
@@ -9365,16 +9377,16 @@
       <c r="B128" s="11" t="n"/>
       <c r="C128" s="12" t="n"/>
       <c r="D128" s="12" t="n"/>
-      <c r="E128" s="13" t="n"/>
+      <c r="E128" s="26" t="n"/>
       <c r="F128" s="14">
         <f>IF(OR($A128="",G128=""),"",-LN(G128)/INDEX($N$82:$N$146,IFERROR(MATCH($A128,$K$82:$K$146,0),MATCH(IF($A128="1Y","12M",IF($A128="12M","1Y",$A128)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G128" s="15">
+      <c r="G128" s="27">
         <f>IF($A128="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A128,$K$82:$K$146,0),MATCH(IF($A128="1Y","12M",IF($A128="12M","1Y",$A128)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H128" s="16">
+      <c r="H128" s="28">
         <f>IF(OR(F128="",NOT(ISNUMBER(D128))),"",(F128-D128)*100)</f>
         <v/>
       </c>
@@ -9425,7 +9437,7 @@
         <f>IFERROR(IF(OR(N128="",N136=""),"",(N128-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U128" s="22">
+      <c r="U128" s="29">
         <f>IFERROR(IF(OR(T128="",U136=""),"",U126*(U136/U126)^T128),"")</f>
         <v/>
       </c>
@@ -9439,16 +9451,16 @@
       <c r="B129" s="11" t="n"/>
       <c r="C129" s="12" t="n"/>
       <c r="D129" s="12" t="n"/>
-      <c r="E129" s="13" t="n"/>
+      <c r="E129" s="26" t="n"/>
       <c r="F129" s="14">
         <f>IF(OR($A129="",G129=""),"",-LN(G129)/INDEX($N$82:$N$146,IFERROR(MATCH($A129,$K$82:$K$146,0),MATCH(IF($A129="1Y","12M",IF($A129="12M","1Y",$A129)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G129" s="15">
+      <c r="G129" s="27">
         <f>IF($A129="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A129,$K$82:$K$146,0),MATCH(IF($A129="1Y","12M",IF($A129="12M","1Y",$A129)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H129" s="16">
+      <c r="H129" s="28">
         <f>IF(OR(F129="",NOT(ISNUMBER(D129))),"",(F129-D129)*100)</f>
         <v/>
       </c>
@@ -9499,7 +9511,7 @@
         <f>IFERROR(IF(OR(N129="",N136=""),"",(N129-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U129" s="22">
+      <c r="U129" s="29">
         <f>IFERROR(IF(OR(T129="",U136=""),"",U126*(U136/U126)^T129),"")</f>
         <v/>
       </c>
@@ -9513,16 +9525,16 @@
       <c r="B130" s="11" t="n"/>
       <c r="C130" s="12" t="n"/>
       <c r="D130" s="12" t="n"/>
-      <c r="E130" s="13" t="n"/>
+      <c r="E130" s="26" t="n"/>
       <c r="F130" s="14">
         <f>IF(OR($A130="",G130=""),"",-LN(G130)/INDEX($N$82:$N$146,IFERROR(MATCH($A130,$K$82:$K$146,0),MATCH(IF($A130="1Y","12M",IF($A130="12M","1Y",$A130)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G130" s="15">
+      <c r="G130" s="27">
         <f>IF($A130="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A130,$K$82:$K$146,0),MATCH(IF($A130="1Y","12M",IF($A130="12M","1Y",$A130)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H130" s="16">
+      <c r="H130" s="28">
         <f>IF(OR(F130="",NOT(ISNUMBER(D130))),"",(F130-D130)*100)</f>
         <v/>
       </c>
@@ -9573,7 +9585,7 @@
         <f>IFERROR(IF(OR(N130="",N136=""),"",(N130-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U130" s="22">
+      <c r="U130" s="29">
         <f>IFERROR(IF(OR(T130="",U136=""),"",U126*(U136/U126)^T130),"")</f>
         <v/>
       </c>
@@ -9587,16 +9599,16 @@
       <c r="B131" s="11" t="n"/>
       <c r="C131" s="12" t="n"/>
       <c r="D131" s="12" t="n"/>
-      <c r="E131" s="13" t="n"/>
+      <c r="E131" s="26" t="n"/>
       <c r="F131" s="14">
         <f>IF(OR($A131="",G131=""),"",-LN(G131)/INDEX($N$82:$N$146,IFERROR(MATCH($A131,$K$82:$K$146,0),MATCH(IF($A131="1Y","12M",IF($A131="12M","1Y",$A131)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G131" s="15">
+      <c r="G131" s="27">
         <f>IF($A131="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A131,$K$82:$K$146,0),MATCH(IF($A131="1Y","12M",IF($A131="12M","1Y",$A131)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H131" s="16">
+      <c r="H131" s="28">
         <f>IF(OR(F131="",NOT(ISNUMBER(D131))),"",(F131-D131)*100)</f>
         <v/>
       </c>
@@ -9647,7 +9659,7 @@
         <f>IFERROR(IF(OR(N131="",N136=""),"",(N131-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U131" s="22">
+      <c r="U131" s="29">
         <f>IFERROR(IF(OR(T131="",U136=""),"",U126*(U136/U126)^T131),"")</f>
         <v/>
       </c>
@@ -9661,16 +9673,16 @@
       <c r="B132" s="11" t="n"/>
       <c r="C132" s="12" t="n"/>
       <c r="D132" s="12" t="n"/>
-      <c r="E132" s="13" t="n"/>
+      <c r="E132" s="26" t="n"/>
       <c r="F132" s="14">
         <f>IF(OR($A132="",G132=""),"",-LN(G132)/INDEX($N$82:$N$146,IFERROR(MATCH($A132,$K$82:$K$146,0),MATCH(IF($A132="1Y","12M",IF($A132="12M","1Y",$A132)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G132" s="15">
+      <c r="G132" s="27">
         <f>IF($A132="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A132,$K$82:$K$146,0),MATCH(IF($A132="1Y","12M",IF($A132="12M","1Y",$A132)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H132" s="16">
+      <c r="H132" s="28">
         <f>IF(OR(F132="",NOT(ISNUMBER(D132))),"",(F132-D132)*100)</f>
         <v/>
       </c>
@@ -9721,7 +9733,7 @@
         <f>IFERROR(IF(OR(N132="",N136=""),"",(N132-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U132" s="22">
+      <c r="U132" s="29">
         <f>IFERROR(IF(OR(T132="",U136=""),"",U126*(U136/U126)^T132),"")</f>
         <v/>
       </c>
@@ -9735,16 +9747,16 @@
       <c r="B133" s="11" t="n"/>
       <c r="C133" s="12" t="n"/>
       <c r="D133" s="12" t="n"/>
-      <c r="E133" s="13" t="n"/>
+      <c r="E133" s="26" t="n"/>
       <c r="F133" s="14">
         <f>IF(OR($A133="",G133=""),"",-LN(G133)/INDEX($N$82:$N$146,IFERROR(MATCH($A133,$K$82:$K$146,0),MATCH(IF($A133="1Y","12M",IF($A133="12M","1Y",$A133)),$K$82:$K$146,0)))*100)</f>
         <v/>
       </c>
-      <c r="G133" s="15">
+      <c r="G133" s="27">
         <f>IF($A133="","",IFERROR(INDEX($U$82:$U$146,IFERROR(MATCH($A133,$K$82:$K$146,0),MATCH(IF($A133="1Y","12M",IF($A133="12M","1Y",$A133)),$K$82:$K$146,0))),""))</f>
         <v/>
       </c>
-      <c r="H133" s="16">
+      <c r="H133" s="28">
         <f>IF(OR(F133="",NOT(ISNUMBER(D133))),"",(F133-D133)*100)</f>
         <v/>
       </c>
@@ -9795,7 +9807,7 @@
         <f>IFERROR(IF(OR(N133="",N136=""),"",(N133-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U133" s="22">
+      <c r="U133" s="29">
         <f>IFERROR(IF(OR(T133="",U136=""),"",U126*(U136/U126)^T133),"")</f>
         <v/>
       </c>
@@ -9844,7 +9856,7 @@
         <f>IFERROR(IF(OR(N134="",N136=""),"",(N134-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U134" s="22">
+      <c r="U134" s="29">
         <f>IFERROR(IF(OR(T134="",U136=""),"",U126*(U136/U126)^T134),"")</f>
         <v/>
       </c>
@@ -9877,7 +9889,7 @@
           <t>max |d zero| bp</t>
         </is>
       </c>
-      <c r="H135" s="24">
+      <c r="H135" s="31">
         <f>IF(COUNT($H$82:$H$133)=0,"",MAX(MAX($H$82:$H$133),-MIN($H$82:$H$133)))</f>
         <v/>
       </c>
@@ -9924,7 +9936,7 @@
         <f>IFERROR(IF(OR(N135="",N136=""),"",(N135-N126)/(N136-N126)),"")</f>
         <v/>
       </c>
-      <c r="U135" s="22">
+      <c r="U135" s="29">
         <f>IFERROR(IF(OR(T135="",U136=""),"",U126*(U136/U126)^T135),"")</f>
         <v/>
       </c>
@@ -9978,7 +9990,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("40Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("40Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U136" s="22">
+      <c r="U136" s="29">
         <f>IFERROR(IF(S136="","",AM136),"")</f>
         <v/>
       </c>
@@ -9986,67 +9998,67 @@
         <f>IFERROR(IF(OR(U136="",Q136=0),0,P136*U136),"")</f>
         <v/>
       </c>
-      <c r="X136" s="23">
+      <c r="X136" s="30">
         <f>IFERROR(IF(S136="","",U126*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y136" s="23">
+      <c r="Y136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(X136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="Z136" s="23">
+      <c r="Z136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(Y136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AA136" s="23">
+      <c r="AA136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(Z136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AB136" s="23">
+      <c r="AB136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AA136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AC136" s="23">
+      <c r="AC136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AB136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AD136" s="23">
+      <c r="AD136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AC136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AE136" s="23">
+      <c r="AE136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AD136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AF136" s="23">
+      <c r="AF136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AE136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AG136" s="23">
+      <c r="AG136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AF136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AH136" s="23">
+      <c r="AH136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AG136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AI136" s="23">
+      <c r="AI136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AH136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AJ136" s="23">
+      <c r="AJ136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AI136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AK136" s="23">
+      <c r="AK136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AJ136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AL136" s="23">
+      <c r="AL136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AK136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
-      <c r="AM136" s="23">
+      <c r="AM136" s="30">
         <f>IFERROR(IF(S136="","",(1-(S136/100)*(SUM($V$82:V126)+SUMPRODUCT($P$127:$P$135,$Q$127:$Q$135,U126*(AL136/U126)^$T$127:$T$135)))/(1+(S136/100)*P136)),"")</f>
         <v/>
       </c>
@@ -10096,7 +10108,7 @@
         <f>IFERROR(IF(OR(N137="",N146=""),"",(N137-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U137" s="22">
+      <c r="U137" s="29">
         <f>IFERROR(IF(OR(T137="",U146=""),"",U136*(U146/U136)^T137),"")</f>
         <v/>
       </c>
@@ -10145,7 +10157,7 @@
         <f>IFERROR(IF(OR(N138="",N146=""),"",(N138-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U138" s="22">
+      <c r="U138" s="29">
         <f>IFERROR(IF(OR(T138="",U146=""),"",U136*(U146/U136)^T138),"")</f>
         <v/>
       </c>
@@ -10194,7 +10206,7 @@
         <f>IFERROR(IF(OR(N139="",N146=""),"",(N139-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U139" s="22">
+      <c r="U139" s="29">
         <f>IFERROR(IF(OR(T139="",U146=""),"",U136*(U146/U136)^T139),"")</f>
         <v/>
       </c>
@@ -10243,7 +10255,7 @@
         <f>IFERROR(IF(OR(N140="",N146=""),"",(N140-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U140" s="22">
+      <c r="U140" s="29">
         <f>IFERROR(IF(OR(T140="",U146=""),"",U136*(U146/U136)^T140),"")</f>
         <v/>
       </c>
@@ -10292,7 +10304,7 @@
         <f>IFERROR(IF(OR(N141="",N146=""),"",(N141-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U141" s="22">
+      <c r="U141" s="29">
         <f>IFERROR(IF(OR(T141="",U146=""),"",U136*(U146/U136)^T141),"")</f>
         <v/>
       </c>
@@ -10341,7 +10353,7 @@
         <f>IFERROR(IF(OR(N142="",N146=""),"",(N142-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U142" s="22">
+      <c r="U142" s="29">
         <f>IFERROR(IF(OR(T142="",U146=""),"",U136*(U146/U136)^T142),"")</f>
         <v/>
       </c>
@@ -10390,7 +10402,7 @@
         <f>IFERROR(IF(OR(N143="",N146=""),"",(N143-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U143" s="22">
+      <c r="U143" s="29">
         <f>IFERROR(IF(OR(T143="",U146=""),"",U136*(U146/U136)^T143),"")</f>
         <v/>
       </c>
@@ -10439,7 +10451,7 @@
         <f>IFERROR(IF(OR(N144="",N146=""),"",(N144-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U144" s="22">
+      <c r="U144" s="29">
         <f>IFERROR(IF(OR(T144="",U146=""),"",U136*(U146/U136)^T144),"")</f>
         <v/>
       </c>
@@ -10488,7 +10500,7 @@
         <f>IFERROR(IF(OR(N145="",N146=""),"",(N145-N136)/(N146-N136)),"")</f>
         <v/>
       </c>
-      <c r="U145" s="22">
+      <c r="U145" s="29">
         <f>IFERROR(IF(OR(T145="",U146=""),"",U136*(U146/U136)^T145),"")</f>
         <v/>
       </c>
@@ -10533,7 +10545,7 @@
         <f>IFERROR(IFERROR(INDEX($C$82:$C$133,MATCH("50Y",$A$82:$A$133,0)),INDEX($C$82:$C$133,MATCH("50Y",$A$82:$A$133,0))),"")</f>
         <v/>
       </c>
-      <c r="U146" s="22">
+      <c r="U146" s="29">
         <f>IFERROR(IF(S146="","",AM146),"")</f>
         <v/>
       </c>
@@ -10541,82 +10553,84 @@
         <f>IFERROR(IF(OR(U146="",Q146=0),0,P146*U146),"")</f>
         <v/>
       </c>
-      <c r="X146" s="23">
+      <c r="X146" s="30">
         <f>IFERROR(IF(S146="","",U136*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y146" s="23">
+      <c r="Y146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(X146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="Z146" s="23">
+      <c r="Z146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(Y146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AA146" s="23">
+      <c r="AA146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(Z146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AB146" s="23">
+      <c r="AB146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AA146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AC146" s="23">
+      <c r="AC146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AB146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AD146" s="23">
+      <c r="AD146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AC146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AE146" s="23">
+      <c r="AE146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AD146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AF146" s="23">
+      <c r="AF146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AE146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AG146" s="23">
+      <c r="AG146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AF146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AH146" s="23">
+      <c r="AH146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AG146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AI146" s="23">
+      <c r="AI146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AH146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AJ146" s="23">
+      <c r="AJ146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AI146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AK146" s="23">
+      <c r="AK146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AJ146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AL146" s="23">
+      <c r="AL146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AK146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
-      <c r="AM146" s="23">
+      <c r="AM146" s="30">
         <f>IFERROR(IF(S146="","",(1-(S146/100)*(SUM($V$82:V136)+SUMPRODUCT($P$137:$P$145,$Q$137:$Q$145,U136*(AL146/U136)^$T$137:$T$145)))/(1+(S146/100)*P146)),"")</f>
         <v/>
       </c>
     </row>
+    <row r="147"/>
+    <row r="148"/>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>CURVE TEST CASE 3 — paste and read</t>
+          <t>CURVE TEST CASE 3: paste and read</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Paste YELLOW A:E straight off the capture — tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed here; this sheet points at nothing outside itself.</t>
+          <t>Paste A:E off the capture: tenor, date, swap mid, BBG zero, BBG discount. Set the curve date. Green is computed on this sheet.</t>
         </is>
       </c>
     </row>
@@ -10643,6 +10657,8 @@
         <v/>
       </c>
     </row>
+    <row r="153"/>
+    <row r="154"/>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
@@ -10765,16 +10781,16 @@
       <c r="B156" s="11" t="n"/>
       <c r="C156" s="12" t="n"/>
       <c r="D156" s="12" t="n"/>
-      <c r="E156" s="13" t="n"/>
+      <c r="E156" s="26" t="n"/>
       <c r="F156" s="14">
         <f>IF(OR($A156="",G156=""),"",-LN(G156)/INDEX($N$156:$N$220,IFERROR(MATCH($A156,$K$156:$K$220,0),MATCH(IF($A156="1Y","12M",IF($A156="12M","1Y",$A156)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G156" s="15">
+      <c r="G156" s="27">
         <f>IF($A156="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A156,$K$156:$K$220,0),MATCH(IF($A156="1Y","12M",IF($A156="12M","1Y",$A156)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H156" s="16">
+      <c r="H156" s="28">
         <f>IF(OR(F156="",NOT(ISNUMBER(D156))),"",(F156-D156)*100)</f>
         <v/>
       </c>
@@ -10821,7 +10837,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("1W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U156" s="22">
+      <c r="U156" s="29">
         <f>IFERROR(IF(S156="","",1/(1+(S156/100)*O156)),"")</f>
         <v/>
       </c>
@@ -10835,16 +10851,16 @@
       <c r="B157" s="11" t="n"/>
       <c r="C157" s="12" t="n"/>
       <c r="D157" s="12" t="n"/>
-      <c r="E157" s="13" t="n"/>
+      <c r="E157" s="26" t="n"/>
       <c r="F157" s="14">
         <f>IF(OR($A157="",G157=""),"",-LN(G157)/INDEX($N$156:$N$220,IFERROR(MATCH($A157,$K$156:$K$220,0),MATCH(IF($A157="1Y","12M",IF($A157="12M","1Y",$A157)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G157" s="15">
+      <c r="G157" s="27">
         <f>IF($A157="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A157,$K$156:$K$220,0),MATCH(IF($A157="1Y","12M",IF($A157="12M","1Y",$A157)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H157" s="16">
+      <c r="H157" s="28">
         <f>IF(OR(F157="",NOT(ISNUMBER(D157))),"",(F157-D157)*100)</f>
         <v/>
       </c>
@@ -10891,7 +10907,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U157" s="22">
+      <c r="U157" s="29">
         <f>IFERROR(IF(S157="","",1/(1+(S157/100)*O157)),"")</f>
         <v/>
       </c>
@@ -10905,16 +10921,16 @@
       <c r="B158" s="11" t="n"/>
       <c r="C158" s="12" t="n"/>
       <c r="D158" s="12" t="n"/>
-      <c r="E158" s="13" t="n"/>
+      <c r="E158" s="26" t="n"/>
       <c r="F158" s="14">
         <f>IF(OR($A158="",G158=""),"",-LN(G158)/INDEX($N$156:$N$220,IFERROR(MATCH($A158,$K$156:$K$220,0),MATCH(IF($A158="1Y","12M",IF($A158="12M","1Y",$A158)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G158" s="15">
+      <c r="G158" s="27">
         <f>IF($A158="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A158,$K$156:$K$220,0),MATCH(IF($A158="1Y","12M",IF($A158="12M","1Y",$A158)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H158" s="16">
+      <c r="H158" s="28">
         <f>IF(OR(F158="",NOT(ISNUMBER(D158))),"",(F158-D158)*100)</f>
         <v/>
       </c>
@@ -10961,7 +10977,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3W",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3W",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U158" s="22">
+      <c r="U158" s="29">
         <f>IFERROR(IF(S158="","",1/(1+(S158/100)*O158)),"")</f>
         <v/>
       </c>
@@ -10975,16 +10991,16 @@
       <c r="B159" s="11" t="n"/>
       <c r="C159" s="12" t="n"/>
       <c r="D159" s="12" t="n"/>
-      <c r="E159" s="13" t="n"/>
+      <c r="E159" s="26" t="n"/>
       <c r="F159" s="14">
         <f>IF(OR($A159="",G159=""),"",-LN(G159)/INDEX($N$156:$N$220,IFERROR(MATCH($A159,$K$156:$K$220,0),MATCH(IF($A159="1Y","12M",IF($A159="12M","1Y",$A159)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G159" s="15">
+      <c r="G159" s="27">
         <f>IF($A159="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A159,$K$156:$K$220,0),MATCH(IF($A159="1Y","12M",IF($A159="12M","1Y",$A159)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H159" s="16">
+      <c r="H159" s="28">
         <f>IF(OR(F159="",NOT(ISNUMBER(D159))),"",(F159-D159)*100)</f>
         <v/>
       </c>
@@ -11031,7 +11047,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("1M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U159" s="22">
+      <c r="U159" s="29">
         <f>IFERROR(IF(S159="","",1/(1+(S159/100)*O159)),"")</f>
         <v/>
       </c>
@@ -11045,16 +11061,16 @@
       <c r="B160" s="11" t="n"/>
       <c r="C160" s="12" t="n"/>
       <c r="D160" s="12" t="n"/>
-      <c r="E160" s="13" t="n"/>
+      <c r="E160" s="26" t="n"/>
       <c r="F160" s="14">
         <f>IF(OR($A160="",G160=""),"",-LN(G160)/INDEX($N$156:$N$220,IFERROR(MATCH($A160,$K$156:$K$220,0),MATCH(IF($A160="1Y","12M",IF($A160="12M","1Y",$A160)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G160" s="15">
+      <c r="G160" s="27">
         <f>IF($A160="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A160,$K$156:$K$220,0),MATCH(IF($A160="1Y","12M",IF($A160="12M","1Y",$A160)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H160" s="16">
+      <c r="H160" s="28">
         <f>IF(OR(F160="",NOT(ISNUMBER(D160))),"",(F160-D160)*100)</f>
         <v/>
       </c>
@@ -11101,7 +11117,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U160" s="22">
+      <c r="U160" s="29">
         <f>IFERROR(IF(S160="","",1/(1+(S160/100)*O160)),"")</f>
         <v/>
       </c>
@@ -11115,16 +11131,16 @@
       <c r="B161" s="11" t="n"/>
       <c r="C161" s="12" t="n"/>
       <c r="D161" s="12" t="n"/>
-      <c r="E161" s="13" t="n"/>
+      <c r="E161" s="26" t="n"/>
       <c r="F161" s="14">
         <f>IF(OR($A161="",G161=""),"",-LN(G161)/INDEX($N$156:$N$220,IFERROR(MATCH($A161,$K$156:$K$220,0),MATCH(IF($A161="1Y","12M",IF($A161="12M","1Y",$A161)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G161" s="15">
+      <c r="G161" s="27">
         <f>IF($A161="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A161,$K$156:$K$220,0),MATCH(IF($A161="1Y","12M",IF($A161="12M","1Y",$A161)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H161" s="16">
+      <c r="H161" s="28">
         <f>IF(OR(F161="",NOT(ISNUMBER(D161))),"",(F161-D161)*100)</f>
         <v/>
       </c>
@@ -11171,7 +11187,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U161" s="22">
+      <c r="U161" s="29">
         <f>IFERROR(IF(S161="","",1/(1+(S161/100)*O161)),"")</f>
         <v/>
       </c>
@@ -11185,16 +11201,16 @@
       <c r="B162" s="11" t="n"/>
       <c r="C162" s="12" t="n"/>
       <c r="D162" s="12" t="n"/>
-      <c r="E162" s="13" t="n"/>
+      <c r="E162" s="26" t="n"/>
       <c r="F162" s="14">
         <f>IF(OR($A162="",G162=""),"",-LN(G162)/INDEX($N$156:$N$220,IFERROR(MATCH($A162,$K$156:$K$220,0),MATCH(IF($A162="1Y","12M",IF($A162="12M","1Y",$A162)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G162" s="15">
+      <c r="G162" s="27">
         <f>IF($A162="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A162,$K$156:$K$220,0),MATCH(IF($A162="1Y","12M",IF($A162="12M","1Y",$A162)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H162" s="16">
+      <c r="H162" s="28">
         <f>IF(OR(F162="",NOT(ISNUMBER(D162))),"",(F162-D162)*100)</f>
         <v/>
       </c>
@@ -11241,7 +11257,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("4M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("4M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U162" s="22">
+      <c r="U162" s="29">
         <f>IFERROR(IF(S162="","",1/(1+(S162/100)*O162)),"")</f>
         <v/>
       </c>
@@ -11255,16 +11271,16 @@
       <c r="B163" s="11" t="n"/>
       <c r="C163" s="12" t="n"/>
       <c r="D163" s="12" t="n"/>
-      <c r="E163" s="13" t="n"/>
+      <c r="E163" s="26" t="n"/>
       <c r="F163" s="14">
         <f>IF(OR($A163="",G163=""),"",-LN(G163)/INDEX($N$156:$N$220,IFERROR(MATCH($A163,$K$156:$K$220,0),MATCH(IF($A163="1Y","12M",IF($A163="12M","1Y",$A163)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G163" s="15">
+      <c r="G163" s="27">
         <f>IF($A163="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A163,$K$156:$K$220,0),MATCH(IF($A163="1Y","12M",IF($A163="12M","1Y",$A163)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H163" s="16">
+      <c r="H163" s="28">
         <f>IF(OR(F163="",NOT(ISNUMBER(D163))),"",(F163-D163)*100)</f>
         <v/>
       </c>
@@ -11311,7 +11327,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("5M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("5M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U163" s="22">
+      <c r="U163" s="29">
         <f>IFERROR(IF(S163="","",1/(1+(S163/100)*O163)),"")</f>
         <v/>
       </c>
@@ -11325,16 +11341,16 @@
       <c r="B164" s="11" t="n"/>
       <c r="C164" s="12" t="n"/>
       <c r="D164" s="12" t="n"/>
-      <c r="E164" s="13" t="n"/>
+      <c r="E164" s="26" t="n"/>
       <c r="F164" s="14">
         <f>IF(OR($A164="",G164=""),"",-LN(G164)/INDEX($N$156:$N$220,IFERROR(MATCH($A164,$K$156:$K$220,0),MATCH(IF($A164="1Y","12M",IF($A164="12M","1Y",$A164)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G164" s="15">
+      <c r="G164" s="27">
         <f>IF($A164="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A164,$K$156:$K$220,0),MATCH(IF($A164="1Y","12M",IF($A164="12M","1Y",$A164)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H164" s="16">
+      <c r="H164" s="28">
         <f>IF(OR(F164="",NOT(ISNUMBER(D164))),"",(F164-D164)*100)</f>
         <v/>
       </c>
@@ -11381,7 +11397,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("6M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("6M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U164" s="22">
+      <c r="U164" s="29">
         <f>IFERROR(IF(S164="","",1/(1+(S164/100)*O164)),"")</f>
         <v/>
       </c>
@@ -11395,16 +11411,16 @@
       <c r="B165" s="11" t="n"/>
       <c r="C165" s="12" t="n"/>
       <c r="D165" s="12" t="n"/>
-      <c r="E165" s="13" t="n"/>
+      <c r="E165" s="26" t="n"/>
       <c r="F165" s="14">
         <f>IF(OR($A165="",G165=""),"",-LN(G165)/INDEX($N$156:$N$220,IFERROR(MATCH($A165,$K$156:$K$220,0),MATCH(IF($A165="1Y","12M",IF($A165="12M","1Y",$A165)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G165" s="15">
+      <c r="G165" s="27">
         <f>IF($A165="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A165,$K$156:$K$220,0),MATCH(IF($A165="1Y","12M",IF($A165="12M","1Y",$A165)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H165" s="16">
+      <c r="H165" s="28">
         <f>IF(OR(F165="",NOT(ISNUMBER(D165))),"",(F165-D165)*100)</f>
         <v/>
       </c>
@@ -11451,7 +11467,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("7M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("7M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U165" s="22">
+      <c r="U165" s="29">
         <f>IFERROR(IF(S165="","",1/(1+(S165/100)*O165)),"")</f>
         <v/>
       </c>
@@ -11465,16 +11481,16 @@
       <c r="B166" s="11" t="n"/>
       <c r="C166" s="12" t="n"/>
       <c r="D166" s="12" t="n"/>
-      <c r="E166" s="13" t="n"/>
+      <c r="E166" s="26" t="n"/>
       <c r="F166" s="14">
         <f>IF(OR($A166="",G166=""),"",-LN(G166)/INDEX($N$156:$N$220,IFERROR(MATCH($A166,$K$156:$K$220,0),MATCH(IF($A166="1Y","12M",IF($A166="12M","1Y",$A166)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G166" s="15">
+      <c r="G166" s="27">
         <f>IF($A166="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A166,$K$156:$K$220,0),MATCH(IF($A166="1Y","12M",IF($A166="12M","1Y",$A166)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H166" s="16">
+      <c r="H166" s="28">
         <f>IF(OR(F166="",NOT(ISNUMBER(D166))),"",(F166-D166)*100)</f>
         <v/>
       </c>
@@ -11521,7 +11537,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("8M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("8M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U166" s="22">
+      <c r="U166" s="29">
         <f>IFERROR(IF(S166="","",1/(1+(S166/100)*O166)),"")</f>
         <v/>
       </c>
@@ -11535,16 +11551,16 @@
       <c r="B167" s="11" t="n"/>
       <c r="C167" s="12" t="n"/>
       <c r="D167" s="12" t="n"/>
-      <c r="E167" s="13" t="n"/>
+      <c r="E167" s="26" t="n"/>
       <c r="F167" s="14">
         <f>IF(OR($A167="",G167=""),"",-LN(G167)/INDEX($N$156:$N$220,IFERROR(MATCH($A167,$K$156:$K$220,0),MATCH(IF($A167="1Y","12M",IF($A167="12M","1Y",$A167)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G167" s="15">
+      <c r="G167" s="27">
         <f>IF($A167="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A167,$K$156:$K$220,0),MATCH(IF($A167="1Y","12M",IF($A167="12M","1Y",$A167)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H167" s="16">
+      <c r="H167" s="28">
         <f>IF(OR(F167="",NOT(ISNUMBER(D167))),"",(F167-D167)*100)</f>
         <v/>
       </c>
@@ -11591,7 +11607,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("9M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("9M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U167" s="22">
+      <c r="U167" s="29">
         <f>IFERROR(IF(S167="","",1/(1+(S167/100)*O167)),"")</f>
         <v/>
       </c>
@@ -11605,16 +11621,16 @@
       <c r="B168" s="11" t="n"/>
       <c r="C168" s="12" t="n"/>
       <c r="D168" s="12" t="n"/>
-      <c r="E168" s="13" t="n"/>
+      <c r="E168" s="26" t="n"/>
       <c r="F168" s="14">
         <f>IF(OR($A168="",G168=""),"",-LN(G168)/INDEX($N$156:$N$220,IFERROR(MATCH($A168,$K$156:$K$220,0),MATCH(IF($A168="1Y","12M",IF($A168="12M","1Y",$A168)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G168" s="15">
+      <c r="G168" s="27">
         <f>IF($A168="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A168,$K$156:$K$220,0),MATCH(IF($A168="1Y","12M",IF($A168="12M","1Y",$A168)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H168" s="16">
+      <c r="H168" s="28">
         <f>IF(OR(F168="",NOT(ISNUMBER(D168))),"",(F168-D168)*100)</f>
         <v/>
       </c>
@@ -11661,7 +11677,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("10M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("10M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U168" s="22">
+      <c r="U168" s="29">
         <f>IFERROR(IF(S168="","",1/(1+(S168/100)*O168)),"")</f>
         <v/>
       </c>
@@ -11675,16 +11691,16 @@
       <c r="B169" s="11" t="n"/>
       <c r="C169" s="12" t="n"/>
       <c r="D169" s="12" t="n"/>
-      <c r="E169" s="13" t="n"/>
+      <c r="E169" s="26" t="n"/>
       <c r="F169" s="14">
         <f>IF(OR($A169="",G169=""),"",-LN(G169)/INDEX($N$156:$N$220,IFERROR(MATCH($A169,$K$156:$K$220,0),MATCH(IF($A169="1Y","12M",IF($A169="12M","1Y",$A169)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G169" s="15">
+      <c r="G169" s="27">
         <f>IF($A169="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A169,$K$156:$K$220,0),MATCH(IF($A169="1Y","12M",IF($A169="12M","1Y",$A169)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H169" s="16">
+      <c r="H169" s="28">
         <f>IF(OR(F169="",NOT(ISNUMBER(D169))),"",(F169-D169)*100)</f>
         <v/>
       </c>
@@ -11731,7 +11747,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("11M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("11M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U169" s="22">
+      <c r="U169" s="29">
         <f>IFERROR(IF(S169="","",1/(1+(S169/100)*O169)),"")</f>
         <v/>
       </c>
@@ -11745,16 +11761,16 @@
       <c r="B170" s="11" t="n"/>
       <c r="C170" s="12" t="n"/>
       <c r="D170" s="12" t="n"/>
-      <c r="E170" s="13" t="n"/>
+      <c r="E170" s="26" t="n"/>
       <c r="F170" s="14">
         <f>IF(OR($A170="",G170=""),"",-LN(G170)/INDEX($N$156:$N$220,IFERROR(MATCH($A170,$K$156:$K$220,0),MATCH(IF($A170="1Y","12M",IF($A170="12M","1Y",$A170)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G170" s="15">
+      <c r="G170" s="27">
         <f>IF($A170="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A170,$K$156:$K$220,0),MATCH(IF($A170="1Y","12M",IF($A170="12M","1Y",$A170)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H170" s="16">
+      <c r="H170" s="28">
         <f>IF(OR(F170="",NOT(ISNUMBER(D170))),"",(F170-D170)*100)</f>
         <v/>
       </c>
@@ -11801,7 +11817,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("12M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("1Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U170" s="22">
+      <c r="U170" s="29">
         <f>IFERROR(IF(S170="","",1/(1+(S170/100)*O170)),"")</f>
         <v/>
       </c>
@@ -11815,16 +11831,16 @@
       <c r="B171" s="11" t="n"/>
       <c r="C171" s="12" t="n"/>
       <c r="D171" s="12" t="n"/>
-      <c r="E171" s="13" t="n"/>
+      <c r="E171" s="26" t="n"/>
       <c r="F171" s="14">
         <f>IF(OR($A171="",G171=""),"",-LN(G171)/INDEX($N$156:$N$220,IFERROR(MATCH($A171,$K$156:$K$220,0),MATCH(IF($A171="1Y","12M",IF($A171="12M","1Y",$A171)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G171" s="15">
+      <c r="G171" s="27">
         <f>IF($A171="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A171,$K$156:$K$220,0),MATCH(IF($A171="1Y","12M",IF($A171="12M","1Y",$A171)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H171" s="16">
+      <c r="H171" s="28">
         <f>IF(OR(F171="",NOT(ISNUMBER(D171))),"",(F171-D171)*100)</f>
         <v/>
       </c>
@@ -11871,7 +11887,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("18M",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("18M",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U171" s="22">
+      <c r="U171" s="29">
         <f>IFERROR(IF(S171="","",(1-(S171/100)*SUM($V$156:V170))/(1+(S171/100)*P171)),"")</f>
         <v/>
       </c>
@@ -11885,16 +11901,16 @@
       <c r="B172" s="11" t="n"/>
       <c r="C172" s="12" t="n"/>
       <c r="D172" s="12" t="n"/>
-      <c r="E172" s="13" t="n"/>
+      <c r="E172" s="26" t="n"/>
       <c r="F172" s="14">
         <f>IF(OR($A172="",G172=""),"",-LN(G172)/INDEX($N$156:$N$220,IFERROR(MATCH($A172,$K$156:$K$220,0),MATCH(IF($A172="1Y","12M",IF($A172="12M","1Y",$A172)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G172" s="15">
+      <c r="G172" s="27">
         <f>IF($A172="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A172,$K$156:$K$220,0),MATCH(IF($A172="1Y","12M",IF($A172="12M","1Y",$A172)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H172" s="16">
+      <c r="H172" s="28">
         <f>IF(OR(F172="",NOT(ISNUMBER(D172))),"",(F172-D172)*100)</f>
         <v/>
       </c>
@@ -11941,7 +11957,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("2Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("2Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U172" s="22">
+      <c r="U172" s="29">
         <f>IFERROR(IF(S172="","",(1-(S172/100)*SUM($V$156:V171))/(1+(S172/100)*P172)),"")</f>
         <v/>
       </c>
@@ -11955,16 +11971,16 @@
       <c r="B173" s="11" t="n"/>
       <c r="C173" s="12" t="n"/>
       <c r="D173" s="12" t="n"/>
-      <c r="E173" s="13" t="n"/>
+      <c r="E173" s="26" t="n"/>
       <c r="F173" s="14">
         <f>IF(OR($A173="",G173=""),"",-LN(G173)/INDEX($N$156:$N$220,IFERROR(MATCH($A173,$K$156:$K$220,0),MATCH(IF($A173="1Y","12M",IF($A173="12M","1Y",$A173)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G173" s="15">
+      <c r="G173" s="27">
         <f>IF($A173="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A173,$K$156:$K$220,0),MATCH(IF($A173="1Y","12M",IF($A173="12M","1Y",$A173)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H173" s="16">
+      <c r="H173" s="28">
         <f>IF(OR(F173="",NOT(ISNUMBER(D173))),"",(F173-D173)*100)</f>
         <v/>
       </c>
@@ -12011,7 +12027,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("3Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("3Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U173" s="22">
+      <c r="U173" s="29">
         <f>IFERROR(IF(S173="","",(1-(S173/100)*SUM($V$156:V172))/(1+(S173/100)*P173)),"")</f>
         <v/>
       </c>
@@ -12025,16 +12041,16 @@
       <c r="B174" s="11" t="n"/>
       <c r="C174" s="12" t="n"/>
       <c r="D174" s="12" t="n"/>
-      <c r="E174" s="13" t="n"/>
+      <c r="E174" s="26" t="n"/>
       <c r="F174" s="14">
         <f>IF(OR($A174="",G174=""),"",-LN(G174)/INDEX($N$156:$N$220,IFERROR(MATCH($A174,$K$156:$K$220,0),MATCH(IF($A174="1Y","12M",IF($A174="12M","1Y",$A174)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G174" s="15">
+      <c r="G174" s="27">
         <f>IF($A174="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A174,$K$156:$K$220,0),MATCH(IF($A174="1Y","12M",IF($A174="12M","1Y",$A174)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H174" s="16">
+      <c r="H174" s="28">
         <f>IF(OR(F174="",NOT(ISNUMBER(D174))),"",(F174-D174)*100)</f>
         <v/>
       </c>
@@ -12081,7 +12097,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("4Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("4Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U174" s="22">
+      <c r="U174" s="29">
         <f>IFERROR(IF(S174="","",(1-(S174/100)*SUM($V$156:V173))/(1+(S174/100)*P174)),"")</f>
         <v/>
       </c>
@@ -12095,16 +12111,16 @@
       <c r="B175" s="11" t="n"/>
       <c r="C175" s="12" t="n"/>
       <c r="D175" s="12" t="n"/>
-      <c r="E175" s="13" t="n"/>
+      <c r="E175" s="26" t="n"/>
       <c r="F175" s="14">
         <f>IF(OR($A175="",G175=""),"",-LN(G175)/INDEX($N$156:$N$220,IFERROR(MATCH($A175,$K$156:$K$220,0),MATCH(IF($A175="1Y","12M",IF($A175="12M","1Y",$A175)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G175" s="15">
+      <c r="G175" s="27">
         <f>IF($A175="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A175,$K$156:$K$220,0),MATCH(IF($A175="1Y","12M",IF($A175="12M","1Y",$A175)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H175" s="16">
+      <c r="H175" s="28">
         <f>IF(OR(F175="",NOT(ISNUMBER(D175))),"",(F175-D175)*100)</f>
         <v/>
       </c>
@@ -12151,7 +12167,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("5Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("5Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U175" s="22">
+      <c r="U175" s="29">
         <f>IFERROR(IF(S175="","",(1-(S175/100)*SUM($V$156:V174))/(1+(S175/100)*P175)),"")</f>
         <v/>
       </c>
@@ -12165,16 +12181,16 @@
       <c r="B176" s="11" t="n"/>
       <c r="C176" s="12" t="n"/>
       <c r="D176" s="12" t="n"/>
-      <c r="E176" s="13" t="n"/>
+      <c r="E176" s="26" t="n"/>
       <c r="F176" s="14">
         <f>IF(OR($A176="",G176=""),"",-LN(G176)/INDEX($N$156:$N$220,IFERROR(MATCH($A176,$K$156:$K$220,0),MATCH(IF($A176="1Y","12M",IF($A176="12M","1Y",$A176)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G176" s="15">
+      <c r="G176" s="27">
         <f>IF($A176="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A176,$K$156:$K$220,0),MATCH(IF($A176="1Y","12M",IF($A176="12M","1Y",$A176)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H176" s="16">
+      <c r="H176" s="28">
         <f>IF(OR(F176="",NOT(ISNUMBER(D176))),"",(F176-D176)*100)</f>
         <v/>
       </c>
@@ -12221,7 +12237,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("6Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("6Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U176" s="22">
+      <c r="U176" s="29">
         <f>IFERROR(IF(S176="","",(1-(S176/100)*SUM($V$156:V175))/(1+(S176/100)*P176)),"")</f>
         <v/>
       </c>
@@ -12235,16 +12251,16 @@
       <c r="B177" s="11" t="n"/>
       <c r="C177" s="12" t="n"/>
       <c r="D177" s="12" t="n"/>
-      <c r="E177" s="13" t="n"/>
+      <c r="E177" s="26" t="n"/>
       <c r="F177" s="14">
         <f>IF(OR($A177="",G177=""),"",-LN(G177)/INDEX($N$156:$N$220,IFERROR(MATCH($A177,$K$156:$K$220,0),MATCH(IF($A177="1Y","12M",IF($A177="12M","1Y",$A177)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G177" s="15">
+      <c r="G177" s="27">
         <f>IF($A177="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A177,$K$156:$K$220,0),MATCH(IF($A177="1Y","12M",IF($A177="12M","1Y",$A177)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H177" s="16">
+      <c r="H177" s="28">
         <f>IF(OR(F177="",NOT(ISNUMBER(D177))),"",(F177-D177)*100)</f>
         <v/>
       </c>
@@ -12291,7 +12307,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("7Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("7Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U177" s="22">
+      <c r="U177" s="29">
         <f>IFERROR(IF(S177="","",(1-(S177/100)*SUM($V$156:V176))/(1+(S177/100)*P177)),"")</f>
         <v/>
       </c>
@@ -12305,16 +12321,16 @@
       <c r="B178" s="11" t="n"/>
       <c r="C178" s="12" t="n"/>
       <c r="D178" s="12" t="n"/>
-      <c r="E178" s="13" t="n"/>
+      <c r="E178" s="26" t="n"/>
       <c r="F178" s="14">
         <f>IF(OR($A178="",G178=""),"",-LN(G178)/INDEX($N$156:$N$220,IFERROR(MATCH($A178,$K$156:$K$220,0),MATCH(IF($A178="1Y","12M",IF($A178="12M","1Y",$A178)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G178" s="15">
+      <c r="G178" s="27">
         <f>IF($A178="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A178,$K$156:$K$220,0),MATCH(IF($A178="1Y","12M",IF($A178="12M","1Y",$A178)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H178" s="16">
+      <c r="H178" s="28">
         <f>IF(OR(F178="",NOT(ISNUMBER(D178))),"",(F178-D178)*100)</f>
         <v/>
       </c>
@@ -12361,7 +12377,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("8Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("8Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U178" s="22">
+      <c r="U178" s="29">
         <f>IFERROR(IF(S178="","",(1-(S178/100)*SUM($V$156:V177))/(1+(S178/100)*P178)),"")</f>
         <v/>
       </c>
@@ -12375,16 +12391,16 @@
       <c r="B179" s="11" t="n"/>
       <c r="C179" s="12" t="n"/>
       <c r="D179" s="12" t="n"/>
-      <c r="E179" s="13" t="n"/>
+      <c r="E179" s="26" t="n"/>
       <c r="F179" s="14">
         <f>IF(OR($A179="",G179=""),"",-LN(G179)/INDEX($N$156:$N$220,IFERROR(MATCH($A179,$K$156:$K$220,0),MATCH(IF($A179="1Y","12M",IF($A179="12M","1Y",$A179)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G179" s="15">
+      <c r="G179" s="27">
         <f>IF($A179="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A179,$K$156:$K$220,0),MATCH(IF($A179="1Y","12M",IF($A179="12M","1Y",$A179)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H179" s="16">
+      <c r="H179" s="28">
         <f>IF(OR(F179="",NOT(ISNUMBER(D179))),"",(F179-D179)*100)</f>
         <v/>
       </c>
@@ -12431,7 +12447,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("9Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("9Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U179" s="22">
+      <c r="U179" s="29">
         <f>IFERROR(IF(S179="","",(1-(S179/100)*SUM($V$156:V178))/(1+(S179/100)*P179)),"")</f>
         <v/>
       </c>
@@ -12445,16 +12461,16 @@
       <c r="B180" s="11" t="n"/>
       <c r="C180" s="12" t="n"/>
       <c r="D180" s="12" t="n"/>
-      <c r="E180" s="13" t="n"/>
+      <c r="E180" s="26" t="n"/>
       <c r="F180" s="14">
         <f>IF(OR($A180="",G180=""),"",-LN(G180)/INDEX($N$156:$N$220,IFERROR(MATCH($A180,$K$156:$K$220,0),MATCH(IF($A180="1Y","12M",IF($A180="12M","1Y",$A180)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G180" s="15">
+      <c r="G180" s="27">
         <f>IF($A180="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A180,$K$156:$K$220,0),MATCH(IF($A180="1Y","12M",IF($A180="12M","1Y",$A180)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H180" s="16">
+      <c r="H180" s="28">
         <f>IF(OR(F180="",NOT(ISNUMBER(D180))),"",(F180-D180)*100)</f>
         <v/>
       </c>
@@ -12501,7 +12517,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("10Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("10Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U180" s="22">
+      <c r="U180" s="29">
         <f>IFERROR(IF(S180="","",(1-(S180/100)*SUM($V$156:V179))/(1+(S180/100)*P180)),"")</f>
         <v/>
       </c>
@@ -12515,16 +12531,16 @@
       <c r="B181" s="11" t="n"/>
       <c r="C181" s="12" t="n"/>
       <c r="D181" s="12" t="n"/>
-      <c r="E181" s="13" t="n"/>
+      <c r="E181" s="26" t="n"/>
       <c r="F181" s="14">
         <f>IF(OR($A181="",G181=""),"",-LN(G181)/INDEX($N$156:$N$220,IFERROR(MATCH($A181,$K$156:$K$220,0),MATCH(IF($A181="1Y","12M",IF($A181="12M","1Y",$A181)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G181" s="15">
+      <c r="G181" s="27">
         <f>IF($A181="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A181,$K$156:$K$220,0),MATCH(IF($A181="1Y","12M",IF($A181="12M","1Y",$A181)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H181" s="16">
+      <c r="H181" s="28">
         <f>IF(OR(F181="",NOT(ISNUMBER(D181))),"",(F181-D181)*100)</f>
         <v/>
       </c>
@@ -12575,7 +12591,7 @@
         <f>IFERROR(IF(OR(N181="",N182=""),"",(N181-N180)/(N182-N180)),"")</f>
         <v/>
       </c>
-      <c r="U181" s="22">
+      <c r="U181" s="29">
         <f>IFERROR(IF(OR(T181="",U182=""),"",U180*(U182/U180)^T181),"")</f>
         <v/>
       </c>
@@ -12589,16 +12605,16 @@
       <c r="B182" s="11" t="n"/>
       <c r="C182" s="12" t="n"/>
       <c r="D182" s="12" t="n"/>
-      <c r="E182" s="13" t="n"/>
+      <c r="E182" s="26" t="n"/>
       <c r="F182" s="14">
         <f>IF(OR($A182="",G182=""),"",-LN(G182)/INDEX($N$156:$N$220,IFERROR(MATCH($A182,$K$156:$K$220,0),MATCH(IF($A182="1Y","12M",IF($A182="12M","1Y",$A182)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G182" s="15">
+      <c r="G182" s="27">
         <f>IF($A182="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A182,$K$156:$K$220,0),MATCH(IF($A182="1Y","12M",IF($A182="12M","1Y",$A182)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H182" s="16">
+      <c r="H182" s="28">
         <f>IF(OR(F182="",NOT(ISNUMBER(D182))),"",(F182-D182)*100)</f>
         <v/>
       </c>
@@ -12645,7 +12661,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("12Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("12Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U182" s="22">
+      <c r="U182" s="29">
         <f>IFERROR(IF(S182="","",AM182),"")</f>
         <v/>
       </c>
@@ -12653,67 +12669,67 @@
         <f>IFERROR(IF(OR(U182="",Q182=0),0,P182*U182),"")</f>
         <v/>
       </c>
-      <c r="X182" s="23">
+      <c r="X182" s="30">
         <f>IFERROR(IF(S182="","",U180*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y182" s="23">
+      <c r="Y182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(X182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="Z182" s="23">
+      <c r="Z182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(Y182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AA182" s="23">
+      <c r="AA182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(Z182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AB182" s="23">
+      <c r="AB182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AA182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AC182" s="23">
+      <c r="AC182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AB182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AD182" s="23">
+      <c r="AD182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AC182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AE182" s="23">
+      <c r="AE182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AD182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AF182" s="23">
+      <c r="AF182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AE182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AG182" s="23">
+      <c r="AG182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AF182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AH182" s="23">
+      <c r="AH182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AG182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AI182" s="23">
+      <c r="AI182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AH182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AJ182" s="23">
+      <c r="AJ182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AI182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AK182" s="23">
+      <c r="AK182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AJ182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AL182" s="23">
+      <c r="AL182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AK182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
-      <c r="AM182" s="23">
+      <c r="AM182" s="30">
         <f>IFERROR(IF(S182="","",(1-(S182/100)*(SUM($V$156:V180)+SUMPRODUCT($P$181:$P$181,$Q$181:$Q$181,U180*(AL182/U180)^$T$181:$T$181)))/(1+(S182/100)*P182)),"")</f>
         <v/>
       </c>
@@ -12723,16 +12739,16 @@
       <c r="B183" s="11" t="n"/>
       <c r="C183" s="12" t="n"/>
       <c r="D183" s="12" t="n"/>
-      <c r="E183" s="13" t="n"/>
+      <c r="E183" s="26" t="n"/>
       <c r="F183" s="14">
         <f>IF(OR($A183="",G183=""),"",-LN(G183)/INDEX($N$156:$N$220,IFERROR(MATCH($A183,$K$156:$K$220,0),MATCH(IF($A183="1Y","12M",IF($A183="12M","1Y",$A183)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G183" s="15">
+      <c r="G183" s="27">
         <f>IF($A183="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A183,$K$156:$K$220,0),MATCH(IF($A183="1Y","12M",IF($A183="12M","1Y",$A183)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H183" s="16">
+      <c r="H183" s="28">
         <f>IF(OR(F183="",NOT(ISNUMBER(D183))),"",(F183-D183)*100)</f>
         <v/>
       </c>
@@ -12783,7 +12799,7 @@
         <f>IFERROR(IF(OR(N183="",N185=""),"",(N183-N182)/(N185-N182)),"")</f>
         <v/>
       </c>
-      <c r="U183" s="22">
+      <c r="U183" s="29">
         <f>IFERROR(IF(OR(T183="",U185=""),"",U182*(U185/U182)^T183),"")</f>
         <v/>
       </c>
@@ -12797,16 +12813,16 @@
       <c r="B184" s="11" t="n"/>
       <c r="C184" s="12" t="n"/>
       <c r="D184" s="12" t="n"/>
-      <c r="E184" s="13" t="n"/>
+      <c r="E184" s="26" t="n"/>
       <c r="F184" s="14">
         <f>IF(OR($A184="",G184=""),"",-LN(G184)/INDEX($N$156:$N$220,IFERROR(MATCH($A184,$K$156:$K$220,0),MATCH(IF($A184="1Y","12M",IF($A184="12M","1Y",$A184)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G184" s="15">
+      <c r="G184" s="27">
         <f>IF($A184="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A184,$K$156:$K$220,0),MATCH(IF($A184="1Y","12M",IF($A184="12M","1Y",$A184)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H184" s="16">
+      <c r="H184" s="28">
         <f>IF(OR(F184="",NOT(ISNUMBER(D184))),"",(F184-D184)*100)</f>
         <v/>
       </c>
@@ -12857,7 +12873,7 @@
         <f>IFERROR(IF(OR(N184="",N185=""),"",(N184-N182)/(N185-N182)),"")</f>
         <v/>
       </c>
-      <c r="U184" s="22">
+      <c r="U184" s="29">
         <f>IFERROR(IF(OR(T184="",U185=""),"",U182*(U185/U182)^T184),"")</f>
         <v/>
       </c>
@@ -12871,16 +12887,16 @@
       <c r="B185" s="11" t="n"/>
       <c r="C185" s="12" t="n"/>
       <c r="D185" s="12" t="n"/>
-      <c r="E185" s="13" t="n"/>
+      <c r="E185" s="26" t="n"/>
       <c r="F185" s="14">
         <f>IF(OR($A185="",G185=""),"",-LN(G185)/INDEX($N$156:$N$220,IFERROR(MATCH($A185,$K$156:$K$220,0),MATCH(IF($A185="1Y","12M",IF($A185="12M","1Y",$A185)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G185" s="15">
+      <c r="G185" s="27">
         <f>IF($A185="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A185,$K$156:$K$220,0),MATCH(IF($A185="1Y","12M",IF($A185="12M","1Y",$A185)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H185" s="16">
+      <c r="H185" s="28">
         <f>IF(OR(F185="",NOT(ISNUMBER(D185))),"",(F185-D185)*100)</f>
         <v/>
       </c>
@@ -12927,7 +12943,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("15Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("15Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U185" s="22">
+      <c r="U185" s="29">
         <f>IFERROR(IF(S185="","",AM185),"")</f>
         <v/>
       </c>
@@ -12935,67 +12951,67 @@
         <f>IFERROR(IF(OR(U185="",Q185=0),0,P185*U185),"")</f>
         <v/>
       </c>
-      <c r="X185" s="23">
+      <c r="X185" s="30">
         <f>IFERROR(IF(S185="","",U182*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y185" s="23">
+      <c r="Y185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(X185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="Z185" s="23">
+      <c r="Z185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(Y185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AA185" s="23">
+      <c r="AA185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(Z185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AB185" s="23">
+      <c r="AB185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AA185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AC185" s="23">
+      <c r="AC185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AB185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AD185" s="23">
+      <c r="AD185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AC185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AE185" s="23">
+      <c r="AE185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AD185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AF185" s="23">
+      <c r="AF185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AE185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AG185" s="23">
+      <c r="AG185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AF185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AH185" s="23">
+      <c r="AH185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AG185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AI185" s="23">
+      <c r="AI185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AH185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AJ185" s="23">
+      <c r="AJ185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AI185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AK185" s="23">
+      <c r="AK185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AJ185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AL185" s="23">
+      <c r="AL185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AK185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
-      <c r="AM185" s="23">
+      <c r="AM185" s="30">
         <f>IFERROR(IF(S185="","",(1-(S185/100)*(SUM($V$156:V182)+SUMPRODUCT($P$183:$P$184,$Q$183:$Q$184,U182*(AL185/U182)^$T$183:$T$184)))/(1+(S185/100)*P185)),"")</f>
         <v/>
       </c>
@@ -13005,16 +13021,16 @@
       <c r="B186" s="11" t="n"/>
       <c r="C186" s="12" t="n"/>
       <c r="D186" s="12" t="n"/>
-      <c r="E186" s="13" t="n"/>
+      <c r="E186" s="26" t="n"/>
       <c r="F186" s="14">
         <f>IF(OR($A186="",G186=""),"",-LN(G186)/INDEX($N$156:$N$220,IFERROR(MATCH($A186,$K$156:$K$220,0),MATCH(IF($A186="1Y","12M",IF($A186="12M","1Y",$A186)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G186" s="15">
+      <c r="G186" s="27">
         <f>IF($A186="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A186,$K$156:$K$220,0),MATCH(IF($A186="1Y","12M",IF($A186="12M","1Y",$A186)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H186" s="16">
+      <c r="H186" s="28">
         <f>IF(OR(F186="",NOT(ISNUMBER(D186))),"",(F186-D186)*100)</f>
         <v/>
       </c>
@@ -13065,7 +13081,7 @@
         <f>IFERROR(IF(OR(N186="",N190=""),"",(N186-N185)/(N190-N185)),"")</f>
         <v/>
       </c>
-      <c r="U186" s="22">
+      <c r="U186" s="29">
         <f>IFERROR(IF(OR(T186="",U190=""),"",U185*(U190/U185)^T186),"")</f>
         <v/>
       </c>
@@ -13079,16 +13095,16 @@
       <c r="B187" s="11" t="n"/>
       <c r="C187" s="12" t="n"/>
       <c r="D187" s="12" t="n"/>
-      <c r="E187" s="13" t="n"/>
+      <c r="E187" s="26" t="n"/>
       <c r="F187" s="14">
         <f>IF(OR($A187="",G187=""),"",-LN(G187)/INDEX($N$156:$N$220,IFERROR(MATCH($A187,$K$156:$K$220,0),MATCH(IF($A187="1Y","12M",IF($A187="12M","1Y",$A187)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G187" s="15">
+      <c r="G187" s="27">
         <f>IF($A187="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A187,$K$156:$K$220,0),MATCH(IF($A187="1Y","12M",IF($A187="12M","1Y",$A187)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H187" s="16">
+      <c r="H187" s="28">
         <f>IF(OR(F187="",NOT(ISNUMBER(D187))),"",(F187-D187)*100)</f>
         <v/>
       </c>
@@ -13139,7 +13155,7 @@
         <f>IFERROR(IF(OR(N187="",N190=""),"",(N187-N185)/(N190-N185)),"")</f>
         <v/>
       </c>
-      <c r="U187" s="22">
+      <c r="U187" s="29">
         <f>IFERROR(IF(OR(T187="",U190=""),"",U185*(U190/U185)^T187),"")</f>
         <v/>
       </c>
@@ -13153,16 +13169,16 @@
       <c r="B188" s="11" t="n"/>
       <c r="C188" s="12" t="n"/>
       <c r="D188" s="12" t="n"/>
-      <c r="E188" s="13" t="n"/>
+      <c r="E188" s="26" t="n"/>
       <c r="F188" s="14">
         <f>IF(OR($A188="",G188=""),"",-LN(G188)/INDEX($N$156:$N$220,IFERROR(MATCH($A188,$K$156:$K$220,0),MATCH(IF($A188="1Y","12M",IF($A188="12M","1Y",$A188)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G188" s="15">
+      <c r="G188" s="27">
         <f>IF($A188="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A188,$K$156:$K$220,0),MATCH(IF($A188="1Y","12M",IF($A188="12M","1Y",$A188)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H188" s="16">
+      <c r="H188" s="28">
         <f>IF(OR(F188="",NOT(ISNUMBER(D188))),"",(F188-D188)*100)</f>
         <v/>
       </c>
@@ -13213,7 +13229,7 @@
         <f>IFERROR(IF(OR(N188="",N190=""),"",(N188-N185)/(N190-N185)),"")</f>
         <v/>
       </c>
-      <c r="U188" s="22">
+      <c r="U188" s="29">
         <f>IFERROR(IF(OR(T188="",U190=""),"",U185*(U190/U185)^T188),"")</f>
         <v/>
       </c>
@@ -13227,16 +13243,16 @@
       <c r="B189" s="11" t="n"/>
       <c r="C189" s="12" t="n"/>
       <c r="D189" s="12" t="n"/>
-      <c r="E189" s="13" t="n"/>
+      <c r="E189" s="26" t="n"/>
       <c r="F189" s="14">
         <f>IF(OR($A189="",G189=""),"",-LN(G189)/INDEX($N$156:$N$220,IFERROR(MATCH($A189,$K$156:$K$220,0),MATCH(IF($A189="1Y","12M",IF($A189="12M","1Y",$A189)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G189" s="15">
+      <c r="G189" s="27">
         <f>IF($A189="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A189,$K$156:$K$220,0),MATCH(IF($A189="1Y","12M",IF($A189="12M","1Y",$A189)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H189" s="16">
+      <c r="H189" s="28">
         <f>IF(OR(F189="",NOT(ISNUMBER(D189))),"",(F189-D189)*100)</f>
         <v/>
       </c>
@@ -13287,7 +13303,7 @@
         <f>IFERROR(IF(OR(N189="",N190=""),"",(N189-N185)/(N190-N185)),"")</f>
         <v/>
       </c>
-      <c r="U189" s="22">
+      <c r="U189" s="29">
         <f>IFERROR(IF(OR(T189="",U190=""),"",U185*(U190/U185)^T189),"")</f>
         <v/>
       </c>
@@ -13301,16 +13317,16 @@
       <c r="B190" s="11" t="n"/>
       <c r="C190" s="12" t="n"/>
       <c r="D190" s="12" t="n"/>
-      <c r="E190" s="13" t="n"/>
+      <c r="E190" s="26" t="n"/>
       <c r="F190" s="14">
         <f>IF(OR($A190="",G190=""),"",-LN(G190)/INDEX($N$156:$N$220,IFERROR(MATCH($A190,$K$156:$K$220,0),MATCH(IF($A190="1Y","12M",IF($A190="12M","1Y",$A190)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G190" s="15">
+      <c r="G190" s="27">
         <f>IF($A190="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A190,$K$156:$K$220,0),MATCH(IF($A190="1Y","12M",IF($A190="12M","1Y",$A190)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H190" s="16">
+      <c r="H190" s="28">
         <f>IF(OR(F190="",NOT(ISNUMBER(D190))),"",(F190-D190)*100)</f>
         <v/>
       </c>
@@ -13357,7 +13373,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("20Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("20Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U190" s="22">
+      <c r="U190" s="29">
         <f>IFERROR(IF(S190="","",AM190),"")</f>
         <v/>
       </c>
@@ -13365,67 +13381,67 @@
         <f>IFERROR(IF(OR(U190="",Q190=0),0,P190*U190),"")</f>
         <v/>
       </c>
-      <c r="X190" s="23">
+      <c r="X190" s="30">
         <f>IFERROR(IF(S190="","",U185*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y190" s="23">
+      <c r="Y190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(X190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="Z190" s="23">
+      <c r="Z190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(Y190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AA190" s="23">
+      <c r="AA190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(Z190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AB190" s="23">
+      <c r="AB190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AA190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AC190" s="23">
+      <c r="AC190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AB190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AD190" s="23">
+      <c r="AD190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AC190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AE190" s="23">
+      <c r="AE190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AD190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AF190" s="23">
+      <c r="AF190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AE190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AG190" s="23">
+      <c r="AG190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AF190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AH190" s="23">
+      <c r="AH190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AG190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AI190" s="23">
+      <c r="AI190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AH190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AJ190" s="23">
+      <c r="AJ190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AI190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AK190" s="23">
+      <c r="AK190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AJ190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AL190" s="23">
+      <c r="AL190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AK190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
-      <c r="AM190" s="23">
+      <c r="AM190" s="30">
         <f>IFERROR(IF(S190="","",(1-(S190/100)*(SUM($V$156:V185)+SUMPRODUCT($P$186:$P$189,$Q$186:$Q$189,U185*(AL190/U185)^$T$186:$T$189)))/(1+(S190/100)*P190)),"")</f>
         <v/>
       </c>
@@ -13435,16 +13451,16 @@
       <c r="B191" s="11" t="n"/>
       <c r="C191" s="12" t="n"/>
       <c r="D191" s="12" t="n"/>
-      <c r="E191" s="13" t="n"/>
+      <c r="E191" s="26" t="n"/>
       <c r="F191" s="14">
         <f>IF(OR($A191="",G191=""),"",-LN(G191)/INDEX($N$156:$N$220,IFERROR(MATCH($A191,$K$156:$K$220,0),MATCH(IF($A191="1Y","12M",IF($A191="12M","1Y",$A191)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G191" s="15">
+      <c r="G191" s="27">
         <f>IF($A191="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A191,$K$156:$K$220,0),MATCH(IF($A191="1Y","12M",IF($A191="12M","1Y",$A191)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H191" s="16">
+      <c r="H191" s="28">
         <f>IF(OR(F191="",NOT(ISNUMBER(D191))),"",(F191-D191)*100)</f>
         <v/>
       </c>
@@ -13495,7 +13511,7 @@
         <f>IFERROR(IF(OR(N191="",N195=""),"",(N191-N190)/(N195-N190)),"")</f>
         <v/>
       </c>
-      <c r="U191" s="22">
+      <c r="U191" s="29">
         <f>IFERROR(IF(OR(T191="",U195=""),"",U190*(U195/U190)^T191),"")</f>
         <v/>
       </c>
@@ -13509,16 +13525,16 @@
       <c r="B192" s="11" t="n"/>
       <c r="C192" s="12" t="n"/>
       <c r="D192" s="12" t="n"/>
-      <c r="E192" s="13" t="n"/>
+      <c r="E192" s="26" t="n"/>
       <c r="F192" s="14">
         <f>IF(OR($A192="",G192=""),"",-LN(G192)/INDEX($N$156:$N$220,IFERROR(MATCH($A192,$K$156:$K$220,0),MATCH(IF($A192="1Y","12M",IF($A192="12M","1Y",$A192)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G192" s="15">
+      <c r="G192" s="27">
         <f>IF($A192="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A192,$K$156:$K$220,0),MATCH(IF($A192="1Y","12M",IF($A192="12M","1Y",$A192)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H192" s="16">
+      <c r="H192" s="28">
         <f>IF(OR(F192="",NOT(ISNUMBER(D192))),"",(F192-D192)*100)</f>
         <v/>
       </c>
@@ -13569,7 +13585,7 @@
         <f>IFERROR(IF(OR(N192="",N195=""),"",(N192-N190)/(N195-N190)),"")</f>
         <v/>
       </c>
-      <c r="U192" s="22">
+      <c r="U192" s="29">
         <f>IFERROR(IF(OR(T192="",U195=""),"",U190*(U195/U190)^T192),"")</f>
         <v/>
       </c>
@@ -13583,16 +13599,16 @@
       <c r="B193" s="11" t="n"/>
       <c r="C193" s="12" t="n"/>
       <c r="D193" s="12" t="n"/>
-      <c r="E193" s="13" t="n"/>
+      <c r="E193" s="26" t="n"/>
       <c r="F193" s="14">
         <f>IF(OR($A193="",G193=""),"",-LN(G193)/INDEX($N$156:$N$220,IFERROR(MATCH($A193,$K$156:$K$220,0),MATCH(IF($A193="1Y","12M",IF($A193="12M","1Y",$A193)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G193" s="15">
+      <c r="G193" s="27">
         <f>IF($A193="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A193,$K$156:$K$220,0),MATCH(IF($A193="1Y","12M",IF($A193="12M","1Y",$A193)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H193" s="16">
+      <c r="H193" s="28">
         <f>IF(OR(F193="",NOT(ISNUMBER(D193))),"",(F193-D193)*100)</f>
         <v/>
       </c>
@@ -13643,7 +13659,7 @@
         <f>IFERROR(IF(OR(N193="",N195=""),"",(N193-N190)/(N195-N190)),"")</f>
         <v/>
       </c>
-      <c r="U193" s="22">
+      <c r="U193" s="29">
         <f>IFERROR(IF(OR(T193="",U195=""),"",U190*(U195/U190)^T193),"")</f>
         <v/>
       </c>
@@ -13657,16 +13673,16 @@
       <c r="B194" s="11" t="n"/>
       <c r="C194" s="12" t="n"/>
       <c r="D194" s="12" t="n"/>
-      <c r="E194" s="13" t="n"/>
+      <c r="E194" s="26" t="n"/>
       <c r="F194" s="14">
         <f>IF(OR($A194="",G194=""),"",-LN(G194)/INDEX($N$156:$N$220,IFERROR(MATCH($A194,$K$156:$K$220,0),MATCH(IF($A194="1Y","12M",IF($A194="12M","1Y",$A194)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G194" s="15">
+      <c r="G194" s="27">
         <f>IF($A194="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A194,$K$156:$K$220,0),MATCH(IF($A194="1Y","12M",IF($A194="12M","1Y",$A194)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H194" s="16">
+      <c r="H194" s="28">
         <f>IF(OR(F194="",NOT(ISNUMBER(D194))),"",(F194-D194)*100)</f>
         <v/>
       </c>
@@ -13717,7 +13733,7 @@
         <f>IFERROR(IF(OR(N194="",N195=""),"",(N194-N190)/(N195-N190)),"")</f>
         <v/>
       </c>
-      <c r="U194" s="22">
+      <c r="U194" s="29">
         <f>IFERROR(IF(OR(T194="",U195=""),"",U190*(U195/U190)^T194),"")</f>
         <v/>
       </c>
@@ -13731,16 +13747,16 @@
       <c r="B195" s="11" t="n"/>
       <c r="C195" s="12" t="n"/>
       <c r="D195" s="12" t="n"/>
-      <c r="E195" s="13" t="n"/>
+      <c r="E195" s="26" t="n"/>
       <c r="F195" s="14">
         <f>IF(OR($A195="",G195=""),"",-LN(G195)/INDEX($N$156:$N$220,IFERROR(MATCH($A195,$K$156:$K$220,0),MATCH(IF($A195="1Y","12M",IF($A195="12M","1Y",$A195)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G195" s="15">
+      <c r="G195" s="27">
         <f>IF($A195="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A195,$K$156:$K$220,0),MATCH(IF($A195="1Y","12M",IF($A195="12M","1Y",$A195)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H195" s="16">
+      <c r="H195" s="28">
         <f>IF(OR(F195="",NOT(ISNUMBER(D195))),"",(F195-D195)*100)</f>
         <v/>
       </c>
@@ -13787,7 +13803,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("25Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("25Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U195" s="22">
+      <c r="U195" s="29">
         <f>IFERROR(IF(S195="","",AM195),"")</f>
         <v/>
       </c>
@@ -13795,67 +13811,67 @@
         <f>IFERROR(IF(OR(U195="",Q195=0),0,P195*U195),"")</f>
         <v/>
       </c>
-      <c r="X195" s="23">
+      <c r="X195" s="30">
         <f>IFERROR(IF(S195="","",U190*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y195" s="23">
+      <c r="Y195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(X195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="Z195" s="23">
+      <c r="Z195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(Y195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AA195" s="23">
+      <c r="AA195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(Z195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AB195" s="23">
+      <c r="AB195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AA195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AC195" s="23">
+      <c r="AC195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AB195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AD195" s="23">
+      <c r="AD195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AC195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AE195" s="23">
+      <c r="AE195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AD195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AF195" s="23">
+      <c r="AF195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AE195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AG195" s="23">
+      <c r="AG195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AF195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AH195" s="23">
+      <c r="AH195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AG195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AI195" s="23">
+      <c r="AI195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AH195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AJ195" s="23">
+      <c r="AJ195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AI195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AK195" s="23">
+      <c r="AK195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AJ195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AL195" s="23">
+      <c r="AL195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AK195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
-      <c r="AM195" s="23">
+      <c r="AM195" s="30">
         <f>IFERROR(IF(S195="","",(1-(S195/100)*(SUM($V$156:V190)+SUMPRODUCT($P$191:$P$194,$Q$191:$Q$194,U190*(AL195/U190)^$T$191:$T$194)))/(1+(S195/100)*P195)),"")</f>
         <v/>
       </c>
@@ -13865,16 +13881,16 @@
       <c r="B196" s="11" t="n"/>
       <c r="C196" s="12" t="n"/>
       <c r="D196" s="12" t="n"/>
-      <c r="E196" s="13" t="n"/>
+      <c r="E196" s="26" t="n"/>
       <c r="F196" s="14">
         <f>IF(OR($A196="",G196=""),"",-LN(G196)/INDEX($N$156:$N$220,IFERROR(MATCH($A196,$K$156:$K$220,0),MATCH(IF($A196="1Y","12M",IF($A196="12M","1Y",$A196)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G196" s="15">
+      <c r="G196" s="27">
         <f>IF($A196="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A196,$K$156:$K$220,0),MATCH(IF($A196="1Y","12M",IF($A196="12M","1Y",$A196)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H196" s="16">
+      <c r="H196" s="28">
         <f>IF(OR(F196="",NOT(ISNUMBER(D196))),"",(F196-D196)*100)</f>
         <v/>
       </c>
@@ -13925,7 +13941,7 @@
         <f>IFERROR(IF(OR(N196="",N200=""),"",(N196-N195)/(N200-N195)),"")</f>
         <v/>
       </c>
-      <c r="U196" s="22">
+      <c r="U196" s="29">
         <f>IFERROR(IF(OR(T196="",U200=""),"",U195*(U200/U195)^T196),"")</f>
         <v/>
       </c>
@@ -13939,16 +13955,16 @@
       <c r="B197" s="11" t="n"/>
       <c r="C197" s="12" t="n"/>
       <c r="D197" s="12" t="n"/>
-      <c r="E197" s="13" t="n"/>
+      <c r="E197" s="26" t="n"/>
       <c r="F197" s="14">
         <f>IF(OR($A197="",G197=""),"",-LN(G197)/INDEX($N$156:$N$220,IFERROR(MATCH($A197,$K$156:$K$220,0),MATCH(IF($A197="1Y","12M",IF($A197="12M","1Y",$A197)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G197" s="15">
+      <c r="G197" s="27">
         <f>IF($A197="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A197,$K$156:$K$220,0),MATCH(IF($A197="1Y","12M",IF($A197="12M","1Y",$A197)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H197" s="16">
+      <c r="H197" s="28">
         <f>IF(OR(F197="",NOT(ISNUMBER(D197))),"",(F197-D197)*100)</f>
         <v/>
       </c>
@@ -13999,7 +14015,7 @@
         <f>IFERROR(IF(OR(N197="",N200=""),"",(N197-N195)/(N200-N195)),"")</f>
         <v/>
       </c>
-      <c r="U197" s="22">
+      <c r="U197" s="29">
         <f>IFERROR(IF(OR(T197="",U200=""),"",U195*(U200/U195)^T197),"")</f>
         <v/>
       </c>
@@ -14013,16 +14029,16 @@
       <c r="B198" s="11" t="n"/>
       <c r="C198" s="12" t="n"/>
       <c r="D198" s="12" t="n"/>
-      <c r="E198" s="13" t="n"/>
+      <c r="E198" s="26" t="n"/>
       <c r="F198" s="14">
         <f>IF(OR($A198="",G198=""),"",-LN(G198)/INDEX($N$156:$N$220,IFERROR(MATCH($A198,$K$156:$K$220,0),MATCH(IF($A198="1Y","12M",IF($A198="12M","1Y",$A198)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G198" s="15">
+      <c r="G198" s="27">
         <f>IF($A198="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A198,$K$156:$K$220,0),MATCH(IF($A198="1Y","12M",IF($A198="12M","1Y",$A198)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H198" s="16">
+      <c r="H198" s="28">
         <f>IF(OR(F198="",NOT(ISNUMBER(D198))),"",(F198-D198)*100)</f>
         <v/>
       </c>
@@ -14073,7 +14089,7 @@
         <f>IFERROR(IF(OR(N198="",N200=""),"",(N198-N195)/(N200-N195)),"")</f>
         <v/>
       </c>
-      <c r="U198" s="22">
+      <c r="U198" s="29">
         <f>IFERROR(IF(OR(T198="",U200=""),"",U195*(U200/U195)^T198),"")</f>
         <v/>
       </c>
@@ -14087,16 +14103,16 @@
       <c r="B199" s="11" t="n"/>
       <c r="C199" s="12" t="n"/>
       <c r="D199" s="12" t="n"/>
-      <c r="E199" s="13" t="n"/>
+      <c r="E199" s="26" t="n"/>
       <c r="F199" s="14">
         <f>IF(OR($A199="",G199=""),"",-LN(G199)/INDEX($N$156:$N$220,IFERROR(MATCH($A199,$K$156:$K$220,0),MATCH(IF($A199="1Y","12M",IF($A199="12M","1Y",$A199)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G199" s="15">
+      <c r="G199" s="27">
         <f>IF($A199="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A199,$K$156:$K$220,0),MATCH(IF($A199="1Y","12M",IF($A199="12M","1Y",$A199)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H199" s="16">
+      <c r="H199" s="28">
         <f>IF(OR(F199="",NOT(ISNUMBER(D199))),"",(F199-D199)*100)</f>
         <v/>
       </c>
@@ -14147,7 +14163,7 @@
         <f>IFERROR(IF(OR(N199="",N200=""),"",(N199-N195)/(N200-N195)),"")</f>
         <v/>
       </c>
-      <c r="U199" s="22">
+      <c r="U199" s="29">
         <f>IFERROR(IF(OR(T199="",U200=""),"",U195*(U200/U195)^T199),"")</f>
         <v/>
       </c>
@@ -14161,16 +14177,16 @@
       <c r="B200" s="11" t="n"/>
       <c r="C200" s="12" t="n"/>
       <c r="D200" s="12" t="n"/>
-      <c r="E200" s="13" t="n"/>
+      <c r="E200" s="26" t="n"/>
       <c r="F200" s="14">
         <f>IF(OR($A200="",G200=""),"",-LN(G200)/INDEX($N$156:$N$220,IFERROR(MATCH($A200,$K$156:$K$220,0),MATCH(IF($A200="1Y","12M",IF($A200="12M","1Y",$A200)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G200" s="15">
+      <c r="G200" s="27">
         <f>IF($A200="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A200,$K$156:$K$220,0),MATCH(IF($A200="1Y","12M",IF($A200="12M","1Y",$A200)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H200" s="16">
+      <c r="H200" s="28">
         <f>IF(OR(F200="",NOT(ISNUMBER(D200))),"",(F200-D200)*100)</f>
         <v/>
       </c>
@@ -14217,7 +14233,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("30Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("30Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U200" s="22">
+      <c r="U200" s="29">
         <f>IFERROR(IF(S200="","",AM200),"")</f>
         <v/>
       </c>
@@ -14225,67 +14241,67 @@
         <f>IFERROR(IF(OR(U200="",Q200=0),0,P200*U200),"")</f>
         <v/>
       </c>
-      <c r="X200" s="23">
+      <c r="X200" s="30">
         <f>IFERROR(IF(S200="","",U195*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y200" s="23">
+      <c r="Y200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(X200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="Z200" s="23">
+      <c r="Z200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(Y200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AA200" s="23">
+      <c r="AA200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(Z200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AB200" s="23">
+      <c r="AB200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AA200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AC200" s="23">
+      <c r="AC200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AB200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AD200" s="23">
+      <c r="AD200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AC200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AE200" s="23">
+      <c r="AE200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AD200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AF200" s="23">
+      <c r="AF200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AE200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AG200" s="23">
+      <c r="AG200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AF200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AH200" s="23">
+      <c r="AH200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AG200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AI200" s="23">
+      <c r="AI200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AH200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AJ200" s="23">
+      <c r="AJ200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AI200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AK200" s="23">
+      <c r="AK200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AJ200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AL200" s="23">
+      <c r="AL200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AK200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
-      <c r="AM200" s="23">
+      <c r="AM200" s="30">
         <f>IFERROR(IF(S200="","",(1-(S200/100)*(SUM($V$156:V195)+SUMPRODUCT($P$196:$P$199,$Q$196:$Q$199,U195*(AL200/U195)^$T$196:$T$199)))/(1+(S200/100)*P200)),"")</f>
         <v/>
       </c>
@@ -14295,16 +14311,16 @@
       <c r="B201" s="11" t="n"/>
       <c r="C201" s="12" t="n"/>
       <c r="D201" s="12" t="n"/>
-      <c r="E201" s="13" t="n"/>
+      <c r="E201" s="26" t="n"/>
       <c r="F201" s="14">
         <f>IF(OR($A201="",G201=""),"",-LN(G201)/INDEX($N$156:$N$220,IFERROR(MATCH($A201,$K$156:$K$220,0),MATCH(IF($A201="1Y","12M",IF($A201="12M","1Y",$A201)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G201" s="15">
+      <c r="G201" s="27">
         <f>IF($A201="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A201,$K$156:$K$220,0),MATCH(IF($A201="1Y","12M",IF($A201="12M","1Y",$A201)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H201" s="16">
+      <c r="H201" s="28">
         <f>IF(OR(F201="",NOT(ISNUMBER(D201))),"",(F201-D201)*100)</f>
         <v/>
       </c>
@@ -14355,7 +14371,7 @@
         <f>IFERROR(IF(OR(N201="",N210=""),"",(N201-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U201" s="22">
+      <c r="U201" s="29">
         <f>IFERROR(IF(OR(T201="",U210=""),"",U200*(U210/U200)^T201),"")</f>
         <v/>
       </c>
@@ -14369,16 +14385,16 @@
       <c r="B202" s="11" t="n"/>
       <c r="C202" s="12" t="n"/>
       <c r="D202" s="12" t="n"/>
-      <c r="E202" s="13" t="n"/>
+      <c r="E202" s="26" t="n"/>
       <c r="F202" s="14">
         <f>IF(OR($A202="",G202=""),"",-LN(G202)/INDEX($N$156:$N$220,IFERROR(MATCH($A202,$K$156:$K$220,0),MATCH(IF($A202="1Y","12M",IF($A202="12M","1Y",$A202)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G202" s="15">
+      <c r="G202" s="27">
         <f>IF($A202="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A202,$K$156:$K$220,0),MATCH(IF($A202="1Y","12M",IF($A202="12M","1Y",$A202)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H202" s="16">
+      <c r="H202" s="28">
         <f>IF(OR(F202="",NOT(ISNUMBER(D202))),"",(F202-D202)*100)</f>
         <v/>
       </c>
@@ -14429,7 +14445,7 @@
         <f>IFERROR(IF(OR(N202="",N210=""),"",(N202-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U202" s="22">
+      <c r="U202" s="29">
         <f>IFERROR(IF(OR(T202="",U210=""),"",U200*(U210/U200)^T202),"")</f>
         <v/>
       </c>
@@ -14443,16 +14459,16 @@
       <c r="B203" s="11" t="n"/>
       <c r="C203" s="12" t="n"/>
       <c r="D203" s="12" t="n"/>
-      <c r="E203" s="13" t="n"/>
+      <c r="E203" s="26" t="n"/>
       <c r="F203" s="14">
         <f>IF(OR($A203="",G203=""),"",-LN(G203)/INDEX($N$156:$N$220,IFERROR(MATCH($A203,$K$156:$K$220,0),MATCH(IF($A203="1Y","12M",IF($A203="12M","1Y",$A203)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G203" s="15">
+      <c r="G203" s="27">
         <f>IF($A203="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A203,$K$156:$K$220,0),MATCH(IF($A203="1Y","12M",IF($A203="12M","1Y",$A203)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H203" s="16">
+      <c r="H203" s="28">
         <f>IF(OR(F203="",NOT(ISNUMBER(D203))),"",(F203-D203)*100)</f>
         <v/>
       </c>
@@ -14503,7 +14519,7 @@
         <f>IFERROR(IF(OR(N203="",N210=""),"",(N203-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U203" s="22">
+      <c r="U203" s="29">
         <f>IFERROR(IF(OR(T203="",U210=""),"",U200*(U210/U200)^T203),"")</f>
         <v/>
       </c>
@@ -14517,16 +14533,16 @@
       <c r="B204" s="11" t="n"/>
       <c r="C204" s="12" t="n"/>
       <c r="D204" s="12" t="n"/>
-      <c r="E204" s="13" t="n"/>
+      <c r="E204" s="26" t="n"/>
       <c r="F204" s="14">
         <f>IF(OR($A204="",G204=""),"",-LN(G204)/INDEX($N$156:$N$220,IFERROR(MATCH($A204,$K$156:$K$220,0),MATCH(IF($A204="1Y","12M",IF($A204="12M","1Y",$A204)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G204" s="15">
+      <c r="G204" s="27">
         <f>IF($A204="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A204,$K$156:$K$220,0),MATCH(IF($A204="1Y","12M",IF($A204="12M","1Y",$A204)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H204" s="16">
+      <c r="H204" s="28">
         <f>IF(OR(F204="",NOT(ISNUMBER(D204))),"",(F204-D204)*100)</f>
         <v/>
       </c>
@@ -14577,7 +14593,7 @@
         <f>IFERROR(IF(OR(N204="",N210=""),"",(N204-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U204" s="22">
+      <c r="U204" s="29">
         <f>IFERROR(IF(OR(T204="",U210=""),"",U200*(U210/U200)^T204),"")</f>
         <v/>
       </c>
@@ -14591,16 +14607,16 @@
       <c r="B205" s="11" t="n"/>
       <c r="C205" s="12" t="n"/>
       <c r="D205" s="12" t="n"/>
-      <c r="E205" s="13" t="n"/>
+      <c r="E205" s="26" t="n"/>
       <c r="F205" s="14">
         <f>IF(OR($A205="",G205=""),"",-LN(G205)/INDEX($N$156:$N$220,IFERROR(MATCH($A205,$K$156:$K$220,0),MATCH(IF($A205="1Y","12M",IF($A205="12M","1Y",$A205)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G205" s="15">
+      <c r="G205" s="27">
         <f>IF($A205="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A205,$K$156:$K$220,0),MATCH(IF($A205="1Y","12M",IF($A205="12M","1Y",$A205)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H205" s="16">
+      <c r="H205" s="28">
         <f>IF(OR(F205="",NOT(ISNUMBER(D205))),"",(F205-D205)*100)</f>
         <v/>
       </c>
@@ -14651,7 +14667,7 @@
         <f>IFERROR(IF(OR(N205="",N210=""),"",(N205-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U205" s="22">
+      <c r="U205" s="29">
         <f>IFERROR(IF(OR(T205="",U210=""),"",U200*(U210/U200)^T205),"")</f>
         <v/>
       </c>
@@ -14665,16 +14681,16 @@
       <c r="B206" s="11" t="n"/>
       <c r="C206" s="12" t="n"/>
       <c r="D206" s="12" t="n"/>
-      <c r="E206" s="13" t="n"/>
+      <c r="E206" s="26" t="n"/>
       <c r="F206" s="14">
         <f>IF(OR($A206="",G206=""),"",-LN(G206)/INDEX($N$156:$N$220,IFERROR(MATCH($A206,$K$156:$K$220,0),MATCH(IF($A206="1Y","12M",IF($A206="12M","1Y",$A206)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G206" s="15">
+      <c r="G206" s="27">
         <f>IF($A206="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A206,$K$156:$K$220,0),MATCH(IF($A206="1Y","12M",IF($A206="12M","1Y",$A206)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H206" s="16">
+      <c r="H206" s="28">
         <f>IF(OR(F206="",NOT(ISNUMBER(D206))),"",(F206-D206)*100)</f>
         <v/>
       </c>
@@ -14725,7 +14741,7 @@
         <f>IFERROR(IF(OR(N206="",N210=""),"",(N206-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U206" s="22">
+      <c r="U206" s="29">
         <f>IFERROR(IF(OR(T206="",U210=""),"",U200*(U210/U200)^T206),"")</f>
         <v/>
       </c>
@@ -14739,16 +14755,16 @@
       <c r="B207" s="11" t="n"/>
       <c r="C207" s="12" t="n"/>
       <c r="D207" s="12" t="n"/>
-      <c r="E207" s="13" t="n"/>
+      <c r="E207" s="26" t="n"/>
       <c r="F207" s="14">
         <f>IF(OR($A207="",G207=""),"",-LN(G207)/INDEX($N$156:$N$220,IFERROR(MATCH($A207,$K$156:$K$220,0),MATCH(IF($A207="1Y","12M",IF($A207="12M","1Y",$A207)),$K$156:$K$220,0)))*100)</f>
         <v/>
       </c>
-      <c r="G207" s="15">
+      <c r="G207" s="27">
         <f>IF($A207="","",IFERROR(INDEX($U$156:$U$220,IFERROR(MATCH($A207,$K$156:$K$220,0),MATCH(IF($A207="1Y","12M",IF($A207="12M","1Y",$A207)),$K$156:$K$220,0))),""))</f>
         <v/>
       </c>
-      <c r="H207" s="16">
+      <c r="H207" s="28">
         <f>IF(OR(F207="",NOT(ISNUMBER(D207))),"",(F207-D207)*100)</f>
         <v/>
       </c>
@@ -14799,7 +14815,7 @@
         <f>IFERROR(IF(OR(N207="",N210=""),"",(N207-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U207" s="22">
+      <c r="U207" s="29">
         <f>IFERROR(IF(OR(T207="",U210=""),"",U200*(U210/U200)^T207),"")</f>
         <v/>
       </c>
@@ -14848,7 +14864,7 @@
         <f>IFERROR(IF(OR(N208="",N210=""),"",(N208-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U208" s="22">
+      <c r="U208" s="29">
         <f>IFERROR(IF(OR(T208="",U210=""),"",U200*(U210/U200)^T208),"")</f>
         <v/>
       </c>
@@ -14881,7 +14897,7 @@
           <t>max |d zero| bp</t>
         </is>
       </c>
-      <c r="H209" s="24">
+      <c r="H209" s="31">
         <f>IF(COUNT($H$156:$H$207)=0,"",MAX(MAX($H$156:$H$207),-MIN($H$156:$H$207)))</f>
         <v/>
       </c>
@@ -14928,7 +14944,7 @@
         <f>IFERROR(IF(OR(N209="",N210=""),"",(N209-N200)/(N210-N200)),"")</f>
         <v/>
       </c>
-      <c r="U209" s="22">
+      <c r="U209" s="29">
         <f>IFERROR(IF(OR(T209="",U210=""),"",U200*(U210/U200)^T209),"")</f>
         <v/>
       </c>
@@ -14982,7 +14998,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("40Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("40Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U210" s="22">
+      <c r="U210" s="29">
         <f>IFERROR(IF(S210="","",AM210),"")</f>
         <v/>
       </c>
@@ -14990,67 +15006,67 @@
         <f>IFERROR(IF(OR(U210="",Q210=0),0,P210*U210),"")</f>
         <v/>
       </c>
-      <c r="X210" s="23">
+      <c r="X210" s="30">
         <f>IFERROR(IF(S210="","",U200*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y210" s="23">
+      <c r="Y210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(X210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="Z210" s="23">
+      <c r="Z210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(Y210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AA210" s="23">
+      <c r="AA210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(Z210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AB210" s="23">
+      <c r="AB210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AA210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AC210" s="23">
+      <c r="AC210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AB210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AD210" s="23">
+      <c r="AD210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AC210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AE210" s="23">
+      <c r="AE210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AD210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AF210" s="23">
+      <c r="AF210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AE210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AG210" s="23">
+      <c r="AG210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AF210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AH210" s="23">
+      <c r="AH210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AG210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AI210" s="23">
+      <c r="AI210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AH210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AJ210" s="23">
+      <c r="AJ210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AI210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AK210" s="23">
+      <c r="AK210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AJ210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AL210" s="23">
+      <c r="AL210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AK210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
-      <c r="AM210" s="23">
+      <c r="AM210" s="30">
         <f>IFERROR(IF(S210="","",(1-(S210/100)*(SUM($V$156:V200)+SUMPRODUCT($P$201:$P$209,$Q$201:$Q$209,U200*(AL210/U200)^$T$201:$T$209)))/(1+(S210/100)*P210)),"")</f>
         <v/>
       </c>
@@ -15100,7 +15116,7 @@
         <f>IFERROR(IF(OR(N211="",N220=""),"",(N211-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U211" s="22">
+      <c r="U211" s="29">
         <f>IFERROR(IF(OR(T211="",U220=""),"",U210*(U220/U210)^T211),"")</f>
         <v/>
       </c>
@@ -15149,7 +15165,7 @@
         <f>IFERROR(IF(OR(N212="",N220=""),"",(N212-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U212" s="22">
+      <c r="U212" s="29">
         <f>IFERROR(IF(OR(T212="",U220=""),"",U210*(U220/U210)^T212),"")</f>
         <v/>
       </c>
@@ -15198,7 +15214,7 @@
         <f>IFERROR(IF(OR(N213="",N220=""),"",(N213-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U213" s="22">
+      <c r="U213" s="29">
         <f>IFERROR(IF(OR(T213="",U220=""),"",U210*(U220/U210)^T213),"")</f>
         <v/>
       </c>
@@ -15247,7 +15263,7 @@
         <f>IFERROR(IF(OR(N214="",N220=""),"",(N214-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U214" s="22">
+      <c r="U214" s="29">
         <f>IFERROR(IF(OR(T214="",U220=""),"",U210*(U220/U210)^T214),"")</f>
         <v/>
       </c>
@@ -15296,7 +15312,7 @@
         <f>IFERROR(IF(OR(N215="",N220=""),"",(N215-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U215" s="22">
+      <c r="U215" s="29">
         <f>IFERROR(IF(OR(T215="",U220=""),"",U210*(U220/U210)^T215),"")</f>
         <v/>
       </c>
@@ -15345,7 +15361,7 @@
         <f>IFERROR(IF(OR(N216="",N220=""),"",(N216-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U216" s="22">
+      <c r="U216" s="29">
         <f>IFERROR(IF(OR(T216="",U220=""),"",U210*(U220/U210)^T216),"")</f>
         <v/>
       </c>
@@ -15394,7 +15410,7 @@
         <f>IFERROR(IF(OR(N217="",N220=""),"",(N217-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U217" s="22">
+      <c r="U217" s="29">
         <f>IFERROR(IF(OR(T217="",U220=""),"",U210*(U220/U210)^T217),"")</f>
         <v/>
       </c>
@@ -15443,7 +15459,7 @@
         <f>IFERROR(IF(OR(N218="",N220=""),"",(N218-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U218" s="22">
+      <c r="U218" s="29">
         <f>IFERROR(IF(OR(T218="",U220=""),"",U210*(U220/U210)^T218),"")</f>
         <v/>
       </c>
@@ -15492,7 +15508,7 @@
         <f>IFERROR(IF(OR(N219="",N220=""),"",(N219-N210)/(N220-N210)),"")</f>
         <v/>
       </c>
-      <c r="U219" s="22">
+      <c r="U219" s="29">
         <f>IFERROR(IF(OR(T219="",U220=""),"",U210*(U220/U210)^T219),"")</f>
         <v/>
       </c>
@@ -15537,7 +15553,7 @@
         <f>IFERROR(IFERROR(INDEX($C$156:$C$207,MATCH("50Y",$A$156:$A$207,0)),INDEX($C$156:$C$207,MATCH("50Y",$A$156:$A$207,0))),"")</f>
         <v/>
       </c>
-      <c r="U220" s="22">
+      <c r="U220" s="29">
         <f>IFERROR(IF(S220="","",AM220),"")</f>
         <v/>
       </c>
@@ -15545,67 +15561,67 @@
         <f>IFERROR(IF(OR(U220="",Q220=0),0,P220*U220),"")</f>
         <v/>
       </c>
-      <c r="X220" s="23">
+      <c r="X220" s="30">
         <f>IFERROR(IF(S220="","",U210*0.9),"")</f>
         <v/>
       </c>
-      <c r="Y220" s="23">
+      <c r="Y220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(X220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="Z220" s="23">
+      <c r="Z220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(Y220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AA220" s="23">
+      <c r="AA220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(Z220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AB220" s="23">
+      <c r="AB220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AA220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AC220" s="23">
+      <c r="AC220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AB220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AD220" s="23">
+      <c r="AD220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AC220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AE220" s="23">
+      <c r="AE220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AD220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AF220" s="23">
+      <c r="AF220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AE220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AG220" s="23">
+      <c r="AG220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AF220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AH220" s="23">
+      <c r="AH220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AG220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AI220" s="23">
+      <c r="AI220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AH220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AJ220" s="23">
+      <c r="AJ220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AI220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AK220" s="23">
+      <c r="AK220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AJ220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AL220" s="23">
+      <c r="AL220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AK220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
-      <c r="AM220" s="23">
+      <c r="AM220" s="30">
         <f>IFERROR(IF(S220="","",(1-(S220/100)*(SUM($V$156:V210)+SUMPRODUCT($P$211:$P$219,$Q$211:$Q$219,U210*(AL220/U210)^$T$211:$T$219)))/(1+(S220/100)*P220)),"")</f>
         <v/>
       </c>
